--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B38123B4-6E76-47CF-BE51-CD0222C432DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE8A868-DBAE-456A-8E42-3E49C4DF4C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="1770" windowWidth="33090" windowHeight="18225" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【テストターゲット名】_クラス単体" sheetId="23" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体" sheetId="24" r:id="rId4"/>
-    <sheet name="取引単体" sheetId="25" r:id="rId5"/>
+    <sheet name="【リクエストID】_クラス単体テスト" sheetId="23" r:id="rId3"/>
+    <sheet name="【リクエストID】_リクエスト単体テスト" sheetId="24" r:id="rId4"/>
+    <sheet name="取引単体テスト" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【テストターゲット名】_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体!$A$10:$R$316</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【テストターゲット名】_クラス単体!$A$1:$R$298</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体!$A$1:$R$316</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【リクエストID】_クラス単体テスト!$A$10:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体テスト!$A$10:$R$316</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">【リクエストID】_クラス単体テスト!$A$1:$R$298</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体テスト!$A$1:$R$316</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$P$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【テストターゲット名】_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">【リクエストID】_クラス単体テスト!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体テスト!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="578">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="577">
   <si>
     <t>システム機能設計書</t>
     <rPh sb="4" eb="6">
@@ -6366,13 +6366,6 @@
       <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>バッチ処理ID：XXX</t>
-    <rPh sb="3" eb="5">
-      <t>ショリ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>バリデーション</t>
@@ -9023,8 +9016,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr bwMode="auto">
         <a:xfrm>
-          <a:off x="7953375" y="285750"/>
-          <a:ext cx="1400175" cy="590550"/>
+          <a:off x="7905750" y="285750"/>
+          <a:ext cx="1390650" cy="590550"/>
           <a:chOff x="591" y="61"/>
           <a:chExt cx="147" cy="62"/>
         </a:xfrm>
@@ -10765,8 +10758,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="16259175" y="1676400"/>
-          <a:ext cx="4914900" cy="2733675"/>
+          <a:off x="16224250" y="1644650"/>
+          <a:ext cx="4899025" cy="2670175"/>
           <a:chOff x="16335375" y="4752975"/>
           <a:chExt cx="4914900" cy="2733675"/>
         </a:xfrm>
@@ -12162,9 +12155,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -12202,9 +12195,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -12237,26 +12230,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -12289,26 +12265,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -12486,9 +12445,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K513"/>
-  <sheetFormatPr defaultColWidth="6.625" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="6.58203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="16384" width="6.625" style="1"/>
+    <col min="1" max="16384" width="6.58203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="13.5" customHeight="1">
@@ -12574,18 +12533,18 @@
       <c r="G31" s="8"/>
       <c r="H31" s="5"/>
     </row>
-    <row r="32" spans="6:11" ht="18.75">
+    <row r="32" spans="6:11" ht="19">
       <c r="F32" s="5"/>
       <c r="G32" s="8"/>
       <c r="H32" s="5"/>
       <c r="J32" s="9"/>
     </row>
-    <row r="33" spans="6:10" ht="18.75">
+    <row r="33" spans="6:10" ht="19">
       <c r="F33" s="5"/>
       <c r="H33" s="5"/>
       <c r="J33" s="10"/>
     </row>
-    <row r="34" spans="6:10" ht="18.75">
+    <row r="34" spans="6:10" ht="19">
       <c r="F34" s="5"/>
       <c r="H34" s="5"/>
       <c r="J34" s="9"/>
@@ -13088,9 +13047,9 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AN34"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="11.25"/>
+  <sheetFormatPr defaultColWidth="3.58203125" defaultRowHeight="11"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="22"/>
+    <col min="1" max="16384" width="3.58203125" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
@@ -13119,7 +13078,7 @@
       <c r="Q1" s="192"/>
       <c r="R1" s="193"/>
       <c r="S1" s="200" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="T1" s="201"/>
       <c r="U1" s="201"/>
@@ -14318,7 +14277,7 @@
       <c r="AH33" s="240"/>
       <c r="AI33" s="241"/>
     </row>
-    <row r="34" spans="1:35" ht="14.25">
+    <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
@@ -14517,18 +14476,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R298"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="2" width="8.625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="8.625" style="29" customWidth="1"/>
-    <col min="4" max="5" width="8.625" style="28" customWidth="1"/>
-    <col min="6" max="6" width="40.625" style="28" customWidth="1"/>
-    <col min="7" max="7" width="40.625" style="28" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="15.625" style="28" customWidth="1"/>
-    <col min="10" max="11" width="25.625" style="28" customWidth="1"/>
+    <col min="1" max="2" width="8.58203125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="8.58203125" style="29" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="28" customWidth="1"/>
+    <col min="6" max="6" width="40.58203125" style="28" customWidth="1"/>
+    <col min="7" max="7" width="40.58203125" style="28" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="15.58203125" style="28" customWidth="1"/>
+    <col min="10" max="11" width="25.58203125" style="28" customWidth="1"/>
     <col min="12" max="12" width="19.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.625" style="28" customWidth="1"/>
-    <col min="14" max="18" width="8.625" style="28" customWidth="1"/>
+    <col min="13" max="13" width="12.58203125" style="28" customWidth="1"/>
+    <col min="14" max="18" width="8.58203125" style="28" customWidth="1"/>
     <col min="19" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -14574,7 +14533,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12" thickBot="1">
+    <row r="8" spans="1:18" ht="11.5" thickBot="1">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="31"/>
@@ -14651,7 +14610,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5">
+    <row r="11" spans="1:18" ht="22">
       <c r="A11" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E11),
@@ -14694,7 +14653,7 @@
       <c r="Q11" s="59"/>
       <c r="R11" s="61"/>
     </row>
-    <row r="12" spans="1:18" ht="22.5">
+    <row r="12" spans="1:18" ht="22">
       <c r="A12" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E12),
@@ -14731,7 +14690,7 @@
       <c r="Q12" s="65"/>
       <c r="R12" s="67"/>
     </row>
-    <row r="13" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="13" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A13" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E13),
@@ -14770,7 +14729,7 @@
       <c r="Q13" s="66"/>
       <c r="R13" s="65"/>
     </row>
-    <row r="14" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="14" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A14" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E14),
@@ -14805,7 +14764,7 @@
       <c r="Q14" s="66"/>
       <c r="R14" s="65"/>
     </row>
-    <row r="15" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="15" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A15" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E15),
@@ -14840,7 +14799,7 @@
       <c r="Q15" s="66"/>
       <c r="R15" s="65"/>
     </row>
-    <row r="16" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="16" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A16" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E16),
@@ -14875,7 +14834,7 @@
       <c r="Q16" s="65"/>
       <c r="R16" s="67"/>
     </row>
-    <row r="17" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="17" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A17" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E17),
@@ -14910,7 +14869,7 @@
       <c r="Q17" s="65"/>
       <c r="R17" s="67"/>
     </row>
-    <row r="18" spans="1:18" ht="22.5">
+    <row r="18" spans="1:18" ht="22">
       <c r="A18" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E18),
@@ -14949,7 +14908,7 @@
       <c r="Q18" s="65"/>
       <c r="R18" s="67"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5">
+    <row r="19" spans="1:18" ht="22">
       <c r="A19" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E19),
@@ -14984,7 +14943,7 @@
       <c r="Q19" s="65"/>
       <c r="R19" s="67"/>
     </row>
-    <row r="20" spans="1:18" ht="22.5">
+    <row r="20" spans="1:18" ht="22">
       <c r="A20" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E20),
@@ -15019,7 +14978,7 @@
       <c r="Q20" s="65"/>
       <c r="R20" s="67"/>
     </row>
-    <row r="21" spans="1:18" ht="22.5">
+    <row r="21" spans="1:18" ht="22">
       <c r="A21" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E21),
@@ -15056,7 +15015,7 @@
       <c r="Q21" s="65"/>
       <c r="R21" s="67"/>
     </row>
-    <row r="22" spans="1:18" ht="22.5">
+    <row r="22" spans="1:18" ht="22">
       <c r="A22" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E22),
@@ -15091,7 +15050,7 @@
       <c r="Q22" s="65"/>
       <c r="R22" s="67"/>
     </row>
-    <row r="23" spans="1:18" ht="22.5">
+    <row r="23" spans="1:18" ht="22">
       <c r="A23" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E23),
@@ -15126,7 +15085,7 @@
       <c r="Q23" s="65"/>
       <c r="R23" s="67"/>
     </row>
-    <row r="24" spans="1:18" ht="22.5">
+    <row r="24" spans="1:18" ht="22">
       <c r="A24" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E24),
@@ -15161,7 +15120,7 @@
       <c r="Q24" s="65"/>
       <c r="R24" s="67"/>
     </row>
-    <row r="25" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="25" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A25" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E25),
@@ -15235,7 +15194,7 @@
       <c r="Q26" s="66"/>
       <c r="R26" s="65"/>
     </row>
-    <row r="27" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="27" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A27" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E27),
@@ -15274,7 +15233,7 @@
       <c r="Q27" s="66"/>
       <c r="R27" s="65"/>
     </row>
-    <row r="28" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="28" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A28" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E28),
@@ -15309,7 +15268,7 @@
       <c r="Q28" s="66"/>
       <c r="R28" s="65"/>
     </row>
-    <row r="29" spans="1:18" ht="22.5">
+    <row r="29" spans="1:18" ht="22">
       <c r="A29" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E29),
@@ -15346,7 +15305,7 @@
       <c r="Q29" s="67"/>
       <c r="R29" s="67"/>
     </row>
-    <row r="30" spans="1:18" ht="22.5">
+    <row r="30" spans="1:18" ht="22">
       <c r="A30" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E30),
@@ -15381,7 +15340,7 @@
       <c r="Q30" s="67"/>
       <c r="R30" s="67"/>
     </row>
-    <row r="31" spans="1:18" ht="22.5">
+    <row r="31" spans="1:18" ht="22">
       <c r="A31" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E31),
@@ -15416,7 +15375,7 @@
       <c r="Q31" s="67"/>
       <c r="R31" s="67"/>
     </row>
-    <row r="32" spans="1:18" ht="22.5">
+    <row r="32" spans="1:18" ht="22">
       <c r="A32" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E32),
@@ -15451,7 +15410,7 @@
       <c r="Q32" s="67"/>
       <c r="R32" s="67"/>
     </row>
-    <row r="33" spans="1:18" ht="22.5">
+    <row r="33" spans="1:18" ht="22">
       <c r="A33" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E33),
@@ -15488,7 +15447,7 @@
       <c r="Q33" s="67"/>
       <c r="R33" s="67"/>
     </row>
-    <row r="34" spans="1:18" ht="22.5">
+    <row r="34" spans="1:18" ht="22">
       <c r="A34" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E34),
@@ -15523,7 +15482,7 @@
       <c r="Q34" s="67"/>
       <c r="R34" s="67"/>
     </row>
-    <row r="35" spans="1:18" ht="45">
+    <row r="35" spans="1:18" ht="44">
       <c r="A35" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E35),
@@ -15560,7 +15519,7 @@
       <c r="Q35" s="67"/>
       <c r="R35" s="67"/>
     </row>
-    <row r="36" spans="1:18" ht="33.75">
+    <row r="36" spans="1:18" ht="33">
       <c r="A36" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E36),
@@ -15601,7 +15560,7 @@
       <c r="Q36" s="61"/>
       <c r="R36" s="61"/>
     </row>
-    <row r="37" spans="1:18" ht="33.75">
+    <row r="37" spans="1:18" ht="33">
       <c r="A37" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E37),
@@ -15636,7 +15595,7 @@
       <c r="Q37" s="61"/>
       <c r="R37" s="61"/>
     </row>
-    <row r="38" spans="1:18" ht="22.5">
+    <row r="38" spans="1:18" ht="22">
       <c r="A38" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E38),
@@ -15671,7 +15630,7 @@
       <c r="Q38" s="61"/>
       <c r="R38" s="61"/>
     </row>
-    <row r="39" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="39" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A39" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E39),
@@ -15706,7 +15665,7 @@
       <c r="Q39" s="59"/>
       <c r="R39" s="61"/>
     </row>
-    <row r="40" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="40" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A40" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E40),
@@ -15780,7 +15739,7 @@
       <c r="Q41" s="59"/>
       <c r="R41" s="61"/>
     </row>
-    <row r="42" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="42" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A42" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E42),
@@ -15813,16 +15772,16 @@
         <v>181</v>
       </c>
       <c r="I42" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J42" s="146" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K42" s="147" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L42" s="148" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M42" s="148" t="s">
         <v>170</v>
@@ -15833,7 +15792,7 @@
       <c r="Q42" s="151"/>
       <c r="R42" s="149"/>
     </row>
-    <row r="43" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="43" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A43" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A43" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E43),
@@ -15858,16 +15817,16 @@
         <v>181</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J43" s="146" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K43" s="147" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L43" s="148" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M43" s="148" t="s">
         <v>172</v>
@@ -15878,7 +15837,7 @@
       <c r="Q43" s="151"/>
       <c r="R43" s="149"/>
     </row>
-    <row r="44" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="44" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A44" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E44),
@@ -15913,7 +15872,7 @@
       <c r="Q44" s="65"/>
       <c r="R44" s="67"/>
     </row>
-    <row r="45" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="45" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A45" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E45),
@@ -15950,7 +15909,7 @@
       <c r="Q45" s="65"/>
       <c r="R45" s="67"/>
     </row>
-    <row r="46" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="46" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A46" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A46" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E46),
@@ -15985,7 +15944,7 @@
       <c r="Q46" s="65"/>
       <c r="R46" s="67"/>
     </row>
-    <row r="47" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="47" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A47" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A47" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E47),
@@ -16020,7 +15979,7 @@
       <c r="Q47" s="65"/>
       <c r="R47" s="67"/>
     </row>
-    <row r="48" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="48" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A48" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E48),
@@ -16057,7 +16016,7 @@
       <c r="Q48" s="65"/>
       <c r="R48" s="67"/>
     </row>
-    <row r="49" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="49" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A49" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E49),
@@ -16092,7 +16051,7 @@
       <c r="Q49" s="65"/>
       <c r="R49" s="67"/>
     </row>
-    <row r="50" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="50" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A50" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A50" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E50),
@@ -16129,7 +16088,7 @@
       <c r="Q50" s="65"/>
       <c r="R50" s="67"/>
     </row>
-    <row r="51" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="51" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A51" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A51" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E51),
@@ -16164,7 +16123,7 @@
       <c r="Q51" s="65"/>
       <c r="R51" s="67"/>
     </row>
-    <row r="52" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="52" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A52" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A52" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E52),
@@ -16199,7 +16158,7 @@
       <c r="Q52" s="65"/>
       <c r="R52" s="67"/>
     </row>
-    <row r="53" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="53" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A53" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A53" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E53),
@@ -16234,7 +16193,7 @@
       <c r="Q53" s="65"/>
       <c r="R53" s="67"/>
     </row>
-    <row r="54" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="54" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A54" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E54),
@@ -16269,7 +16228,7 @@
       <c r="Q54" s="65"/>
       <c r="R54" s="67"/>
     </row>
-    <row r="55" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="55" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A55" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E55),
@@ -16304,7 +16263,7 @@
       <c r="Q55" s="65"/>
       <c r="R55" s="67"/>
     </row>
-    <row r="56" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="56" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A56" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E56),
@@ -16341,7 +16300,7 @@
       <c r="Q56" s="65"/>
       <c r="R56" s="67"/>
     </row>
-    <row r="57" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="57" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A57" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E57),
@@ -16378,7 +16337,7 @@
       <c r="Q57" s="65"/>
       <c r="R57" s="67"/>
     </row>
-    <row r="58" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="58" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A58" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E58),
@@ -16415,7 +16374,7 @@
       <c r="Q58" s="65"/>
       <c r="R58" s="67"/>
     </row>
-    <row r="59" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="59" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A59" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E59),
@@ -16440,7 +16399,7 @@
         <v>163</v>
       </c>
       <c r="G59" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H59" s="56"/>
       <c r="I59" s="56"/>
@@ -16454,7 +16413,7 @@
       <c r="Q59" s="59"/>
       <c r="R59" s="61"/>
     </row>
-    <row r="60" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="60" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A60" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A60" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E60),
@@ -16475,7 +16434,7 @@
         <v>164</v>
       </c>
       <c r="G60" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H60" s="56"/>
       <c r="I60" s="56"/>
@@ -16489,7 +16448,7 @@
       <c r="Q60" s="59"/>
       <c r="R60" s="61"/>
     </row>
-    <row r="61" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="61" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A61" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E61),
@@ -16510,7 +16469,7 @@
         <v>165</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H61" s="56"/>
       <c r="I61" s="56"/>
@@ -16524,7 +16483,7 @@
       <c r="Q61" s="59"/>
       <c r="R61" s="61"/>
     </row>
-    <row r="62" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="62" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A62" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A62" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E62),
@@ -16545,7 +16504,7 @@
         <v>166</v>
       </c>
       <c r="G62" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H62" s="56"/>
       <c r="I62" s="56"/>
@@ -16559,7 +16518,7 @@
       <c r="Q62" s="59"/>
       <c r="R62" s="61"/>
     </row>
-    <row r="63" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="63" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A63" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E63),
@@ -16580,7 +16539,7 @@
         <v>167</v>
       </c>
       <c r="G63" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H63" s="56"/>
       <c r="I63" s="56"/>
@@ -16594,7 +16553,7 @@
       <c r="Q63" s="59"/>
       <c r="R63" s="61"/>
     </row>
-    <row r="64" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="64" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A64" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E64),
@@ -16617,7 +16576,7 @@
         <v>169</v>
       </c>
       <c r="G64" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H64" s="56"/>
       <c r="I64" s="56"/>
@@ -16631,7 +16590,7 @@
       <c r="Q64" s="59"/>
       <c r="R64" s="61"/>
     </row>
-    <row r="65" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="65" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A65" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E65),
@@ -16652,7 +16611,7 @@
         <v>171</v>
       </c>
       <c r="G65" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H65" s="56"/>
       <c r="I65" s="56"/>
@@ -16685,7 +16644,7 @@
       <c r="E66" s="55"/>
       <c r="F66" s="70"/>
       <c r="G66" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H66" s="56"/>
       <c r="I66" s="56"/>
@@ -16699,7 +16658,7 @@
       <c r="Q66" s="59"/>
       <c r="R66" s="61"/>
     </row>
-    <row r="67" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="67" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A67" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A67" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E67),
@@ -16720,7 +16679,7 @@
         <v>173</v>
       </c>
       <c r="G67" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H67" s="56"/>
       <c r="I67" s="56"/>
@@ -16734,7 +16693,7 @@
       <c r="Q67" s="59"/>
       <c r="R67" s="61"/>
     </row>
-    <row r="68" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="68" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A68" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A68" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E68),
@@ -16755,7 +16714,7 @@
         <v>174</v>
       </c>
       <c r="G68" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H68" s="56"/>
       <c r="I68" s="56"/>
@@ -16769,7 +16728,7 @@
       <c r="Q68" s="59"/>
       <c r="R68" s="61"/>
     </row>
-    <row r="69" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="69" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A69" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A69" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E69),
@@ -16790,7 +16749,7 @@
         <v>175</v>
       </c>
       <c r="G69" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H69" s="56"/>
       <c r="I69" s="56"/>
@@ -16804,7 +16763,7 @@
       <c r="Q69" s="59"/>
       <c r="R69" s="61"/>
     </row>
-    <row r="70" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="70" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A70" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A70" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E70),
@@ -16825,7 +16784,7 @@
         <v>176</v>
       </c>
       <c r="G70" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H70" s="56"/>
       <c r="I70" s="56"/>
@@ -16839,7 +16798,7 @@
       <c r="Q70" s="59"/>
       <c r="R70" s="61"/>
     </row>
-    <row r="71" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="71" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A71" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A71" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E71),
@@ -16860,7 +16819,7 @@
         <v>177</v>
       </c>
       <c r="G71" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H71" s="56"/>
       <c r="I71" s="56"/>
@@ -16874,7 +16833,7 @@
       <c r="Q71" s="59"/>
       <c r="R71" s="61"/>
     </row>
-    <row r="72" spans="1:18" s="35" customFormat="1" ht="33.75">
+    <row r="72" spans="1:18" s="35" customFormat="1" ht="33">
       <c r="A72" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A72" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E72),
@@ -16895,7 +16854,7 @@
         <v>178</v>
       </c>
       <c r="G72" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H72" s="56"/>
       <c r="I72" s="56"/>
@@ -16909,7 +16868,7 @@
       <c r="Q72" s="59"/>
       <c r="R72" s="61"/>
     </row>
-    <row r="73" spans="1:18" s="35" customFormat="1" ht="22.5">
+    <row r="73" spans="1:18" s="35" customFormat="1" ht="22">
       <c r="A73" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A73" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E73),
@@ -16932,7 +16891,7 @@
         <v>180</v>
       </c>
       <c r="G73" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H73" s="54"/>
       <c r="I73" s="54"/>
@@ -16969,7 +16928,7 @@
         <v>183</v>
       </c>
       <c r="G74" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H74" s="54"/>
       <c r="I74" s="54"/>
@@ -17004,7 +16963,7 @@
         <v>184</v>
       </c>
       <c r="G75" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -17039,7 +16998,7 @@
         <v>185</v>
       </c>
       <c r="G76" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H76" s="56"/>
       <c r="I76" s="56"/>
@@ -17074,7 +17033,7 @@
         <v>187</v>
       </c>
       <c r="G77" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H77" s="56"/>
       <c r="I77" s="56"/>
@@ -17088,7 +17047,7 @@
       <c r="Q77" s="61"/>
       <c r="R77" s="61"/>
     </row>
-    <row r="78" spans="1:18" ht="22.5">
+    <row r="78" spans="1:18" ht="22">
       <c r="A78" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A78" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E78),
@@ -17109,7 +17068,7 @@
         <v>188</v>
       </c>
       <c r="G78" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H78" s="56"/>
       <c r="I78" s="56"/>
@@ -17123,7 +17082,7 @@
       <c r="Q78" s="61"/>
       <c r="R78" s="61"/>
     </row>
-    <row r="79" spans="1:18" ht="22.5">
+    <row r="79" spans="1:18" ht="22">
       <c r="A79" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A79" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E79),
@@ -17156,16 +17115,16 @@
         <v>181</v>
       </c>
       <c r="I79" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J79" s="146" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="K79" s="147" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="L79" s="148" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M79" s="148" t="s">
         <v>170</v>
@@ -17176,7 +17135,7 @@
       <c r="Q79" s="149"/>
       <c r="R79" s="149"/>
     </row>
-    <row r="80" spans="1:18" ht="45">
+    <row r="80" spans="1:18" ht="44">
       <c r="A80" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A80" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E80),
@@ -17199,16 +17158,16 @@
         <v>181</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J80" s="37" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="K80" s="37" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L80" s="148" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M80" s="148" t="s">
         <v>36</v>
@@ -17219,7 +17178,7 @@
       <c r="Q80" s="149"/>
       <c r="R80" s="149"/>
     </row>
-    <row r="81" spans="1:18" ht="45">
+    <row r="81" spans="1:18" ht="44">
       <c r="A81" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A81" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E81),
@@ -17242,16 +17201,16 @@
         <v>181</v>
       </c>
       <c r="I81" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J81" s="37" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K81" s="37" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="L81" s="148" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M81" s="148" t="s">
         <v>41</v>
@@ -17262,7 +17221,7 @@
       <c r="Q81" s="149"/>
       <c r="R81" s="149"/>
     </row>
-    <row r="82" spans="1:18" ht="33.75">
+    <row r="82" spans="1:18" ht="33">
       <c r="A82" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A82" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E82),
@@ -17289,16 +17248,16 @@
         <v>181</v>
       </c>
       <c r="I82" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J82" s="146" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K82" s="147" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="L82" s="148" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M82" s="148" t="s">
         <v>172</v>
@@ -17332,7 +17291,7 @@
         <v>194</v>
       </c>
       <c r="G83" s="56" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H83" s="68"/>
       <c r="I83" s="68"/>
@@ -17346,7 +17305,7 @@
       <c r="Q83" s="67"/>
       <c r="R83" s="67"/>
     </row>
-    <row r="84" spans="1:18" ht="33.75">
+    <row r="84" spans="1:18" ht="33">
       <c r="A84" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A84" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E84),
@@ -17373,16 +17332,16 @@
         <v>181</v>
       </c>
       <c r="I84" s="36" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J84" s="146" t="s">
+        <v>550</v>
+      </c>
+      <c r="K84" s="147" t="s">
         <v>551</v>
       </c>
-      <c r="K84" s="147" t="s">
-        <v>552</v>
-      </c>
       <c r="L84" s="148" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="M84" s="148" t="s">
         <v>35</v>
@@ -17393,7 +17352,7 @@
       <c r="Q84" s="149"/>
       <c r="R84" s="149"/>
     </row>
-    <row r="85" spans="1:18" ht="33.75">
+    <row r="85" spans="1:18" ht="33">
       <c r="A85" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A85" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E85),
@@ -17428,7 +17387,7 @@
       <c r="Q85" s="67"/>
       <c r="R85" s="67"/>
     </row>
-    <row r="86" spans="1:18" ht="22.5">
+    <row r="86" spans="1:18" ht="22">
       <c r="A86" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A86" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E86),
@@ -17451,7 +17410,7 @@
         <v>199</v>
       </c>
       <c r="G86" s="56" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H86" s="68"/>
       <c r="I86" s="68"/>
@@ -17465,7 +17424,7 @@
       <c r="Q86" s="67"/>
       <c r="R86" s="67"/>
     </row>
-    <row r="87" spans="1:18" ht="22.5">
+    <row r="87" spans="1:18" ht="22">
       <c r="A87" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A87" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E87),
@@ -17502,7 +17461,7 @@
       <c r="Q87" s="67"/>
       <c r="R87" s="67"/>
     </row>
-    <row r="88" spans="1:18" ht="22.5">
+    <row r="88" spans="1:18" ht="22">
       <c r="A88" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A88" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E88),
@@ -17529,7 +17488,7 @@
         <v>203</v>
       </c>
       <c r="G88" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H88" s="56"/>
       <c r="I88" s="56"/>
@@ -17566,7 +17525,7 @@
         <v>204</v>
       </c>
       <c r="G89" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H89" s="56"/>
       <c r="I89" s="56"/>
@@ -17580,7 +17539,7 @@
       <c r="Q89" s="61"/>
       <c r="R89" s="61"/>
     </row>
-    <row r="90" spans="1:18" ht="33.75">
+    <row r="90" spans="1:18" ht="33">
       <c r="A90" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A90" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E90),
@@ -17603,7 +17562,7 @@
         <v>206</v>
       </c>
       <c r="G90" s="56" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H90" s="56"/>
       <c r="I90" s="56"/>
@@ -17617,7 +17576,7 @@
       <c r="Q90" s="61"/>
       <c r="R90" s="61"/>
     </row>
-    <row r="91" spans="1:18" ht="22.5">
+    <row r="91" spans="1:18" ht="22">
       <c r="A91" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A91" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E91),
@@ -17658,7 +17617,7 @@
       <c r="Q91" s="67"/>
       <c r="R91" s="67"/>
     </row>
-    <row r="92" spans="1:18" ht="33.75">
+    <row r="92" spans="1:18" ht="33">
       <c r="A92" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A92" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E92),
@@ -17730,7 +17689,7 @@
       <c r="Q93" s="67"/>
       <c r="R93" s="67"/>
     </row>
-    <row r="94" spans="1:18" ht="33.75">
+    <row r="94" spans="1:18" ht="33">
       <c r="A94" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A94" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E94),
@@ -17767,7 +17726,7 @@
       <c r="Q94" s="67"/>
       <c r="R94" s="67"/>
     </row>
-    <row r="95" spans="1:18" ht="33.75">
+    <row r="95" spans="1:18" ht="33">
       <c r="A95" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A95" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E95),
@@ -17802,7 +17761,7 @@
       <c r="Q95" s="67"/>
       <c r="R95" s="67"/>
     </row>
-    <row r="96" spans="1:18" ht="33.75">
+    <row r="96" spans="1:18" ht="33">
       <c r="A96" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A96" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E96),
@@ -17839,7 +17798,7 @@
       <c r="Q96" s="67"/>
       <c r="R96" s="67"/>
     </row>
-    <row r="97" spans="1:18" ht="22.5">
+    <row r="97" spans="1:18" ht="22">
       <c r="A97" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A97" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E97),
@@ -17880,7 +17839,7 @@
       <c r="Q97" s="67"/>
       <c r="R97" s="67"/>
     </row>
-    <row r="98" spans="1:18" ht="33.75">
+    <row r="98" spans="1:18" ht="33">
       <c r="A98" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A98" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E98),
@@ -17950,7 +17909,7 @@
       <c r="Q99" s="67"/>
       <c r="R99" s="67"/>
     </row>
-    <row r="100" spans="1:18" ht="33.75">
+    <row r="100" spans="1:18" ht="33">
       <c r="A100" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A100" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E100),
@@ -17985,7 +17944,7 @@
       <c r="Q100" s="67"/>
       <c r="R100" s="67"/>
     </row>
-    <row r="101" spans="1:18" ht="33.75">
+    <row r="101" spans="1:18" ht="33">
       <c r="A101" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A101" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E101),
@@ -18020,7 +17979,7 @@
       <c r="Q101" s="67"/>
       <c r="R101" s="67"/>
     </row>
-    <row r="102" spans="1:18" ht="22.5">
+    <row r="102" spans="1:18" ht="22">
       <c r="A102" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A102" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E102),
@@ -18057,7 +18016,7 @@
       <c r="Q102" s="67"/>
       <c r="R102" s="67"/>
     </row>
-    <row r="103" spans="1:18" ht="33.75">
+    <row r="103" spans="1:18" ht="33">
       <c r="A103" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A103" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E103),
@@ -18127,7 +18086,7 @@
       <c r="Q104" s="67"/>
       <c r="R104" s="67"/>
     </row>
-    <row r="105" spans="1:18" ht="33.75">
+    <row r="105" spans="1:18" ht="33">
       <c r="A105" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A105" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E105),
@@ -18162,7 +18121,7 @@
       <c r="Q105" s="67"/>
       <c r="R105" s="67"/>
     </row>
-    <row r="106" spans="1:18" ht="33.75">
+    <row r="106" spans="1:18" ht="33">
       <c r="A106" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A106" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E106),
@@ -18197,7 +18156,7 @@
       <c r="Q106" s="67"/>
       <c r="R106" s="67"/>
     </row>
-    <row r="107" spans="1:18" ht="33.75">
+    <row r="107" spans="1:18" ht="33">
       <c r="A107" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A107" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E107),
@@ -18234,7 +18193,7 @@
       <c r="Q107" s="67"/>
       <c r="R107" s="67"/>
     </row>
-    <row r="108" spans="1:18" ht="33.75">
+    <row r="108" spans="1:18" ht="33">
       <c r="A108" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A108" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E108),
@@ -18353,7 +18312,7 @@
       <c r="Q110" s="67"/>
       <c r="R110" s="67"/>
     </row>
-    <row r="111" spans="1:18" ht="22.5">
+    <row r="111" spans="1:18" ht="22">
       <c r="A111" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A111" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E111),
@@ -18394,7 +18353,7 @@
       <c r="Q111" s="67"/>
       <c r="R111" s="67"/>
     </row>
-    <row r="112" spans="1:18" ht="22.5">
+    <row r="112" spans="1:18" ht="22">
       <c r="A112" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A112" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E112),
@@ -18470,7 +18429,7 @@
       <c r="Q113" s="67"/>
       <c r="R113" s="67"/>
     </row>
-    <row r="114" spans="1:18" ht="22.5">
+    <row r="114" spans="1:18" ht="22">
       <c r="A114" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A114" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E114),
@@ -18513,7 +18472,7 @@
       <c r="Q114" s="61"/>
       <c r="R114" s="61"/>
     </row>
-    <row r="115" spans="1:18" ht="22.5">
+    <row r="115" spans="1:18" ht="22">
       <c r="A115" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A115" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E115),
@@ -18550,7 +18509,7 @@
       <c r="Q115" s="61"/>
       <c r="R115" s="61"/>
     </row>
-    <row r="116" spans="1:18" ht="22.5">
+    <row r="116" spans="1:18" ht="22">
       <c r="A116" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A116" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E116),
@@ -18585,7 +18544,7 @@
       <c r="Q116" s="61"/>
       <c r="R116" s="61"/>
     </row>
-    <row r="117" spans="1:18" ht="22.5">
+    <row r="117" spans="1:18" ht="22">
       <c r="A117" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A117" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E117),
@@ -18620,7 +18579,7 @@
       <c r="Q117" s="61"/>
       <c r="R117" s="61"/>
     </row>
-    <row r="118" spans="1:18" ht="22.5">
+    <row r="118" spans="1:18" ht="22">
       <c r="A118" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A118" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E118),
@@ -18657,7 +18616,7 @@
       <c r="Q118" s="61"/>
       <c r="R118" s="61"/>
     </row>
-    <row r="119" spans="1:18" ht="22.5">
+    <row r="119" spans="1:18" ht="22">
       <c r="A119" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A119" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E119),
@@ -18692,7 +18651,7 @@
       <c r="Q119" s="61"/>
       <c r="R119" s="61"/>
     </row>
-    <row r="120" spans="1:18" ht="22.5">
+    <row r="120" spans="1:18" ht="22">
       <c r="A120" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A120" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E120),
@@ -18727,7 +18686,7 @@
       <c r="Q120" s="61"/>
       <c r="R120" s="61"/>
     </row>
-    <row r="121" spans="1:18" ht="22.5">
+    <row r="121" spans="1:18" ht="22">
       <c r="A121" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A121" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E121),
@@ -18762,7 +18721,7 @@
       <c r="Q121" s="61"/>
       <c r="R121" s="61"/>
     </row>
-    <row r="122" spans="1:18" ht="33.75">
+    <row r="122" spans="1:18" ht="33">
       <c r="A122" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A122" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E122),
@@ -18797,7 +18756,7 @@
       <c r="Q122" s="61"/>
       <c r="R122" s="61"/>
     </row>
-    <row r="123" spans="1:18" ht="33.75">
+    <row r="123" spans="1:18" ht="33">
       <c r="A123" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A123" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E123),
@@ -18834,7 +18793,7 @@
       <c r="Q123" s="61"/>
       <c r="R123" s="61"/>
     </row>
-    <row r="124" spans="1:18" ht="33.75">
+    <row r="124" spans="1:18" ht="33">
       <c r="A124" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A124" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E124),
@@ -18869,7 +18828,7 @@
       <c r="Q124" s="61"/>
       <c r="R124" s="61"/>
     </row>
-    <row r="125" spans="1:18" ht="45">
+    <row r="125" spans="1:18" ht="44">
       <c r="A125" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A125" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E125),
@@ -18904,7 +18863,7 @@
       <c r="Q125" s="61"/>
       <c r="R125" s="61"/>
     </row>
-    <row r="126" spans="1:18" ht="45">
+    <row r="126" spans="1:18" ht="44">
       <c r="A126" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A126" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E126),
@@ -18939,7 +18898,7 @@
       <c r="Q126" s="61"/>
       <c r="R126" s="61"/>
     </row>
-    <row r="127" spans="1:18" ht="33.75">
+    <row r="127" spans="1:18" ht="33">
       <c r="A127" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A127" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E127),
@@ -18974,7 +18933,7 @@
       <c r="Q127" s="61"/>
       <c r="R127" s="61"/>
     </row>
-    <row r="128" spans="1:18" ht="33.75">
+    <row r="128" spans="1:18" ht="33">
       <c r="A128" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A128" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E128),
@@ -19011,7 +18970,7 @@
       <c r="Q128" s="61"/>
       <c r="R128" s="61"/>
     </row>
-    <row r="129" spans="1:18" ht="33.75">
+    <row r="129" spans="1:18" ht="33">
       <c r="A129" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A129" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E129),
@@ -19050,7 +19009,7 @@
       <c r="Q129" s="61"/>
       <c r="R129" s="61"/>
     </row>
-    <row r="130" spans="1:18" ht="33.75">
+    <row r="130" spans="1:18" ht="33">
       <c r="A130" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A130" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E130),
@@ -19091,7 +19050,7 @@
       <c r="Q130" s="61"/>
       <c r="R130" s="61"/>
     </row>
-    <row r="131" spans="1:18" ht="22.5">
+    <row r="131" spans="1:18" ht="22">
       <c r="A131" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A131" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E131),
@@ -19128,7 +19087,7 @@
       <c r="Q131" s="61"/>
       <c r="R131" s="61"/>
     </row>
-    <row r="132" spans="1:18" ht="22.5">
+    <row r="132" spans="1:18" ht="22">
       <c r="A132" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A132" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E132),
@@ -19163,7 +19122,7 @@
       <c r="Q132" s="61"/>
       <c r="R132" s="61"/>
     </row>
-    <row r="133" spans="1:18" ht="45">
+    <row r="133" spans="1:18" ht="44">
       <c r="A133" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A133" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E133),
@@ -19198,7 +19157,7 @@
       <c r="Q133" s="61"/>
       <c r="R133" s="61"/>
     </row>
-    <row r="134" spans="1:18" ht="22.5">
+    <row r="134" spans="1:18" ht="22">
       <c r="A134" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A134" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E134),
@@ -19241,7 +19200,7 @@
       <c r="Q134" s="61"/>
       <c r="R134" s="61"/>
     </row>
-    <row r="135" spans="1:18" ht="22.5">
+    <row r="135" spans="1:18" ht="22">
       <c r="A135" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A135" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E135),
@@ -19278,7 +19237,7 @@
       <c r="Q135" s="61"/>
       <c r="R135" s="61"/>
     </row>
-    <row r="136" spans="1:18" ht="22.5">
+    <row r="136" spans="1:18" ht="22">
       <c r="A136" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E136),
@@ -19313,7 +19272,7 @@
       <c r="Q136" s="61"/>
       <c r="R136" s="61"/>
     </row>
-    <row r="137" spans="1:18" ht="22.5">
+    <row r="137" spans="1:18" ht="22">
       <c r="A137" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A137" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E137),
@@ -19348,7 +19307,7 @@
       <c r="Q137" s="61"/>
       <c r="R137" s="61"/>
     </row>
-    <row r="138" spans="1:18" ht="22.5">
+    <row r="138" spans="1:18" ht="22">
       <c r="A138" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E138),
@@ -19385,7 +19344,7 @@
       <c r="Q138" s="61"/>
       <c r="R138" s="61"/>
     </row>
-    <row r="139" spans="1:18" ht="33.75">
+    <row r="139" spans="1:18" ht="33">
       <c r="A139" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A139" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E139),
@@ -19420,7 +19379,7 @@
       <c r="Q139" s="61"/>
       <c r="R139" s="61"/>
     </row>
-    <row r="140" spans="1:18" ht="33.75">
+    <row r="140" spans="1:18" ht="33">
       <c r="A140" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A140" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E140),
@@ -19459,7 +19418,7 @@
       <c r="Q140" s="61"/>
       <c r="R140" s="61"/>
     </row>
-    <row r="141" spans="1:18" ht="33.75">
+    <row r="141" spans="1:18" ht="33">
       <c r="A141" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A141" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E141),
@@ -19500,7 +19459,7 @@
       <c r="Q141" s="61"/>
       <c r="R141" s="61"/>
     </row>
-    <row r="142" spans="1:18" ht="33.75">
+    <row r="142" spans="1:18" ht="33">
       <c r="A142" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A142" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E142),
@@ -19537,7 +19496,7 @@
       <c r="Q142" s="61"/>
       <c r="R142" s="61"/>
     </row>
-    <row r="143" spans="1:18" ht="33.75">
+    <row r="143" spans="1:18" ht="33">
       <c r="A143" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A143" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E143),
@@ -19574,7 +19533,7 @@
       <c r="Q143" s="61"/>
       <c r="R143" s="61"/>
     </row>
-    <row r="144" spans="1:18" ht="33.75">
+    <row r="144" spans="1:18" ht="33">
       <c r="A144" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A144" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E144),
@@ -19611,7 +19570,7 @@
       <c r="Q144" s="61"/>
       <c r="R144" s="61"/>
     </row>
-    <row r="145" spans="1:18" ht="33.75">
+    <row r="145" spans="1:18" ht="33">
       <c r="A145" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E145),
@@ -19648,7 +19607,7 @@
       <c r="Q145" s="61"/>
       <c r="R145" s="61"/>
     </row>
-    <row r="146" spans="1:18" ht="22.5">
+    <row r="146" spans="1:18" ht="22">
       <c r="A146" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A146" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E146),
@@ -19685,7 +19644,7 @@
       <c r="Q146" s="61"/>
       <c r="R146" s="61"/>
     </row>
-    <row r="147" spans="1:18" ht="22.5">
+    <row r="147" spans="1:18" ht="22">
       <c r="A147" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A147" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E147),
@@ -19720,7 +19679,7 @@
       <c r="Q147" s="61"/>
       <c r="R147" s="61"/>
     </row>
-    <row r="148" spans="1:18" ht="22.5">
+    <row r="148" spans="1:18" ht="22">
       <c r="A148" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A148" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E148),
@@ -19755,7 +19714,7 @@
       <c r="Q148" s="61"/>
       <c r="R148" s="61"/>
     </row>
-    <row r="149" spans="1:18" ht="22.5">
+    <row r="149" spans="1:18" ht="22">
       <c r="A149" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A149" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E149),
@@ -19790,7 +19749,7 @@
       <c r="Q149" s="61"/>
       <c r="R149" s="61"/>
     </row>
-    <row r="150" spans="1:18" ht="22.5">
+    <row r="150" spans="1:18" ht="22">
       <c r="A150" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A150" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E150),
@@ -19825,7 +19784,7 @@
       <c r="Q150" s="61"/>
       <c r="R150" s="61"/>
     </row>
-    <row r="151" spans="1:18" ht="22.5">
+    <row r="151" spans="1:18" ht="22">
       <c r="A151" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A151" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E151),
@@ -19860,7 +19819,7 @@
       <c r="Q151" s="61"/>
       <c r="R151" s="61"/>
     </row>
-    <row r="152" spans="1:18" ht="22.5">
+    <row r="152" spans="1:18" ht="22">
       <c r="A152" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A152" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E152),
@@ -19899,7 +19858,7 @@
       <c r="Q152" s="61"/>
       <c r="R152" s="61"/>
     </row>
-    <row r="153" spans="1:18" ht="22.5">
+    <row r="153" spans="1:18" ht="22">
       <c r="A153" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A153" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E153),
@@ -19934,7 +19893,7 @@
       <c r="Q153" s="61"/>
       <c r="R153" s="61"/>
     </row>
-    <row r="154" spans="1:18" ht="33.75">
+    <row r="154" spans="1:18" ht="33">
       <c r="A154" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A154" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E154),
@@ -19971,7 +19930,7 @@
       <c r="Q154" s="61"/>
       <c r="R154" s="61"/>
     </row>
-    <row r="155" spans="1:18" ht="33.75">
+    <row r="155" spans="1:18" ht="33">
       <c r="A155" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A155" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E155),
@@ -20006,7 +19965,7 @@
       <c r="Q155" s="61"/>
       <c r="R155" s="61"/>
     </row>
-    <row r="156" spans="1:18" ht="33.75">
+    <row r="156" spans="1:18" ht="33">
       <c r="A156" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A156" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E156),
@@ -20041,7 +20000,7 @@
       <c r="Q156" s="61"/>
       <c r="R156" s="61"/>
     </row>
-    <row r="157" spans="1:18" ht="33.75">
+    <row r="157" spans="1:18" ht="33">
       <c r="A157" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A157" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E157),
@@ -20076,7 +20035,7 @@
       <c r="Q157" s="61"/>
       <c r="R157" s="61"/>
     </row>
-    <row r="158" spans="1:18" ht="33.75">
+    <row r="158" spans="1:18" ht="33">
       <c r="A158" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A158" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E158),
@@ -20111,7 +20070,7 @@
       <c r="Q158" s="61"/>
       <c r="R158" s="61"/>
     </row>
-    <row r="159" spans="1:18" ht="22.5">
+    <row r="159" spans="1:18" ht="22">
       <c r="A159" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A159" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E159),
@@ -20146,7 +20105,7 @@
       <c r="Q159" s="61"/>
       <c r="R159" s="61"/>
     </row>
-    <row r="160" spans="1:18" ht="22.5">
+    <row r="160" spans="1:18" ht="22">
       <c r="A160" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A160" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E160),
@@ -20181,7 +20140,7 @@
       <c r="Q160" s="61"/>
       <c r="R160" s="61"/>
     </row>
-    <row r="161" spans="1:18" ht="33.75">
+    <row r="161" spans="1:18" ht="33">
       <c r="A161" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A161" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E161),
@@ -20216,7 +20175,7 @@
       <c r="Q161" s="61"/>
       <c r="R161" s="61"/>
     </row>
-    <row r="162" spans="1:18" ht="33.75">
+    <row r="162" spans="1:18" ht="33">
       <c r="A162" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A162" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E162),
@@ -20251,7 +20210,7 @@
       <c r="Q162" s="61"/>
       <c r="R162" s="61"/>
     </row>
-    <row r="163" spans="1:18" ht="33.75">
+    <row r="163" spans="1:18" ht="33">
       <c r="A163" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A163" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E163),
@@ -20286,7 +20245,7 @@
       <c r="Q163" s="61"/>
       <c r="R163" s="61"/>
     </row>
-    <row r="164" spans="1:18" ht="33.75">
+    <row r="164" spans="1:18" ht="33">
       <c r="A164" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A164" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E164),
@@ -20393,7 +20352,7 @@
       <c r="Q166" s="61"/>
       <c r="R166" s="61"/>
     </row>
-    <row r="167" spans="1:18" ht="22.5">
+    <row r="167" spans="1:18" ht="22">
       <c r="A167" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A167" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E167),
@@ -20428,7 +20387,7 @@
       <c r="Q167" s="61"/>
       <c r="R167" s="61"/>
     </row>
-    <row r="168" spans="1:18" ht="22.5">
+    <row r="168" spans="1:18" ht="22">
       <c r="A168" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A168" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E168),
@@ -20463,7 +20422,7 @@
       <c r="Q168" s="61"/>
       <c r="R168" s="61"/>
     </row>
-    <row r="169" spans="1:18" ht="22.5">
+    <row r="169" spans="1:18" ht="22">
       <c r="A169" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A169" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E169),
@@ -20498,7 +20457,7 @@
       <c r="Q169" s="61"/>
       <c r="R169" s="61"/>
     </row>
-    <row r="170" spans="1:18" ht="33.75">
+    <row r="170" spans="1:18" ht="33">
       <c r="A170" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A170" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E170),
@@ -20533,7 +20492,7 @@
       <c r="Q170" s="61"/>
       <c r="R170" s="61"/>
     </row>
-    <row r="171" spans="1:18" ht="22.5">
+    <row r="171" spans="1:18" ht="22">
       <c r="A171" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A171" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E171),
@@ -20568,7 +20527,7 @@
       <c r="Q171" s="61"/>
       <c r="R171" s="61"/>
     </row>
-    <row r="172" spans="1:18" ht="22.5">
+    <row r="172" spans="1:18" ht="22">
       <c r="A172" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A172" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E172),
@@ -20605,7 +20564,7 @@
       <c r="Q172" s="61"/>
       <c r="R172" s="61"/>
     </row>
-    <row r="173" spans="1:18" ht="33.75">
+    <row r="173" spans="1:18" ht="33">
       <c r="A173" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A173" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E173),
@@ -20640,7 +20599,7 @@
       <c r="Q173" s="61"/>
       <c r="R173" s="61"/>
     </row>
-    <row r="174" spans="1:18" ht="33.75">
+    <row r="174" spans="1:18" ht="33">
       <c r="A174" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A174" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E174),
@@ -20675,7 +20634,7 @@
       <c r="Q174" s="61"/>
       <c r="R174" s="61"/>
     </row>
-    <row r="175" spans="1:18" ht="45">
+    <row r="175" spans="1:18" ht="44">
       <c r="A175" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A175" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E175),
@@ -20710,7 +20669,7 @@
       <c r="Q175" s="61"/>
       <c r="R175" s="61"/>
     </row>
-    <row r="176" spans="1:18" ht="45">
+    <row r="176" spans="1:18" ht="44">
       <c r="A176" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A176" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E176),
@@ -20745,7 +20704,7 @@
       <c r="Q176" s="61"/>
       <c r="R176" s="61"/>
     </row>
-    <row r="177" spans="1:18" ht="33.75">
+    <row r="177" spans="1:18" ht="33">
       <c r="A177" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A177" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E177),
@@ -20780,7 +20739,7 @@
       <c r="Q177" s="61"/>
       <c r="R177" s="61"/>
     </row>
-    <row r="178" spans="1:18" ht="45">
+    <row r="178" spans="1:18" ht="44">
       <c r="A178" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A178" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E178),
@@ -20815,7 +20774,7 @@
       <c r="Q178" s="61"/>
       <c r="R178" s="61"/>
     </row>
-    <row r="179" spans="1:18" ht="45">
+    <row r="179" spans="1:18" ht="44">
       <c r="A179" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A179" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E179),
@@ -20850,7 +20809,7 @@
       <c r="Q179" s="61"/>
       <c r="R179" s="61"/>
     </row>
-    <row r="180" spans="1:18" ht="22.5">
+    <row r="180" spans="1:18" ht="22">
       <c r="A180" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A180" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E180),
@@ -20885,7 +20844,7 @@
       <c r="Q180" s="61"/>
       <c r="R180" s="61"/>
     </row>
-    <row r="181" spans="1:18" ht="33.75">
+    <row r="181" spans="1:18" ht="33">
       <c r="A181" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A181" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E181),
@@ -20922,7 +20881,7 @@
       <c r="Q181" s="61"/>
       <c r="R181" s="61"/>
     </row>
-    <row r="182" spans="1:18" ht="22.5">
+    <row r="182" spans="1:18" ht="22">
       <c r="A182" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A182" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E182),
@@ -20959,7 +20918,7 @@
       <c r="Q182" s="61"/>
       <c r="R182" s="61"/>
     </row>
-    <row r="183" spans="1:18" ht="22.5">
+    <row r="183" spans="1:18" ht="22">
       <c r="A183" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A183" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E183),
@@ -21002,7 +20961,7 @@
       <c r="Q183" s="67"/>
       <c r="R183" s="67"/>
     </row>
-    <row r="184" spans="1:18" ht="22.5">
+    <row r="184" spans="1:18" ht="22">
       <c r="A184" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A184" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E184),
@@ -21080,7 +21039,7 @@
       <c r="Q185" s="67"/>
       <c r="R185" s="67"/>
     </row>
-    <row r="186" spans="1:18" ht="22.5">
+    <row r="186" spans="1:18" ht="22">
       <c r="A186" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A186" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E186),
@@ -21123,7 +21082,7 @@
       <c r="Q186" s="67"/>
       <c r="R186" s="67"/>
     </row>
-    <row r="187" spans="1:18" ht="22.5">
+    <row r="187" spans="1:18" ht="22">
       <c r="A187" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A187" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E187),
@@ -21160,7 +21119,7 @@
       <c r="Q187" s="67"/>
       <c r="R187" s="67"/>
     </row>
-    <row r="188" spans="1:18" ht="22.5">
+    <row r="188" spans="1:18" ht="22">
       <c r="A188" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A188" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E188),
@@ -21195,7 +21154,7 @@
       <c r="Q188" s="67"/>
       <c r="R188" s="67"/>
     </row>
-    <row r="189" spans="1:18" ht="22.5">
+    <row r="189" spans="1:18" ht="22">
       <c r="A189" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A189" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E189),
@@ -21232,7 +21191,7 @@
       <c r="Q189" s="67"/>
       <c r="R189" s="67"/>
     </row>
-    <row r="190" spans="1:18" ht="22.5">
+    <row r="190" spans="1:18" ht="22">
       <c r="A190" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A190" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E190),
@@ -21267,7 +21226,7 @@
       <c r="Q190" s="67"/>
       <c r="R190" s="67"/>
     </row>
-    <row r="191" spans="1:18" ht="33.75">
+    <row r="191" spans="1:18" ht="33">
       <c r="A191" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A191" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E191),
@@ -21306,7 +21265,7 @@
       <c r="Q191" s="67"/>
       <c r="R191" s="67"/>
     </row>
-    <row r="192" spans="1:18" ht="22.5">
+    <row r="192" spans="1:18" ht="22">
       <c r="A192" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A192" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E192),
@@ -21347,7 +21306,7 @@
       <c r="Q192" s="67"/>
       <c r="R192" s="67"/>
     </row>
-    <row r="193" spans="1:18" ht="22.5">
+    <row r="193" spans="1:18" ht="22">
       <c r="A193" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A193" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E193),
@@ -21382,7 +21341,7 @@
       <c r="Q193" s="67"/>
       <c r="R193" s="67"/>
     </row>
-    <row r="194" spans="1:18" ht="22.5">
+    <row r="194" spans="1:18" ht="22">
       <c r="A194" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A194" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E194),
@@ -21417,7 +21376,7 @@
       <c r="Q194" s="67"/>
       <c r="R194" s="67"/>
     </row>
-    <row r="195" spans="1:18" ht="22.5">
+    <row r="195" spans="1:18" ht="22">
       <c r="A195" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A195" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E195),
@@ -21452,7 +21411,7 @@
       <c r="Q195" s="67"/>
       <c r="R195" s="67"/>
     </row>
-    <row r="196" spans="1:18" ht="22.5">
+    <row r="196" spans="1:18" ht="22">
       <c r="A196" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A196" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E196),
@@ -21487,7 +21446,7 @@
       <c r="Q196" s="67"/>
       <c r="R196" s="67"/>
     </row>
-    <row r="197" spans="1:18" ht="22.5">
+    <row r="197" spans="1:18" ht="22">
       <c r="A197" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A197" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E197),
@@ -21522,7 +21481,7 @@
       <c r="Q197" s="67"/>
       <c r="R197" s="67"/>
     </row>
-    <row r="198" spans="1:18" ht="22.5">
+    <row r="198" spans="1:18" ht="22">
       <c r="A198" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A198" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E198),
@@ -21557,7 +21516,7 @@
       <c r="Q198" s="67"/>
       <c r="R198" s="67"/>
     </row>
-    <row r="199" spans="1:18" ht="22.5">
+    <row r="199" spans="1:18" ht="22">
       <c r="A199" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A199" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E199),
@@ -21594,7 +21553,7 @@
       <c r="Q199" s="67"/>
       <c r="R199" s="67"/>
     </row>
-    <row r="200" spans="1:18" ht="22.5">
+    <row r="200" spans="1:18" ht="22">
       <c r="A200" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A200" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E200),
@@ -21633,7 +21592,7 @@
       <c r="Q200" s="67"/>
       <c r="R200" s="67"/>
     </row>
-    <row r="201" spans="1:18" ht="22.5">
+    <row r="201" spans="1:18" ht="22">
       <c r="A201" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A201" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E201),
@@ -21703,7 +21662,7 @@
       <c r="Q202" s="67"/>
       <c r="R202" s="67"/>
     </row>
-    <row r="203" spans="1:18" ht="22.5">
+    <row r="203" spans="1:18" ht="22">
       <c r="A203" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A203" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E203),
@@ -21738,7 +21697,7 @@
       <c r="Q203" s="67"/>
       <c r="R203" s="67"/>
     </row>
-    <row r="204" spans="1:18" ht="33.75">
+    <row r="204" spans="1:18" ht="33">
       <c r="A204" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A204" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E204),
@@ -21773,7 +21732,7 @@
       <c r="Q204" s="67"/>
       <c r="R204" s="67"/>
     </row>
-    <row r="205" spans="1:18" ht="33.75">
+    <row r="205" spans="1:18" ht="33">
       <c r="A205" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A205" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E205),
@@ -21808,7 +21767,7 @@
       <c r="Q205" s="67"/>
       <c r="R205" s="67"/>
     </row>
-    <row r="206" spans="1:18" ht="45">
+    <row r="206" spans="1:18" ht="44">
       <c r="A206" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A206" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E206),
@@ -21843,7 +21802,7 @@
       <c r="Q206" s="67"/>
       <c r="R206" s="67"/>
     </row>
-    <row r="207" spans="1:18" ht="33.75">
+    <row r="207" spans="1:18" ht="33">
       <c r="A207" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A207" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E207),
@@ -21878,7 +21837,7 @@
       <c r="Q207" s="67"/>
       <c r="R207" s="67"/>
     </row>
-    <row r="208" spans="1:18" ht="33.75">
+    <row r="208" spans="1:18" ht="33">
       <c r="A208" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A208" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E208),
@@ -21913,7 +21872,7 @@
       <c r="Q208" s="67"/>
       <c r="R208" s="67"/>
     </row>
-    <row r="209" spans="1:18" ht="22.5">
+    <row r="209" spans="1:18" ht="22">
       <c r="A209" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A209" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E209),
@@ -21948,7 +21907,7 @@
       <c r="Q209" s="67"/>
       <c r="R209" s="67"/>
     </row>
-    <row r="210" spans="1:18" ht="22.5">
+    <row r="210" spans="1:18" ht="22">
       <c r="A210" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A210" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E210),
@@ -21983,7 +21942,7 @@
       <c r="Q210" s="67"/>
       <c r="R210" s="67"/>
     </row>
-    <row r="211" spans="1:18" ht="33.75">
+    <row r="211" spans="1:18" ht="33">
       <c r="A211" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A211" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E211),
@@ -22018,7 +21977,7 @@
       <c r="Q211" s="67"/>
       <c r="R211" s="67"/>
     </row>
-    <row r="212" spans="1:18" ht="22.5">
+    <row r="212" spans="1:18" ht="22">
       <c r="A212" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A212" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E212),
@@ -22053,7 +22012,7 @@
       <c r="Q212" s="67"/>
       <c r="R212" s="67"/>
     </row>
-    <row r="213" spans="1:18" ht="22.5">
+    <row r="213" spans="1:18" ht="22">
       <c r="A213" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A213" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E213),
@@ -22092,7 +22051,7 @@
       <c r="Q213" s="67"/>
       <c r="R213" s="67"/>
     </row>
-    <row r="214" spans="1:18" ht="22.5">
+    <row r="214" spans="1:18" ht="22">
       <c r="A214" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A214" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E214),
@@ -22127,7 +22086,7 @@
       <c r="Q214" s="67"/>
       <c r="R214" s="67"/>
     </row>
-    <row r="215" spans="1:18" ht="22.5">
+    <row r="215" spans="1:18" ht="22">
       <c r="A215" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A215" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E215),
@@ -22197,7 +22156,7 @@
       <c r="Q216" s="67"/>
       <c r="R216" s="67"/>
     </row>
-    <row r="217" spans="1:18" ht="22.5">
+    <row r="217" spans="1:18" ht="22">
       <c r="A217" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A217" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E217),
@@ -22232,7 +22191,7 @@
       <c r="Q217" s="67"/>
       <c r="R217" s="67"/>
     </row>
-    <row r="218" spans="1:18" ht="45">
+    <row r="218" spans="1:18" ht="44">
       <c r="A218" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A218" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E218),
@@ -22267,7 +22226,7 @@
       <c r="Q218" s="67"/>
       <c r="R218" s="67"/>
     </row>
-    <row r="219" spans="1:18" ht="33.75">
+    <row r="219" spans="1:18" ht="33">
       <c r="A219" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A219" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E219),
@@ -22302,7 +22261,7 @@
       <c r="Q219" s="67"/>
       <c r="R219" s="67"/>
     </row>
-    <row r="220" spans="1:18" ht="33.75">
+    <row r="220" spans="1:18" ht="33">
       <c r="A220" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A220" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E220),
@@ -22337,7 +22296,7 @@
       <c r="Q220" s="67"/>
       <c r="R220" s="67"/>
     </row>
-    <row r="221" spans="1:18" ht="45">
+    <row r="221" spans="1:18" ht="44">
       <c r="A221" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A221" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E221),
@@ -22372,7 +22331,7 @@
       <c r="Q221" s="67"/>
       <c r="R221" s="67"/>
     </row>
-    <row r="222" spans="1:18" ht="33.75">
+    <row r="222" spans="1:18" ht="33">
       <c r="A222" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A222" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E222),
@@ -22407,7 +22366,7 @@
       <c r="Q222" s="67"/>
       <c r="R222" s="67"/>
     </row>
-    <row r="223" spans="1:18" ht="33.75">
+    <row r="223" spans="1:18" ht="33">
       <c r="A223" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A223" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E223),
@@ -22442,7 +22401,7 @@
       <c r="Q223" s="67"/>
       <c r="R223" s="67"/>
     </row>
-    <row r="224" spans="1:18" ht="22.5">
+    <row r="224" spans="1:18" ht="22">
       <c r="A224" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A224" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E224),
@@ -22477,7 +22436,7 @@
       <c r="Q224" s="67"/>
       <c r="R224" s="67"/>
     </row>
-    <row r="225" spans="1:18" ht="22.5">
+    <row r="225" spans="1:18" ht="22">
       <c r="A225" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A225" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E225),
@@ -22512,7 +22471,7 @@
       <c r="Q225" s="67"/>
       <c r="R225" s="67"/>
     </row>
-    <row r="226" spans="1:18" ht="33.75">
+    <row r="226" spans="1:18" ht="33">
       <c r="A226" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A226" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E226),
@@ -22547,7 +22506,7 @@
       <c r="Q226" s="67"/>
       <c r="R226" s="67"/>
     </row>
-    <row r="227" spans="1:18" ht="22.5">
+    <row r="227" spans="1:18" ht="22">
       <c r="A227" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A227" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E227),
@@ -22582,7 +22541,7 @@
       <c r="Q227" s="67"/>
       <c r="R227" s="67"/>
     </row>
-    <row r="228" spans="1:18" ht="45">
+    <row r="228" spans="1:18" ht="44">
       <c r="A228" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A228" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E228),
@@ -22619,7 +22578,7 @@
       <c r="Q228" s="67"/>
       <c r="R228" s="67"/>
     </row>
-    <row r="229" spans="1:18" ht="45">
+    <row r="229" spans="1:18" ht="44">
       <c r="A229" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A229" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E229),
@@ -22654,7 +22613,7 @@
       <c r="Q229" s="67"/>
       <c r="R229" s="67"/>
     </row>
-    <row r="230" spans="1:18" ht="33.75">
+    <row r="230" spans="1:18" ht="33">
       <c r="A230" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A230" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E230),
@@ -22689,7 +22648,7 @@
       <c r="Q230" s="67"/>
       <c r="R230" s="67"/>
     </row>
-    <row r="231" spans="1:18" ht="33.75">
+    <row r="231" spans="1:18" ht="33">
       <c r="A231" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A231" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E231),
@@ -22726,7 +22685,7 @@
       <c r="Q231" s="67"/>
       <c r="R231" s="67"/>
     </row>
-    <row r="232" spans="1:18" ht="22.5">
+    <row r="232" spans="1:18" ht="22">
       <c r="A232" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A232" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E232),
@@ -22763,7 +22722,7 @@
       <c r="Q232" s="67"/>
       <c r="R232" s="67"/>
     </row>
-    <row r="233" spans="1:18" ht="22.5">
+    <row r="233" spans="1:18" ht="22">
       <c r="A233" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A233" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E233),
@@ -22806,7 +22765,7 @@
       <c r="Q233" s="67"/>
       <c r="R233" s="67"/>
     </row>
-    <row r="234" spans="1:18" ht="22.5">
+    <row r="234" spans="1:18" ht="22">
       <c r="A234" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A234" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E234),
@@ -22843,7 +22802,7 @@
       <c r="Q234" s="67"/>
       <c r="R234" s="67"/>
     </row>
-    <row r="235" spans="1:18" ht="22.5">
+    <row r="235" spans="1:18" ht="22">
       <c r="A235" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A235" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E235),
@@ -22878,7 +22837,7 @@
       <c r="Q235" s="67"/>
       <c r="R235" s="67"/>
     </row>
-    <row r="236" spans="1:18" ht="22.5">
+    <row r="236" spans="1:18" ht="22">
       <c r="A236" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A236" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E236),
@@ -22913,7 +22872,7 @@
       <c r="Q236" s="67"/>
       <c r="R236" s="67"/>
     </row>
-    <row r="237" spans="1:18" ht="22.5">
+    <row r="237" spans="1:18" ht="22">
       <c r="A237" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A237" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E237),
@@ -22948,7 +22907,7 @@
       <c r="Q237" s="67"/>
       <c r="R237" s="67"/>
     </row>
-    <row r="238" spans="1:18" ht="33.75">
+    <row r="238" spans="1:18" ht="33">
       <c r="A238" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A238" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E238),
@@ -22983,7 +22942,7 @@
       <c r="Q238" s="67"/>
       <c r="R238" s="67"/>
     </row>
-    <row r="239" spans="1:18" ht="33.75">
+    <row r="239" spans="1:18" ht="33">
       <c r="A239" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A239" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E239),
@@ -23020,7 +22979,7 @@
       <c r="Q239" s="67"/>
       <c r="R239" s="67"/>
     </row>
-    <row r="240" spans="1:18" ht="33.75">
+    <row r="240" spans="1:18" ht="33">
       <c r="A240" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A240" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E240),
@@ -23055,7 +23014,7 @@
       <c r="Q240" s="67"/>
       <c r="R240" s="67"/>
     </row>
-    <row r="241" spans="1:18" ht="45">
+    <row r="241" spans="1:18" ht="44">
       <c r="A241" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A241" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E241),
@@ -23090,7 +23049,7 @@
       <c r="Q241" s="67"/>
       <c r="R241" s="67"/>
     </row>
-    <row r="242" spans="1:18" ht="45">
+    <row r="242" spans="1:18" ht="44">
       <c r="A242" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A242" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E242),
@@ -23125,7 +23084,7 @@
       <c r="Q242" s="67"/>
       <c r="R242" s="67"/>
     </row>
-    <row r="243" spans="1:18" ht="33.75">
+    <row r="243" spans="1:18" ht="33">
       <c r="A243" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A243" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E243),
@@ -23160,7 +23119,7 @@
       <c r="Q243" s="67"/>
       <c r="R243" s="67"/>
     </row>
-    <row r="244" spans="1:18" ht="33.75">
+    <row r="244" spans="1:18" ht="33">
       <c r="A244" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A244" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E244),
@@ -23197,7 +23156,7 @@
       <c r="Q244" s="67"/>
       <c r="R244" s="67"/>
     </row>
-    <row r="245" spans="1:18" ht="33.75">
+    <row r="245" spans="1:18" ht="33">
       <c r="A245" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A245" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E245),
@@ -23238,7 +23197,7 @@
       <c r="Q245" s="67"/>
       <c r="R245" s="67"/>
     </row>
-    <row r="246" spans="1:18" ht="22.5">
+    <row r="246" spans="1:18" ht="22">
       <c r="A246" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A246" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E246),
@@ -23281,7 +23240,7 @@
       <c r="Q246" s="67"/>
       <c r="R246" s="67"/>
     </row>
-    <row r="247" spans="1:18" ht="22.5">
+    <row r="247" spans="1:18" ht="22">
       <c r="A247" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A247" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E247),
@@ -23316,7 +23275,7 @@
       <c r="Q247" s="67"/>
       <c r="R247" s="67"/>
     </row>
-    <row r="248" spans="1:18" ht="33.75">
+    <row r="248" spans="1:18" ht="33">
       <c r="A248" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A248" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E248),
@@ -23355,7 +23314,7 @@
       <c r="Q248" s="67"/>
       <c r="R248" s="67"/>
     </row>
-    <row r="249" spans="1:18" ht="33.75">
+    <row r="249" spans="1:18" ht="33">
       <c r="A249" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A249" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E249),
@@ -23390,7 +23349,7 @@
       <c r="Q249" s="67"/>
       <c r="R249" s="67"/>
     </row>
-    <row r="250" spans="1:18" ht="33.75">
+    <row r="250" spans="1:18" ht="33">
       <c r="A250" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A250" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E250),
@@ -23431,7 +23390,7 @@
       <c r="Q250" s="67"/>
       <c r="R250" s="67"/>
     </row>
-    <row r="251" spans="1:18" ht="33.75">
+    <row r="251" spans="1:18" ht="33">
       <c r="A251" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A251" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E251),
@@ -23468,7 +23427,7 @@
       <c r="Q251" s="67"/>
       <c r="R251" s="67"/>
     </row>
-    <row r="252" spans="1:18" ht="33.75">
+    <row r="252" spans="1:18" ht="33">
       <c r="A252" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A252" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E252),
@@ -23505,7 +23464,7 @@
       <c r="Q252" s="67"/>
       <c r="R252" s="67"/>
     </row>
-    <row r="253" spans="1:18" ht="33.75">
+    <row r="253" spans="1:18" ht="33">
       <c r="A253" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A253" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E253),
@@ -23542,7 +23501,7 @@
       <c r="Q253" s="67"/>
       <c r="R253" s="67"/>
     </row>
-    <row r="254" spans="1:18" ht="22.5">
+    <row r="254" spans="1:18" ht="22">
       <c r="A254" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A254" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E254),
@@ -23581,7 +23540,7 @@
       <c r="Q254" s="67"/>
       <c r="R254" s="67"/>
     </row>
-    <row r="255" spans="1:18" ht="22.5">
+    <row r="255" spans="1:18" ht="22">
       <c r="A255" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A255" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E255),
@@ -23616,7 +23575,7 @@
       <c r="Q255" s="67"/>
       <c r="R255" s="67"/>
     </row>
-    <row r="256" spans="1:18" ht="33.75">
+    <row r="256" spans="1:18" ht="33">
       <c r="A256" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A256" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E256),
@@ -23653,7 +23612,7 @@
       <c r="Q256" s="67"/>
       <c r="R256" s="67"/>
     </row>
-    <row r="257" spans="1:18" ht="33.75">
+    <row r="257" spans="1:18" ht="33">
       <c r="A257" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A257" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E257),
@@ -23688,7 +23647,7 @@
       <c r="Q257" s="67"/>
       <c r="R257" s="67"/>
     </row>
-    <row r="258" spans="1:18" ht="33.75">
+    <row r="258" spans="1:18" ht="33">
       <c r="A258" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A258" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E258),
@@ -23723,7 +23682,7 @@
       <c r="Q258" s="67"/>
       <c r="R258" s="67"/>
     </row>
-    <row r="259" spans="1:18" ht="33.75">
+    <row r="259" spans="1:18" ht="33">
       <c r="A259" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A259" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E259),
@@ -23758,7 +23717,7 @@
       <c r="Q259" s="67"/>
       <c r="R259" s="67"/>
     </row>
-    <row r="260" spans="1:18" ht="33.75">
+    <row r="260" spans="1:18" ht="33">
       <c r="A260" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A260" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E260),
@@ -23793,7 +23752,7 @@
       <c r="Q260" s="67"/>
       <c r="R260" s="67"/>
     </row>
-    <row r="261" spans="1:18" ht="22.5">
+    <row r="261" spans="1:18" ht="22">
       <c r="A261" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A261" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E261),
@@ -23828,7 +23787,7 @@
       <c r="Q261" s="67"/>
       <c r="R261" s="67"/>
     </row>
-    <row r="262" spans="1:18" ht="22.5">
+    <row r="262" spans="1:18" ht="22">
       <c r="A262" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A262" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E262),
@@ -23863,7 +23822,7 @@
       <c r="Q262" s="67"/>
       <c r="R262" s="67"/>
     </row>
-    <row r="263" spans="1:18" ht="33.75">
+    <row r="263" spans="1:18" ht="33">
       <c r="A263" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A263" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E263),
@@ -23898,7 +23857,7 @@
       <c r="Q263" s="67"/>
       <c r="R263" s="67"/>
     </row>
-    <row r="264" spans="1:18" ht="33.75">
+    <row r="264" spans="1:18" ht="33">
       <c r="A264" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A264" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E264),
@@ -23933,7 +23892,7 @@
       <c r="Q264" s="67"/>
       <c r="R264" s="67"/>
     </row>
-    <row r="265" spans="1:18" ht="33.75">
+    <row r="265" spans="1:18" ht="33">
       <c r="A265" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A265" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E265),
@@ -23968,7 +23927,7 @@
       <c r="Q265" s="67"/>
       <c r="R265" s="67"/>
     </row>
-    <row r="266" spans="1:18" ht="33.75">
+    <row r="266" spans="1:18" ht="33">
       <c r="A266" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A266" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E266),
@@ -24075,7 +24034,7 @@
       <c r="Q268" s="67"/>
       <c r="R268" s="67"/>
     </row>
-    <row r="269" spans="1:18" ht="22.5">
+    <row r="269" spans="1:18" ht="22">
       <c r="A269" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A269" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E269),
@@ -24110,7 +24069,7 @@
       <c r="Q269" s="67"/>
       <c r="R269" s="67"/>
     </row>
-    <row r="270" spans="1:18" ht="22.5">
+    <row r="270" spans="1:18" ht="22">
       <c r="A270" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A270" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E270),
@@ -24145,7 +24104,7 @@
       <c r="Q270" s="67"/>
       <c r="R270" s="67"/>
     </row>
-    <row r="271" spans="1:18" ht="22.5">
+    <row r="271" spans="1:18" ht="22">
       <c r="A271" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A271" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E271),
@@ -24180,7 +24139,7 @@
       <c r="Q271" s="67"/>
       <c r="R271" s="67"/>
     </row>
-    <row r="272" spans="1:18" ht="33.75">
+    <row r="272" spans="1:18" ht="33">
       <c r="A272" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A272" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E272),
@@ -24215,7 +24174,7 @@
       <c r="Q272" s="67"/>
       <c r="R272" s="67"/>
     </row>
-    <row r="273" spans="1:18" ht="22.5">
+    <row r="273" spans="1:18" ht="22">
       <c r="A273" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A273" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E273),
@@ -24252,7 +24211,7 @@
       <c r="Q273" s="67"/>
       <c r="R273" s="67"/>
     </row>
-    <row r="274" spans="1:18" ht="33.75">
+    <row r="274" spans="1:18" ht="33">
       <c r="A274" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A274" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E274),
@@ -24287,7 +24246,7 @@
       <c r="Q274" s="67"/>
       <c r="R274" s="67"/>
     </row>
-    <row r="275" spans="1:18" ht="45">
+    <row r="275" spans="1:18" ht="44">
       <c r="A275" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A275" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E275),
@@ -24322,7 +24281,7 @@
       <c r="Q275" s="67"/>
       <c r="R275" s="67"/>
     </row>
-    <row r="276" spans="1:18" ht="45">
+    <row r="276" spans="1:18" ht="44">
       <c r="A276" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A276" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E276),
@@ -24357,7 +24316,7 @@
       <c r="Q276" s="67"/>
       <c r="R276" s="67"/>
     </row>
-    <row r="277" spans="1:18" ht="22.5">
+    <row r="277" spans="1:18" ht="22">
       <c r="A277" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A277" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E277),
@@ -24392,7 +24351,7 @@
       <c r="Q277" s="67"/>
       <c r="R277" s="67"/>
     </row>
-    <row r="278" spans="1:18" ht="45">
+    <row r="278" spans="1:18" ht="44">
       <c r="A278" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A278" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E278),
@@ -24427,7 +24386,7 @@
       <c r="Q278" s="67"/>
       <c r="R278" s="67"/>
     </row>
-    <row r="279" spans="1:18" ht="45">
+    <row r="279" spans="1:18" ht="44">
       <c r="A279" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A279" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E279),
@@ -24462,7 +24421,7 @@
       <c r="Q279" s="67"/>
       <c r="R279" s="67"/>
     </row>
-    <row r="280" spans="1:18" ht="22.5">
+    <row r="280" spans="1:18" ht="22">
       <c r="A280" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A280" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E280),
@@ -24497,7 +24456,7 @@
       <c r="Q280" s="67"/>
       <c r="R280" s="67"/>
     </row>
-    <row r="281" spans="1:18" ht="22.5">
+    <row r="281" spans="1:18" ht="22">
       <c r="A281" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A281" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E281),
@@ -24534,7 +24493,7 @@
       <c r="Q281" s="67"/>
       <c r="R281" s="67"/>
     </row>
-    <row r="282" spans="1:18" ht="22.5">
+    <row r="282" spans="1:18" ht="22">
       <c r="A282" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A282" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E282),
@@ -24577,7 +24536,7 @@
       <c r="Q282" s="61"/>
       <c r="R282" s="61"/>
     </row>
-    <row r="283" spans="1:18" ht="22.5">
+    <row r="283" spans="1:18" ht="22">
       <c r="A283" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A283" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E283),
@@ -24612,7 +24571,7 @@
       <c r="Q283" s="61"/>
       <c r="R283" s="61"/>
     </row>
-    <row r="284" spans="1:18" ht="22.5">
+    <row r="284" spans="1:18" ht="22">
       <c r="A284" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A284" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E284),
@@ -24647,7 +24606,7 @@
       <c r="Q284" s="61"/>
       <c r="R284" s="61"/>
     </row>
-    <row r="285" spans="1:18" ht="22.5">
+    <row r="285" spans="1:18" ht="22">
       <c r="A285" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A285" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E285),
@@ -24682,7 +24641,7 @@
       <c r="Q285" s="61"/>
       <c r="R285" s="61"/>
     </row>
-    <row r="286" spans="1:18" ht="22.5">
+    <row r="286" spans="1:18" ht="22">
       <c r="A286" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A286" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E286),
@@ -24723,7 +24682,7 @@
       <c r="Q286" s="61"/>
       <c r="R286" s="61"/>
     </row>
-    <row r="287" spans="1:18" ht="22.5">
+    <row r="287" spans="1:18" ht="22">
       <c r="A287" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A287" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E287),
@@ -24760,7 +24719,7 @@
       <c r="Q287" s="61"/>
       <c r="R287" s="61"/>
     </row>
-    <row r="288" spans="1:18" ht="22.5">
+    <row r="288" spans="1:18" ht="22">
       <c r="A288" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A288" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E288),
@@ -24797,7 +24756,7 @@
       <c r="Q288" s="61"/>
       <c r="R288" s="61"/>
     </row>
-    <row r="289" spans="1:18" ht="22.5">
+    <row r="289" spans="1:18" ht="22">
       <c r="A289" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A289" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E289),
@@ -24834,7 +24793,7 @@
       <c r="Q289" s="61"/>
       <c r="R289" s="61"/>
     </row>
-    <row r="290" spans="1:18" ht="22.5">
+    <row r="290" spans="1:18" ht="22">
       <c r="A290" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A290" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E290),
@@ -24873,7 +24832,7 @@
       <c r="Q290" s="61"/>
       <c r="R290" s="61"/>
     </row>
-    <row r="291" spans="1:18" ht="22.5">
+    <row r="291" spans="1:18" ht="22">
       <c r="A291" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A291" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E291),
@@ -24908,7 +24867,7 @@
       <c r="Q291" s="61"/>
       <c r="R291" s="61"/>
     </row>
-    <row r="292" spans="1:18" ht="33.75">
+    <row r="292" spans="1:18" ht="33">
       <c r="A292" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A292" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E292),
@@ -24943,7 +24902,7 @@
       <c r="Q292" s="61"/>
       <c r="R292" s="61"/>
     </row>
-    <row r="293" spans="1:18" ht="33.75">
+    <row r="293" spans="1:18" ht="33">
       <c r="A293" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A293" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E293),
@@ -24978,7 +24937,7 @@
       <c r="Q293" s="61"/>
       <c r="R293" s="61"/>
     </row>
-    <row r="294" spans="1:18" ht="33.75">
+    <row r="294" spans="1:18" ht="33">
       <c r="A294" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A294" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E294),
@@ -25013,7 +24972,7 @@
       <c r="Q294" s="61"/>
       <c r="R294" s="61"/>
     </row>
-    <row r="295" spans="1:18" ht="33.75">
+    <row r="295" spans="1:18" ht="33">
       <c r="A295" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A295" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E295),
@@ -25048,7 +25007,7 @@
       <c r="Q295" s="61"/>
       <c r="R295" s="61"/>
     </row>
-    <row r="296" spans="1:18" ht="33.75">
+    <row r="296" spans="1:18" ht="33">
       <c r="A296" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A296" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E296),
@@ -25083,7 +25042,7 @@
       <c r="Q296" s="61"/>
       <c r="R296" s="61"/>
     </row>
-    <row r="297" spans="1:18" ht="22.5">
+    <row r="297" spans="1:18" ht="22">
       <c r="A297" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A297" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E297),
@@ -25118,7 +25077,7 @@
       <c r="Q297" s="61"/>
       <c r="R297" s="61"/>
     </row>
-    <row r="298" spans="1:18" ht="22.5">
+    <row r="298" spans="1:18" ht="22">
       <c r="A298" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A298" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E298),
@@ -25190,16 +25149,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R316"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="3" width="8.625" style="28" customWidth="1"/>
-    <col min="4" max="5" width="8.625" style="29" customWidth="1"/>
+    <col min="1" max="3" width="8.58203125" style="28" customWidth="1"/>
+    <col min="4" max="5" width="8.58203125" style="29" customWidth="1"/>
     <col min="6" max="6" width="39" style="29" customWidth="1"/>
-    <col min="7" max="7" width="40.625" style="107" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="16.375" style="28" customWidth="1"/>
-    <col min="10" max="11" width="23.625" style="28" customWidth="1"/>
-    <col min="12" max="12" width="15.625" style="28" customWidth="1"/>
-    <col min="13" max="18" width="8.625" style="28" customWidth="1"/>
+    <col min="7" max="7" width="40.58203125" style="107" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="16.33203125" style="28" customWidth="1"/>
+    <col min="10" max="11" width="23.58203125" style="28" customWidth="1"/>
+    <col min="12" max="12" width="15.58203125" style="28" customWidth="1"/>
+    <col min="13" max="18" width="8.58203125" style="28" customWidth="1"/>
     <col min="19" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -25245,10 +25204,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="12" thickBot="1">
-      <c r="A8" s="30" t="s">
-        <v>469</v>
-      </c>
+    <row r="8" spans="1:18" ht="11.5" thickBot="1">
+      <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
       <c r="D8" s="31"/>
@@ -25324,7 +25281,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="22.5">
+    <row r="11" spans="1:18" ht="22">
       <c r="A11" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A11" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E11),
@@ -25338,7 +25295,7 @@
         <v>1-1-1</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C11" s="110" t="s">
         <v>85</v>
@@ -25353,7 +25310,7 @@
         <v>88</v>
       </c>
       <c r="G11" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H11" s="61"/>
       <c r="I11" s="61"/>
@@ -25367,7 +25324,7 @@
       <c r="Q11" s="113"/>
       <c r="R11" s="58"/>
     </row>
-    <row r="12" spans="1:18" ht="22.5">
+    <row r="12" spans="1:18" ht="22">
       <c r="A12" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A12" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E12),
@@ -25390,7 +25347,7 @@
         <v>91</v>
       </c>
       <c r="G12" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H12" s="61"/>
       <c r="I12" s="61"/>
@@ -25404,7 +25361,7 @@
       <c r="Q12" s="113"/>
       <c r="R12" s="58"/>
     </row>
-    <row r="13" spans="1:18" ht="33.75">
+    <row r="13" spans="1:18" ht="33">
       <c r="A13" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A13" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E13),
@@ -25429,7 +25386,7 @@
         <v>94</v>
       </c>
       <c r="G13" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H13" s="61"/>
       <c r="I13" s="61"/>
@@ -25443,7 +25400,7 @@
       <c r="Q13" s="113"/>
       <c r="R13" s="58"/>
     </row>
-    <row r="14" spans="1:18" ht="22.5">
+    <row r="14" spans="1:18" ht="22">
       <c r="A14" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A14" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E14),
@@ -25464,7 +25421,7 @@
         <v>95</v>
       </c>
       <c r="G14" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H14" s="61"/>
       <c r="I14" s="61"/>
@@ -25478,7 +25435,7 @@
       <c r="Q14" s="113"/>
       <c r="R14" s="58"/>
     </row>
-    <row r="15" spans="1:18" ht="22.5">
+    <row r="15" spans="1:18" ht="22">
       <c r="A15" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A15" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E15),
@@ -25499,7 +25456,7 @@
         <v>96</v>
       </c>
       <c r="G15" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H15" s="61"/>
       <c r="I15" s="61"/>
@@ -25513,7 +25470,7 @@
       <c r="Q15" s="113"/>
       <c r="R15" s="58"/>
     </row>
-    <row r="16" spans="1:18" ht="22.5">
+    <row r="16" spans="1:18" ht="22">
       <c r="A16" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A16" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E16),
@@ -25534,7 +25491,7 @@
         <v>97</v>
       </c>
       <c r="G16" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H16" s="61"/>
       <c r="I16" s="61"/>
@@ -25548,7 +25505,7 @@
       <c r="Q16" s="113"/>
       <c r="R16" s="58"/>
     </row>
-    <row r="17" spans="1:18" ht="33.75">
+    <row r="17" spans="1:18" ht="33">
       <c r="A17" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A17" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E17),
@@ -25569,7 +25526,7 @@
         <v>98</v>
       </c>
       <c r="G17" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H17" s="61"/>
       <c r="I17" s="61"/>
@@ -25583,7 +25540,7 @@
       <c r="Q17" s="113"/>
       <c r="R17" s="58"/>
     </row>
-    <row r="18" spans="1:18" ht="22.5">
+    <row r="18" spans="1:18" ht="22">
       <c r="A18" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A18" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E18),
@@ -25608,7 +25565,7 @@
         <v>101</v>
       </c>
       <c r="G18" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H18" s="61"/>
       <c r="I18" s="61"/>
@@ -25622,7 +25579,7 @@
       <c r="Q18" s="113"/>
       <c r="R18" s="58"/>
     </row>
-    <row r="19" spans="1:18" ht="22.5">
+    <row r="19" spans="1:18" ht="22">
       <c r="A19" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A19" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E19),
@@ -25643,7 +25600,7 @@
         <v>102</v>
       </c>
       <c r="G19" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H19" s="61"/>
       <c r="I19" s="61"/>
@@ -25657,7 +25614,7 @@
       <c r="Q19" s="113"/>
       <c r="R19" s="58"/>
     </row>
-    <row r="20" spans="1:18" ht="22.5">
+    <row r="20" spans="1:18" ht="22">
       <c r="A20" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A20" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E20),
@@ -25678,7 +25635,7 @@
         <v>103</v>
       </c>
       <c r="G20" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H20" s="61"/>
       <c r="I20" s="61"/>
@@ -25692,7 +25649,7 @@
       <c r="Q20" s="113"/>
       <c r="R20" s="58"/>
     </row>
-    <row r="21" spans="1:18" ht="22.5">
+    <row r="21" spans="1:18" ht="22">
       <c r="A21" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A21" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E21),
@@ -25715,7 +25672,7 @@
         <v>105</v>
       </c>
       <c r="G21" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H21" s="61"/>
       <c r="I21" s="61"/>
@@ -25729,7 +25686,7 @@
       <c r="Q21" s="113"/>
       <c r="R21" s="58"/>
     </row>
-    <row r="22" spans="1:18" ht="22.5">
+    <row r="22" spans="1:18" ht="22">
       <c r="A22" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A22" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E22),
@@ -25750,7 +25707,7 @@
         <v>106</v>
       </c>
       <c r="G22" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H22" s="61"/>
       <c r="I22" s="61"/>
@@ -25764,7 +25721,7 @@
       <c r="Q22" s="113"/>
       <c r="R22" s="58"/>
     </row>
-    <row r="23" spans="1:18" ht="22.5">
+    <row r="23" spans="1:18" ht="22">
       <c r="A23" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A23" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E23),
@@ -25782,10 +25739,10 @@
       <c r="D23" s="116"/>
       <c r="E23" s="116"/>
       <c r="F23" s="112" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G23" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H23" s="61"/>
       <c r="I23" s="61"/>
@@ -25799,7 +25756,7 @@
       <c r="Q23" s="113"/>
       <c r="R23" s="58"/>
     </row>
-    <row r="24" spans="1:18" ht="22.5">
+    <row r="24" spans="1:18" ht="22">
       <c r="A24" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A24" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E24),
@@ -25817,10 +25774,10 @@
       <c r="D24" s="117"/>
       <c r="E24" s="115"/>
       <c r="F24" s="112" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G24" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H24" s="61"/>
       <c r="I24" s="61"/>
@@ -25834,7 +25791,7 @@
       <c r="Q24" s="113"/>
       <c r="R24" s="58"/>
     </row>
-    <row r="25" spans="1:18" ht="22.5">
+    <row r="25" spans="1:18" ht="22">
       <c r="A25" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A25" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E25),
@@ -25859,7 +25816,7 @@
         <v>110</v>
       </c>
       <c r="G25" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H25" s="61"/>
       <c r="I25" s="61"/>
@@ -25873,7 +25830,7 @@
       <c r="Q25" s="113"/>
       <c r="R25" s="58"/>
     </row>
-    <row r="26" spans="1:18" ht="22.5">
+    <row r="26" spans="1:18" ht="22">
       <c r="A26" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A26" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E26),
@@ -25894,7 +25851,7 @@
         <v>111</v>
       </c>
       <c r="G26" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H26" s="61"/>
       <c r="I26" s="61"/>
@@ -25908,7 +25865,7 @@
       <c r="Q26" s="113"/>
       <c r="R26" s="58"/>
     </row>
-    <row r="27" spans="1:18" ht="33.75">
+    <row r="27" spans="1:18" ht="33">
       <c r="A27" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A27" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E27),
@@ -25933,7 +25890,7 @@
         <v>114</v>
       </c>
       <c r="G27" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H27" s="61"/>
       <c r="I27" s="61"/>
@@ -25947,7 +25904,7 @@
       <c r="Q27" s="113"/>
       <c r="R27" s="58"/>
     </row>
-    <row r="28" spans="1:18" ht="22.5">
+    <row r="28" spans="1:18" ht="22">
       <c r="A28" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A28" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E28),
@@ -25968,7 +25925,7 @@
         <v>115</v>
       </c>
       <c r="G28" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H28" s="61"/>
       <c r="I28" s="61"/>
@@ -25982,7 +25939,7 @@
       <c r="Q28" s="113"/>
       <c r="R28" s="58"/>
     </row>
-    <row r="29" spans="1:18" ht="22.5">
+    <row r="29" spans="1:18" ht="22">
       <c r="A29" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A29" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E29),
@@ -26005,7 +25962,7 @@
         <v>117</v>
       </c>
       <c r="G29" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H29" s="61"/>
       <c r="I29" s="61"/>
@@ -26019,7 +25976,7 @@
       <c r="Q29" s="113"/>
       <c r="R29" s="58"/>
     </row>
-    <row r="30" spans="1:18" ht="22.5">
+    <row r="30" spans="1:18" ht="22">
       <c r="A30" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A30" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E30),
@@ -26040,7 +25997,7 @@
         <v>118</v>
       </c>
       <c r="G30" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H30" s="61"/>
       <c r="I30" s="61"/>
@@ -26054,7 +26011,7 @@
       <c r="Q30" s="113"/>
       <c r="R30" s="58"/>
     </row>
-    <row r="31" spans="1:18" ht="22.5">
+    <row r="31" spans="1:18" ht="22">
       <c r="A31" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A31" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E31),
@@ -26075,7 +26032,7 @@
         <v>119</v>
       </c>
       <c r="G31" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H31" s="61"/>
       <c r="I31" s="61"/>
@@ -26089,7 +26046,7 @@
       <c r="Q31" s="113"/>
       <c r="R31" s="58"/>
     </row>
-    <row r="32" spans="1:18" ht="22.5">
+    <row r="32" spans="1:18" ht="22">
       <c r="A32" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A32" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E32),
@@ -26110,7 +26067,7 @@
         <v>120</v>
       </c>
       <c r="G32" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H32" s="61"/>
       <c r="I32" s="61"/>
@@ -26124,7 +26081,7 @@
       <c r="Q32" s="113"/>
       <c r="R32" s="58"/>
     </row>
-    <row r="33" spans="1:18" ht="22.5">
+    <row r="33" spans="1:18" ht="22">
       <c r="A33" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A33" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E33),
@@ -26141,13 +26098,13 @@
       <c r="C33" s="114"/>
       <c r="D33" s="116"/>
       <c r="E33" s="116" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F33" s="112" t="s">
         <v>122</v>
       </c>
       <c r="G33" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H33" s="61"/>
       <c r="I33" s="61"/>
@@ -26161,7 +26118,7 @@
       <c r="Q33" s="113"/>
       <c r="R33" s="58"/>
     </row>
-    <row r="34" spans="1:18" ht="22.5">
+    <row r="34" spans="1:18" ht="22">
       <c r="A34" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A34" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E34),
@@ -26182,7 +26139,7 @@
         <v>123</v>
       </c>
       <c r="G34" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H34" s="61"/>
       <c r="I34" s="61"/>
@@ -26196,7 +26153,7 @@
       <c r="Q34" s="113"/>
       <c r="R34" s="58"/>
     </row>
-    <row r="35" spans="1:18" ht="45">
+    <row r="35" spans="1:18" ht="44">
       <c r="A35" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A35" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E35),
@@ -26216,10 +26173,10 @@
         <v>124</v>
       </c>
       <c r="F35" s="112" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G35" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H35" s="56"/>
       <c r="I35" s="56"/>
@@ -26233,7 +26190,7 @@
       <c r="Q35" s="113"/>
       <c r="R35" s="58"/>
     </row>
-    <row r="36" spans="1:18" ht="33.75">
+    <row r="36" spans="1:18" ht="33">
       <c r="A36" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A36" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E36),
@@ -26251,16 +26208,16 @@
         <v>126</v>
       </c>
       <c r="D36" s="118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E36" s="110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F36" s="115" t="s">
         <v>128</v>
       </c>
       <c r="G36" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H36" s="61"/>
       <c r="I36" s="61"/>
@@ -26274,7 +26231,7 @@
       <c r="Q36" s="113"/>
       <c r="R36" s="58"/>
     </row>
-    <row r="37" spans="1:18" ht="33.75">
+    <row r="37" spans="1:18" ht="33">
       <c r="A37" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A37" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E37),
@@ -26292,10 +26249,10 @@
       <c r="D37" s="116"/>
       <c r="E37" s="111"/>
       <c r="F37" s="112" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G37" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H37" s="61"/>
       <c r="I37" s="61"/>
@@ -26309,7 +26266,7 @@
       <c r="Q37" s="113"/>
       <c r="R37" s="58"/>
     </row>
-    <row r="38" spans="1:18" ht="33.75">
+    <row r="38" spans="1:18" ht="33">
       <c r="A38" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A38" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E38),
@@ -26330,7 +26287,7 @@
         <v>130</v>
       </c>
       <c r="G38" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H38" s="61"/>
       <c r="I38" s="61"/>
@@ -26344,7 +26301,7 @@
       <c r="Q38" s="113"/>
       <c r="R38" s="58"/>
     </row>
-    <row r="39" spans="1:18" ht="22.5">
+    <row r="39" spans="1:18" ht="22">
       <c r="A39" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A39" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E39),
@@ -26365,7 +26322,7 @@
         <v>131</v>
       </c>
       <c r="G39" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H39" s="61"/>
       <c r="I39" s="61"/>
@@ -26379,7 +26336,7 @@
       <c r="Q39" s="113"/>
       <c r="R39" s="58"/>
     </row>
-    <row r="40" spans="1:18" ht="33.75">
+    <row r="40" spans="1:18" ht="33">
       <c r="A40" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A40" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E40),
@@ -26401,10 +26358,10 @@
         <v>93</v>
       </c>
       <c r="F40" s="112" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G40" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H40" s="61"/>
       <c r="I40" s="61"/>
@@ -26436,10 +26393,10 @@
       <c r="D41" s="117"/>
       <c r="E41" s="115"/>
       <c r="F41" s="112" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G41" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H41" s="61"/>
       <c r="I41" s="61"/>
@@ -26453,7 +26410,7 @@
       <c r="Q41" s="113"/>
       <c r="R41" s="58"/>
     </row>
-    <row r="42" spans="1:18" ht="22.5">
+    <row r="42" spans="1:18" ht="22">
       <c r="A42" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A42" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E42),
@@ -26496,7 +26453,7 @@
       <c r="Q42" s="113"/>
       <c r="R42" s="58"/>
     </row>
-    <row r="43" spans="1:18" ht="22.5">
+    <row r="43" spans="1:18" ht="22">
       <c r="A43" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A43" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E43),
@@ -26531,7 +26488,7 @@
       <c r="Q43" s="113"/>
       <c r="R43" s="58"/>
     </row>
-    <row r="44" spans="1:18" ht="33.75">
+    <row r="44" spans="1:18" ht="33">
       <c r="A44" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A44" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E44),
@@ -26566,7 +26523,7 @@
       <c r="Q44" s="113"/>
       <c r="R44" s="58"/>
     </row>
-    <row r="45" spans="1:18" ht="22.5">
+    <row r="45" spans="1:18" ht="22">
       <c r="A45" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A45" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E45),
@@ -26603,7 +26560,7 @@
       <c r="Q45" s="113"/>
       <c r="R45" s="58"/>
     </row>
-    <row r="46" spans="1:18" ht="22.5">
+    <row r="46" spans="1:18" ht="22">
       <c r="A46" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A46" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E46),
@@ -26638,7 +26595,7 @@
       <c r="Q46" s="113"/>
       <c r="R46" s="58"/>
     </row>
-    <row r="47" spans="1:18" ht="33.75">
+    <row r="47" spans="1:18" ht="33">
       <c r="A47" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A47" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E47),
@@ -26673,7 +26630,7 @@
       <c r="Q47" s="113"/>
       <c r="R47" s="58"/>
     </row>
-    <row r="48" spans="1:18" ht="22.5">
+    <row r="48" spans="1:18" ht="22">
       <c r="A48" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A48" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E48),
@@ -26710,7 +26667,7 @@
       <c r="Q48" s="113"/>
       <c r="R48" s="58"/>
     </row>
-    <row r="49" spans="1:18" ht="22.5">
+    <row r="49" spans="1:18" ht="22">
       <c r="A49" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A49" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E49),
@@ -26745,7 +26702,7 @@
       <c r="Q49" s="113"/>
       <c r="R49" s="58"/>
     </row>
-    <row r="50" spans="1:18" ht="22.5">
+    <row r="50" spans="1:18" ht="22">
       <c r="A50" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A50" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E50),
@@ -26782,7 +26739,7 @@
       <c r="Q50" s="113"/>
       <c r="R50" s="58"/>
     </row>
-    <row r="51" spans="1:18" ht="22.5">
+    <row r="51" spans="1:18" ht="22">
       <c r="A51" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A51" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E51),
@@ -26817,7 +26774,7 @@
       <c r="Q51" s="113"/>
       <c r="R51" s="58"/>
     </row>
-    <row r="52" spans="1:18" ht="22.5">
+    <row r="52" spans="1:18" ht="22">
       <c r="A52" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A52" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E52),
@@ -26852,7 +26809,7 @@
       <c r="Q52" s="113"/>
       <c r="R52" s="58"/>
     </row>
-    <row r="53" spans="1:18" ht="22.5">
+    <row r="53" spans="1:18" ht="22">
       <c r="A53" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A53" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E53),
@@ -26887,7 +26844,7 @@
       <c r="Q53" s="113"/>
       <c r="R53" s="58"/>
     </row>
-    <row r="54" spans="1:18" ht="22.5">
+    <row r="54" spans="1:18" ht="22">
       <c r="A54" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A54" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E54),
@@ -26922,7 +26879,7 @@
       <c r="Q54" s="113"/>
       <c r="R54" s="58"/>
     </row>
-    <row r="55" spans="1:18" ht="22.5">
+    <row r="55" spans="1:18" ht="22">
       <c r="A55" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A55" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E55),
@@ -26957,7 +26914,7 @@
       <c r="Q55" s="113"/>
       <c r="R55" s="58"/>
     </row>
-    <row r="56" spans="1:18" ht="33.75">
+    <row r="56" spans="1:18" ht="33">
       <c r="A56" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A56" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E56),
@@ -26994,7 +26951,7 @@
       <c r="Q56" s="113"/>
       <c r="R56" s="58"/>
     </row>
-    <row r="57" spans="1:18" ht="22.5">
+    <row r="57" spans="1:18" ht="22">
       <c r="A57" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A57" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E57),
@@ -27011,7 +26968,7 @@
       <c r="C57" s="111"/>
       <c r="D57" s="111"/>
       <c r="E57" s="112" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F57" s="112" t="s">
         <v>159</v>
@@ -27031,7 +26988,7 @@
       <c r="Q57" s="113"/>
       <c r="R57" s="58"/>
     </row>
-    <row r="58" spans="1:18" ht="22.5">
+    <row r="58" spans="1:18" ht="22">
       <c r="A58" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A58" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E58),
@@ -27068,7 +27025,7 @@
       <c r="Q58" s="113"/>
       <c r="R58" s="58"/>
     </row>
-    <row r="59" spans="1:18" ht="22.5">
+    <row r="59" spans="1:18" ht="22">
       <c r="A59" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A59" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E59),
@@ -27087,10 +27044,10 @@
         <v>162</v>
       </c>
       <c r="E59" s="116" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F59" s="112" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="G59" s="58" t="s">
         <v>140</v>
@@ -27107,7 +27064,7 @@
       <c r="Q59" s="113"/>
       <c r="R59" s="58"/>
     </row>
-    <row r="60" spans="1:18" ht="22.5">
+    <row r="60" spans="1:18" ht="22">
       <c r="A60" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A60" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E60),
@@ -27125,7 +27082,7 @@
       <c r="D60" s="111"/>
       <c r="E60" s="116"/>
       <c r="F60" s="110" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G60" s="58" t="s">
         <v>140</v>
@@ -27142,7 +27099,7 @@
       <c r="Q60" s="113"/>
       <c r="R60" s="58"/>
     </row>
-    <row r="61" spans="1:18" ht="22.5">
+    <row r="61" spans="1:18" ht="22">
       <c r="A61" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A61" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E61),
@@ -27160,7 +27117,7 @@
       <c r="D61" s="111"/>
       <c r="E61" s="116"/>
       <c r="F61" s="112" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G61" s="58" t="s">
         <v>140</v>
@@ -27177,7 +27134,7 @@
       <c r="Q61" s="113"/>
       <c r="R61" s="58"/>
     </row>
-    <row r="62" spans="1:18" ht="22.5">
+    <row r="62" spans="1:18" ht="22">
       <c r="A62" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A62" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E62),
@@ -27195,7 +27152,7 @@
       <c r="D62" s="111"/>
       <c r="E62" s="116"/>
       <c r="F62" s="112" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G62" s="58" t="s">
         <v>140</v>
@@ -27212,7 +27169,7 @@
       <c r="Q62" s="113"/>
       <c r="R62" s="58"/>
     </row>
-    <row r="63" spans="1:18" ht="22.5">
+    <row r="63" spans="1:18" ht="22">
       <c r="A63" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A63" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E63),
@@ -27247,7 +27204,7 @@
       <c r="Q63" s="113"/>
       <c r="R63" s="58"/>
     </row>
-    <row r="64" spans="1:18" ht="33.75">
+    <row r="64" spans="1:18" ht="33">
       <c r="A64" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A64" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E64),
@@ -27284,7 +27241,7 @@
       <c r="Q64" s="113"/>
       <c r="R64" s="58"/>
     </row>
-    <row r="65" spans="1:18" ht="33.75">
+    <row r="65" spans="1:18" ht="33">
       <c r="A65" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A65" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E65),
@@ -27319,7 +27276,7 @@
       <c r="Q65" s="113"/>
       <c r="R65" s="58"/>
     </row>
-    <row r="66" spans="1:18" ht="45">
+    <row r="66" spans="1:18" ht="44">
       <c r="A66" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A66" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E66),
@@ -27354,7 +27311,7 @@
       <c r="Q66" s="113"/>
       <c r="R66" s="58"/>
     </row>
-    <row r="67" spans="1:18" ht="33.75">
+    <row r="67" spans="1:18" ht="33">
       <c r="A67" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A67" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E67),
@@ -27389,7 +27346,7 @@
       <c r="Q67" s="113"/>
       <c r="R67" s="58"/>
     </row>
-    <row r="68" spans="1:18" ht="33.75">
+    <row r="68" spans="1:18" ht="33">
       <c r="A68" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A68" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E68),
@@ -27424,7 +27381,7 @@
       <c r="Q68" s="113"/>
       <c r="R68" s="58"/>
     </row>
-    <row r="69" spans="1:18" ht="22.5">
+    <row r="69" spans="1:18" ht="22">
       <c r="A69" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A69" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E69),
@@ -27459,7 +27416,7 @@
       <c r="Q69" s="113"/>
       <c r="R69" s="58"/>
     </row>
-    <row r="70" spans="1:18" ht="22.5">
+    <row r="70" spans="1:18" ht="22">
       <c r="A70" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A70" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E70),
@@ -27494,7 +27451,7 @@
       <c r="Q70" s="113"/>
       <c r="R70" s="58"/>
     </row>
-    <row r="71" spans="1:18" ht="33.75">
+    <row r="71" spans="1:18" ht="33">
       <c r="A71" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A71" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E71),
@@ -27529,7 +27486,7 @@
       <c r="Q71" s="113"/>
       <c r="R71" s="58"/>
     </row>
-    <row r="72" spans="1:18" ht="22.5">
+    <row r="72" spans="1:18" ht="22">
       <c r="A72" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A72" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E72),
@@ -27708,7 +27665,7 @@
       <c r="Q76" s="113"/>
       <c r="R76" s="58"/>
     </row>
-    <row r="77" spans="1:18" ht="22.5">
+    <row r="77" spans="1:18" ht="22">
       <c r="A77" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A77" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E77),
@@ -27743,7 +27700,7 @@
       <c r="Q77" s="113"/>
       <c r="R77" s="58"/>
     </row>
-    <row r="78" spans="1:18" ht="22.5">
+    <row r="78" spans="1:18" ht="22">
       <c r="A78" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A78" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E78),
@@ -27784,7 +27741,7 @@
       <c r="Q78" s="113"/>
       <c r="R78" s="58"/>
     </row>
-    <row r="79" spans="1:18" ht="33.75">
+    <row r="79" spans="1:18" ht="33">
       <c r="A79" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A79" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E79),
@@ -27856,7 +27813,7 @@
       <c r="Q80" s="113"/>
       <c r="R80" s="58"/>
     </row>
-    <row r="81" spans="1:18" ht="33.75">
+    <row r="81" spans="1:18" ht="33">
       <c r="A81" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A81" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E81),
@@ -27893,7 +27850,7 @@
       <c r="Q81" s="113"/>
       <c r="R81" s="58"/>
     </row>
-    <row r="82" spans="1:18" ht="33.75">
+    <row r="82" spans="1:18" ht="33">
       <c r="A82" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A82" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E82),
@@ -27928,7 +27885,7 @@
       <c r="Q82" s="113"/>
       <c r="R82" s="58"/>
     </row>
-    <row r="83" spans="1:18" ht="22.5">
+    <row r="83" spans="1:18" ht="22">
       <c r="A83" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A83" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E83),
@@ -27965,7 +27922,7 @@
       <c r="Q83" s="113"/>
       <c r="R83" s="58"/>
     </row>
-    <row r="84" spans="1:18" ht="22.5">
+    <row r="84" spans="1:18" ht="22">
       <c r="A84" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A84" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E84),
@@ -28002,7 +27959,7 @@
       <c r="Q84" s="113"/>
       <c r="R84" s="58"/>
     </row>
-    <row r="85" spans="1:18" ht="22.5">
+    <row r="85" spans="1:18" ht="22">
       <c r="A85" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A85" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E85),
@@ -28023,7 +27980,7 @@
         <v>190</v>
       </c>
       <c r="E85" s="112" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F85" s="112" t="s">
         <v>203</v>
@@ -28080,7 +28037,7 @@
       <c r="Q86" s="113"/>
       <c r="R86" s="58"/>
     </row>
-    <row r="87" spans="1:18" ht="33.75">
+    <row r="87" spans="1:18" ht="33">
       <c r="A87" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A87" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E87),
@@ -28097,7 +28054,7 @@
       <c r="C87" s="115"/>
       <c r="D87" s="115"/>
       <c r="E87" s="115" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F87" s="112" t="s">
         <v>206</v>
@@ -28117,7 +28074,7 @@
       <c r="Q87" s="113"/>
       <c r="R87" s="58"/>
     </row>
-    <row r="88" spans="1:18" ht="22.5">
+    <row r="88" spans="1:18" ht="22">
       <c r="A88" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A88" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E88),
@@ -28138,7 +28095,7 @@
         <v>190</v>
       </c>
       <c r="E88" s="116" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F88" s="110" t="s">
         <v>209</v>
@@ -28158,7 +28115,7 @@
       <c r="Q88" s="113"/>
       <c r="R88" s="58"/>
     </row>
-    <row r="89" spans="1:18" ht="33.75">
+    <row r="89" spans="1:18" ht="33">
       <c r="A89" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A89" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E89),
@@ -28230,7 +28187,7 @@
       <c r="Q90" s="113"/>
       <c r="R90" s="58"/>
     </row>
-    <row r="91" spans="1:18" ht="33.75">
+    <row r="91" spans="1:18" ht="33">
       <c r="A91" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A91" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E91),
@@ -28267,7 +28224,7 @@
       <c r="Q91" s="113"/>
       <c r="R91" s="58"/>
     </row>
-    <row r="92" spans="1:18" ht="33.75">
+    <row r="92" spans="1:18" ht="33">
       <c r="A92" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A92" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E92),
@@ -28302,7 +28259,7 @@
       <c r="Q92" s="113"/>
       <c r="R92" s="58"/>
     </row>
-    <row r="93" spans="1:18" ht="33.75">
+    <row r="93" spans="1:18" ht="33">
       <c r="A93" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A93" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E93),
@@ -28319,7 +28276,7 @@
       <c r="C93" s="115"/>
       <c r="D93" s="115"/>
       <c r="E93" s="115" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F93" s="112" t="s">
         <v>215</v>
@@ -28339,7 +28296,7 @@
       <c r="Q93" s="113"/>
       <c r="R93" s="58"/>
     </row>
-    <row r="94" spans="1:18" ht="22.5">
+    <row r="94" spans="1:18" ht="22">
       <c r="A94" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A94" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E94),
@@ -28380,7 +28337,7 @@
       <c r="Q94" s="113"/>
       <c r="R94" s="58"/>
     </row>
-    <row r="95" spans="1:18" ht="33.75">
+    <row r="95" spans="1:18" ht="33">
       <c r="A95" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A95" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E95),
@@ -28450,7 +28407,7 @@
       <c r="Q96" s="113"/>
       <c r="R96" s="58"/>
     </row>
-    <row r="97" spans="1:18" ht="33.75">
+    <row r="97" spans="1:18" ht="33">
       <c r="A97" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A97" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E97),
@@ -28485,7 +28442,7 @@
       <c r="Q97" s="113"/>
       <c r="R97" s="58"/>
     </row>
-    <row r="98" spans="1:18" ht="33.75">
+    <row r="98" spans="1:18" ht="33">
       <c r="A98" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A98" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E98),
@@ -28520,7 +28477,7 @@
       <c r="Q98" s="113"/>
       <c r="R98" s="58"/>
     </row>
-    <row r="99" spans="1:18" ht="22.5">
+    <row r="99" spans="1:18" ht="22">
       <c r="A99" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A99" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E99),
@@ -28557,7 +28514,7 @@
       <c r="Q99" s="113"/>
       <c r="R99" s="58"/>
     </row>
-    <row r="100" spans="1:18" ht="33.75">
+    <row r="100" spans="1:18" ht="33">
       <c r="A100" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A100" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E100),
@@ -28627,7 +28584,7 @@
       <c r="Q101" s="113"/>
       <c r="R101" s="58"/>
     </row>
-    <row r="102" spans="1:18" ht="33.75">
+    <row r="102" spans="1:18" ht="33">
       <c r="A102" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A102" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E102),
@@ -28662,7 +28619,7 @@
       <c r="Q102" s="113"/>
       <c r="R102" s="58"/>
     </row>
-    <row r="103" spans="1:18" ht="33.75">
+    <row r="103" spans="1:18" ht="33">
       <c r="A103" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A103" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E103),
@@ -28697,7 +28654,7 @@
       <c r="Q103" s="113"/>
       <c r="R103" s="58"/>
     </row>
-    <row r="104" spans="1:18" ht="33.75">
+    <row r="104" spans="1:18" ht="33">
       <c r="A104" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A104" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E104),
@@ -28714,7 +28671,7 @@
       <c r="C104" s="115"/>
       <c r="D104" s="111"/>
       <c r="E104" s="117" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F104" s="112" t="s">
         <v>230</v>
@@ -28734,7 +28691,7 @@
       <c r="Q104" s="113"/>
       <c r="R104" s="58"/>
     </row>
-    <row r="105" spans="1:18" ht="33.75">
+    <row r="105" spans="1:18" ht="33">
       <c r="A105" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A105" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E105),
@@ -28777,7 +28734,7 @@
       <c r="Q105" s="113"/>
       <c r="R105" s="58"/>
     </row>
-    <row r="106" spans="1:18" ht="22.5">
+    <row r="106" spans="1:18" ht="22">
       <c r="A106" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A106" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E106),
@@ -28818,7 +28775,7 @@
       <c r="Q106" s="113"/>
       <c r="R106" s="58"/>
     </row>
-    <row r="107" spans="1:18" ht="22.5">
+    <row r="107" spans="1:18" ht="22">
       <c r="A107" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A107" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E107),
@@ -28853,7 +28810,7 @@
       <c r="Q107" s="113"/>
       <c r="R107" s="58"/>
     </row>
-    <row r="108" spans="1:18" ht="22.5">
+    <row r="108" spans="1:18" ht="22">
       <c r="A108" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A108" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E108),
@@ -28868,7 +28825,7 @@
       </c>
       <c r="B108" s="111"/>
       <c r="C108" s="112" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D108" s="112" t="s">
         <v>93</v>
@@ -28894,7 +28851,7 @@
       <c r="Q108" s="113"/>
       <c r="R108" s="58"/>
     </row>
-    <row r="109" spans="1:18" ht="22.5">
+    <row r="109" spans="1:18" ht="22">
       <c r="A109" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A109" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E109),
@@ -28909,7 +28866,7 @@
       </c>
       <c r="B109" s="111"/>
       <c r="C109" s="111" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D109" s="111" t="s">
         <v>93</v>
@@ -28935,7 +28892,7 @@
       <c r="Q109" s="113"/>
       <c r="R109" s="58"/>
     </row>
-    <row r="110" spans="1:18" ht="22.5">
+    <row r="110" spans="1:18" ht="22">
       <c r="A110" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A110" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E110),
@@ -28970,7 +28927,7 @@
       <c r="Q110" s="113"/>
       <c r="R110" s="58"/>
     </row>
-    <row r="111" spans="1:18" ht="22.5">
+    <row r="111" spans="1:18" ht="22">
       <c r="A111" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A111" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E111),
@@ -28990,16 +28947,16 @@
         <v>243</v>
       </c>
       <c r="D111" s="110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E111" s="127" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F111" s="112" t="s">
         <v>244</v>
       </c>
       <c r="G111" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H111" s="61"/>
       <c r="I111" s="61"/>
@@ -29013,7 +28970,7 @@
       <c r="Q111" s="113"/>
       <c r="R111" s="58"/>
     </row>
-    <row r="112" spans="1:18" ht="22.5">
+    <row r="112" spans="1:18" ht="22">
       <c r="A112" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A112" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E112),
@@ -29027,7 +28984,7 @@
         <v>43-2-1</v>
       </c>
       <c r="B112" s="247" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C112" s="116"/>
       <c r="D112" s="111"/>
@@ -29036,7 +28993,7 @@
         <v>246</v>
       </c>
       <c r="G112" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H112" s="61"/>
       <c r="I112" s="61"/>
@@ -29050,7 +29007,7 @@
       <c r="Q112" s="113"/>
       <c r="R112" s="58"/>
     </row>
-    <row r="113" spans="1:18" ht="33.75">
+    <row r="113" spans="1:18" ht="33">
       <c r="A113" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A113" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E113),
@@ -29071,7 +29028,7 @@
         <v>247</v>
       </c>
       <c r="G113" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H113" s="61"/>
       <c r="I113" s="61"/>
@@ -29085,7 +29042,7 @@
       <c r="Q113" s="113"/>
       <c r="R113" s="58"/>
     </row>
-    <row r="114" spans="1:18" ht="22.5">
+    <row r="114" spans="1:18" ht="22">
       <c r="A114" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A114" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E114),
@@ -29106,7 +29063,7 @@
         <v>248</v>
       </c>
       <c r="G114" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H114" s="61"/>
       <c r="I114" s="61"/>
@@ -29120,7 +29077,7 @@
       <c r="Q114" s="113"/>
       <c r="R114" s="58"/>
     </row>
-    <row r="115" spans="1:18" ht="22.5">
+    <row r="115" spans="1:18" ht="22">
       <c r="A115" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A115" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E115),
@@ -29143,7 +29100,7 @@
         <v>249</v>
       </c>
       <c r="G115" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H115" s="61"/>
       <c r="I115" s="61"/>
@@ -29157,7 +29114,7 @@
       <c r="Q115" s="113"/>
       <c r="R115" s="58"/>
     </row>
-    <row r="116" spans="1:18" ht="22.5">
+    <row r="116" spans="1:18" ht="22">
       <c r="A116" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A116" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E116),
@@ -29178,7 +29135,7 @@
         <v>250</v>
       </c>
       <c r="G116" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H116" s="61"/>
       <c r="I116" s="61"/>
@@ -29192,7 +29149,7 @@
       <c r="Q116" s="113"/>
       <c r="R116" s="58"/>
     </row>
-    <row r="117" spans="1:18" ht="22.5">
+    <row r="117" spans="1:18" ht="22">
       <c r="A117" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A117" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E117),
@@ -29213,7 +29170,7 @@
         <v>251</v>
       </c>
       <c r="G117" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H117" s="61"/>
       <c r="I117" s="61"/>
@@ -29227,7 +29184,7 @@
       <c r="Q117" s="113"/>
       <c r="R117" s="58"/>
     </row>
-    <row r="118" spans="1:18" ht="22.5">
+    <row r="118" spans="1:18" ht="22">
       <c r="A118" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A118" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E118),
@@ -29248,7 +29205,7 @@
         <v>252</v>
       </c>
       <c r="G118" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H118" s="61"/>
       <c r="I118" s="61"/>
@@ -29262,7 +29219,7 @@
       <c r="Q118" s="113"/>
       <c r="R118" s="58"/>
     </row>
-    <row r="119" spans="1:18" ht="33.75">
+    <row r="119" spans="1:18" ht="33">
       <c r="A119" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A119" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E119),
@@ -29283,7 +29240,7 @@
         <v>253</v>
       </c>
       <c r="G119" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H119" s="61"/>
       <c r="I119" s="61"/>
@@ -29297,7 +29254,7 @@
       <c r="Q119" s="113"/>
       <c r="R119" s="58"/>
     </row>
-    <row r="120" spans="1:18" ht="33.75">
+    <row r="120" spans="1:18" ht="33">
       <c r="A120" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A120" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E120),
@@ -29320,7 +29277,7 @@
         <v>255</v>
       </c>
       <c r="G120" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H120" s="61"/>
       <c r="I120" s="61"/>
@@ -29334,7 +29291,7 @@
       <c r="Q120" s="113"/>
       <c r="R120" s="58"/>
     </row>
-    <row r="121" spans="1:18" ht="33.75">
+    <row r="121" spans="1:18" ht="33">
       <c r="A121" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A121" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E121),
@@ -29355,7 +29312,7 @@
         <v>256</v>
       </c>
       <c r="G121" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H121" s="61"/>
       <c r="I121" s="61"/>
@@ -29369,7 +29326,7 @@
       <c r="Q121" s="113"/>
       <c r="R121" s="58"/>
     </row>
-    <row r="122" spans="1:18" ht="45">
+    <row r="122" spans="1:18" ht="44">
       <c r="A122" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A122" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E122),
@@ -29390,7 +29347,7 @@
         <v>257</v>
       </c>
       <c r="G122" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H122" s="61"/>
       <c r="I122" s="61"/>
@@ -29404,7 +29361,7 @@
       <c r="Q122" s="113"/>
       <c r="R122" s="58"/>
     </row>
-    <row r="123" spans="1:18" ht="45">
+    <row r="123" spans="1:18" ht="44">
       <c r="A123" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A123" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E123),
@@ -29425,7 +29382,7 @@
         <v>258</v>
       </c>
       <c r="G123" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H123" s="61"/>
       <c r="I123" s="61"/>
@@ -29439,7 +29396,7 @@
       <c r="Q123" s="113"/>
       <c r="R123" s="58"/>
     </row>
-    <row r="124" spans="1:18" ht="45">
+    <row r="124" spans="1:18" ht="44">
       <c r="A124" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A124" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E124),
@@ -29460,7 +29417,7 @@
         <v>259</v>
       </c>
       <c r="G124" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H124" s="61"/>
       <c r="I124" s="61"/>
@@ -29474,7 +29431,7 @@
       <c r="Q124" s="113"/>
       <c r="R124" s="58"/>
     </row>
-    <row r="125" spans="1:18" ht="33.75">
+    <row r="125" spans="1:18" ht="33">
       <c r="A125" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A125" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E125),
@@ -29491,13 +29448,13 @@
       <c r="C125" s="116"/>
       <c r="D125" s="115"/>
       <c r="E125" s="115" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F125" s="112" t="s">
         <v>261</v>
       </c>
       <c r="G125" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H125" s="61"/>
       <c r="I125" s="61"/>
@@ -29511,7 +29468,7 @@
       <c r="Q125" s="113"/>
       <c r="R125" s="58"/>
     </row>
-    <row r="126" spans="1:18" ht="33.75">
+    <row r="126" spans="1:18" ht="33">
       <c r="A126" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A126" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E126),
@@ -29527,16 +29484,16 @@
       <c r="B126" s="111"/>
       <c r="C126" s="117"/>
       <c r="D126" s="115" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E126" s="115" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F126" s="112" t="s">
         <v>262</v>
       </c>
       <c r="G126" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H126" s="61"/>
       <c r="I126" s="61"/>
@@ -29550,7 +29507,7 @@
       <c r="Q126" s="113"/>
       <c r="R126" s="58"/>
     </row>
-    <row r="127" spans="1:18" ht="45">
+    <row r="127" spans="1:18" ht="44">
       <c r="A127" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A127" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E127),
@@ -29565,7 +29522,7 @@
       </c>
       <c r="B127" s="111"/>
       <c r="C127" s="111" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D127" s="111" t="s">
         <v>263</v>
@@ -29577,7 +29534,7 @@
         <v>265</v>
       </c>
       <c r="G127" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H127" s="61"/>
       <c r="I127" s="61"/>
@@ -29591,7 +29548,7 @@
       <c r="Q127" s="113"/>
       <c r="R127" s="58"/>
     </row>
-    <row r="128" spans="1:18" ht="22.5">
+    <row r="128" spans="1:18" ht="22">
       <c r="A128" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A128" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E128),
@@ -29608,13 +29565,13 @@
       <c r="C128" s="111"/>
       <c r="D128" s="111"/>
       <c r="E128" s="116" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="F128" s="112" t="s">
         <v>267</v>
       </c>
       <c r="G128" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H128" s="61"/>
       <c r="I128" s="61"/>
@@ -29628,7 +29585,7 @@
       <c r="Q128" s="113"/>
       <c r="R128" s="58"/>
     </row>
-    <row r="129" spans="1:18" ht="22.5">
+    <row r="129" spans="1:18" ht="22">
       <c r="A129" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A129" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E129),
@@ -29649,7 +29606,7 @@
         <v>268</v>
       </c>
       <c r="G129" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H129" s="61"/>
       <c r="I129" s="61"/>
@@ -29663,7 +29620,7 @@
       <c r="Q129" s="113"/>
       <c r="R129" s="58"/>
     </row>
-    <row r="130" spans="1:18" ht="45">
+    <row r="130" spans="1:18" ht="44">
       <c r="A130" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A130" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E130),
@@ -29684,7 +29641,7 @@
         <v>269</v>
       </c>
       <c r="G130" s="58" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H130" s="61"/>
       <c r="I130" s="61"/>
@@ -29698,7 +29655,7 @@
       <c r="Q130" s="113"/>
       <c r="R130" s="58"/>
     </row>
-    <row r="131" spans="1:18" ht="22.5">
+    <row r="131" spans="1:18" ht="22">
       <c r="A131" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A131" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E131),
@@ -29718,10 +29675,10 @@
         <v>243</v>
       </c>
       <c r="D131" s="110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E131" s="127" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F131" s="112" t="s">
         <v>271</v>
@@ -29741,7 +29698,7 @@
       <c r="Q131" s="113"/>
       <c r="R131" s="58"/>
     </row>
-    <row r="132" spans="1:18" ht="22.5">
+    <row r="132" spans="1:18" ht="22">
       <c r="A132" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A132" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E132),
@@ -29778,7 +29735,7 @@
       <c r="Q132" s="113"/>
       <c r="R132" s="58"/>
     </row>
-    <row r="133" spans="1:18" ht="22.5">
+    <row r="133" spans="1:18" ht="22">
       <c r="A133" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A133" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E133),
@@ -29813,7 +29770,7 @@
       <c r="Q133" s="113"/>
       <c r="R133" s="58"/>
     </row>
-    <row r="134" spans="1:18" ht="22.5">
+    <row r="134" spans="1:18" ht="22">
       <c r="A134" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A134" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E134),
@@ -29848,7 +29805,7 @@
       <c r="Q134" s="113"/>
       <c r="R134" s="58"/>
     </row>
-    <row r="135" spans="1:18" ht="22.5">
+    <row r="135" spans="1:18" ht="22">
       <c r="A135" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A135" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E135),
@@ -29885,7 +29842,7 @@
       <c r="Q135" s="113"/>
       <c r="R135" s="58"/>
     </row>
-    <row r="136" spans="1:18" ht="33.75">
+    <row r="136" spans="1:18" ht="33">
       <c r="A136" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A136" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E136),
@@ -29920,7 +29877,7 @@
       <c r="Q136" s="113"/>
       <c r="R136" s="58"/>
     </row>
-    <row r="137" spans="1:18" ht="33.75">
+    <row r="137" spans="1:18" ht="33">
       <c r="A137" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A137" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E137),
@@ -29936,10 +29893,10 @@
       <c r="B137" s="111"/>
       <c r="C137" s="117"/>
       <c r="D137" s="115" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E137" s="115" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F137" s="112" t="s">
         <v>280</v>
@@ -29959,7 +29916,7 @@
       <c r="Q137" s="113"/>
       <c r="R137" s="58"/>
     </row>
-    <row r="138" spans="1:18" ht="33.75">
+    <row r="138" spans="1:18" ht="33">
       <c r="A138" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A138" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E138),
@@ -30000,7 +29957,7 @@
       <c r="Q138" s="113"/>
       <c r="R138" s="58"/>
     </row>
-    <row r="139" spans="1:18" ht="33.75">
+    <row r="139" spans="1:18" ht="33">
       <c r="A139" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A139" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E139),
@@ -30037,7 +29994,7 @@
       <c r="Q139" s="113"/>
       <c r="R139" s="58"/>
     </row>
-    <row r="140" spans="1:18" ht="33.75">
+    <row r="140" spans="1:18" ht="33">
       <c r="A140" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A140" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E140),
@@ -30074,7 +30031,7 @@
       <c r="Q140" s="113"/>
       <c r="R140" s="58"/>
     </row>
-    <row r="141" spans="1:18" ht="33.75">
+    <row r="141" spans="1:18" ht="33">
       <c r="A141" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A141" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E141),
@@ -30111,7 +30068,7 @@
       <c r="Q141" s="113"/>
       <c r="R141" s="58"/>
     </row>
-    <row r="142" spans="1:18" ht="33.75">
+    <row r="142" spans="1:18" ht="33">
       <c r="A142" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A142" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E142),
@@ -30128,7 +30085,7 @@
       <c r="C142" s="116"/>
       <c r="D142" s="111"/>
       <c r="E142" s="112" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="F142" s="112" t="s">
         <v>290</v>
@@ -30148,7 +30105,7 @@
       <c r="Q142" s="113"/>
       <c r="R142" s="58"/>
     </row>
-    <row r="143" spans="1:18" ht="22.5">
+    <row r="143" spans="1:18" ht="22">
       <c r="A143" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A143" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E143),
@@ -30165,7 +30122,7 @@
       <c r="C143" s="116"/>
       <c r="D143" s="111"/>
       <c r="E143" s="124" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F143" s="112" t="s">
         <v>292</v>
@@ -30185,7 +30142,7 @@
       <c r="Q143" s="113"/>
       <c r="R143" s="58"/>
     </row>
-    <row r="144" spans="1:18" ht="22.5">
+    <row r="144" spans="1:18" ht="22">
       <c r="A144" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A144" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E144),
@@ -30220,7 +30177,7 @@
       <c r="Q144" s="113"/>
       <c r="R144" s="58"/>
     </row>
-    <row r="145" spans="1:18" ht="22.5">
+    <row r="145" spans="1:18" ht="22">
       <c r="A145" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A145" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E145),
@@ -30255,7 +30212,7 @@
       <c r="Q145" s="113"/>
       <c r="R145" s="58"/>
     </row>
-    <row r="146" spans="1:18" ht="22.5">
+    <row r="146" spans="1:18" ht="22">
       <c r="A146" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A146" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E146),
@@ -30290,7 +30247,7 @@
       <c r="Q146" s="113"/>
       <c r="R146" s="58"/>
     </row>
-    <row r="147" spans="1:18" ht="22.5">
+    <row r="147" spans="1:18" ht="22">
       <c r="A147" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A147" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E147),
@@ -30325,7 +30282,7 @@
       <c r="Q147" s="113"/>
       <c r="R147" s="58"/>
     </row>
-    <row r="148" spans="1:18" ht="22.5">
+    <row r="148" spans="1:18" ht="22">
       <c r="A148" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A148" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E148),
@@ -30360,7 +30317,7 @@
       <c r="Q148" s="113"/>
       <c r="R148" s="58"/>
     </row>
-    <row r="149" spans="1:18" ht="22.5">
+    <row r="149" spans="1:18" ht="22">
       <c r="A149" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A149" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E149),
@@ -30379,7 +30336,7 @@
         <v>298</v>
       </c>
       <c r="E149" s="110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F149" s="112" t="s">
         <v>299</v>
@@ -30399,7 +30356,7 @@
       <c r="Q149" s="113"/>
       <c r="R149" s="58"/>
     </row>
-    <row r="150" spans="1:18" ht="22.5">
+    <row r="150" spans="1:18" ht="22">
       <c r="A150" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A150" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E150),
@@ -30434,7 +30391,7 @@
       <c r="Q150" s="113"/>
       <c r="R150" s="58"/>
     </row>
-    <row r="151" spans="1:18" ht="33.75">
+    <row r="151" spans="1:18" ht="33">
       <c r="A151" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A151" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E151),
@@ -30471,7 +30428,7 @@
       <c r="Q151" s="113"/>
       <c r="R151" s="58"/>
     </row>
-    <row r="152" spans="1:18" ht="33.75">
+    <row r="152" spans="1:18" ht="33">
       <c r="A152" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A152" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E152),
@@ -30506,7 +30463,7 @@
       <c r="Q152" s="113"/>
       <c r="R152" s="58"/>
     </row>
-    <row r="153" spans="1:18" ht="33.75">
+    <row r="153" spans="1:18" ht="33">
       <c r="A153" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A153" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E153),
@@ -30524,7 +30481,7 @@
       <c r="D153" s="111"/>
       <c r="E153" s="124"/>
       <c r="F153" s="112" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G153" s="56" t="s">
         <v>272</v>
@@ -30541,7 +30498,7 @@
       <c r="Q153" s="113"/>
       <c r="R153" s="58"/>
     </row>
-    <row r="154" spans="1:18" ht="33.75">
+    <row r="154" spans="1:18" ht="33">
       <c r="A154" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A154" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E154),
@@ -30559,7 +30516,7 @@
       <c r="D154" s="111"/>
       <c r="E154" s="124"/>
       <c r="F154" s="112" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G154" s="56" t="s">
         <v>272</v>
@@ -30576,7 +30533,7 @@
       <c r="Q154" s="113"/>
       <c r="R154" s="58"/>
     </row>
-    <row r="155" spans="1:18" ht="33.75">
+    <row r="155" spans="1:18" ht="33">
       <c r="A155" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A155" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E155),
@@ -30611,7 +30568,7 @@
       <c r="Q155" s="113"/>
       <c r="R155" s="58"/>
     </row>
-    <row r="156" spans="1:18" ht="22.5">
+    <row r="156" spans="1:18" ht="22">
       <c r="A156" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A156" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E156),
@@ -30646,7 +30603,7 @@
       <c r="Q156" s="113"/>
       <c r="R156" s="58"/>
     </row>
-    <row r="157" spans="1:18" ht="22.5">
+    <row r="157" spans="1:18" ht="22">
       <c r="A157" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A157" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E157),
@@ -30681,7 +30638,7 @@
       <c r="Q157" s="113"/>
       <c r="R157" s="58"/>
     </row>
-    <row r="158" spans="1:18" ht="33.75">
+    <row r="158" spans="1:18" ht="33">
       <c r="A158" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A158" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E158),
@@ -30716,7 +30673,7 @@
       <c r="Q158" s="113"/>
       <c r="R158" s="58"/>
     </row>
-    <row r="159" spans="1:18" ht="33.75">
+    <row r="159" spans="1:18" ht="33">
       <c r="A159" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A159" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E159),
@@ -30751,7 +30708,7 @@
       <c r="Q159" s="113"/>
       <c r="R159" s="58"/>
     </row>
-    <row r="160" spans="1:18" ht="33.75">
+    <row r="160" spans="1:18" ht="33">
       <c r="A160" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A160" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E160),
@@ -30786,7 +30743,7 @@
       <c r="Q160" s="113"/>
       <c r="R160" s="58"/>
     </row>
-    <row r="161" spans="1:18" ht="33.75">
+    <row r="161" spans="1:18" ht="33">
       <c r="A161" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A161" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E161),
@@ -30893,7 +30850,7 @@
       <c r="Q163" s="113"/>
       <c r="R163" s="58"/>
     </row>
-    <row r="164" spans="1:18" ht="33.75">
+    <row r="164" spans="1:18" ht="33">
       <c r="A164" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A164" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E164),
@@ -30928,7 +30885,7 @@
       <c r="Q164" s="113"/>
       <c r="R164" s="58"/>
     </row>
-    <row r="165" spans="1:18" ht="22.5">
+    <row r="165" spans="1:18" ht="22">
       <c r="A165" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A165" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E165),
@@ -30963,7 +30920,7 @@
       <c r="Q165" s="113"/>
       <c r="R165" s="58"/>
     </row>
-    <row r="166" spans="1:18" ht="22.5">
+    <row r="166" spans="1:18" ht="22">
       <c r="A166" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A166" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E166),
@@ -30998,7 +30955,7 @@
       <c r="Q166" s="113"/>
       <c r="R166" s="58"/>
     </row>
-    <row r="167" spans="1:18" ht="33.75">
+    <row r="167" spans="1:18" ht="33">
       <c r="A167" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A167" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E167),
@@ -31033,7 +30990,7 @@
       <c r="Q167" s="113"/>
       <c r="R167" s="58"/>
     </row>
-    <row r="168" spans="1:18" ht="22.5">
+    <row r="168" spans="1:18" ht="22">
       <c r="A168" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A168" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E168),
@@ -31068,7 +31025,7 @@
       <c r="Q168" s="113"/>
       <c r="R168" s="58"/>
     </row>
-    <row r="169" spans="1:18" ht="22.5">
+    <row r="169" spans="1:18" ht="22">
       <c r="A169" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A169" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E169),
@@ -31105,7 +31062,7 @@
       <c r="Q169" s="113"/>
       <c r="R169" s="58"/>
     </row>
-    <row r="170" spans="1:18" ht="33.75">
+    <row r="170" spans="1:18" ht="33">
       <c r="A170" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A170" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E170),
@@ -31140,7 +31097,7 @@
       <c r="Q170" s="113"/>
       <c r="R170" s="58"/>
     </row>
-    <row r="171" spans="1:18" ht="33.75">
+    <row r="171" spans="1:18" ht="33">
       <c r="A171" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A171" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E171),
@@ -31175,7 +31132,7 @@
       <c r="Q171" s="113"/>
       <c r="R171" s="58"/>
     </row>
-    <row r="172" spans="1:18" ht="45">
+    <row r="172" spans="1:18" ht="44">
       <c r="A172" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A172" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E172),
@@ -31210,7 +31167,7 @@
       <c r="Q172" s="113"/>
       <c r="R172" s="58"/>
     </row>
-    <row r="173" spans="1:18" ht="45">
+    <row r="173" spans="1:18" ht="44">
       <c r="A173" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A173" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E173),
@@ -31245,7 +31202,7 @@
       <c r="Q173" s="113"/>
       <c r="R173" s="58"/>
     </row>
-    <row r="174" spans="1:18" ht="33.75">
+    <row r="174" spans="1:18" ht="33">
       <c r="A174" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A174" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E174),
@@ -31280,7 +31237,7 @@
       <c r="Q174" s="113"/>
       <c r="R174" s="58"/>
     </row>
-    <row r="175" spans="1:18" ht="45">
+    <row r="175" spans="1:18" ht="44">
       <c r="A175" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A175" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E175),
@@ -31315,7 +31272,7 @@
       <c r="Q175" s="113"/>
       <c r="R175" s="58"/>
     </row>
-    <row r="176" spans="1:18" ht="45">
+    <row r="176" spans="1:18" ht="44">
       <c r="A176" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A176" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E176),
@@ -31350,7 +31307,7 @@
       <c r="Q176" s="113"/>
       <c r="R176" s="58"/>
     </row>
-    <row r="177" spans="1:18" ht="22.5">
+    <row r="177" spans="1:18" ht="22">
       <c r="A177" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A177" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E177),
@@ -31385,7 +31342,7 @@
       <c r="Q177" s="113"/>
       <c r="R177" s="58"/>
     </row>
-    <row r="178" spans="1:18" ht="33.75">
+    <row r="178" spans="1:18" ht="33">
       <c r="A178" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A178" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E178),
@@ -31422,7 +31379,7 @@
       <c r="Q178" s="113"/>
       <c r="R178" s="58"/>
     </row>
-    <row r="179" spans="1:18" ht="22.5">
+    <row r="179" spans="1:18" ht="22">
       <c r="A179" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A179" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E179),
@@ -31459,7 +31416,7 @@
       <c r="Q179" s="113"/>
       <c r="R179" s="58"/>
     </row>
-    <row r="180" spans="1:18" ht="22.5">
+    <row r="180" spans="1:18" ht="22">
       <c r="A180" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A180" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E180),
@@ -31502,7 +31459,7 @@
       <c r="Q180" s="113"/>
       <c r="R180" s="58"/>
     </row>
-    <row r="181" spans="1:18" ht="22.5">
+    <row r="181" spans="1:18" ht="22">
       <c r="A181" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A181" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E181),
@@ -31557,7 +31514,7 @@
       <c r="B182" s="115"/>
       <c r="C182" s="117"/>
       <c r="D182" s="117" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E182" s="117" t="s">
         <v>93</v>
@@ -31580,7 +31537,7 @@
       <c r="Q182" s="113"/>
       <c r="R182" s="58"/>
     </row>
-    <row r="183" spans="1:18" ht="22.5">
+    <row r="183" spans="1:18" ht="22">
       <c r="A183" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A183" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E183),
@@ -31600,7 +31557,7 @@
         <v>243</v>
       </c>
       <c r="D183" s="110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E183" s="112" t="s">
         <v>340</v>
@@ -31623,7 +31580,7 @@
       <c r="Q183" s="113"/>
       <c r="R183" s="58"/>
     </row>
-    <row r="184" spans="1:18" ht="22.5">
+    <row r="184" spans="1:18" ht="22">
       <c r="A184" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A184" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E184),
@@ -31660,7 +31617,7 @@
       <c r="Q184" s="113"/>
       <c r="R184" s="58"/>
     </row>
-    <row r="185" spans="1:18" ht="22.5">
+    <row r="185" spans="1:18" ht="22">
       <c r="A185" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A185" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E185),
@@ -31695,7 +31652,7 @@
       <c r="Q185" s="113"/>
       <c r="R185" s="58"/>
     </row>
-    <row r="186" spans="1:18" ht="33.75">
+    <row r="186" spans="1:18" ht="33">
       <c r="A186" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A186" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E186),
@@ -31732,7 +31689,7 @@
       <c r="Q186" s="113"/>
       <c r="R186" s="58"/>
     </row>
-    <row r="187" spans="1:18" ht="33.75">
+    <row r="187" spans="1:18" ht="33">
       <c r="A187" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A187" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E187),
@@ -31767,7 +31724,7 @@
       <c r="Q187" s="113"/>
       <c r="R187" s="58"/>
     </row>
-    <row r="188" spans="1:18" ht="33.75">
+    <row r="188" spans="1:18" ht="33">
       <c r="A188" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A188" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E188),
@@ -31783,10 +31740,10 @@
       <c r="B188" s="111"/>
       <c r="C188" s="115"/>
       <c r="D188" s="115" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E188" s="115" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F188" s="112" t="s">
         <v>348</v>
@@ -31806,7 +31763,7 @@
       <c r="Q188" s="113"/>
       <c r="R188" s="58"/>
     </row>
-    <row r="189" spans="1:18" ht="22.5">
+    <row r="189" spans="1:18" ht="22">
       <c r="A189" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A189" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E189),
@@ -31824,7 +31781,7 @@
         <v>349</v>
       </c>
       <c r="D189" s="111" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E189" s="116" t="s">
         <v>351</v>
@@ -31847,7 +31804,7 @@
       <c r="Q189" s="113"/>
       <c r="R189" s="58"/>
     </row>
-    <row r="190" spans="1:18" ht="22.5">
+    <row r="190" spans="1:18" ht="22">
       <c r="A190" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A190" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E190),
@@ -31882,7 +31839,7 @@
       <c r="Q190" s="113"/>
       <c r="R190" s="58"/>
     </row>
-    <row r="191" spans="1:18" ht="22.5">
+    <row r="191" spans="1:18" ht="22">
       <c r="A191" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A191" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E191),
@@ -31917,7 +31874,7 @@
       <c r="Q191" s="113"/>
       <c r="R191" s="58"/>
     </row>
-    <row r="192" spans="1:18" ht="22.5">
+    <row r="192" spans="1:18" ht="22">
       <c r="A192" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A192" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E192),
@@ -31952,7 +31909,7 @@
       <c r="Q192" s="113"/>
       <c r="R192" s="58"/>
     </row>
-    <row r="193" spans="1:18" ht="22.5">
+    <row r="193" spans="1:18" ht="22">
       <c r="A193" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A193" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E193),
@@ -31987,7 +31944,7 @@
       <c r="Q193" s="113"/>
       <c r="R193" s="58"/>
     </row>
-    <row r="194" spans="1:18" ht="22.5">
+    <row r="194" spans="1:18" ht="22">
       <c r="A194" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A194" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E194),
@@ -32022,7 +31979,7 @@
       <c r="Q194" s="113"/>
       <c r="R194" s="58"/>
     </row>
-    <row r="195" spans="1:18" ht="22.5">
+    <row r="195" spans="1:18" ht="22">
       <c r="A195" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A195" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E195),
@@ -32057,7 +32014,7 @@
       <c r="Q195" s="113"/>
       <c r="R195" s="58"/>
     </row>
-    <row r="196" spans="1:18" ht="22.5">
+    <row r="196" spans="1:18" ht="22">
       <c r="A196" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A196" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E196),
@@ -32077,7 +32034,7 @@
         <v>359</v>
       </c>
       <c r="F196" s="112" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G196" s="56" t="s">
         <v>342</v>
@@ -32094,7 +32051,7 @@
       <c r="Q196" s="113"/>
       <c r="R196" s="58"/>
     </row>
-    <row r="197" spans="1:18" ht="22.5">
+    <row r="197" spans="1:18" ht="22">
       <c r="A197" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A197" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E197),
@@ -32133,7 +32090,7 @@
       <c r="Q197" s="113"/>
       <c r="R197" s="58"/>
     </row>
-    <row r="198" spans="1:18" ht="22.5">
+    <row r="198" spans="1:18" ht="22">
       <c r="A198" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A198" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E198),
@@ -32203,7 +32160,7 @@
       <c r="Q199" s="113"/>
       <c r="R199" s="58"/>
     </row>
-    <row r="200" spans="1:18" ht="22.5">
+    <row r="200" spans="1:18" ht="22">
       <c r="A200" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A200" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E200),
@@ -32238,7 +32195,7 @@
       <c r="Q200" s="113"/>
       <c r="R200" s="58"/>
     </row>
-    <row r="201" spans="1:18" ht="33.75">
+    <row r="201" spans="1:18" ht="33">
       <c r="A201" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A201" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E201),
@@ -32273,7 +32230,7 @@
       <c r="Q201" s="113"/>
       <c r="R201" s="58"/>
     </row>
-    <row r="202" spans="1:18" ht="45">
+    <row r="202" spans="1:18" ht="44">
       <c r="A202" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A202" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E202),
@@ -32308,7 +32265,7 @@
       <c r="Q202" s="113"/>
       <c r="R202" s="58"/>
     </row>
-    <row r="203" spans="1:18" ht="45">
+    <row r="203" spans="1:18" ht="44">
       <c r="A203" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A203" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E203),
@@ -32326,7 +32283,7 @@
       <c r="D203" s="111"/>
       <c r="E203" s="116"/>
       <c r="F203" s="112" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G203" s="56" t="s">
         <v>342</v>
@@ -32343,7 +32300,7 @@
       <c r="Q203" s="113"/>
       <c r="R203" s="58"/>
     </row>
-    <row r="204" spans="1:18" ht="45">
+    <row r="204" spans="1:18" ht="44">
       <c r="A204" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A204" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E204),
@@ -32378,7 +32335,7 @@
       <c r="Q204" s="113"/>
       <c r="R204" s="58"/>
     </row>
-    <row r="205" spans="1:18" ht="33.75">
+    <row r="205" spans="1:18" ht="33">
       <c r="A205" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A205" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E205),
@@ -32413,7 +32370,7 @@
       <c r="Q205" s="113"/>
       <c r="R205" s="58"/>
     </row>
-    <row r="206" spans="1:18" ht="22.5">
+    <row r="206" spans="1:18" ht="22">
       <c r="A206" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A206" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E206),
@@ -32448,7 +32405,7 @@
       <c r="Q206" s="113"/>
       <c r="R206" s="58"/>
     </row>
-    <row r="207" spans="1:18" ht="22.5">
+    <row r="207" spans="1:18" ht="22">
       <c r="A207" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A207" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E207),
@@ -32483,7 +32440,7 @@
       <c r="Q207" s="113"/>
       <c r="R207" s="58"/>
     </row>
-    <row r="208" spans="1:18" ht="33.75">
+    <row r="208" spans="1:18" ht="33">
       <c r="A208" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A208" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E208),
@@ -32518,7 +32475,7 @@
       <c r="Q208" s="113"/>
       <c r="R208" s="58"/>
     </row>
-    <row r="209" spans="1:18" ht="22.5">
+    <row r="209" spans="1:18" ht="22">
       <c r="A209" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A209" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E209),
@@ -32553,7 +32510,7 @@
       <c r="Q209" s="113"/>
       <c r="R209" s="58"/>
     </row>
-    <row r="210" spans="1:18" ht="22.5">
+    <row r="210" spans="1:18" ht="22">
       <c r="A210" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A210" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E210),
@@ -32569,7 +32526,7 @@
       <c r="B210" s="111"/>
       <c r="C210" s="114"/>
       <c r="D210" s="110" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E210" s="118" t="s">
         <v>168</v>
@@ -32592,7 +32549,7 @@
       <c r="Q210" s="113"/>
       <c r="R210" s="58"/>
     </row>
-    <row r="211" spans="1:18" ht="22.5">
+    <row r="211" spans="1:18" ht="22">
       <c r="A211" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A211" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E211),
@@ -32627,7 +32584,7 @@
       <c r="Q211" s="113"/>
       <c r="R211" s="58"/>
     </row>
-    <row r="212" spans="1:18" ht="22.5">
+    <row r="212" spans="1:18" ht="22">
       <c r="A212" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A212" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E212),
@@ -32697,7 +32654,7 @@
       <c r="Q213" s="113"/>
       <c r="R213" s="58"/>
     </row>
-    <row r="214" spans="1:18" ht="22.5">
+    <row r="214" spans="1:18" ht="22">
       <c r="A214" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A214" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E214),
@@ -32732,7 +32689,7 @@
       <c r="Q214" s="113"/>
       <c r="R214" s="58"/>
     </row>
-    <row r="215" spans="1:18" ht="45">
+    <row r="215" spans="1:18" ht="44">
       <c r="A215" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A215" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E215),
@@ -32767,7 +32724,7 @@
       <c r="Q215" s="113"/>
       <c r="R215" s="58"/>
     </row>
-    <row r="216" spans="1:18" ht="33.75">
+    <row r="216" spans="1:18" ht="33">
       <c r="A216" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A216" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E216),
@@ -32802,7 +32759,7 @@
       <c r="Q216" s="113"/>
       <c r="R216" s="58"/>
     </row>
-    <row r="217" spans="1:18" ht="45">
+    <row r="217" spans="1:18" ht="44">
       <c r="A217" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A217" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E217),
@@ -32820,7 +32777,7 @@
       <c r="D217" s="111"/>
       <c r="E217" s="116"/>
       <c r="F217" s="112" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G217" s="56" t="s">
         <v>342</v>
@@ -32837,7 +32794,7 @@
       <c r="Q217" s="113"/>
       <c r="R217" s="58"/>
     </row>
-    <row r="218" spans="1:18" ht="45">
+    <row r="218" spans="1:18" ht="44">
       <c r="A218" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A218" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E218),
@@ -32855,7 +32812,7 @@
       <c r="D218" s="111"/>
       <c r="E218" s="116"/>
       <c r="F218" s="112" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G218" s="56" t="s">
         <v>342</v>
@@ -32872,7 +32829,7 @@
       <c r="Q218" s="113"/>
       <c r="R218" s="58"/>
     </row>
-    <row r="219" spans="1:18" ht="45">
+    <row r="219" spans="1:18" ht="44">
       <c r="A219" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A219" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E219),
@@ -32907,7 +32864,7 @@
       <c r="Q219" s="113"/>
       <c r="R219" s="58"/>
     </row>
-    <row r="220" spans="1:18" ht="33.75">
+    <row r="220" spans="1:18" ht="33">
       <c r="A220" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A220" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E220),
@@ -32942,7 +32899,7 @@
       <c r="Q220" s="113"/>
       <c r="R220" s="58"/>
     </row>
-    <row r="221" spans="1:18" ht="22.5">
+    <row r="221" spans="1:18" ht="22">
       <c r="A221" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A221" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E221),
@@ -32977,7 +32934,7 @@
       <c r="Q221" s="113"/>
       <c r="R221" s="58"/>
     </row>
-    <row r="222" spans="1:18" ht="22.5">
+    <row r="222" spans="1:18" ht="22">
       <c r="A222" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A222" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E222),
@@ -33012,7 +32969,7 @@
       <c r="Q222" s="113"/>
       <c r="R222" s="58"/>
     </row>
-    <row r="223" spans="1:18" ht="33.75">
+    <row r="223" spans="1:18" ht="33">
       <c r="A223" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A223" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E223),
@@ -33047,7 +33004,7 @@
       <c r="Q223" s="113"/>
       <c r="R223" s="58"/>
     </row>
-    <row r="224" spans="1:18" ht="22.5">
+    <row r="224" spans="1:18" ht="22">
       <c r="A224" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A224" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E224),
@@ -33082,7 +33039,7 @@
       <c r="Q224" s="113"/>
       <c r="R224" s="58"/>
     </row>
-    <row r="225" spans="1:18" ht="45">
+    <row r="225" spans="1:18" ht="44">
       <c r="A225" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A225" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E225),
@@ -33119,7 +33076,7 @@
       <c r="Q225" s="113"/>
       <c r="R225" s="58"/>
     </row>
-    <row r="226" spans="1:18" ht="45">
+    <row r="226" spans="1:18" ht="44">
       <c r="A226" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A226" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E226),
@@ -33154,7 +33111,7 @@
       <c r="Q226" s="113"/>
       <c r="R226" s="58"/>
     </row>
-    <row r="227" spans="1:18" ht="45">
+    <row r="227" spans="1:18" ht="44">
       <c r="A227" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A227" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E227),
@@ -33189,7 +33146,7 @@
       <c r="Q227" s="113"/>
       <c r="R227" s="58"/>
     </row>
-    <row r="228" spans="1:18" ht="45">
+    <row r="228" spans="1:18" ht="44">
       <c r="A228" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A228" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E228),
@@ -33209,7 +33166,7 @@
         <v>198</v>
       </c>
       <c r="F228" s="112" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G228" s="56" t="s">
         <v>342</v>
@@ -33226,7 +33183,7 @@
       <c r="Q228" s="113"/>
       <c r="R228" s="58"/>
     </row>
-    <row r="229" spans="1:18" ht="22.5">
+    <row r="229" spans="1:18" ht="22">
       <c r="A229" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A229" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E229),
@@ -33263,7 +33220,7 @@
       <c r="Q229" s="113"/>
       <c r="R229" s="58"/>
     </row>
-    <row r="230" spans="1:18" ht="22.5">
+    <row r="230" spans="1:18" ht="22">
       <c r="A230" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A230" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E230),
@@ -33283,16 +33240,16 @@
         <v>243</v>
       </c>
       <c r="D230" s="161" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E230" s="112" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F230" s="112" t="s">
         <v>396</v>
       </c>
       <c r="G230" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H230" s="61"/>
       <c r="I230" s="61"/>
@@ -33306,7 +33263,7 @@
       <c r="Q230" s="113"/>
       <c r="R230" s="58"/>
     </row>
-    <row r="231" spans="1:18" ht="56.25">
+    <row r="231" spans="1:18" ht="55">
       <c r="A231" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A231" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E231),
@@ -33330,19 +33287,19 @@
       </c>
       <c r="G231" s="148"/>
       <c r="H231" s="38" t="s">
+        <v>560</v>
+      </c>
+      <c r="I231" s="39" t="s">
         <v>561</v>
       </c>
-      <c r="I231" s="39" t="s">
-        <v>562</v>
-      </c>
       <c r="J231" s="42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K231" s="42" t="s">
         <v>30</v>
       </c>
       <c r="L231" s="149" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M231" s="149">
         <v>3</v>
@@ -33353,7 +33310,7 @@
       <c r="Q231" s="163"/>
       <c r="R231" s="148"/>
     </row>
-    <row r="232" spans="1:18" ht="22.5">
+    <row r="232" spans="1:18" ht="22">
       <c r="A232" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A232" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E232),
@@ -33374,7 +33331,7 @@
         <v>399</v>
       </c>
       <c r="G232" s="58" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H232" s="61"/>
       <c r="I232" s="61"/>
@@ -33388,7 +33345,7 @@
       <c r="Q232" s="113"/>
       <c r="R232" s="58"/>
     </row>
-    <row r="233" spans="1:18" ht="22.5">
+    <row r="233" spans="1:18" ht="22">
       <c r="A233" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A233" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E233),
@@ -33423,7 +33380,7 @@
       <c r="Q233" s="113"/>
       <c r="R233" s="58"/>
     </row>
-    <row r="234" spans="1:18" ht="22.5">
+    <row r="234" spans="1:18" ht="22">
       <c r="A234" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A234" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E234),
@@ -33458,7 +33415,7 @@
       <c r="Q234" s="113"/>
       <c r="R234" s="58"/>
     </row>
-    <row r="235" spans="1:18" ht="33.75">
+    <row r="235" spans="1:18" ht="33">
       <c r="A235" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A235" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E235),
@@ -33493,7 +33450,7 @@
       <c r="Q235" s="113"/>
       <c r="R235" s="58"/>
     </row>
-    <row r="236" spans="1:18" ht="33.75">
+    <row r="236" spans="1:18" ht="33">
       <c r="A236" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A236" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E236),
@@ -33530,7 +33487,7 @@
       <c r="Q236" s="113"/>
       <c r="R236" s="58"/>
     </row>
-    <row r="237" spans="1:18" ht="33.75">
+    <row r="237" spans="1:18" ht="33">
       <c r="A237" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A237" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E237),
@@ -33565,7 +33522,7 @@
       <c r="Q237" s="113"/>
       <c r="R237" s="58"/>
     </row>
-    <row r="238" spans="1:18" ht="45">
+    <row r="238" spans="1:18" ht="44">
       <c r="A238" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A238" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E238),
@@ -33600,7 +33557,7 @@
       <c r="Q238" s="113"/>
       <c r="R238" s="58"/>
     </row>
-    <row r="239" spans="1:18" ht="45">
+    <row r="239" spans="1:18" ht="44">
       <c r="A239" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A239" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E239),
@@ -33635,7 +33592,7 @@
       <c r="Q239" s="113"/>
       <c r="R239" s="58"/>
     </row>
-    <row r="240" spans="1:18" ht="33.75">
+    <row r="240" spans="1:18" ht="33">
       <c r="A240" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A240" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E240),
@@ -33657,19 +33614,19 @@
       </c>
       <c r="G240" s="148"/>
       <c r="H240" s="38" t="s">
+        <v>560</v>
+      </c>
+      <c r="I240" s="39" t="s">
         <v>561</v>
       </c>
-      <c r="I240" s="39" t="s">
-        <v>562</v>
-      </c>
       <c r="J240" s="42" t="s">
+        <v>568</v>
+      </c>
+      <c r="K240" s="42" t="s">
         <v>569</v>
       </c>
-      <c r="K240" s="42" t="s">
-        <v>570</v>
-      </c>
       <c r="L240" s="87" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M240" s="87">
         <v>1</v>
@@ -33680,7 +33637,7 @@
       <c r="Q240" s="163"/>
       <c r="R240" s="148"/>
     </row>
-    <row r="241" spans="1:18" ht="45">
+    <row r="241" spans="1:18" ht="44">
       <c r="A241" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A241" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E241),
@@ -33697,23 +33654,23 @@
       <c r="C241" s="164"/>
       <c r="D241" s="164"/>
       <c r="E241" s="164" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F241" s="161" t="s">
         <v>408</v>
       </c>
       <c r="G241" s="171"/>
       <c r="H241" s="38" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I241" s="39" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J241" s="37" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K241" s="40" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="L241" s="149" t="s">
         <v>34</v>
@@ -33727,7 +33684,7 @@
       <c r="Q241" s="163"/>
       <c r="R241" s="148"/>
     </row>
-    <row r="242" spans="1:18" ht="45">
+    <row r="242" spans="1:18" ht="44">
       <c r="A242" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A242" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E242),
@@ -33747,13 +33704,13 @@
       <c r="F242" s="166"/>
       <c r="G242" s="174"/>
       <c r="H242" s="38" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="I242" s="39" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J242" s="37" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="K242" s="40" t="s">
         <v>33</v>
@@ -33770,7 +33727,7 @@
       <c r="Q242" s="163"/>
       <c r="R242" s="148"/>
     </row>
-    <row r="243" spans="1:18" ht="33.75">
+    <row r="243" spans="1:18" ht="33">
       <c r="A243" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A243" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E243),
@@ -33785,7 +33742,7 @@
       </c>
       <c r="B243" s="166"/>
       <c r="C243" s="166" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="D243" s="166" t="s">
         <v>263</v>
@@ -33798,19 +33755,19 @@
       </c>
       <c r="G243" s="148"/>
       <c r="H243" s="38" t="s">
+        <v>560</v>
+      </c>
+      <c r="I243" s="39" t="s">
         <v>561</v>
       </c>
-      <c r="I243" s="39" t="s">
-        <v>562</v>
-      </c>
       <c r="J243" s="42" t="s">
+        <v>568</v>
+      </c>
+      <c r="K243" s="42" t="s">
         <v>569</v>
       </c>
-      <c r="K243" s="42" t="s">
-        <v>570</v>
-      </c>
       <c r="L243" s="87" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M243" s="87">
         <v>1</v>
@@ -33821,7 +33778,7 @@
       <c r="Q243" s="163"/>
       <c r="R243" s="148"/>
     </row>
-    <row r="244" spans="1:18" ht="22.5">
+    <row r="244" spans="1:18" ht="22">
       <c r="A244" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A244" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E244),
@@ -33841,16 +33798,16 @@
         <v>411</v>
       </c>
       <c r="D244" s="110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E244" s="118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F244" s="112" t="s">
         <v>412</v>
       </c>
       <c r="G244" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H244" s="61"/>
       <c r="I244" s="61"/>
@@ -33864,7 +33821,7 @@
       <c r="Q244" s="113"/>
       <c r="R244" s="58"/>
     </row>
-    <row r="245" spans="1:18" ht="22.5">
+    <row r="245" spans="1:18" ht="22">
       <c r="A245" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A245" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E245),
@@ -33885,7 +33842,7 @@
         <v>413</v>
       </c>
       <c r="G245" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H245" s="61"/>
       <c r="I245" s="61"/>
@@ -33899,7 +33856,7 @@
       <c r="Q245" s="113"/>
       <c r="R245" s="58"/>
     </row>
-    <row r="246" spans="1:18" ht="33.75">
+    <row r="246" spans="1:18" ht="33">
       <c r="A246" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A246" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E246),
@@ -33915,16 +33872,16 @@
       <c r="B246" s="164"/>
       <c r="C246" s="132"/>
       <c r="D246" s="132" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E246" s="116" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F246" s="112" t="s">
         <v>414</v>
       </c>
       <c r="G246" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H246" s="61"/>
       <c r="I246" s="61"/>
@@ -33938,7 +33895,7 @@
       <c r="Q246" s="113"/>
       <c r="R246" s="58"/>
     </row>
-    <row r="247" spans="1:18" ht="33.75">
+    <row r="247" spans="1:18" ht="33">
       <c r="A247" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A247" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E247),
@@ -33959,7 +33916,7 @@
         <v>415</v>
       </c>
       <c r="G247" s="58" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H247" s="61"/>
       <c r="I247" s="61"/>
@@ -33973,7 +33930,7 @@
       <c r="Q247" s="113"/>
       <c r="R247" s="58"/>
     </row>
-    <row r="248" spans="1:18" ht="33.75">
+    <row r="248" spans="1:18" ht="33">
       <c r="A248" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A248" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E248),
@@ -34014,7 +33971,7 @@
       <c r="Q248" s="113"/>
       <c r="R248" s="58"/>
     </row>
-    <row r="249" spans="1:18" ht="33.75">
+    <row r="249" spans="1:18" ht="33">
       <c r="A249" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A249" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E249),
@@ -34051,7 +34008,7 @@
       <c r="Q249" s="113"/>
       <c r="R249" s="58"/>
     </row>
-    <row r="250" spans="1:18" ht="33.75">
+    <row r="250" spans="1:18" ht="33">
       <c r="A250" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A250" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E250),
@@ -34075,19 +34032,19 @@
       </c>
       <c r="G250" s="148"/>
       <c r="H250" s="38" t="s">
+        <v>560</v>
+      </c>
+      <c r="I250" s="39" t="s">
         <v>561</v>
-      </c>
-      <c r="I250" s="39" t="s">
-        <v>562</v>
       </c>
       <c r="J250" s="41" t="s">
         <v>31</v>
       </c>
       <c r="K250" s="41" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="L250" s="149" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M250" s="149">
         <v>2</v>
@@ -34098,7 +34055,7 @@
       <c r="Q250" s="163"/>
       <c r="R250" s="148"/>
     </row>
-    <row r="251" spans="1:18" ht="33.75">
+    <row r="251" spans="1:18" ht="33">
       <c r="A251" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A251" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E251),
@@ -34135,7 +34092,7 @@
       <c r="Q251" s="113"/>
       <c r="R251" s="58"/>
     </row>
-    <row r="252" spans="1:18" ht="33.75">
+    <row r="252" spans="1:18" ht="33">
       <c r="A252" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A252" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E252),
@@ -34154,26 +34111,26 @@
         <v>298</v>
       </c>
       <c r="E252" s="169" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F252" s="162" t="s">
         <v>421</v>
       </c>
       <c r="G252" s="148"/>
       <c r="H252" s="38" t="s">
+        <v>560</v>
+      </c>
+      <c r="I252" s="39" t="s">
         <v>561</v>
       </c>
-      <c r="I252" s="39" t="s">
-        <v>562</v>
-      </c>
       <c r="J252" s="42" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="K252" s="41" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="L252" s="149" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M252" s="149">
         <v>2</v>
@@ -34184,7 +34141,7 @@
       <c r="Q252" s="163"/>
       <c r="R252" s="148"/>
     </row>
-    <row r="253" spans="1:18" ht="22.5">
+    <row r="253" spans="1:18" ht="22">
       <c r="A253" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A253" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E253),
@@ -34219,7 +34176,7 @@
       <c r="Q253" s="113"/>
       <c r="R253" s="58"/>
     </row>
-    <row r="254" spans="1:18" ht="33.75">
+    <row r="254" spans="1:18" ht="33">
       <c r="A254" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A254" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E254),
@@ -34256,7 +34213,7 @@
       <c r="Q254" s="113"/>
       <c r="R254" s="58"/>
     </row>
-    <row r="255" spans="1:18" ht="33.75">
+    <row r="255" spans="1:18" ht="33">
       <c r="A255" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A255" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E255),
@@ -34278,19 +34235,19 @@
       </c>
       <c r="G255" s="148"/>
       <c r="H255" s="38" t="s">
+        <v>560</v>
+      </c>
+      <c r="I255" s="39" t="s">
         <v>561</v>
       </c>
-      <c r="I255" s="39" t="s">
-        <v>562</v>
-      </c>
       <c r="J255" s="42" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="K255" s="41" t="s">
         <v>32</v>
       </c>
       <c r="L255" s="149" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M255" s="149">
         <v>4</v>
@@ -34301,7 +34258,7 @@
       <c r="Q255" s="163"/>
       <c r="R255" s="148"/>
     </row>
-    <row r="256" spans="1:18" ht="33.75">
+    <row r="256" spans="1:18" ht="33">
       <c r="A256" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A256" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E256),
@@ -34319,7 +34276,7 @@
       <c r="D256" s="165"/>
       <c r="E256" s="165"/>
       <c r="F256" s="112" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G256" s="58" t="s">
         <v>186</v>
@@ -34336,7 +34293,7 @@
       <c r="Q256" s="113"/>
       <c r="R256" s="58"/>
     </row>
-    <row r="257" spans="1:18" ht="33.75">
+    <row r="257" spans="1:18" ht="33">
       <c r="A257" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A257" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E257),
@@ -34371,7 +34328,7 @@
       <c r="Q257" s="113"/>
       <c r="R257" s="58"/>
     </row>
-    <row r="258" spans="1:18" ht="33.75">
+    <row r="258" spans="1:18" ht="33">
       <c r="A258" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A258" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E258),
@@ -34406,7 +34363,7 @@
       <c r="Q258" s="113"/>
       <c r="R258" s="58"/>
     </row>
-    <row r="259" spans="1:18" ht="22.5">
+    <row r="259" spans="1:18" ht="22">
       <c r="A259" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A259" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E259),
@@ -34441,7 +34398,7 @@
       <c r="Q259" s="113"/>
       <c r="R259" s="58"/>
     </row>
-    <row r="260" spans="1:18" ht="22.5">
+    <row r="260" spans="1:18" ht="22">
       <c r="A260" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A260" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E260),
@@ -34476,7 +34433,7 @@
       <c r="Q260" s="113"/>
       <c r="R260" s="58"/>
     </row>
-    <row r="261" spans="1:18" ht="33.75">
+    <row r="261" spans="1:18" ht="33">
       <c r="A261" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A261" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E261),
@@ -34511,7 +34468,7 @@
       <c r="Q261" s="113"/>
       <c r="R261" s="58"/>
     </row>
-    <row r="262" spans="1:18" ht="33.75">
+    <row r="262" spans="1:18" ht="33">
       <c r="A262" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A262" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E262),
@@ -34546,7 +34503,7 @@
       <c r="Q262" s="113"/>
       <c r="R262" s="58"/>
     </row>
-    <row r="263" spans="1:18" ht="33.75">
+    <row r="263" spans="1:18" ht="33">
       <c r="A263" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A263" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E263),
@@ -34581,7 +34538,7 @@
       <c r="Q263" s="113"/>
       <c r="R263" s="58"/>
     </row>
-    <row r="264" spans="1:18" ht="33.75">
+    <row r="264" spans="1:18" ht="33">
       <c r="A264" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A264" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E264),
@@ -34616,7 +34573,7 @@
       <c r="Q264" s="113"/>
       <c r="R264" s="58"/>
     </row>
-    <row r="265" spans="1:18" ht="56.25">
+    <row r="265" spans="1:18" ht="55">
       <c r="A265" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A265" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E265),
@@ -34640,19 +34597,19 @@
       </c>
       <c r="G265" s="148"/>
       <c r="H265" s="38" t="s">
+        <v>560</v>
+      </c>
+      <c r="I265" s="39" t="s">
         <v>561</v>
       </c>
-      <c r="I265" s="39" t="s">
-        <v>562</v>
-      </c>
       <c r="J265" s="42" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K265" s="42" t="s">
         <v>30</v>
       </c>
       <c r="L265" s="149" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M265" s="149">
         <v>3</v>
@@ -34698,7 +34655,7 @@
       <c r="Q266" s="113"/>
       <c r="R266" s="58"/>
     </row>
-    <row r="267" spans="1:18" ht="33.75">
+    <row r="267" spans="1:18" ht="33">
       <c r="A267" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A267" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E267),
@@ -34733,7 +34690,7 @@
       <c r="Q267" s="113"/>
       <c r="R267" s="58"/>
     </row>
-    <row r="268" spans="1:18" ht="22.5">
+    <row r="268" spans="1:18" ht="22">
       <c r="A268" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A268" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E268),
@@ -34768,7 +34725,7 @@
       <c r="Q268" s="113"/>
       <c r="R268" s="58"/>
     </row>
-    <row r="269" spans="1:18" ht="22.5">
+    <row r="269" spans="1:18" ht="22">
       <c r="A269" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A269" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E269),
@@ -34803,7 +34760,7 @@
       <c r="Q269" s="113"/>
       <c r="R269" s="58"/>
     </row>
-    <row r="270" spans="1:18" ht="33.75">
+    <row r="270" spans="1:18" ht="33">
       <c r="A270" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A270" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E270),
@@ -34838,7 +34795,7 @@
       <c r="Q270" s="113"/>
       <c r="R270" s="58"/>
     </row>
-    <row r="271" spans="1:18" ht="33.75">
+    <row r="271" spans="1:18" ht="33">
       <c r="A271" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A271" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E271),
@@ -34867,16 +34824,16 @@
         <v>27</v>
       </c>
       <c r="I271" s="39" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J271" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K271" s="42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="L271" s="87" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M271" s="87">
         <v>2</v>
@@ -34887,7 +34844,7 @@
       <c r="Q271" s="163"/>
       <c r="R271" s="148"/>
     </row>
-    <row r="272" spans="1:18" ht="33.75">
+    <row r="272" spans="1:18" ht="33">
       <c r="A272" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A272" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E272),
@@ -34922,7 +34879,7 @@
       <c r="Q272" s="113"/>
       <c r="R272" s="58"/>
     </row>
-    <row r="273" spans="1:18" ht="45">
+    <row r="273" spans="1:18" ht="44">
       <c r="A273" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A273" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E273),
@@ -34957,7 +34914,7 @@
       <c r="Q273" s="113"/>
       <c r="R273" s="58"/>
     </row>
-    <row r="274" spans="1:18" ht="45">
+    <row r="274" spans="1:18" ht="44">
       <c r="A274" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A274" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E274),
@@ -34992,7 +34949,7 @@
       <c r="Q274" s="113"/>
       <c r="R274" s="58"/>
     </row>
-    <row r="275" spans="1:18" ht="33.75">
+    <row r="275" spans="1:18" ht="33">
       <c r="A275" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A275" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E275),
@@ -35027,7 +34984,7 @@
       <c r="Q275" s="113"/>
       <c r="R275" s="58"/>
     </row>
-    <row r="276" spans="1:18" ht="45">
+    <row r="276" spans="1:18" ht="44">
       <c r="A276" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A276" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E276),
@@ -35062,7 +35019,7 @@
       <c r="Q276" s="113"/>
       <c r="R276" s="58"/>
     </row>
-    <row r="277" spans="1:18" ht="45">
+    <row r="277" spans="1:18" ht="44">
       <c r="A277" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A277" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E277),
@@ -35097,7 +35054,7 @@
       <c r="Q277" s="113"/>
       <c r="R277" s="58"/>
     </row>
-    <row r="278" spans="1:18" ht="22.5">
+    <row r="278" spans="1:18" ht="22">
       <c r="A278" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A278" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E278),
@@ -35132,7 +35089,7 @@
       <c r="Q278" s="113"/>
       <c r="R278" s="58"/>
     </row>
-    <row r="279" spans="1:18" ht="22.5">
+    <row r="279" spans="1:18" ht="22">
       <c r="A279" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A279" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E279),
@@ -35169,7 +35126,7 @@
       <c r="Q279" s="113"/>
       <c r="R279" s="58"/>
     </row>
-    <row r="280" spans="1:18" ht="22.5">
+    <row r="280" spans="1:18" ht="22">
       <c r="A280" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A280" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E280),
@@ -35189,10 +35146,10 @@
         <v>450</v>
       </c>
       <c r="D280" s="110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E280" s="118" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F280" s="112" t="s">
         <v>451</v>
@@ -35212,7 +35169,7 @@
       <c r="Q280" s="113"/>
       <c r="R280" s="58"/>
     </row>
-    <row r="281" spans="1:18" ht="22.5">
+    <row r="281" spans="1:18" ht="22">
       <c r="A281" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A281" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E281),
@@ -35247,7 +35204,7 @@
       <c r="Q281" s="113"/>
       <c r="R281" s="58"/>
     </row>
-    <row r="282" spans="1:18" ht="22.5">
+    <row r="282" spans="1:18" ht="22">
       <c r="A282" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A282" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E282),
@@ -35282,7 +35239,7 @@
       <c r="Q282" s="113"/>
       <c r="R282" s="58"/>
     </row>
-    <row r="283" spans="1:18" ht="22.5">
+    <row r="283" spans="1:18" ht="22">
       <c r="A283" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A283" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E283),
@@ -35317,7 +35274,7 @@
       <c r="Q283" s="113"/>
       <c r="R283" s="58"/>
     </row>
-    <row r="284" spans="1:18" ht="22.5">
+    <row r="284" spans="1:18" ht="22">
       <c r="A284" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A284" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E284),
@@ -35358,7 +35315,7 @@
       <c r="Q284" s="113"/>
       <c r="R284" s="58"/>
     </row>
-    <row r="285" spans="1:18" ht="22.5">
+    <row r="285" spans="1:18" ht="22">
       <c r="A285" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A285" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E285),
@@ -35395,7 +35352,7 @@
       <c r="Q285" s="113"/>
       <c r="R285" s="58"/>
     </row>
-    <row r="286" spans="1:18" ht="22.5">
+    <row r="286" spans="1:18" ht="22">
       <c r="A286" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A286" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E286),
@@ -35432,7 +35389,7 @@
       <c r="Q286" s="113"/>
       <c r="R286" s="58"/>
     </row>
-    <row r="287" spans="1:18" ht="22.5">
+    <row r="287" spans="1:18" ht="22">
       <c r="A287" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A287" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E287),
@@ -35469,7 +35426,7 @@
       <c r="Q287" s="113"/>
       <c r="R287" s="58"/>
     </row>
-    <row r="288" spans="1:18" ht="22.5">
+    <row r="288" spans="1:18" ht="22">
       <c r="A288" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A288" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E288),
@@ -35508,7 +35465,7 @@
       <c r="Q288" s="113"/>
       <c r="R288" s="58"/>
     </row>
-    <row r="289" spans="1:18" ht="22.5">
+    <row r="289" spans="1:18" ht="22">
       <c r="A289" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A289" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E289),
@@ -35543,7 +35500,7 @@
       <c r="Q289" s="113"/>
       <c r="R289" s="58"/>
     </row>
-    <row r="290" spans="1:18" ht="33.75">
+    <row r="290" spans="1:18" ht="33">
       <c r="A290" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A290" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E290),
@@ -35578,7 +35535,7 @@
       <c r="Q290" s="113"/>
       <c r="R290" s="58"/>
     </row>
-    <row r="291" spans="1:18" ht="33.75">
+    <row r="291" spans="1:18" ht="33">
       <c r="A291" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A291" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E291),
@@ -35596,7 +35553,7 @@
       <c r="D291" s="116"/>
       <c r="E291" s="116"/>
       <c r="F291" s="112" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G291" s="56" t="s">
         <v>452</v>
@@ -35613,7 +35570,7 @@
       <c r="Q291" s="113"/>
       <c r="R291" s="58"/>
     </row>
-    <row r="292" spans="1:18" ht="33.75">
+    <row r="292" spans="1:18" ht="33">
       <c r="A292" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A292" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E292),
@@ -35631,7 +35588,7 @@
       <c r="D292" s="116"/>
       <c r="E292" s="116"/>
       <c r="F292" s="112" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G292" s="56" t="s">
         <v>452</v>
@@ -35648,7 +35605,7 @@
       <c r="Q292" s="113"/>
       <c r="R292" s="58"/>
     </row>
-    <row r="293" spans="1:18" ht="33.75">
+    <row r="293" spans="1:18" ht="33">
       <c r="A293" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A293" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E293),
@@ -35666,7 +35623,7 @@
       <c r="D293" s="116"/>
       <c r="E293" s="116"/>
       <c r="F293" s="112" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G293" s="56" t="s">
         <v>452</v>
@@ -35683,7 +35640,7 @@
       <c r="Q293" s="113"/>
       <c r="R293" s="58"/>
     </row>
-    <row r="294" spans="1:18" ht="33.75">
+    <row r="294" spans="1:18" ht="33">
       <c r="A294" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A294" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E294),
@@ -35701,7 +35658,7 @@
       <c r="D294" s="116"/>
       <c r="E294" s="116"/>
       <c r="F294" s="112" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G294" s="56" t="s">
         <v>452</v>
@@ -35718,7 +35675,7 @@
       <c r="Q294" s="113"/>
       <c r="R294" s="58"/>
     </row>
-    <row r="295" spans="1:18" ht="22.5">
+    <row r="295" spans="1:18" ht="22">
       <c r="A295" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A295" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E295),
@@ -35753,7 +35710,7 @@
       <c r="Q295" s="113"/>
       <c r="R295" s="58"/>
     </row>
-    <row r="296" spans="1:18" ht="22.5">
+    <row r="296" spans="1:18" ht="22">
       <c r="A296" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A296" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E296),
@@ -35788,7 +35745,7 @@
       <c r="Q296" s="113"/>
       <c r="R296" s="58"/>
     </row>
-    <row r="297" spans="1:18" ht="33.75">
+    <row r="297" spans="1:18" ht="33">
       <c r="A297" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A297" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E297),
@@ -35802,19 +35759,19 @@
         <v>101-1-1</v>
       </c>
       <c r="B297" s="126" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C297" s="126" t="s">
         <v>243</v>
       </c>
       <c r="D297" s="110" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E297" s="110" t="s">
+        <v>512</v>
+      </c>
+      <c r="F297" s="110" t="s">
         <v>513</v>
-      </c>
-      <c r="F297" s="110" t="s">
-        <v>514</v>
       </c>
       <c r="G297" s="58" t="s">
         <v>186</v>
@@ -35831,7 +35788,7 @@
       <c r="Q297" s="61"/>
       <c r="R297" s="61"/>
     </row>
-    <row r="298" spans="1:18" ht="22.5">
+    <row r="298" spans="1:18" ht="22">
       <c r="A298" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A298" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E298),
@@ -35851,7 +35808,7 @@
         <v>198</v>
       </c>
       <c r="F298" s="112" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G298" s="58" t="s">
         <v>186</v>
@@ -35868,7 +35825,7 @@
       <c r="Q298" s="61"/>
       <c r="R298" s="61"/>
     </row>
-    <row r="299" spans="1:18" ht="33.75">
+    <row r="299" spans="1:18" ht="33">
       <c r="A299" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A299" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E299),
@@ -35885,10 +35842,10 @@
       <c r="C299" s="129"/>
       <c r="D299" s="116"/>
       <c r="E299" s="110" t="s">
+        <v>515</v>
+      </c>
+      <c r="F299" s="110" t="s">
         <v>516</v>
-      </c>
-      <c r="F299" s="110" t="s">
-        <v>517</v>
       </c>
       <c r="G299" s="58" t="s">
         <v>186</v>
@@ -35905,7 +35862,7 @@
       <c r="Q299" s="61"/>
       <c r="R299" s="61"/>
     </row>
-    <row r="300" spans="1:18" ht="33.75">
+    <row r="300" spans="1:18" ht="33">
       <c r="A300" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A300" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E300),
@@ -35921,29 +35878,29 @@
       <c r="B300" s="129"/>
       <c r="C300" s="129"/>
       <c r="D300" s="126" t="s">
+        <v>517</v>
+      </c>
+      <c r="E300" s="126" t="s">
+        <v>475</v>
+      </c>
+      <c r="F300" s="126" t="s">
         <v>518</v>
-      </c>
-      <c r="E300" s="126" t="s">
-        <v>476</v>
-      </c>
-      <c r="F300" s="126" t="s">
-        <v>519</v>
       </c>
       <c r="G300" s="136"/>
       <c r="H300" s="38" t="s">
         <v>27</v>
       </c>
       <c r="I300" s="39" t="s">
+        <v>562</v>
+      </c>
+      <c r="J300" s="42" t="s">
         <v>563</v>
       </c>
-      <c r="J300" s="42" t="s">
-        <v>564</v>
-      </c>
       <c r="K300" s="42" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L300" s="87" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M300" s="87">
         <v>1</v>
@@ -35954,7 +35911,7 @@
       <c r="Q300" s="87"/>
       <c r="R300" s="87"/>
     </row>
-    <row r="301" spans="1:18" ht="56.25">
+    <row r="301" spans="1:18" ht="55">
       <c r="A301" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A301" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E301),
@@ -35977,16 +35934,16 @@
         <v>27</v>
       </c>
       <c r="I301" s="39" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J301" s="42" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="K301" s="42" t="s">
         <v>30</v>
       </c>
       <c r="L301" s="87" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="M301" s="87">
         <v>2</v>
@@ -35997,7 +35954,7 @@
       <c r="Q301" s="87"/>
       <c r="R301" s="87"/>
     </row>
-    <row r="302" spans="1:18" ht="33.75">
+    <row r="302" spans="1:18" ht="33">
       <c r="A302" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A302" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E302),
@@ -36015,20 +35972,20 @@
       <c r="D302" s="129"/>
       <c r="E302" s="128"/>
       <c r="F302" s="126" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G302" s="136"/>
       <c r="H302" s="38" t="s">
         <v>27</v>
       </c>
       <c r="I302" s="39" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J302" s="37" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="K302" s="40" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L302" s="149" t="s">
         <v>34</v>
@@ -36042,7 +35999,7 @@
       <c r="Q302" s="87"/>
       <c r="R302" s="87"/>
     </row>
-    <row r="303" spans="1:18" ht="33.75">
+    <row r="303" spans="1:18" ht="33">
       <c r="A303" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A303" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E303),
@@ -36060,7 +36017,7 @@
       <c r="D303" s="128"/>
       <c r="E303" s="128"/>
       <c r="F303" s="112" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G303" s="58" t="s">
         <v>186</v>
@@ -36095,7 +36052,7 @@
       <c r="D304" s="128"/>
       <c r="E304" s="129"/>
       <c r="F304" s="114" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G304" s="58" t="s">
         <v>186</v>
@@ -36112,7 +36069,7 @@
       <c r="Q304" s="61"/>
       <c r="R304" s="61"/>
     </row>
-    <row r="305" spans="1:18" ht="45">
+    <row r="305" spans="1:18" ht="44">
       <c r="A305" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A305" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E305),
@@ -36128,26 +36085,26 @@
       <c r="B305" s="129"/>
       <c r="C305" s="129"/>
       <c r="D305" s="126" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E305" s="126" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F305" s="126" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G305" s="171"/>
       <c r="H305" s="38" t="s">
         <v>27</v>
       </c>
       <c r="I305" s="39" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J305" s="37" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="K305" s="40" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="L305" s="149" t="s">
         <v>34</v>
@@ -36161,7 +36118,7 @@
       <c r="Q305" s="149"/>
       <c r="R305" s="149"/>
     </row>
-    <row r="306" spans="1:18" ht="45">
+    <row r="306" spans="1:18" ht="44">
       <c r="A306" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A306" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E306),
@@ -36184,13 +36141,13 @@
         <v>27</v>
       </c>
       <c r="I306" s="39" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J306" s="37" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="K306" s="40" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="L306" s="149" t="s">
         <v>34</v>
@@ -36204,7 +36161,7 @@
       <c r="Q306" s="149"/>
       <c r="R306" s="149"/>
     </row>
-    <row r="307" spans="1:18" ht="45">
+    <row r="307" spans="1:18" ht="44">
       <c r="A307" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A307" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E307),
@@ -36222,7 +36179,7 @@
       <c r="D307" s="128"/>
       <c r="E307" s="129"/>
       <c r="F307" s="112" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G307" s="58" t="s">
         <v>186</v>
@@ -36239,7 +36196,7 @@
       <c r="Q307" s="61"/>
       <c r="R307" s="61"/>
     </row>
-    <row r="308" spans="1:18" ht="45">
+    <row r="308" spans="1:18" ht="44">
       <c r="A308" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A308" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E308),
@@ -36257,7 +36214,7 @@
       <c r="D308" s="128"/>
       <c r="E308" s="129"/>
       <c r="F308" s="112" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G308" s="58" t="s">
         <v>186</v>
@@ -36274,7 +36231,7 @@
       <c r="Q308" s="61"/>
       <c r="R308" s="61"/>
     </row>
-    <row r="309" spans="1:18" ht="33.75">
+    <row r="309" spans="1:18" ht="33">
       <c r="A309" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A309" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E309),
@@ -36292,7 +36249,7 @@
       <c r="D309" s="128"/>
       <c r="E309" s="129"/>
       <c r="F309" s="112" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G309" s="58" t="s">
         <v>186</v>
@@ -36309,7 +36266,7 @@
       <c r="Q309" s="61"/>
       <c r="R309" s="61"/>
     </row>
-    <row r="310" spans="1:18" ht="45">
+    <row r="310" spans="1:18" ht="44">
       <c r="A310" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A310" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E310),
@@ -36327,7 +36284,7 @@
       <c r="D310" s="128"/>
       <c r="E310" s="129"/>
       <c r="F310" s="112" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G310" s="58" t="s">
         <v>186</v>
@@ -36344,7 +36301,7 @@
       <c r="Q310" s="61"/>
       <c r="R310" s="61"/>
     </row>
-    <row r="311" spans="1:18" ht="45">
+    <row r="311" spans="1:18" ht="44">
       <c r="A311" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A311" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E311),
@@ -36362,7 +36319,7 @@
       <c r="D311" s="128"/>
       <c r="E311" s="129"/>
       <c r="F311" s="112" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G311" s="58" t="s">
         <v>186</v>
@@ -36379,7 +36336,7 @@
       <c r="Q311" s="61"/>
       <c r="R311" s="61"/>
     </row>
-    <row r="312" spans="1:18" ht="45">
+    <row r="312" spans="1:18" ht="44">
       <c r="A312" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A312" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E312),
@@ -36397,7 +36354,7 @@
       <c r="D312" s="128"/>
       <c r="E312" s="129"/>
       <c r="F312" s="112" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G312" s="58" t="s">
         <v>186</v>
@@ -36414,7 +36371,7 @@
       <c r="Q312" s="61"/>
       <c r="R312" s="61"/>
     </row>
-    <row r="313" spans="1:18" ht="22.5">
+    <row r="313" spans="1:18" ht="22">
       <c r="A313" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A313" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E313),
@@ -36432,7 +36389,7 @@
       <c r="D313" s="128"/>
       <c r="E313" s="129"/>
       <c r="F313" s="112" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G313" s="58" t="s">
         <v>186</v>
@@ -36449,7 +36406,7 @@
       <c r="Q313" s="61"/>
       <c r="R313" s="61"/>
     </row>
-    <row r="314" spans="1:18" ht="33.75">
+    <row r="314" spans="1:18" ht="33">
       <c r="A314" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A314" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E314),
@@ -36467,10 +36424,10 @@
       <c r="D314" s="128"/>
       <c r="E314" s="128"/>
       <c r="F314" s="112" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="G314" s="58" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H314" s="61"/>
       <c r="I314" s="61"/>
@@ -36484,7 +36441,7 @@
       <c r="Q314" s="61"/>
       <c r="R314" s="61"/>
     </row>
-    <row r="315" spans="1:18" ht="33.75">
+    <row r="315" spans="1:18" ht="33">
       <c r="A315" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A315" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E315),
@@ -36502,7 +36459,7 @@
       <c r="D315" s="128"/>
       <c r="E315" s="128"/>
       <c r="F315" s="112" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G315" s="58" t="s">
         <v>186</v>
@@ -36519,7 +36476,7 @@
       <c r="Q315" s="61"/>
       <c r="R315" s="61"/>
     </row>
-    <row r="316" spans="1:18" ht="22.5">
+    <row r="316" spans="1:18" ht="22">
       <c r="A316" s="52" t="str" cm="1">
         <f t="array" aca="1" ref="A316" ca="1">_xlfn.LET(
 _xlpm.詳細項目数, COUNTA($E$11:E316),
@@ -36537,7 +36494,7 @@
       <c r="D316" s="131"/>
       <c r="E316" s="131"/>
       <c r="F316" s="112" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="G316" s="58" t="s">
         <v>186</v>
@@ -36596,18 +36553,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P551"/>
-  <sheetFormatPr defaultRowHeight="11.25" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="8.625" style="28" customWidth="1"/>
-    <col min="2" max="2" width="10.625" style="28" customWidth="1"/>
+    <col min="1" max="1" width="8.58203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="10.58203125" style="28" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.625" style="29" customWidth="1"/>
+    <col min="4" max="4" width="15.58203125" style="29" customWidth="1"/>
     <col min="5" max="5" width="15.5" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.875" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.125" style="107" customWidth="1" outlineLevel="1"/>
-    <col min="8" max="9" width="30.625" style="28" customWidth="1"/>
-    <col min="10" max="10" width="20.625" style="28" customWidth="1"/>
-    <col min="11" max="14" width="8.625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="13.83203125" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.08203125" style="107" customWidth="1" outlineLevel="1"/>
+    <col min="8" max="9" width="30.58203125" style="28" customWidth="1"/>
+    <col min="10" max="10" width="20.58203125" style="28" customWidth="1"/>
+    <col min="11" max="14" width="8.58203125" style="28" customWidth="1"/>
     <col min="15" max="16384" width="9" style="28"/>
   </cols>
   <sheetData>
@@ -36648,7 +36605,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="12" thickBot="1">
+    <row r="8" spans="1:16" ht="11.5" thickBot="1">
       <c r="A8" s="30"/>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
@@ -36717,7 +36674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="35" customFormat="1" ht="33.75">
+    <row r="11" spans="1:16" s="35" customFormat="1" ht="33">
       <c r="A11" s="138" t="s">
         <v>28</v>
       </c>
@@ -36725,7 +36682,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="139" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D11" s="139" t="s">
         <v>18</v>
@@ -36734,17 +36691,17 @@
         <v>0</v>
       </c>
       <c r="F11" s="139" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G11" s="136"/>
       <c r="H11" s="43" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I11" s="37" t="s">
         <v>38</v>
       </c>
       <c r="J11" s="140" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="K11" s="141">
         <v>1</v>
@@ -36755,7 +36712,7 @@
       <c r="O11" s="141"/>
       <c r="P11" s="141"/>
     </row>
-    <row r="12" spans="1:16" s="35" customFormat="1" ht="45">
+    <row r="12" spans="1:16" s="35" customFormat="1" ht="44">
       <c r="A12" s="138" t="s">
         <v>29</v>
       </c>
@@ -36775,10 +36732,10 @@
         <v>39</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J12" s="140" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K12" s="141">
         <v>1</v>
@@ -36789,7 +36746,7 @@
       <c r="O12" s="141"/>
       <c r="P12" s="141"/>
     </row>
-    <row r="13" spans="1:16" s="35" customFormat="1" ht="56.25">
+    <row r="13" spans="1:16" s="35" customFormat="1" ht="55">
       <c r="A13" s="138" t="s">
         <v>37</v>
       </c>
@@ -36803,10 +36760,10 @@
         <v>40</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="J13" s="141" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K13" s="141">
         <v>2</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
@@ -3,28 +3,28 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE8A868-DBAE-456A-8E42-3E49C4DF4C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DC2D97A-56D7-4050-B322-5612FD5755B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
-    <sheet name="【リクエストID】_クラス単体テスト" sheetId="23" r:id="rId3"/>
-    <sheet name="【リクエストID】_リクエスト単体テスト" sheetId="24" r:id="rId4"/>
-    <sheet name="取引単体テスト" sheetId="25" r:id="rId5"/>
+    <sheet name="XxxAction_クラス単体" sheetId="23" r:id="rId3"/>
+    <sheet name="RMxxxxxxxx_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="取引単体" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">【リクエストID】_クラス単体テスト!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">【リクエストID】_リクエスト単体テスト!$A$10:$R$316</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">【リクエストID】_クラス単体テスト!$A$1:$R$298</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">【リクエストID】_リクエスト単体テスト!$A$1:$R$316</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体テスト!$A$1:$P$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RMxxxxxxxx_リクエスト単体!$A$10:$R$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">RMxxxxxxxx_リクエスト単体!$A$1:$R$316</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$298</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">【リクエストID】_クラス単体テスト!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">【リクエストID】_リクエスト単体テスト!$1:$9</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体テスト!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">RMxxxxxxxx_リクエスト単体!$1:$9</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="578">
   <si>
     <t>システム機能設計書</t>
     <rPh sb="4" eb="6">
@@ -7657,6 +7657,10 @@
   <si>
     <t>単体テスト仕様書(メッセージ)
 サンプル取引/RMXXXXXXXX</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リクエストID：RMxxxxxxxx</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -25195,7 +25199,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>73</v>
+        <v>577</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>21</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91529BF0-D08C-461B-B59F-5A9BA3881944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51AC6ED-40D5-4EE2-8ED6-5D06584C1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7648,7 +7648,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>リクエストID：RMxxxxxxxx</t>
+    <t>テストターゲット名：RMxxxxxxxx</t>
+    <rPh sb="8" eb="9">
+      <t>メイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8666,108 +8669,6 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8874,6 +8775,108 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13042,57 +13045,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="181" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="216"/>
-      <c r="C1" s="216"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218" t="s">
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="219"/>
-      <c r="M1" s="219"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="224" t="s">
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="186"/>
+      <c r="O1" s="190" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="233" t="s">
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="199" t="s">
         <v>573</v>
       </c>
-      <c r="T1" s="234"/>
-      <c r="U1" s="234"/>
-      <c r="V1" s="234"/>
-      <c r="W1" s="234"/>
-      <c r="X1" s="234"/>
-      <c r="Y1" s="234"/>
-      <c r="Z1" s="235"/>
-      <c r="AA1" s="215" t="s">
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="201"/>
+      <c r="AA1" s="181" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="242" t="str">
+      <c r="AB1" s="183"/>
+      <c r="AC1" s="208" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="243"/>
-      <c r="AE1" s="243"/>
-      <c r="AF1" s="244"/>
-      <c r="AG1" s="209">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="175">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="210"/>
-      <c r="AI1" s="211"/>
+      <c r="AH1" s="176"/>
+      <c r="AI1" s="177"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -13100,53 +13103,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="215" t="s">
+      <c r="A2" s="181" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="216"/>
-      <c r="C2" s="216"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="218" t="s">
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="184" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="219"/>
-      <c r="G2" s="219"/>
-      <c r="H2" s="219"/>
-      <c r="I2" s="219"/>
-      <c r="J2" s="219"/>
-      <c r="K2" s="219"/>
-      <c r="L2" s="219"/>
-      <c r="M2" s="219"/>
-      <c r="N2" s="220"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="228"/>
-      <c r="Q2" s="228"/>
-      <c r="R2" s="229"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="215" t="s">
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="195"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="203"/>
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="203"/>
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="204"/>
+      <c r="AA2" s="181" t="s">
         <v>43</v>
       </c>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="221" t="str">
+      <c r="AB2" s="183"/>
+      <c r="AC2" s="187" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="222"/>
-      <c r="AE2" s="222"/>
-      <c r="AF2" s="223"/>
-      <c r="AG2" s="209">
+      <c r="AD2" s="188"/>
+      <c r="AE2" s="188"/>
+      <c r="AF2" s="189"/>
+      <c r="AG2" s="175">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="210"/>
-      <c r="AI2" s="211"/>
+      <c r="AH2" s="176"/>
+      <c r="AI2" s="177"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -13154,45 +13157,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="215" t="s">
+      <c r="A3" s="181" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="216"/>
-      <c r="C3" s="216"/>
-      <c r="D3" s="217"/>
-      <c r="E3" s="218" t="s">
+      <c r="B3" s="182"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="184" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="219"/>
-      <c r="G3" s="219"/>
-      <c r="H3" s="219"/>
-      <c r="I3" s="219"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="219"/>
-      <c r="L3" s="219"/>
-      <c r="M3" s="219"/>
-      <c r="N3" s="220"/>
-      <c r="O3" s="230"/>
-      <c r="P3" s="231"/>
-      <c r="Q3" s="231"/>
-      <c r="R3" s="232"/>
-      <c r="S3" s="239"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="241"/>
-      <c r="AA3" s="215"/>
-      <c r="AB3" s="217"/>
-      <c r="AC3" s="242"/>
-      <c r="AD3" s="243"/>
-      <c r="AE3" s="243"/>
-      <c r="AF3" s="244"/>
-      <c r="AG3" s="209"/>
-      <c r="AH3" s="210"/>
-      <c r="AI3" s="211"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="186"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="197"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="198"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="206"/>
+      <c r="U3" s="206"/>
+      <c r="V3" s="206"/>
+      <c r="W3" s="206"/>
+      <c r="X3" s="206"/>
+      <c r="Y3" s="206"/>
+      <c r="Z3" s="207"/>
+      <c r="AA3" s="181"/>
+      <c r="AB3" s="183"/>
+      <c r="AC3" s="208"/>
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="175"/>
+      <c r="AH3" s="176"/>
+      <c r="AI3" s="177"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -13229,97 +13232,97 @@
       <c r="A7" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="212" t="s">
+      <c r="B7" s="178" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="213"/>
-      <c r="D7" s="212" t="s">
+      <c r="C7" s="179"/>
+      <c r="D7" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="214"/>
-      <c r="F7" s="213"/>
-      <c r="G7" s="212" t="s">
+      <c r="E7" s="180"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="178" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="214"/>
-      <c r="I7" s="213"/>
-      <c r="J7" s="212" t="s">
+      <c r="H7" s="180"/>
+      <c r="I7" s="179"/>
+      <c r="J7" s="178" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="214"/>
-      <c r="L7" s="214"/>
-      <c r="M7" s="214"/>
-      <c r="N7" s="214"/>
-      <c r="O7" s="214"/>
-      <c r="P7" s="213"/>
-      <c r="Q7" s="212" t="s">
+      <c r="K7" s="180"/>
+      <c r="L7" s="180"/>
+      <c r="M7" s="180"/>
+      <c r="N7" s="180"/>
+      <c r="O7" s="180"/>
+      <c r="P7" s="179"/>
+      <c r="Q7" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="214"/>
-      <c r="S7" s="214"/>
-      <c r="T7" s="214"/>
-      <c r="U7" s="214"/>
-      <c r="V7" s="214"/>
-      <c r="W7" s="214"/>
-      <c r="X7" s="214"/>
-      <c r="Y7" s="214"/>
-      <c r="Z7" s="214"/>
-      <c r="AA7" s="214"/>
-      <c r="AB7" s="214"/>
-      <c r="AC7" s="214"/>
-      <c r="AD7" s="214"/>
-      <c r="AE7" s="213"/>
-      <c r="AF7" s="212" t="s">
+      <c r="R7" s="180"/>
+      <c r="S7" s="180"/>
+      <c r="T7" s="180"/>
+      <c r="U7" s="180"/>
+      <c r="V7" s="180"/>
+      <c r="W7" s="180"/>
+      <c r="X7" s="180"/>
+      <c r="Y7" s="180"/>
+      <c r="Z7" s="180"/>
+      <c r="AA7" s="180"/>
+      <c r="AB7" s="180"/>
+      <c r="AC7" s="180"/>
+      <c r="AD7" s="180"/>
+      <c r="AE7" s="179"/>
+      <c r="AF7" s="178" t="s">
         <v>51</v>
       </c>
-      <c r="AG7" s="214"/>
-      <c r="AH7" s="214"/>
-      <c r="AI7" s="213"/>
+      <c r="AG7" s="180"/>
+      <c r="AH7" s="180"/>
+      <c r="AI7" s="179"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="223" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="201"/>
-      <c r="D8" s="202">
+      <c r="C8" s="224"/>
+      <c r="D8" s="225">
         <v>43336</v>
       </c>
-      <c r="E8" s="203"/>
-      <c r="F8" s="204"/>
-      <c r="G8" s="200" t="s">
+      <c r="E8" s="226"/>
+      <c r="F8" s="227"/>
+      <c r="G8" s="223" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="205"/>
-      <c r="I8" s="201"/>
-      <c r="J8" s="206" t="s">
+      <c r="H8" s="228"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="229" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="207"/>
-      <c r="L8" s="207"/>
-      <c r="M8" s="207"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="207"/>
-      <c r="P8" s="208"/>
-      <c r="Q8" s="206" t="s">
+      <c r="K8" s="230"/>
+      <c r="L8" s="230"/>
+      <c r="M8" s="230"/>
+      <c r="N8" s="230"/>
+      <c r="O8" s="230"/>
+      <c r="P8" s="231"/>
+      <c r="Q8" s="229" t="s">
         <v>60</v>
       </c>
-      <c r="R8" s="207"/>
-      <c r="S8" s="207"/>
-      <c r="T8" s="207"/>
-      <c r="U8" s="207"/>
-      <c r="V8" s="207"/>
-      <c r="W8" s="207"/>
-      <c r="X8" s="207"/>
-      <c r="Y8" s="207"/>
-      <c r="Z8" s="207"/>
-      <c r="AA8" s="207"/>
-      <c r="AB8" s="207"/>
-      <c r="AC8" s="207"/>
-      <c r="AD8" s="207"/>
-      <c r="AE8" s="208"/>
+      <c r="R8" s="230"/>
+      <c r="S8" s="230"/>
+      <c r="T8" s="230"/>
+      <c r="U8" s="230"/>
+      <c r="V8" s="230"/>
+      <c r="W8" s="230"/>
+      <c r="X8" s="230"/>
+      <c r="Y8" s="230"/>
+      <c r="Z8" s="230"/>
+      <c r="AA8" s="230"/>
+      <c r="AB8" s="230"/>
+      <c r="AC8" s="230"/>
+      <c r="AD8" s="230"/>
+      <c r="AE8" s="231"/>
       <c r="AF8" s="25" t="s">
         <v>61</v>
       </c>
@@ -13331,946 +13334,1101 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="188" t="s">
+      <c r="B9" s="211" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="189"/>
-      <c r="D9" s="190">
+      <c r="C9" s="212"/>
+      <c r="D9" s="213">
         <v>44852</v>
       </c>
-      <c r="E9" s="191"/>
-      <c r="F9" s="192"/>
-      <c r="G9" s="190" t="s">
+      <c r="E9" s="214"/>
+      <c r="F9" s="215"/>
+      <c r="G9" s="213" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="193"/>
-      <c r="I9" s="189"/>
-      <c r="J9" s="194" t="s">
+      <c r="H9" s="216"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="217" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="195"/>
-      <c r="L9" s="195"/>
-      <c r="M9" s="195"/>
-      <c r="N9" s="195"/>
-      <c r="O9" s="195"/>
-      <c r="P9" s="196"/>
-      <c r="Q9" s="194" t="s">
+      <c r="K9" s="218"/>
+      <c r="L9" s="218"/>
+      <c r="M9" s="218"/>
+      <c r="N9" s="218"/>
+      <c r="O9" s="218"/>
+      <c r="P9" s="219"/>
+      <c r="Q9" s="217" t="s">
         <v>67</v>
       </c>
-      <c r="R9" s="197"/>
-      <c r="S9" s="197"/>
-      <c r="T9" s="197"/>
-      <c r="U9" s="197"/>
-      <c r="V9" s="197"/>
-      <c r="W9" s="197"/>
-      <c r="X9" s="197"/>
-      <c r="Y9" s="197"/>
-      <c r="Z9" s="197"/>
-      <c r="AA9" s="197"/>
-      <c r="AB9" s="197"/>
-      <c r="AC9" s="197"/>
-      <c r="AD9" s="197"/>
-      <c r="AE9" s="198"/>
-      <c r="AF9" s="199" t="s">
+      <c r="R9" s="220"/>
+      <c r="S9" s="220"/>
+      <c r="T9" s="220"/>
+      <c r="U9" s="220"/>
+      <c r="V9" s="220"/>
+      <c r="W9" s="220"/>
+      <c r="X9" s="220"/>
+      <c r="Y9" s="220"/>
+      <c r="Z9" s="220"/>
+      <c r="AA9" s="220"/>
+      <c r="AB9" s="220"/>
+      <c r="AC9" s="220"/>
+      <c r="AD9" s="220"/>
+      <c r="AE9" s="221"/>
+      <c r="AF9" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="AG9" s="195"/>
-      <c r="AH9" s="195"/>
-      <c r="AI9" s="196"/>
+      <c r="AG9" s="218"/>
+      <c r="AH9" s="218"/>
+      <c r="AI9" s="219"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="175"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="179"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="180"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="181"/>
-      <c r="K10" s="182"/>
-      <c r="L10" s="182"/>
-      <c r="M10" s="182"/>
-      <c r="N10" s="182"/>
-      <c r="O10" s="182"/>
-      <c r="P10" s="183"/>
-      <c r="Q10" s="184"/>
-      <c r="R10" s="185"/>
-      <c r="S10" s="185"/>
-      <c r="T10" s="185"/>
-      <c r="U10" s="185"/>
-      <c r="V10" s="185"/>
-      <c r="W10" s="185"/>
-      <c r="X10" s="185"/>
-      <c r="Y10" s="185"/>
-      <c r="Z10" s="185"/>
-      <c r="AA10" s="185"/>
-      <c r="AB10" s="185"/>
-      <c r="AC10" s="185"/>
-      <c r="AD10" s="185"/>
-      <c r="AE10" s="186"/>
-      <c r="AF10" s="181"/>
-      <c r="AG10" s="182"/>
-      <c r="AH10" s="182"/>
-      <c r="AI10" s="183"/>
+      <c r="B10" s="232"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="232"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
+      <c r="N10" s="239"/>
+      <c r="O10" s="239"/>
+      <c r="P10" s="240"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="242"/>
+      <c r="S10" s="242"/>
+      <c r="T10" s="242"/>
+      <c r="U10" s="242"/>
+      <c r="V10" s="242"/>
+      <c r="W10" s="242"/>
+      <c r="X10" s="242"/>
+      <c r="Y10" s="242"/>
+      <c r="Z10" s="242"/>
+      <c r="AA10" s="242"/>
+      <c r="AB10" s="242"/>
+      <c r="AC10" s="242"/>
+      <c r="AD10" s="242"/>
+      <c r="AE10" s="243"/>
+      <c r="AF10" s="238"/>
+      <c r="AG10" s="239"/>
+      <c r="AH10" s="239"/>
+      <c r="AI10" s="240"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="175"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="177"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="179"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="180"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
-      <c r="L11" s="182"/>
-      <c r="M11" s="182"/>
-      <c r="N11" s="182"/>
-      <c r="O11" s="182"/>
-      <c r="P11" s="183"/>
-      <c r="Q11" s="184"/>
-      <c r="R11" s="185"/>
-      <c r="S11" s="185"/>
-      <c r="T11" s="185"/>
-      <c r="U11" s="185"/>
-      <c r="V11" s="185"/>
-      <c r="W11" s="185"/>
-      <c r="X11" s="185"/>
-      <c r="Y11" s="185"/>
-      <c r="Z11" s="185"/>
-      <c r="AA11" s="185"/>
-      <c r="AB11" s="185"/>
-      <c r="AC11" s="185"/>
-      <c r="AD11" s="185"/>
-      <c r="AE11" s="186"/>
-      <c r="AF11" s="181"/>
-      <c r="AG11" s="182"/>
-      <c r="AH11" s="182"/>
-      <c r="AI11" s="183"/>
+      <c r="B11" s="232"/>
+      <c r="C11" s="233"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="235"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="232"/>
+      <c r="H11" s="237"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="238"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
+      <c r="N11" s="239"/>
+      <c r="O11" s="239"/>
+      <c r="P11" s="240"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="242"/>
+      <c r="S11" s="242"/>
+      <c r="T11" s="242"/>
+      <c r="U11" s="242"/>
+      <c r="V11" s="242"/>
+      <c r="W11" s="242"/>
+      <c r="X11" s="242"/>
+      <c r="Y11" s="242"/>
+      <c r="Z11" s="242"/>
+      <c r="AA11" s="242"/>
+      <c r="AB11" s="242"/>
+      <c r="AC11" s="242"/>
+      <c r="AD11" s="242"/>
+      <c r="AE11" s="243"/>
+      <c r="AF11" s="238"/>
+      <c r="AG11" s="239"/>
+      <c r="AH11" s="239"/>
+      <c r="AI11" s="240"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="175"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="177"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="175"/>
-      <c r="H12" s="180"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="182"/>
-      <c r="L12" s="182"/>
-      <c r="M12" s="182"/>
-      <c r="N12" s="182"/>
-      <c r="O12" s="182"/>
-      <c r="P12" s="183"/>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185"/>
-      <c r="S12" s="185"/>
-      <c r="T12" s="185"/>
-      <c r="U12" s="185"/>
-      <c r="V12" s="185"/>
-      <c r="W12" s="185"/>
-      <c r="X12" s="185"/>
-      <c r="Y12" s="185"/>
-      <c r="Z12" s="185"/>
-      <c r="AA12" s="185"/>
-      <c r="AB12" s="185"/>
-      <c r="AC12" s="185"/>
-      <c r="AD12" s="185"/>
-      <c r="AE12" s="186"/>
-      <c r="AF12" s="181"/>
-      <c r="AG12" s="182"/>
-      <c r="AH12" s="182"/>
-      <c r="AI12" s="183"/>
+      <c r="B12" s="232"/>
+      <c r="C12" s="233"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="232"/>
+      <c r="H12" s="237"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="238"/>
+      <c r="K12" s="239"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="239"/>
+      <c r="N12" s="239"/>
+      <c r="O12" s="239"/>
+      <c r="P12" s="240"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="242"/>
+      <c r="S12" s="242"/>
+      <c r="T12" s="242"/>
+      <c r="U12" s="242"/>
+      <c r="V12" s="242"/>
+      <c r="W12" s="242"/>
+      <c r="X12" s="242"/>
+      <c r="Y12" s="242"/>
+      <c r="Z12" s="242"/>
+      <c r="AA12" s="242"/>
+      <c r="AB12" s="242"/>
+      <c r="AC12" s="242"/>
+      <c r="AD12" s="242"/>
+      <c r="AE12" s="243"/>
+      <c r="AF12" s="238"/>
+      <c r="AG12" s="239"/>
+      <c r="AH12" s="239"/>
+      <c r="AI12" s="240"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="177"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="180"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="182"/>
-      <c r="L13" s="182"/>
-      <c r="M13" s="182"/>
-      <c r="N13" s="182"/>
-      <c r="O13" s="182"/>
-      <c r="P13" s="183"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
-      <c r="S13" s="185"/>
-      <c r="T13" s="185"/>
-      <c r="U13" s="185"/>
-      <c r="V13" s="185"/>
-      <c r="W13" s="185"/>
-      <c r="X13" s="185"/>
-      <c r="Y13" s="185"/>
-      <c r="Z13" s="185"/>
-      <c r="AA13" s="185"/>
-      <c r="AB13" s="185"/>
-      <c r="AC13" s="185"/>
-      <c r="AD13" s="185"/>
-      <c r="AE13" s="186"/>
-      <c r="AF13" s="181"/>
-      <c r="AG13" s="182"/>
-      <c r="AH13" s="182"/>
-      <c r="AI13" s="183"/>
+      <c r="B13" s="232"/>
+      <c r="C13" s="233"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="237"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="238"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
+      <c r="M13" s="239"/>
+      <c r="N13" s="239"/>
+      <c r="O13" s="239"/>
+      <c r="P13" s="240"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="242"/>
+      <c r="S13" s="242"/>
+      <c r="T13" s="242"/>
+      <c r="U13" s="242"/>
+      <c r="V13" s="242"/>
+      <c r="W13" s="242"/>
+      <c r="X13" s="242"/>
+      <c r="Y13" s="242"/>
+      <c r="Z13" s="242"/>
+      <c r="AA13" s="242"/>
+      <c r="AB13" s="242"/>
+      <c r="AC13" s="242"/>
+      <c r="AD13" s="242"/>
+      <c r="AE13" s="243"/>
+      <c r="AF13" s="238"/>
+      <c r="AG13" s="239"/>
+      <c r="AH13" s="239"/>
+      <c r="AI13" s="240"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="175"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="179"/>
-      <c r="G14" s="175"/>
-      <c r="H14" s="180"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="181"/>
-      <c r="K14" s="182"/>
-      <c r="L14" s="182"/>
-      <c r="M14" s="182"/>
-      <c r="N14" s="182"/>
-      <c r="O14" s="182"/>
-      <c r="P14" s="183"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
-      <c r="S14" s="185"/>
-      <c r="T14" s="185"/>
-      <c r="U14" s="185"/>
-      <c r="V14" s="185"/>
-      <c r="W14" s="185"/>
-      <c r="X14" s="185"/>
-      <c r="Y14" s="185"/>
-      <c r="Z14" s="185"/>
-      <c r="AA14" s="185"/>
-      <c r="AB14" s="185"/>
-      <c r="AC14" s="185"/>
-      <c r="AD14" s="185"/>
-      <c r="AE14" s="186"/>
-      <c r="AF14" s="181"/>
-      <c r="AG14" s="182"/>
-      <c r="AH14" s="182"/>
-      <c r="AI14" s="183"/>
+      <c r="B14" s="232"/>
+      <c r="C14" s="233"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="237"/>
+      <c r="I14" s="233"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="239"/>
+      <c r="L14" s="239"/>
+      <c r="M14" s="239"/>
+      <c r="N14" s="239"/>
+      <c r="O14" s="239"/>
+      <c r="P14" s="240"/>
+      <c r="Q14" s="241"/>
+      <c r="R14" s="242"/>
+      <c r="S14" s="242"/>
+      <c r="T14" s="242"/>
+      <c r="U14" s="242"/>
+      <c r="V14" s="242"/>
+      <c r="W14" s="242"/>
+      <c r="X14" s="242"/>
+      <c r="Y14" s="242"/>
+      <c r="Z14" s="242"/>
+      <c r="AA14" s="242"/>
+      <c r="AB14" s="242"/>
+      <c r="AC14" s="242"/>
+      <c r="AD14" s="242"/>
+      <c r="AE14" s="243"/>
+      <c r="AF14" s="238"/>
+      <c r="AG14" s="239"/>
+      <c r="AH14" s="239"/>
+      <c r="AI14" s="240"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="175"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="177"/>
-      <c r="E15" s="178"/>
-      <c r="F15" s="179"/>
-      <c r="G15" s="175"/>
-      <c r="H15" s="180"/>
-      <c r="I15" s="176"/>
-      <c r="J15" s="181"/>
-      <c r="K15" s="182"/>
-      <c r="L15" s="182"/>
-      <c r="M15" s="182"/>
-      <c r="N15" s="182"/>
-      <c r="O15" s="182"/>
-      <c r="P15" s="183"/>
-      <c r="Q15" s="184"/>
-      <c r="R15" s="185"/>
-      <c r="S15" s="185"/>
-      <c r="T15" s="185"/>
-      <c r="U15" s="185"/>
-      <c r="V15" s="185"/>
-      <c r="W15" s="185"/>
-      <c r="X15" s="185"/>
-      <c r="Y15" s="185"/>
-      <c r="Z15" s="185"/>
-      <c r="AA15" s="185"/>
-      <c r="AB15" s="185"/>
-      <c r="AC15" s="185"/>
-      <c r="AD15" s="185"/>
-      <c r="AE15" s="186"/>
-      <c r="AF15" s="181"/>
-      <c r="AG15" s="182"/>
-      <c r="AH15" s="182"/>
-      <c r="AI15" s="183"/>
+      <c r="B15" s="232"/>
+      <c r="C15" s="233"/>
+      <c r="D15" s="234"/>
+      <c r="E15" s="235"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="232"/>
+      <c r="H15" s="237"/>
+      <c r="I15" s="233"/>
+      <c r="J15" s="238"/>
+      <c r="K15" s="239"/>
+      <c r="L15" s="239"/>
+      <c r="M15" s="239"/>
+      <c r="N15" s="239"/>
+      <c r="O15" s="239"/>
+      <c r="P15" s="240"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="242"/>
+      <c r="S15" s="242"/>
+      <c r="T15" s="242"/>
+      <c r="U15" s="242"/>
+      <c r="V15" s="242"/>
+      <c r="W15" s="242"/>
+      <c r="X15" s="242"/>
+      <c r="Y15" s="242"/>
+      <c r="Z15" s="242"/>
+      <c r="AA15" s="242"/>
+      <c r="AB15" s="242"/>
+      <c r="AC15" s="242"/>
+      <c r="AD15" s="242"/>
+      <c r="AE15" s="243"/>
+      <c r="AF15" s="238"/>
+      <c r="AG15" s="239"/>
+      <c r="AH15" s="239"/>
+      <c r="AI15" s="240"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="175"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="177"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="179"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="180"/>
-      <c r="I16" s="176"/>
-      <c r="J16" s="181"/>
-      <c r="K16" s="182"/>
-      <c r="L16" s="182"/>
-      <c r="M16" s="182"/>
-      <c r="N16" s="182"/>
-      <c r="O16" s="182"/>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="184"/>
-      <c r="R16" s="185"/>
-      <c r="S16" s="185"/>
-      <c r="T16" s="185"/>
-      <c r="U16" s="185"/>
-      <c r="V16" s="185"/>
-      <c r="W16" s="185"/>
-      <c r="X16" s="185"/>
-      <c r="Y16" s="185"/>
-      <c r="Z16" s="185"/>
-      <c r="AA16" s="185"/>
-      <c r="AB16" s="185"/>
-      <c r="AC16" s="185"/>
-      <c r="AD16" s="185"/>
-      <c r="AE16" s="186"/>
-      <c r="AF16" s="181"/>
-      <c r="AG16" s="182"/>
-      <c r="AH16" s="182"/>
-      <c r="AI16" s="183"/>
+      <c r="B16" s="232"/>
+      <c r="C16" s="233"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="233"/>
+      <c r="J16" s="238"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="239"/>
+      <c r="M16" s="239"/>
+      <c r="N16" s="239"/>
+      <c r="O16" s="239"/>
+      <c r="P16" s="240"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="242"/>
+      <c r="S16" s="242"/>
+      <c r="T16" s="242"/>
+      <c r="U16" s="242"/>
+      <c r="V16" s="242"/>
+      <c r="W16" s="242"/>
+      <c r="X16" s="242"/>
+      <c r="Y16" s="242"/>
+      <c r="Z16" s="242"/>
+      <c r="AA16" s="242"/>
+      <c r="AB16" s="242"/>
+      <c r="AC16" s="242"/>
+      <c r="AD16" s="242"/>
+      <c r="AE16" s="243"/>
+      <c r="AF16" s="238"/>
+      <c r="AG16" s="239"/>
+      <c r="AH16" s="239"/>
+      <c r="AI16" s="240"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="175"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="175"/>
-      <c r="H17" s="180"/>
-      <c r="I17" s="176"/>
-      <c r="J17" s="181"/>
-      <c r="K17" s="182"/>
-      <c r="L17" s="182"/>
-      <c r="M17" s="182"/>
-      <c r="N17" s="182"/>
-      <c r="O17" s="182"/>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="184"/>
-      <c r="R17" s="185"/>
-      <c r="S17" s="185"/>
-      <c r="T17" s="185"/>
-      <c r="U17" s="185"/>
-      <c r="V17" s="185"/>
-      <c r="W17" s="185"/>
-      <c r="X17" s="185"/>
-      <c r="Y17" s="185"/>
-      <c r="Z17" s="185"/>
-      <c r="AA17" s="185"/>
-      <c r="AB17" s="185"/>
-      <c r="AC17" s="185"/>
-      <c r="AD17" s="185"/>
-      <c r="AE17" s="186"/>
-      <c r="AF17" s="181"/>
-      <c r="AG17" s="182"/>
-      <c r="AH17" s="182"/>
-      <c r="AI17" s="183"/>
+      <c r="B17" s="232"/>
+      <c r="C17" s="233"/>
+      <c r="D17" s="234"/>
+      <c r="E17" s="235"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="232"/>
+      <c r="H17" s="237"/>
+      <c r="I17" s="233"/>
+      <c r="J17" s="238"/>
+      <c r="K17" s="239"/>
+      <c r="L17" s="239"/>
+      <c r="M17" s="239"/>
+      <c r="N17" s="239"/>
+      <c r="O17" s="239"/>
+      <c r="P17" s="240"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="242"/>
+      <c r="S17" s="242"/>
+      <c r="T17" s="242"/>
+      <c r="U17" s="242"/>
+      <c r="V17" s="242"/>
+      <c r="W17" s="242"/>
+      <c r="X17" s="242"/>
+      <c r="Y17" s="242"/>
+      <c r="Z17" s="242"/>
+      <c r="AA17" s="242"/>
+      <c r="AB17" s="242"/>
+      <c r="AC17" s="242"/>
+      <c r="AD17" s="242"/>
+      <c r="AE17" s="243"/>
+      <c r="AF17" s="238"/>
+      <c r="AG17" s="239"/>
+      <c r="AH17" s="239"/>
+      <c r="AI17" s="240"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="175"/>
-      <c r="C18" s="176"/>
-      <c r="D18" s="177"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="179"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="180"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="181"/>
-      <c r="K18" s="182"/>
-      <c r="L18" s="182"/>
-      <c r="M18" s="182"/>
-      <c r="N18" s="182"/>
-      <c r="O18" s="182"/>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="184"/>
-      <c r="R18" s="185"/>
-      <c r="S18" s="185"/>
-      <c r="T18" s="185"/>
-      <c r="U18" s="185"/>
-      <c r="V18" s="185"/>
-      <c r="W18" s="185"/>
-      <c r="X18" s="185"/>
-      <c r="Y18" s="185"/>
-      <c r="Z18" s="185"/>
-      <c r="AA18" s="185"/>
-      <c r="AB18" s="185"/>
-      <c r="AC18" s="185"/>
-      <c r="AD18" s="185"/>
-      <c r="AE18" s="186"/>
-      <c r="AF18" s="181"/>
-      <c r="AG18" s="182"/>
-      <c r="AH18" s="182"/>
-      <c r="AI18" s="183"/>
+      <c r="B18" s="232"/>
+      <c r="C18" s="233"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="237"/>
+      <c r="I18" s="233"/>
+      <c r="J18" s="238"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
+      <c r="M18" s="239"/>
+      <c r="N18" s="239"/>
+      <c r="O18" s="239"/>
+      <c r="P18" s="240"/>
+      <c r="Q18" s="241"/>
+      <c r="R18" s="242"/>
+      <c r="S18" s="242"/>
+      <c r="T18" s="242"/>
+      <c r="U18" s="242"/>
+      <c r="V18" s="242"/>
+      <c r="W18" s="242"/>
+      <c r="X18" s="242"/>
+      <c r="Y18" s="242"/>
+      <c r="Z18" s="242"/>
+      <c r="AA18" s="242"/>
+      <c r="AB18" s="242"/>
+      <c r="AC18" s="242"/>
+      <c r="AD18" s="242"/>
+      <c r="AE18" s="243"/>
+      <c r="AF18" s="238"/>
+      <c r="AG18" s="239"/>
+      <c r="AH18" s="239"/>
+      <c r="AI18" s="240"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="177"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="179"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="180"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="181"/>
-      <c r="K19" s="182"/>
-      <c r="L19" s="182"/>
-      <c r="M19" s="182"/>
-      <c r="N19" s="182"/>
-      <c r="O19" s="182"/>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="184"/>
-      <c r="R19" s="185"/>
-      <c r="S19" s="185"/>
-      <c r="T19" s="185"/>
-      <c r="U19" s="185"/>
-      <c r="V19" s="185"/>
-      <c r="W19" s="185"/>
-      <c r="X19" s="185"/>
-      <c r="Y19" s="185"/>
-      <c r="Z19" s="185"/>
-      <c r="AA19" s="185"/>
-      <c r="AB19" s="185"/>
-      <c r="AC19" s="185"/>
-      <c r="AD19" s="185"/>
-      <c r="AE19" s="186"/>
-      <c r="AF19" s="181"/>
-      <c r="AG19" s="182"/>
-      <c r="AH19" s="182"/>
-      <c r="AI19" s="183"/>
+      <c r="B19" s="232"/>
+      <c r="C19" s="233"/>
+      <c r="D19" s="234"/>
+      <c r="E19" s="235"/>
+      <c r="F19" s="236"/>
+      <c r="G19" s="232"/>
+      <c r="H19" s="237"/>
+      <c r="I19" s="233"/>
+      <c r="J19" s="238"/>
+      <c r="K19" s="239"/>
+      <c r="L19" s="239"/>
+      <c r="M19" s="239"/>
+      <c r="N19" s="239"/>
+      <c r="O19" s="239"/>
+      <c r="P19" s="240"/>
+      <c r="Q19" s="241"/>
+      <c r="R19" s="242"/>
+      <c r="S19" s="242"/>
+      <c r="T19" s="242"/>
+      <c r="U19" s="242"/>
+      <c r="V19" s="242"/>
+      <c r="W19" s="242"/>
+      <c r="X19" s="242"/>
+      <c r="Y19" s="242"/>
+      <c r="Z19" s="242"/>
+      <c r="AA19" s="242"/>
+      <c r="AB19" s="242"/>
+      <c r="AC19" s="242"/>
+      <c r="AD19" s="242"/>
+      <c r="AE19" s="243"/>
+      <c r="AF19" s="238"/>
+      <c r="AG19" s="239"/>
+      <c r="AH19" s="239"/>
+      <c r="AI19" s="240"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="176"/>
-      <c r="D20" s="177"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="180"/>
-      <c r="I20" s="176"/>
-      <c r="J20" s="181"/>
-      <c r="K20" s="182"/>
-      <c r="L20" s="182"/>
-      <c r="M20" s="182"/>
-      <c r="N20" s="182"/>
-      <c r="O20" s="182"/>
-      <c r="P20" s="183"/>
-      <c r="Q20" s="184"/>
-      <c r="R20" s="185"/>
-      <c r="S20" s="185"/>
-      <c r="T20" s="185"/>
-      <c r="U20" s="185"/>
-      <c r="V20" s="185"/>
-      <c r="W20" s="185"/>
-      <c r="X20" s="185"/>
-      <c r="Y20" s="185"/>
-      <c r="Z20" s="185"/>
-      <c r="AA20" s="185"/>
-      <c r="AB20" s="185"/>
-      <c r="AC20" s="185"/>
-      <c r="AD20" s="185"/>
-      <c r="AE20" s="186"/>
-      <c r="AF20" s="181"/>
-      <c r="AG20" s="182"/>
-      <c r="AH20" s="182"/>
-      <c r="AI20" s="183"/>
+      <c r="B20" s="232"/>
+      <c r="C20" s="233"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="235"/>
+      <c r="F20" s="236"/>
+      <c r="G20" s="232"/>
+      <c r="H20" s="237"/>
+      <c r="I20" s="233"/>
+      <c r="J20" s="238"/>
+      <c r="K20" s="239"/>
+      <c r="L20" s="239"/>
+      <c r="M20" s="239"/>
+      <c r="N20" s="239"/>
+      <c r="O20" s="239"/>
+      <c r="P20" s="240"/>
+      <c r="Q20" s="241"/>
+      <c r="R20" s="242"/>
+      <c r="S20" s="242"/>
+      <c r="T20" s="242"/>
+      <c r="U20" s="242"/>
+      <c r="V20" s="242"/>
+      <c r="W20" s="242"/>
+      <c r="X20" s="242"/>
+      <c r="Y20" s="242"/>
+      <c r="Z20" s="242"/>
+      <c r="AA20" s="242"/>
+      <c r="AB20" s="242"/>
+      <c r="AC20" s="242"/>
+      <c r="AD20" s="242"/>
+      <c r="AE20" s="243"/>
+      <c r="AF20" s="238"/>
+      <c r="AG20" s="239"/>
+      <c r="AH20" s="239"/>
+      <c r="AI20" s="240"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="177"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="180"/>
-      <c r="I21" s="176"/>
-      <c r="J21" s="181"/>
-      <c r="K21" s="182"/>
-      <c r="L21" s="182"/>
-      <c r="M21" s="182"/>
-      <c r="N21" s="182"/>
-      <c r="O21" s="182"/>
-      <c r="P21" s="183"/>
-      <c r="Q21" s="184"/>
-      <c r="R21" s="185"/>
-      <c r="S21" s="185"/>
-      <c r="T21" s="185"/>
-      <c r="U21" s="185"/>
-      <c r="V21" s="185"/>
-      <c r="W21" s="185"/>
-      <c r="X21" s="185"/>
-      <c r="Y21" s="185"/>
-      <c r="Z21" s="185"/>
-      <c r="AA21" s="185"/>
-      <c r="AB21" s="185"/>
-      <c r="AC21" s="185"/>
-      <c r="AD21" s="185"/>
-      <c r="AE21" s="186"/>
-      <c r="AF21" s="181"/>
-      <c r="AG21" s="182"/>
-      <c r="AH21" s="182"/>
-      <c r="AI21" s="183"/>
+      <c r="B21" s="232"/>
+      <c r="C21" s="233"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="232"/>
+      <c r="H21" s="237"/>
+      <c r="I21" s="233"/>
+      <c r="J21" s="238"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="239"/>
+      <c r="M21" s="239"/>
+      <c r="N21" s="239"/>
+      <c r="O21" s="239"/>
+      <c r="P21" s="240"/>
+      <c r="Q21" s="241"/>
+      <c r="R21" s="242"/>
+      <c r="S21" s="242"/>
+      <c r="T21" s="242"/>
+      <c r="U21" s="242"/>
+      <c r="V21" s="242"/>
+      <c r="W21" s="242"/>
+      <c r="X21" s="242"/>
+      <c r="Y21" s="242"/>
+      <c r="Z21" s="242"/>
+      <c r="AA21" s="242"/>
+      <c r="AB21" s="242"/>
+      <c r="AC21" s="242"/>
+      <c r="AD21" s="242"/>
+      <c r="AE21" s="243"/>
+      <c r="AF21" s="238"/>
+      <c r="AG21" s="239"/>
+      <c r="AH21" s="239"/>
+      <c r="AI21" s="240"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="175"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="177"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="180"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="181"/>
-      <c r="K22" s="182"/>
-      <c r="L22" s="182"/>
-      <c r="M22" s="182"/>
-      <c r="N22" s="182"/>
-      <c r="O22" s="182"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="184"/>
-      <c r="R22" s="185"/>
-      <c r="S22" s="185"/>
-      <c r="T22" s="185"/>
-      <c r="U22" s="185"/>
-      <c r="V22" s="185"/>
-      <c r="W22" s="185"/>
-      <c r="X22" s="185"/>
-      <c r="Y22" s="185"/>
-      <c r="Z22" s="185"/>
-      <c r="AA22" s="185"/>
-      <c r="AB22" s="185"/>
-      <c r="AC22" s="185"/>
-      <c r="AD22" s="185"/>
-      <c r="AE22" s="186"/>
-      <c r="AF22" s="181"/>
-      <c r="AG22" s="182"/>
-      <c r="AH22" s="182"/>
-      <c r="AI22" s="183"/>
+      <c r="B22" s="232"/>
+      <c r="C22" s="233"/>
+      <c r="D22" s="234"/>
+      <c r="E22" s="235"/>
+      <c r="F22" s="236"/>
+      <c r="G22" s="232"/>
+      <c r="H22" s="237"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="238"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="239"/>
+      <c r="M22" s="239"/>
+      <c r="N22" s="239"/>
+      <c r="O22" s="239"/>
+      <c r="P22" s="240"/>
+      <c r="Q22" s="241"/>
+      <c r="R22" s="242"/>
+      <c r="S22" s="242"/>
+      <c r="T22" s="242"/>
+      <c r="U22" s="242"/>
+      <c r="V22" s="242"/>
+      <c r="W22" s="242"/>
+      <c r="X22" s="242"/>
+      <c r="Y22" s="242"/>
+      <c r="Z22" s="242"/>
+      <c r="AA22" s="242"/>
+      <c r="AB22" s="242"/>
+      <c r="AC22" s="242"/>
+      <c r="AD22" s="242"/>
+      <c r="AE22" s="243"/>
+      <c r="AF22" s="238"/>
+      <c r="AG22" s="239"/>
+      <c r="AH22" s="239"/>
+      <c r="AI22" s="240"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="175"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="177"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="180"/>
-      <c r="I23" s="176"/>
-      <c r="J23" s="181"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="182"/>
-      <c r="M23" s="182"/>
-      <c r="N23" s="182"/>
-      <c r="O23" s="182"/>
-      <c r="P23" s="183"/>
-      <c r="Q23" s="184"/>
-      <c r="R23" s="185"/>
-      <c r="S23" s="185"/>
-      <c r="T23" s="185"/>
-      <c r="U23" s="185"/>
-      <c r="V23" s="185"/>
-      <c r="W23" s="185"/>
-      <c r="X23" s="185"/>
-      <c r="Y23" s="185"/>
-      <c r="Z23" s="185"/>
-      <c r="AA23" s="185"/>
-      <c r="AB23" s="185"/>
-      <c r="AC23" s="185"/>
-      <c r="AD23" s="185"/>
-      <c r="AE23" s="186"/>
-      <c r="AF23" s="181"/>
-      <c r="AG23" s="182"/>
-      <c r="AH23" s="182"/>
-      <c r="AI23" s="183"/>
+      <c r="B23" s="232"/>
+      <c r="C23" s="233"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="235"/>
+      <c r="F23" s="236"/>
+      <c r="G23" s="232"/>
+      <c r="H23" s="237"/>
+      <c r="I23" s="233"/>
+      <c r="J23" s="238"/>
+      <c r="K23" s="239"/>
+      <c r="L23" s="239"/>
+      <c r="M23" s="239"/>
+      <c r="N23" s="239"/>
+      <c r="O23" s="239"/>
+      <c r="P23" s="240"/>
+      <c r="Q23" s="241"/>
+      <c r="R23" s="242"/>
+      <c r="S23" s="242"/>
+      <c r="T23" s="242"/>
+      <c r="U23" s="242"/>
+      <c r="V23" s="242"/>
+      <c r="W23" s="242"/>
+      <c r="X23" s="242"/>
+      <c r="Y23" s="242"/>
+      <c r="Z23" s="242"/>
+      <c r="AA23" s="242"/>
+      <c r="AB23" s="242"/>
+      <c r="AC23" s="242"/>
+      <c r="AD23" s="242"/>
+      <c r="AE23" s="243"/>
+      <c r="AF23" s="238"/>
+      <c r="AG23" s="239"/>
+      <c r="AH23" s="239"/>
+      <c r="AI23" s="240"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="175"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="177"/>
-      <c r="E24" s="178"/>
-      <c r="F24" s="179"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="180"/>
-      <c r="I24" s="176"/>
-      <c r="J24" s="181"/>
-      <c r="K24" s="182"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="182"/>
-      <c r="N24" s="182"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="183"/>
-      <c r="Q24" s="184"/>
-      <c r="R24" s="185"/>
-      <c r="S24" s="185"/>
-      <c r="T24" s="185"/>
-      <c r="U24" s="185"/>
-      <c r="V24" s="185"/>
-      <c r="W24" s="185"/>
-      <c r="X24" s="185"/>
-      <c r="Y24" s="185"/>
-      <c r="Z24" s="185"/>
-      <c r="AA24" s="185"/>
-      <c r="AB24" s="185"/>
-      <c r="AC24" s="185"/>
-      <c r="AD24" s="185"/>
-      <c r="AE24" s="186"/>
-      <c r="AF24" s="181"/>
-      <c r="AG24" s="182"/>
-      <c r="AH24" s="182"/>
-      <c r="AI24" s="183"/>
+      <c r="B24" s="232"/>
+      <c r="C24" s="233"/>
+      <c r="D24" s="234"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="236"/>
+      <c r="G24" s="232"/>
+      <c r="H24" s="237"/>
+      <c r="I24" s="233"/>
+      <c r="J24" s="238"/>
+      <c r="K24" s="239"/>
+      <c r="L24" s="239"/>
+      <c r="M24" s="239"/>
+      <c r="N24" s="239"/>
+      <c r="O24" s="239"/>
+      <c r="P24" s="240"/>
+      <c r="Q24" s="241"/>
+      <c r="R24" s="242"/>
+      <c r="S24" s="242"/>
+      <c r="T24" s="242"/>
+      <c r="U24" s="242"/>
+      <c r="V24" s="242"/>
+      <c r="W24" s="242"/>
+      <c r="X24" s="242"/>
+      <c r="Y24" s="242"/>
+      <c r="Z24" s="242"/>
+      <c r="AA24" s="242"/>
+      <c r="AB24" s="242"/>
+      <c r="AC24" s="242"/>
+      <c r="AD24" s="242"/>
+      <c r="AE24" s="243"/>
+      <c r="AF24" s="238"/>
+      <c r="AG24" s="239"/>
+      <c r="AH24" s="239"/>
+      <c r="AI24" s="240"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="177"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="179"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="180"/>
-      <c r="I25" s="176"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="182"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="182"/>
-      <c r="N25" s="182"/>
-      <c r="O25" s="182"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="184"/>
-      <c r="R25" s="185"/>
-      <c r="S25" s="185"/>
-      <c r="T25" s="185"/>
-      <c r="U25" s="185"/>
-      <c r="V25" s="185"/>
-      <c r="W25" s="185"/>
-      <c r="X25" s="185"/>
-      <c r="Y25" s="185"/>
-      <c r="Z25" s="185"/>
-      <c r="AA25" s="185"/>
-      <c r="AB25" s="185"/>
-      <c r="AC25" s="185"/>
-      <c r="AD25" s="185"/>
-      <c r="AE25" s="186"/>
-      <c r="AF25" s="181"/>
-      <c r="AG25" s="182"/>
-      <c r="AH25" s="182"/>
-      <c r="AI25" s="183"/>
+      <c r="B25" s="232"/>
+      <c r="C25" s="233"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="236"/>
+      <c r="G25" s="232"/>
+      <c r="H25" s="237"/>
+      <c r="I25" s="233"/>
+      <c r="J25" s="238"/>
+      <c r="K25" s="239"/>
+      <c r="L25" s="239"/>
+      <c r="M25" s="239"/>
+      <c r="N25" s="239"/>
+      <c r="O25" s="239"/>
+      <c r="P25" s="240"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="242"/>
+      <c r="S25" s="242"/>
+      <c r="T25" s="242"/>
+      <c r="U25" s="242"/>
+      <c r="V25" s="242"/>
+      <c r="W25" s="242"/>
+      <c r="X25" s="242"/>
+      <c r="Y25" s="242"/>
+      <c r="Z25" s="242"/>
+      <c r="AA25" s="242"/>
+      <c r="AB25" s="242"/>
+      <c r="AC25" s="242"/>
+      <c r="AD25" s="242"/>
+      <c r="AE25" s="243"/>
+      <c r="AF25" s="238"/>
+      <c r="AG25" s="239"/>
+      <c r="AH25" s="239"/>
+      <c r="AI25" s="240"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="175"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="177"/>
-      <c r="E26" s="178"/>
-      <c r="F26" s="179"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="180"/>
-      <c r="I26" s="176"/>
-      <c r="J26" s="181"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="182"/>
-      <c r="M26" s="182"/>
-      <c r="N26" s="182"/>
-      <c r="O26" s="182"/>
-      <c r="P26" s="183"/>
-      <c r="Q26" s="184"/>
-      <c r="R26" s="185"/>
-      <c r="S26" s="185"/>
-      <c r="T26" s="185"/>
-      <c r="U26" s="185"/>
-      <c r="V26" s="185"/>
-      <c r="W26" s="185"/>
-      <c r="X26" s="185"/>
-      <c r="Y26" s="185"/>
-      <c r="Z26" s="185"/>
-      <c r="AA26" s="185"/>
-      <c r="AB26" s="185"/>
-      <c r="AC26" s="185"/>
-      <c r="AD26" s="185"/>
-      <c r="AE26" s="186"/>
-      <c r="AF26" s="181"/>
-      <c r="AG26" s="182"/>
-      <c r="AH26" s="182"/>
-      <c r="AI26" s="183"/>
+      <c r="B26" s="232"/>
+      <c r="C26" s="233"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="236"/>
+      <c r="G26" s="232"/>
+      <c r="H26" s="237"/>
+      <c r="I26" s="233"/>
+      <c r="J26" s="238"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
+      <c r="M26" s="239"/>
+      <c r="N26" s="239"/>
+      <c r="O26" s="239"/>
+      <c r="P26" s="240"/>
+      <c r="Q26" s="241"/>
+      <c r="R26" s="242"/>
+      <c r="S26" s="242"/>
+      <c r="T26" s="242"/>
+      <c r="U26" s="242"/>
+      <c r="V26" s="242"/>
+      <c r="W26" s="242"/>
+      <c r="X26" s="242"/>
+      <c r="Y26" s="242"/>
+      <c r="Z26" s="242"/>
+      <c r="AA26" s="242"/>
+      <c r="AB26" s="242"/>
+      <c r="AC26" s="242"/>
+      <c r="AD26" s="242"/>
+      <c r="AE26" s="243"/>
+      <c r="AF26" s="238"/>
+      <c r="AG26" s="239"/>
+      <c r="AH26" s="239"/>
+      <c r="AI26" s="240"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="175"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="179"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="180"/>
-      <c r="I27" s="176"/>
-      <c r="J27" s="181"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="182"/>
-      <c r="M27" s="182"/>
-      <c r="N27" s="182"/>
-      <c r="O27" s="182"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="184"/>
-      <c r="R27" s="185"/>
-      <c r="S27" s="185"/>
-      <c r="T27" s="185"/>
-      <c r="U27" s="185"/>
-      <c r="V27" s="185"/>
-      <c r="W27" s="185"/>
-      <c r="X27" s="185"/>
-      <c r="Y27" s="185"/>
-      <c r="Z27" s="185"/>
-      <c r="AA27" s="185"/>
-      <c r="AB27" s="185"/>
-      <c r="AC27" s="185"/>
-      <c r="AD27" s="185"/>
-      <c r="AE27" s="186"/>
-      <c r="AF27" s="181"/>
-      <c r="AG27" s="182"/>
-      <c r="AH27" s="182"/>
-      <c r="AI27" s="183"/>
+      <c r="B27" s="232"/>
+      <c r="C27" s="233"/>
+      <c r="D27" s="234"/>
+      <c r="E27" s="235"/>
+      <c r="F27" s="236"/>
+      <c r="G27" s="232"/>
+      <c r="H27" s="237"/>
+      <c r="I27" s="233"/>
+      <c r="J27" s="238"/>
+      <c r="K27" s="239"/>
+      <c r="L27" s="239"/>
+      <c r="M27" s="239"/>
+      <c r="N27" s="239"/>
+      <c r="O27" s="239"/>
+      <c r="P27" s="240"/>
+      <c r="Q27" s="241"/>
+      <c r="R27" s="242"/>
+      <c r="S27" s="242"/>
+      <c r="T27" s="242"/>
+      <c r="U27" s="242"/>
+      <c r="V27" s="242"/>
+      <c r="W27" s="242"/>
+      <c r="X27" s="242"/>
+      <c r="Y27" s="242"/>
+      <c r="Z27" s="242"/>
+      <c r="AA27" s="242"/>
+      <c r="AB27" s="242"/>
+      <c r="AC27" s="242"/>
+      <c r="AD27" s="242"/>
+      <c r="AE27" s="243"/>
+      <c r="AF27" s="238"/>
+      <c r="AG27" s="239"/>
+      <c r="AH27" s="239"/>
+      <c r="AI27" s="240"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="175"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="177"/>
-      <c r="E28" s="178"/>
-      <c r="F28" s="179"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="180"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="181"/>
-      <c r="K28" s="182"/>
-      <c r="L28" s="182"/>
-      <c r="M28" s="182"/>
-      <c r="N28" s="182"/>
-      <c r="O28" s="182"/>
-      <c r="P28" s="183"/>
-      <c r="Q28" s="184"/>
-      <c r="R28" s="185"/>
-      <c r="S28" s="185"/>
-      <c r="T28" s="185"/>
-      <c r="U28" s="185"/>
-      <c r="V28" s="185"/>
-      <c r="W28" s="185"/>
-      <c r="X28" s="185"/>
-      <c r="Y28" s="185"/>
-      <c r="Z28" s="185"/>
-      <c r="AA28" s="185"/>
-      <c r="AB28" s="185"/>
-      <c r="AC28" s="185"/>
-      <c r="AD28" s="185"/>
-      <c r="AE28" s="186"/>
-      <c r="AF28" s="181"/>
-      <c r="AG28" s="182"/>
-      <c r="AH28" s="182"/>
-      <c r="AI28" s="183"/>
+      <c r="B28" s="232"/>
+      <c r="C28" s="233"/>
+      <c r="D28" s="234"/>
+      <c r="E28" s="235"/>
+      <c r="F28" s="236"/>
+      <c r="G28" s="232"/>
+      <c r="H28" s="237"/>
+      <c r="I28" s="233"/>
+      <c r="J28" s="238"/>
+      <c r="K28" s="239"/>
+      <c r="L28" s="239"/>
+      <c r="M28" s="239"/>
+      <c r="N28" s="239"/>
+      <c r="O28" s="239"/>
+      <c r="P28" s="240"/>
+      <c r="Q28" s="241"/>
+      <c r="R28" s="242"/>
+      <c r="S28" s="242"/>
+      <c r="T28" s="242"/>
+      <c r="U28" s="242"/>
+      <c r="V28" s="242"/>
+      <c r="W28" s="242"/>
+      <c r="X28" s="242"/>
+      <c r="Y28" s="242"/>
+      <c r="Z28" s="242"/>
+      <c r="AA28" s="242"/>
+      <c r="AB28" s="242"/>
+      <c r="AC28" s="242"/>
+      <c r="AD28" s="242"/>
+      <c r="AE28" s="243"/>
+      <c r="AF28" s="238"/>
+      <c r="AG28" s="239"/>
+      <c r="AH28" s="239"/>
+      <c r="AI28" s="240"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="175"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="177"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="180"/>
-      <c r="I29" s="176"/>
-      <c r="J29" s="181"/>
-      <c r="K29" s="182"/>
-      <c r="L29" s="182"/>
-      <c r="M29" s="182"/>
-      <c r="N29" s="182"/>
-      <c r="O29" s="182"/>
-      <c r="P29" s="183"/>
-      <c r="Q29" s="184"/>
-      <c r="R29" s="185"/>
-      <c r="S29" s="185"/>
-      <c r="T29" s="185"/>
-      <c r="U29" s="185"/>
-      <c r="V29" s="185"/>
-      <c r="W29" s="185"/>
-      <c r="X29" s="185"/>
-      <c r="Y29" s="185"/>
-      <c r="Z29" s="185"/>
-      <c r="AA29" s="185"/>
-      <c r="AB29" s="185"/>
-      <c r="AC29" s="185"/>
-      <c r="AD29" s="185"/>
-      <c r="AE29" s="186"/>
-      <c r="AF29" s="181"/>
-      <c r="AG29" s="182"/>
-      <c r="AH29" s="182"/>
-      <c r="AI29" s="183"/>
+      <c r="B29" s="232"/>
+      <c r="C29" s="233"/>
+      <c r="D29" s="234"/>
+      <c r="E29" s="235"/>
+      <c r="F29" s="236"/>
+      <c r="G29" s="232"/>
+      <c r="H29" s="237"/>
+      <c r="I29" s="233"/>
+      <c r="J29" s="238"/>
+      <c r="K29" s="239"/>
+      <c r="L29" s="239"/>
+      <c r="M29" s="239"/>
+      <c r="N29" s="239"/>
+      <c r="O29" s="239"/>
+      <c r="P29" s="240"/>
+      <c r="Q29" s="241"/>
+      <c r="R29" s="242"/>
+      <c r="S29" s="242"/>
+      <c r="T29" s="242"/>
+      <c r="U29" s="242"/>
+      <c r="V29" s="242"/>
+      <c r="W29" s="242"/>
+      <c r="X29" s="242"/>
+      <c r="Y29" s="242"/>
+      <c r="Z29" s="242"/>
+      <c r="AA29" s="242"/>
+      <c r="AB29" s="242"/>
+      <c r="AC29" s="242"/>
+      <c r="AD29" s="242"/>
+      <c r="AE29" s="243"/>
+      <c r="AF29" s="238"/>
+      <c r="AG29" s="239"/>
+      <c r="AH29" s="239"/>
+      <c r="AI29" s="240"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="175"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="177"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="180"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="181"/>
-      <c r="K30" s="182"/>
-      <c r="L30" s="182"/>
-      <c r="M30" s="182"/>
-      <c r="N30" s="182"/>
-      <c r="O30" s="182"/>
-      <c r="P30" s="183"/>
-      <c r="Q30" s="184"/>
-      <c r="R30" s="185"/>
-      <c r="S30" s="185"/>
-      <c r="T30" s="185"/>
-      <c r="U30" s="185"/>
-      <c r="V30" s="185"/>
-      <c r="W30" s="185"/>
-      <c r="X30" s="185"/>
-      <c r="Y30" s="185"/>
-      <c r="Z30" s="185"/>
-      <c r="AA30" s="185"/>
-      <c r="AB30" s="185"/>
-      <c r="AC30" s="185"/>
-      <c r="AD30" s="185"/>
-      <c r="AE30" s="186"/>
-      <c r="AF30" s="181"/>
-      <c r="AG30" s="182"/>
-      <c r="AH30" s="182"/>
-      <c r="AI30" s="183"/>
+      <c r="B30" s="232"/>
+      <c r="C30" s="233"/>
+      <c r="D30" s="234"/>
+      <c r="E30" s="235"/>
+      <c r="F30" s="236"/>
+      <c r="G30" s="232"/>
+      <c r="H30" s="237"/>
+      <c r="I30" s="233"/>
+      <c r="J30" s="238"/>
+      <c r="K30" s="239"/>
+      <c r="L30" s="239"/>
+      <c r="M30" s="239"/>
+      <c r="N30" s="239"/>
+      <c r="O30" s="239"/>
+      <c r="P30" s="240"/>
+      <c r="Q30" s="241"/>
+      <c r="R30" s="242"/>
+      <c r="S30" s="242"/>
+      <c r="T30" s="242"/>
+      <c r="U30" s="242"/>
+      <c r="V30" s="242"/>
+      <c r="W30" s="242"/>
+      <c r="X30" s="242"/>
+      <c r="Y30" s="242"/>
+      <c r="Z30" s="242"/>
+      <c r="AA30" s="242"/>
+      <c r="AB30" s="242"/>
+      <c r="AC30" s="242"/>
+      <c r="AD30" s="242"/>
+      <c r="AE30" s="243"/>
+      <c r="AF30" s="238"/>
+      <c r="AG30" s="239"/>
+      <c r="AH30" s="239"/>
+      <c r="AI30" s="240"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="175"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="177"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="180"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="182"/>
-      <c r="L31" s="182"/>
-      <c r="M31" s="182"/>
-      <c r="N31" s="182"/>
-      <c r="O31" s="182"/>
-      <c r="P31" s="183"/>
-      <c r="Q31" s="184"/>
-      <c r="R31" s="185"/>
-      <c r="S31" s="185"/>
-      <c r="T31" s="185"/>
-      <c r="U31" s="185"/>
-      <c r="V31" s="185"/>
-      <c r="W31" s="185"/>
-      <c r="X31" s="185"/>
-      <c r="Y31" s="185"/>
-      <c r="Z31" s="185"/>
-      <c r="AA31" s="185"/>
-      <c r="AB31" s="185"/>
-      <c r="AC31" s="185"/>
-      <c r="AD31" s="185"/>
-      <c r="AE31" s="186"/>
-      <c r="AF31" s="181"/>
-      <c r="AG31" s="182"/>
-      <c r="AH31" s="182"/>
-      <c r="AI31" s="183"/>
+      <c r="B31" s="232"/>
+      <c r="C31" s="233"/>
+      <c r="D31" s="234"/>
+      <c r="E31" s="235"/>
+      <c r="F31" s="236"/>
+      <c r="G31" s="232"/>
+      <c r="H31" s="237"/>
+      <c r="I31" s="233"/>
+      <c r="J31" s="238"/>
+      <c r="K31" s="239"/>
+      <c r="L31" s="239"/>
+      <c r="M31" s="239"/>
+      <c r="N31" s="239"/>
+      <c r="O31" s="239"/>
+      <c r="P31" s="240"/>
+      <c r="Q31" s="241"/>
+      <c r="R31" s="242"/>
+      <c r="S31" s="242"/>
+      <c r="T31" s="242"/>
+      <c r="U31" s="242"/>
+      <c r="V31" s="242"/>
+      <c r="W31" s="242"/>
+      <c r="X31" s="242"/>
+      <c r="Y31" s="242"/>
+      <c r="Z31" s="242"/>
+      <c r="AA31" s="242"/>
+      <c r="AB31" s="242"/>
+      <c r="AC31" s="242"/>
+      <c r="AD31" s="242"/>
+      <c r="AE31" s="243"/>
+      <c r="AF31" s="238"/>
+      <c r="AG31" s="239"/>
+      <c r="AH31" s="239"/>
+      <c r="AI31" s="240"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="175"/>
-      <c r="C32" s="176"/>
-      <c r="D32" s="177"/>
-      <c r="E32" s="178"/>
-      <c r="F32" s="179"/>
-      <c r="G32" s="175"/>
-      <c r="H32" s="180"/>
-      <c r="I32" s="176"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="187"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="182"/>
-      <c r="N32" s="182"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="183"/>
-      <c r="Q32" s="184"/>
-      <c r="R32" s="185"/>
-      <c r="S32" s="185"/>
-      <c r="T32" s="185"/>
-      <c r="U32" s="185"/>
-      <c r="V32" s="185"/>
-      <c r="W32" s="185"/>
-      <c r="X32" s="185"/>
-      <c r="Y32" s="185"/>
-      <c r="Z32" s="185"/>
-      <c r="AA32" s="185"/>
-      <c r="AB32" s="185"/>
-      <c r="AC32" s="185"/>
-      <c r="AD32" s="185"/>
-      <c r="AE32" s="186"/>
-      <c r="AF32" s="181"/>
-      <c r="AG32" s="182"/>
-      <c r="AH32" s="182"/>
-      <c r="AI32" s="183"/>
+      <c r="B32" s="232"/>
+      <c r="C32" s="233"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="235"/>
+      <c r="F32" s="236"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="237"/>
+      <c r="I32" s="233"/>
+      <c r="J32" s="238"/>
+      <c r="K32" s="244"/>
+      <c r="L32" s="239"/>
+      <c r="M32" s="239"/>
+      <c r="N32" s="239"/>
+      <c r="O32" s="239"/>
+      <c r="P32" s="240"/>
+      <c r="Q32" s="241"/>
+      <c r="R32" s="242"/>
+      <c r="S32" s="242"/>
+      <c r="T32" s="242"/>
+      <c r="U32" s="242"/>
+      <c r="V32" s="242"/>
+      <c r="W32" s="242"/>
+      <c r="X32" s="242"/>
+      <c r="Y32" s="242"/>
+      <c r="Z32" s="242"/>
+      <c r="AA32" s="242"/>
+      <c r="AB32" s="242"/>
+      <c r="AC32" s="242"/>
+      <c r="AD32" s="242"/>
+      <c r="AE32" s="243"/>
+      <c r="AF32" s="238"/>
+      <c r="AG32" s="239"/>
+      <c r="AH32" s="239"/>
+      <c r="AI32" s="240"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="175"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="177"/>
-      <c r="E33" s="178"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="180"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="182"/>
-      <c r="L33" s="182"/>
-      <c r="M33" s="182"/>
-      <c r="N33" s="182"/>
-      <c r="O33" s="182"/>
-      <c r="P33" s="183"/>
-      <c r="Q33" s="184"/>
-      <c r="R33" s="185"/>
-      <c r="S33" s="185"/>
-      <c r="T33" s="185"/>
-      <c r="U33" s="185"/>
-      <c r="V33" s="185"/>
-      <c r="W33" s="185"/>
-      <c r="X33" s="185"/>
-      <c r="Y33" s="185"/>
-      <c r="Z33" s="185"/>
-      <c r="AA33" s="185"/>
-      <c r="AB33" s="185"/>
-      <c r="AC33" s="185"/>
-      <c r="AD33" s="185"/>
-      <c r="AE33" s="186"/>
-      <c r="AF33" s="181"/>
-      <c r="AG33" s="182"/>
-      <c r="AH33" s="182"/>
-      <c r="AI33" s="183"/>
+      <c r="B33" s="232"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="236"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="237"/>
+      <c r="I33" s="233"/>
+      <c r="J33" s="238"/>
+      <c r="K33" s="239"/>
+      <c r="L33" s="239"/>
+      <c r="M33" s="239"/>
+      <c r="N33" s="239"/>
+      <c r="O33" s="239"/>
+      <c r="P33" s="240"/>
+      <c r="Q33" s="241"/>
+      <c r="R33" s="242"/>
+      <c r="S33" s="242"/>
+      <c r="T33" s="242"/>
+      <c r="U33" s="242"/>
+      <c r="V33" s="242"/>
+      <c r="W33" s="242"/>
+      <c r="X33" s="242"/>
+      <c r="Y33" s="242"/>
+      <c r="Z33" s="242"/>
+      <c r="AA33" s="242"/>
+      <c r="AB33" s="242"/>
+      <c r="AC33" s="242"/>
+      <c r="AD33" s="242"/>
+      <c r="AE33" s="243"/>
+      <c r="AF33" s="238"/>
+      <c r="AG33" s="239"/>
+      <c r="AH33" s="239"/>
+      <c r="AI33" s="240"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -14294,161 +14452,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51AC6ED-40D5-4EE2-8ED6-5D06584C1E0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A084154A-592F-41F3-BF33-FCF33A599CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="574">
   <si>
     <t>システム機能設計書</t>
     <rPh sb="4" eb="6">
@@ -6393,34 +6393,6 @@
       <t>ニュウリョク</t>
     </rPh>
     <rPh sb="19" eb="21">
-      <t>バアイ</t>
-    </rPh>
-    <phoneticPr fontId="20"/>
-  </si>
-  <si>
-    <t>数値項目に有効範囲の下限値＋1が入力された場合、エラーとなること。</t>
-    <rPh sb="0" eb="2">
-      <t>スウチ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>コウモク</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ユウコウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ハンイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カゲン</t>
-    </rPh>
-    <rPh sb="12" eb="13">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
       <t>バアイ</t>
     </rPh>
     <phoneticPr fontId="20"/>
@@ -8669,6 +8641,108 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8775,108 +8849,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13045,57 +13017,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="215" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="184" t="s">
+      <c r="B1" s="216"/>
+      <c r="C1" s="216"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="218" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="185"/>
-      <c r="N1" s="186"/>
-      <c r="O1" s="190" t="s">
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="220"/>
+      <c r="O1" s="224" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="191"/>
-      <c r="Q1" s="191"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="199" t="s">
-        <v>573</v>
-      </c>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="200"/>
-      <c r="Y1" s="200"/>
-      <c r="Z1" s="201"/>
-      <c r="AA1" s="181" t="s">
+      <c r="P1" s="225"/>
+      <c r="Q1" s="225"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="233" t="s">
+        <v>572</v>
+      </c>
+      <c r="T1" s="234"/>
+      <c r="U1" s="234"/>
+      <c r="V1" s="234"/>
+      <c r="W1" s="234"/>
+      <c r="X1" s="234"/>
+      <c r="Y1" s="234"/>
+      <c r="Z1" s="235"/>
+      <c r="AA1" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" s="183"/>
-      <c r="AC1" s="208" t="str">
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="242" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="209"/>
-      <c r="AE1" s="209"/>
-      <c r="AF1" s="210"/>
-      <c r="AG1" s="175">
+      <c r="AD1" s="243"/>
+      <c r="AE1" s="243"/>
+      <c r="AF1" s="244"/>
+      <c r="AG1" s="209">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="176"/>
-      <c r="AI1" s="177"/>
+      <c r="AH1" s="210"/>
+      <c r="AI1" s="211"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -13103,53 +13075,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="184" t="s">
+      <c r="B2" s="216"/>
+      <c r="C2" s="216"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="186"/>
-      <c r="O2" s="193"/>
-      <c r="P2" s="194"/>
-      <c r="Q2" s="194"/>
-      <c r="R2" s="195"/>
-      <c r="S2" s="202"/>
-      <c r="T2" s="203"/>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
-      <c r="W2" s="203"/>
-      <c r="X2" s="203"/>
-      <c r="Y2" s="203"/>
-      <c r="Z2" s="204"/>
-      <c r="AA2" s="181" t="s">
+      <c r="F2" s="219"/>
+      <c r="G2" s="219"/>
+      <c r="H2" s="219"/>
+      <c r="I2" s="219"/>
+      <c r="J2" s="219"/>
+      <c r="K2" s="219"/>
+      <c r="L2" s="219"/>
+      <c r="M2" s="219"/>
+      <c r="N2" s="220"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="228"/>
+      <c r="Q2" s="228"/>
+      <c r="R2" s="229"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="215" t="s">
         <v>43</v>
       </c>
-      <c r="AB2" s="183"/>
-      <c r="AC2" s="187" t="str">
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="221" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="188"/>
-      <c r="AE2" s="188"/>
-      <c r="AF2" s="189"/>
-      <c r="AG2" s="175">
+      <c r="AD2" s="222"/>
+      <c r="AE2" s="222"/>
+      <c r="AF2" s="223"/>
+      <c r="AG2" s="209">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="176"/>
-      <c r="AI2" s="177"/>
+      <c r="AH2" s="210"/>
+      <c r="AI2" s="211"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -13157,45 +13129,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="181" t="s">
+      <c r="A3" s="215" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="184" t="s">
+      <c r="B3" s="216"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="218" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
-      <c r="L3" s="185"/>
-      <c r="M3" s="185"/>
-      <c r="N3" s="186"/>
-      <c r="O3" s="196"/>
-      <c r="P3" s="197"/>
-      <c r="Q3" s="197"/>
-      <c r="R3" s="198"/>
-      <c r="S3" s="205"/>
-      <c r="T3" s="206"/>
-      <c r="U3" s="206"/>
-      <c r="V3" s="206"/>
-      <c r="W3" s="206"/>
-      <c r="X3" s="206"/>
-      <c r="Y3" s="206"/>
-      <c r="Z3" s="207"/>
-      <c r="AA3" s="181"/>
-      <c r="AB3" s="183"/>
-      <c r="AC3" s="208"/>
-      <c r="AD3" s="209"/>
-      <c r="AE3" s="209"/>
-      <c r="AF3" s="210"/>
-      <c r="AG3" s="175"/>
-      <c r="AH3" s="176"/>
-      <c r="AI3" s="177"/>
+      <c r="F3" s="219"/>
+      <c r="G3" s="219"/>
+      <c r="H3" s="219"/>
+      <c r="I3" s="219"/>
+      <c r="J3" s="219"/>
+      <c r="K3" s="219"/>
+      <c r="L3" s="219"/>
+      <c r="M3" s="219"/>
+      <c r="N3" s="220"/>
+      <c r="O3" s="230"/>
+      <c r="P3" s="231"/>
+      <c r="Q3" s="231"/>
+      <c r="R3" s="232"/>
+      <c r="S3" s="239"/>
+      <c r="T3" s="240"/>
+      <c r="U3" s="240"/>
+      <c r="V3" s="240"/>
+      <c r="W3" s="240"/>
+      <c r="X3" s="240"/>
+      <c r="Y3" s="240"/>
+      <c r="Z3" s="241"/>
+      <c r="AA3" s="215"/>
+      <c r="AB3" s="217"/>
+      <c r="AC3" s="242"/>
+      <c r="AD3" s="243"/>
+      <c r="AE3" s="243"/>
+      <c r="AF3" s="244"/>
+      <c r="AG3" s="209"/>
+      <c r="AH3" s="210"/>
+      <c r="AI3" s="211"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -13232,97 +13204,97 @@
       <c r="A7" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="178" t="s">
+      <c r="B7" s="212" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="179"/>
-      <c r="D7" s="178" t="s">
+      <c r="C7" s="213"/>
+      <c r="D7" s="212" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="180"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="178" t="s">
+      <c r="E7" s="214"/>
+      <c r="F7" s="213"/>
+      <c r="G7" s="212" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="180"/>
-      <c r="I7" s="179"/>
-      <c r="J7" s="178" t="s">
+      <c r="H7" s="214"/>
+      <c r="I7" s="213"/>
+      <c r="J7" s="212" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="180"/>
-      <c r="L7" s="180"/>
-      <c r="M7" s="180"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="180"/>
-      <c r="P7" s="179"/>
-      <c r="Q7" s="178" t="s">
+      <c r="K7" s="214"/>
+      <c r="L7" s="214"/>
+      <c r="M7" s="214"/>
+      <c r="N7" s="214"/>
+      <c r="O7" s="214"/>
+      <c r="P7" s="213"/>
+      <c r="Q7" s="212" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="180"/>
-      <c r="S7" s="180"/>
-      <c r="T7" s="180"/>
-      <c r="U7" s="180"/>
-      <c r="V7" s="180"/>
-      <c r="W7" s="180"/>
-      <c r="X7" s="180"/>
-      <c r="Y7" s="180"/>
-      <c r="Z7" s="180"/>
-      <c r="AA7" s="180"/>
-      <c r="AB7" s="180"/>
-      <c r="AC7" s="180"/>
-      <c r="AD7" s="180"/>
-      <c r="AE7" s="179"/>
-      <c r="AF7" s="178" t="s">
+      <c r="R7" s="214"/>
+      <c r="S7" s="214"/>
+      <c r="T7" s="214"/>
+      <c r="U7" s="214"/>
+      <c r="V7" s="214"/>
+      <c r="W7" s="214"/>
+      <c r="X7" s="214"/>
+      <c r="Y7" s="214"/>
+      <c r="Z7" s="214"/>
+      <c r="AA7" s="214"/>
+      <c r="AB7" s="214"/>
+      <c r="AC7" s="214"/>
+      <c r="AD7" s="214"/>
+      <c r="AE7" s="213"/>
+      <c r="AF7" s="212" t="s">
         <v>51</v>
       </c>
-      <c r="AG7" s="180"/>
-      <c r="AH7" s="180"/>
-      <c r="AI7" s="179"/>
+      <c r="AG7" s="214"/>
+      <c r="AH7" s="214"/>
+      <c r="AI7" s="213"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="223" t="s">
+      <c r="B8" s="200" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="224"/>
-      <c r="D8" s="225">
+      <c r="C8" s="201"/>
+      <c r="D8" s="202">
         <v>43336</v>
       </c>
-      <c r="E8" s="226"/>
-      <c r="F8" s="227"/>
-      <c r="G8" s="223" t="s">
+      <c r="E8" s="203"/>
+      <c r="F8" s="204"/>
+      <c r="G8" s="200" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="228"/>
-      <c r="I8" s="224"/>
-      <c r="J8" s="229" t="s">
+      <c r="H8" s="205"/>
+      <c r="I8" s="201"/>
+      <c r="J8" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="230"/>
-      <c r="L8" s="230"/>
-      <c r="M8" s="230"/>
-      <c r="N8" s="230"/>
-      <c r="O8" s="230"/>
-      <c r="P8" s="231"/>
-      <c r="Q8" s="229" t="s">
+      <c r="K8" s="207"/>
+      <c r="L8" s="207"/>
+      <c r="M8" s="207"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
+      <c r="P8" s="208"/>
+      <c r="Q8" s="206" t="s">
         <v>60</v>
       </c>
-      <c r="R8" s="230"/>
-      <c r="S8" s="230"/>
-      <c r="T8" s="230"/>
-      <c r="U8" s="230"/>
-      <c r="V8" s="230"/>
-      <c r="W8" s="230"/>
-      <c r="X8" s="230"/>
-      <c r="Y8" s="230"/>
-      <c r="Z8" s="230"/>
-      <c r="AA8" s="230"/>
-      <c r="AB8" s="230"/>
-      <c r="AC8" s="230"/>
-      <c r="AD8" s="230"/>
-      <c r="AE8" s="231"/>
+      <c r="R8" s="207"/>
+      <c r="S8" s="207"/>
+      <c r="T8" s="207"/>
+      <c r="U8" s="207"/>
+      <c r="V8" s="207"/>
+      <c r="W8" s="207"/>
+      <c r="X8" s="207"/>
+      <c r="Y8" s="207"/>
+      <c r="Z8" s="207"/>
+      <c r="AA8" s="207"/>
+      <c r="AB8" s="207"/>
+      <c r="AC8" s="207"/>
+      <c r="AD8" s="207"/>
+      <c r="AE8" s="208"/>
       <c r="AF8" s="25" t="s">
         <v>61</v>
       </c>
@@ -13334,1101 +13306,946 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="211" t="s">
+      <c r="B9" s="188" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="212"/>
-      <c r="D9" s="213">
+      <c r="C9" s="189"/>
+      <c r="D9" s="190">
         <v>44852</v>
       </c>
-      <c r="E9" s="214"/>
-      <c r="F9" s="215"/>
-      <c r="G9" s="213" t="s">
+      <c r="E9" s="191"/>
+      <c r="F9" s="192"/>
+      <c r="G9" s="190" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="216"/>
-      <c r="I9" s="212"/>
-      <c r="J9" s="217" t="s">
+      <c r="H9" s="193"/>
+      <c r="I9" s="189"/>
+      <c r="J9" s="194" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="218"/>
-      <c r="L9" s="218"/>
-      <c r="M9" s="218"/>
-      <c r="N9" s="218"/>
-      <c r="O9" s="218"/>
-      <c r="P9" s="219"/>
-      <c r="Q9" s="217" t="s">
+      <c r="K9" s="195"/>
+      <c r="L9" s="195"/>
+      <c r="M9" s="195"/>
+      <c r="N9" s="195"/>
+      <c r="O9" s="195"/>
+      <c r="P9" s="196"/>
+      <c r="Q9" s="194" t="s">
         <v>67</v>
       </c>
-      <c r="R9" s="220"/>
-      <c r="S9" s="220"/>
-      <c r="T9" s="220"/>
-      <c r="U9" s="220"/>
-      <c r="V9" s="220"/>
-      <c r="W9" s="220"/>
-      <c r="X9" s="220"/>
-      <c r="Y9" s="220"/>
-      <c r="Z9" s="220"/>
-      <c r="AA9" s="220"/>
-      <c r="AB9" s="220"/>
-      <c r="AC9" s="220"/>
-      <c r="AD9" s="220"/>
-      <c r="AE9" s="221"/>
-      <c r="AF9" s="222" t="s">
+      <c r="R9" s="197"/>
+      <c r="S9" s="197"/>
+      <c r="T9" s="197"/>
+      <c r="U9" s="197"/>
+      <c r="V9" s="197"/>
+      <c r="W9" s="197"/>
+      <c r="X9" s="197"/>
+      <c r="Y9" s="197"/>
+      <c r="Z9" s="197"/>
+      <c r="AA9" s="197"/>
+      <c r="AB9" s="197"/>
+      <c r="AC9" s="197"/>
+      <c r="AD9" s="197"/>
+      <c r="AE9" s="198"/>
+      <c r="AF9" s="199" t="s">
         <v>61</v>
       </c>
-      <c r="AG9" s="218"/>
-      <c r="AH9" s="218"/>
-      <c r="AI9" s="219"/>
+      <c r="AG9" s="195"/>
+      <c r="AH9" s="195"/>
+      <c r="AI9" s="196"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="232"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="232"/>
-      <c r="H10" s="237"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
-      <c r="M10" s="239"/>
-      <c r="N10" s="239"/>
-      <c r="O10" s="239"/>
-      <c r="P10" s="240"/>
-      <c r="Q10" s="241"/>
-      <c r="R10" s="242"/>
-      <c r="S10" s="242"/>
-      <c r="T10" s="242"/>
-      <c r="U10" s="242"/>
-      <c r="V10" s="242"/>
-      <c r="W10" s="242"/>
-      <c r="X10" s="242"/>
-      <c r="Y10" s="242"/>
-      <c r="Z10" s="242"/>
-      <c r="AA10" s="242"/>
-      <c r="AB10" s="242"/>
-      <c r="AC10" s="242"/>
-      <c r="AD10" s="242"/>
-      <c r="AE10" s="243"/>
-      <c r="AF10" s="238"/>
-      <c r="AG10" s="239"/>
-      <c r="AH10" s="239"/>
-      <c r="AI10" s="240"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="177"/>
+      <c r="E10" s="178"/>
+      <c r="F10" s="179"/>
+      <c r="G10" s="175"/>
+      <c r="H10" s="180"/>
+      <c r="I10" s="176"/>
+      <c r="J10" s="181"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="182"/>
+      <c r="M10" s="182"/>
+      <c r="N10" s="182"/>
+      <c r="O10" s="182"/>
+      <c r="P10" s="183"/>
+      <c r="Q10" s="184"/>
+      <c r="R10" s="185"/>
+      <c r="S10" s="185"/>
+      <c r="T10" s="185"/>
+      <c r="U10" s="185"/>
+      <c r="V10" s="185"/>
+      <c r="W10" s="185"/>
+      <c r="X10" s="185"/>
+      <c r="Y10" s="185"/>
+      <c r="Z10" s="185"/>
+      <c r="AA10" s="185"/>
+      <c r="AB10" s="185"/>
+      <c r="AC10" s="185"/>
+      <c r="AD10" s="185"/>
+      <c r="AE10" s="186"/>
+      <c r="AF10" s="181"/>
+      <c r="AG10" s="182"/>
+      <c r="AH10" s="182"/>
+      <c r="AI10" s="183"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="232"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="235"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="232"/>
-      <c r="H11" s="237"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
-      <c r="M11" s="239"/>
-      <c r="N11" s="239"/>
-      <c r="O11" s="239"/>
-      <c r="P11" s="240"/>
-      <c r="Q11" s="241"/>
-      <c r="R11" s="242"/>
-      <c r="S11" s="242"/>
-      <c r="T11" s="242"/>
-      <c r="U11" s="242"/>
-      <c r="V11" s="242"/>
-      <c r="W11" s="242"/>
-      <c r="X11" s="242"/>
-      <c r="Y11" s="242"/>
-      <c r="Z11" s="242"/>
-      <c r="AA11" s="242"/>
-      <c r="AB11" s="242"/>
-      <c r="AC11" s="242"/>
-      <c r="AD11" s="242"/>
-      <c r="AE11" s="243"/>
-      <c r="AF11" s="238"/>
-      <c r="AG11" s="239"/>
-      <c r="AH11" s="239"/>
-      <c r="AI11" s="240"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="176"/>
+      <c r="D11" s="177"/>
+      <c r="E11" s="178"/>
+      <c r="F11" s="179"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="180"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="181"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="182"/>
+      <c r="M11" s="182"/>
+      <c r="N11" s="182"/>
+      <c r="O11" s="182"/>
+      <c r="P11" s="183"/>
+      <c r="Q11" s="184"/>
+      <c r="R11" s="185"/>
+      <c r="S11" s="185"/>
+      <c r="T11" s="185"/>
+      <c r="U11" s="185"/>
+      <c r="V11" s="185"/>
+      <c r="W11" s="185"/>
+      <c r="X11" s="185"/>
+      <c r="Y11" s="185"/>
+      <c r="Z11" s="185"/>
+      <c r="AA11" s="185"/>
+      <c r="AB11" s="185"/>
+      <c r="AC11" s="185"/>
+      <c r="AD11" s="185"/>
+      <c r="AE11" s="186"/>
+      <c r="AF11" s="181"/>
+      <c r="AG11" s="182"/>
+      <c r="AH11" s="182"/>
+      <c r="AI11" s="183"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="232"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="235"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="232"/>
-      <c r="H12" s="237"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="239"/>
-      <c r="L12" s="239"/>
-      <c r="M12" s="239"/>
-      <c r="N12" s="239"/>
-      <c r="O12" s="239"/>
-      <c r="P12" s="240"/>
-      <c r="Q12" s="241"/>
-      <c r="R12" s="242"/>
-      <c r="S12" s="242"/>
-      <c r="T12" s="242"/>
-      <c r="U12" s="242"/>
-      <c r="V12" s="242"/>
-      <c r="W12" s="242"/>
-      <c r="X12" s="242"/>
-      <c r="Y12" s="242"/>
-      <c r="Z12" s="242"/>
-      <c r="AA12" s="242"/>
-      <c r="AB12" s="242"/>
-      <c r="AC12" s="242"/>
-      <c r="AD12" s="242"/>
-      <c r="AE12" s="243"/>
-      <c r="AF12" s="238"/>
-      <c r="AG12" s="239"/>
-      <c r="AH12" s="239"/>
-      <c r="AI12" s="240"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="177"/>
+      <c r="E12" s="178"/>
+      <c r="F12" s="179"/>
+      <c r="G12" s="175"/>
+      <c r="H12" s="180"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="181"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="182"/>
+      <c r="M12" s="182"/>
+      <c r="N12" s="182"/>
+      <c r="O12" s="182"/>
+      <c r="P12" s="183"/>
+      <c r="Q12" s="184"/>
+      <c r="R12" s="185"/>
+      <c r="S12" s="185"/>
+      <c r="T12" s="185"/>
+      <c r="U12" s="185"/>
+      <c r="V12" s="185"/>
+      <c r="W12" s="185"/>
+      <c r="X12" s="185"/>
+      <c r="Y12" s="185"/>
+      <c r="Z12" s="185"/>
+      <c r="AA12" s="185"/>
+      <c r="AB12" s="185"/>
+      <c r="AC12" s="185"/>
+      <c r="AD12" s="185"/>
+      <c r="AE12" s="186"/>
+      <c r="AF12" s="181"/>
+      <c r="AG12" s="182"/>
+      <c r="AH12" s="182"/>
+      <c r="AI12" s="183"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="232"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="236"/>
-      <c r="G13" s="232"/>
-      <c r="H13" s="237"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
-      <c r="M13" s="239"/>
-      <c r="N13" s="239"/>
-      <c r="O13" s="239"/>
-      <c r="P13" s="240"/>
-      <c r="Q13" s="241"/>
-      <c r="R13" s="242"/>
-      <c r="S13" s="242"/>
-      <c r="T13" s="242"/>
-      <c r="U13" s="242"/>
-      <c r="V13" s="242"/>
-      <c r="W13" s="242"/>
-      <c r="X13" s="242"/>
-      <c r="Y13" s="242"/>
-      <c r="Z13" s="242"/>
-      <c r="AA13" s="242"/>
-      <c r="AB13" s="242"/>
-      <c r="AC13" s="242"/>
-      <c r="AD13" s="242"/>
-      <c r="AE13" s="243"/>
-      <c r="AF13" s="238"/>
-      <c r="AG13" s="239"/>
-      <c r="AH13" s="239"/>
-      <c r="AI13" s="240"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="177"/>
+      <c r="E13" s="178"/>
+      <c r="F13" s="179"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="180"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="182"/>
+      <c r="L13" s="182"/>
+      <c r="M13" s="182"/>
+      <c r="N13" s="182"/>
+      <c r="O13" s="182"/>
+      <c r="P13" s="183"/>
+      <c r="Q13" s="184"/>
+      <c r="R13" s="185"/>
+      <c r="S13" s="185"/>
+      <c r="T13" s="185"/>
+      <c r="U13" s="185"/>
+      <c r="V13" s="185"/>
+      <c r="W13" s="185"/>
+      <c r="X13" s="185"/>
+      <c r="Y13" s="185"/>
+      <c r="Z13" s="185"/>
+      <c r="AA13" s="185"/>
+      <c r="AB13" s="185"/>
+      <c r="AC13" s="185"/>
+      <c r="AD13" s="185"/>
+      <c r="AE13" s="186"/>
+      <c r="AF13" s="181"/>
+      <c r="AG13" s="182"/>
+      <c r="AH13" s="182"/>
+      <c r="AI13" s="183"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="232"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="235"/>
-      <c r="F14" s="236"/>
-      <c r="G14" s="232"/>
-      <c r="H14" s="237"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="239"/>
-      <c r="L14" s="239"/>
-      <c r="M14" s="239"/>
-      <c r="N14" s="239"/>
-      <c r="O14" s="239"/>
-      <c r="P14" s="240"/>
-      <c r="Q14" s="241"/>
-      <c r="R14" s="242"/>
-      <c r="S14" s="242"/>
-      <c r="T14" s="242"/>
-      <c r="U14" s="242"/>
-      <c r="V14" s="242"/>
-      <c r="W14" s="242"/>
-      <c r="X14" s="242"/>
-      <c r="Y14" s="242"/>
-      <c r="Z14" s="242"/>
-      <c r="AA14" s="242"/>
-      <c r="AB14" s="242"/>
-      <c r="AC14" s="242"/>
-      <c r="AD14" s="242"/>
-      <c r="AE14" s="243"/>
-      <c r="AF14" s="238"/>
-      <c r="AG14" s="239"/>
-      <c r="AH14" s="239"/>
-      <c r="AI14" s="240"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="177"/>
+      <c r="E14" s="178"/>
+      <c r="F14" s="179"/>
+      <c r="G14" s="175"/>
+      <c r="H14" s="180"/>
+      <c r="I14" s="176"/>
+      <c r="J14" s="181"/>
+      <c r="K14" s="182"/>
+      <c r="L14" s="182"/>
+      <c r="M14" s="182"/>
+      <c r="N14" s="182"/>
+      <c r="O14" s="182"/>
+      <c r="P14" s="183"/>
+      <c r="Q14" s="184"/>
+      <c r="R14" s="185"/>
+      <c r="S14" s="185"/>
+      <c r="T14" s="185"/>
+      <c r="U14" s="185"/>
+      <c r="V14" s="185"/>
+      <c r="W14" s="185"/>
+      <c r="X14" s="185"/>
+      <c r="Y14" s="185"/>
+      <c r="Z14" s="185"/>
+      <c r="AA14" s="185"/>
+      <c r="AB14" s="185"/>
+      <c r="AC14" s="185"/>
+      <c r="AD14" s="185"/>
+      <c r="AE14" s="186"/>
+      <c r="AF14" s="181"/>
+      <c r="AG14" s="182"/>
+      <c r="AH14" s="182"/>
+      <c r="AI14" s="183"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="232"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="235"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="232"/>
-      <c r="H15" s="237"/>
-      <c r="I15" s="233"/>
-      <c r="J15" s="238"/>
-      <c r="K15" s="239"/>
-      <c r="L15" s="239"/>
-      <c r="M15" s="239"/>
-      <c r="N15" s="239"/>
-      <c r="O15" s="239"/>
-      <c r="P15" s="240"/>
-      <c r="Q15" s="241"/>
-      <c r="R15" s="242"/>
-      <c r="S15" s="242"/>
-      <c r="T15" s="242"/>
-      <c r="U15" s="242"/>
-      <c r="V15" s="242"/>
-      <c r="W15" s="242"/>
-      <c r="X15" s="242"/>
-      <c r="Y15" s="242"/>
-      <c r="Z15" s="242"/>
-      <c r="AA15" s="242"/>
-      <c r="AB15" s="242"/>
-      <c r="AC15" s="242"/>
-      <c r="AD15" s="242"/>
-      <c r="AE15" s="243"/>
-      <c r="AF15" s="238"/>
-      <c r="AG15" s="239"/>
-      <c r="AH15" s="239"/>
-      <c r="AI15" s="240"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="177"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="175"/>
+      <c r="H15" s="180"/>
+      <c r="I15" s="176"/>
+      <c r="J15" s="181"/>
+      <c r="K15" s="182"/>
+      <c r="L15" s="182"/>
+      <c r="M15" s="182"/>
+      <c r="N15" s="182"/>
+      <c r="O15" s="182"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="184"/>
+      <c r="R15" s="185"/>
+      <c r="S15" s="185"/>
+      <c r="T15" s="185"/>
+      <c r="U15" s="185"/>
+      <c r="V15" s="185"/>
+      <c r="W15" s="185"/>
+      <c r="X15" s="185"/>
+      <c r="Y15" s="185"/>
+      <c r="Z15" s="185"/>
+      <c r="AA15" s="185"/>
+      <c r="AB15" s="185"/>
+      <c r="AC15" s="185"/>
+      <c r="AD15" s="185"/>
+      <c r="AE15" s="186"/>
+      <c r="AF15" s="181"/>
+      <c r="AG15" s="182"/>
+      <c r="AH15" s="182"/>
+      <c r="AI15" s="183"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="232"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="235"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="232"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="239"/>
-      <c r="L16" s="239"/>
-      <c r="M16" s="239"/>
-      <c r="N16" s="239"/>
-      <c r="O16" s="239"/>
-      <c r="P16" s="240"/>
-      <c r="Q16" s="241"/>
-      <c r="R16" s="242"/>
-      <c r="S16" s="242"/>
-      <c r="T16" s="242"/>
-      <c r="U16" s="242"/>
-      <c r="V16" s="242"/>
-      <c r="W16" s="242"/>
-      <c r="X16" s="242"/>
-      <c r="Y16" s="242"/>
-      <c r="Z16" s="242"/>
-      <c r="AA16" s="242"/>
-      <c r="AB16" s="242"/>
-      <c r="AC16" s="242"/>
-      <c r="AD16" s="242"/>
-      <c r="AE16" s="243"/>
-      <c r="AF16" s="238"/>
-      <c r="AG16" s="239"/>
-      <c r="AH16" s="239"/>
-      <c r="AI16" s="240"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="177"/>
+      <c r="E16" s="178"/>
+      <c r="F16" s="179"/>
+      <c r="G16" s="175"/>
+      <c r="H16" s="180"/>
+      <c r="I16" s="176"/>
+      <c r="J16" s="181"/>
+      <c r="K16" s="182"/>
+      <c r="L16" s="182"/>
+      <c r="M16" s="182"/>
+      <c r="N16" s="182"/>
+      <c r="O16" s="182"/>
+      <c r="P16" s="183"/>
+      <c r="Q16" s="184"/>
+      <c r="R16" s="185"/>
+      <c r="S16" s="185"/>
+      <c r="T16" s="185"/>
+      <c r="U16" s="185"/>
+      <c r="V16" s="185"/>
+      <c r="W16" s="185"/>
+      <c r="X16" s="185"/>
+      <c r="Y16" s="185"/>
+      <c r="Z16" s="185"/>
+      <c r="AA16" s="185"/>
+      <c r="AB16" s="185"/>
+      <c r="AC16" s="185"/>
+      <c r="AD16" s="185"/>
+      <c r="AE16" s="186"/>
+      <c r="AF16" s="181"/>
+      <c r="AG16" s="182"/>
+      <c r="AH16" s="182"/>
+      <c r="AI16" s="183"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="232"/>
-      <c r="C17" s="233"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="235"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="232"/>
-      <c r="H17" s="237"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="238"/>
-      <c r="K17" s="239"/>
-      <c r="L17" s="239"/>
-      <c r="M17" s="239"/>
-      <c r="N17" s="239"/>
-      <c r="O17" s="239"/>
-      <c r="P17" s="240"/>
-      <c r="Q17" s="241"/>
-      <c r="R17" s="242"/>
-      <c r="S17" s="242"/>
-      <c r="T17" s="242"/>
-      <c r="U17" s="242"/>
-      <c r="V17" s="242"/>
-      <c r="W17" s="242"/>
-      <c r="X17" s="242"/>
-      <c r="Y17" s="242"/>
-      <c r="Z17" s="242"/>
-      <c r="AA17" s="242"/>
-      <c r="AB17" s="242"/>
-      <c r="AC17" s="242"/>
-      <c r="AD17" s="242"/>
-      <c r="AE17" s="243"/>
-      <c r="AF17" s="238"/>
-      <c r="AG17" s="239"/>
-      <c r="AH17" s="239"/>
-      <c r="AI17" s="240"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="177"/>
+      <c r="E17" s="178"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="175"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="176"/>
+      <c r="J17" s="181"/>
+      <c r="K17" s="182"/>
+      <c r="L17" s="182"/>
+      <c r="M17" s="182"/>
+      <c r="N17" s="182"/>
+      <c r="O17" s="182"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="184"/>
+      <c r="R17" s="185"/>
+      <c r="S17" s="185"/>
+      <c r="T17" s="185"/>
+      <c r="U17" s="185"/>
+      <c r="V17" s="185"/>
+      <c r="W17" s="185"/>
+      <c r="X17" s="185"/>
+      <c r="Y17" s="185"/>
+      <c r="Z17" s="185"/>
+      <c r="AA17" s="185"/>
+      <c r="AB17" s="185"/>
+      <c r="AC17" s="185"/>
+      <c r="AD17" s="185"/>
+      <c r="AE17" s="186"/>
+      <c r="AF17" s="181"/>
+      <c r="AG17" s="182"/>
+      <c r="AH17" s="182"/>
+      <c r="AI17" s="183"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="232"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="234"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="232"/>
-      <c r="H18" s="237"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
-      <c r="M18" s="239"/>
-      <c r="N18" s="239"/>
-      <c r="O18" s="239"/>
-      <c r="P18" s="240"/>
-      <c r="Q18" s="241"/>
-      <c r="R18" s="242"/>
-      <c r="S18" s="242"/>
-      <c r="T18" s="242"/>
-      <c r="U18" s="242"/>
-      <c r="V18" s="242"/>
-      <c r="W18" s="242"/>
-      <c r="X18" s="242"/>
-      <c r="Y18" s="242"/>
-      <c r="Z18" s="242"/>
-      <c r="AA18" s="242"/>
-      <c r="AB18" s="242"/>
-      <c r="AC18" s="242"/>
-      <c r="AD18" s="242"/>
-      <c r="AE18" s="243"/>
-      <c r="AF18" s="238"/>
-      <c r="AG18" s="239"/>
-      <c r="AH18" s="239"/>
-      <c r="AI18" s="240"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="178"/>
+      <c r="F18" s="179"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="180"/>
+      <c r="I18" s="176"/>
+      <c r="J18" s="181"/>
+      <c r="K18" s="182"/>
+      <c r="L18" s="182"/>
+      <c r="M18" s="182"/>
+      <c r="N18" s="182"/>
+      <c r="O18" s="182"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="184"/>
+      <c r="R18" s="185"/>
+      <c r="S18" s="185"/>
+      <c r="T18" s="185"/>
+      <c r="U18" s="185"/>
+      <c r="V18" s="185"/>
+      <c r="W18" s="185"/>
+      <c r="X18" s="185"/>
+      <c r="Y18" s="185"/>
+      <c r="Z18" s="185"/>
+      <c r="AA18" s="185"/>
+      <c r="AB18" s="185"/>
+      <c r="AC18" s="185"/>
+      <c r="AD18" s="185"/>
+      <c r="AE18" s="186"/>
+      <c r="AF18" s="181"/>
+      <c r="AG18" s="182"/>
+      <c r="AH18" s="182"/>
+      <c r="AI18" s="183"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="232"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="234"/>
-      <c r="E19" s="235"/>
-      <c r="F19" s="236"/>
-      <c r="G19" s="232"/>
-      <c r="H19" s="237"/>
-      <c r="I19" s="233"/>
-      <c r="J19" s="238"/>
-      <c r="K19" s="239"/>
-      <c r="L19" s="239"/>
-      <c r="M19" s="239"/>
-      <c r="N19" s="239"/>
-      <c r="O19" s="239"/>
-      <c r="P19" s="240"/>
-      <c r="Q19" s="241"/>
-      <c r="R19" s="242"/>
-      <c r="S19" s="242"/>
-      <c r="T19" s="242"/>
-      <c r="U19" s="242"/>
-      <c r="V19" s="242"/>
-      <c r="W19" s="242"/>
-      <c r="X19" s="242"/>
-      <c r="Y19" s="242"/>
-      <c r="Z19" s="242"/>
-      <c r="AA19" s="242"/>
-      <c r="AB19" s="242"/>
-      <c r="AC19" s="242"/>
-      <c r="AD19" s="242"/>
-      <c r="AE19" s="243"/>
-      <c r="AF19" s="238"/>
-      <c r="AG19" s="239"/>
-      <c r="AH19" s="239"/>
-      <c r="AI19" s="240"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="179"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="180"/>
+      <c r="I19" s="176"/>
+      <c r="J19" s="181"/>
+      <c r="K19" s="182"/>
+      <c r="L19" s="182"/>
+      <c r="M19" s="182"/>
+      <c r="N19" s="182"/>
+      <c r="O19" s="182"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="184"/>
+      <c r="R19" s="185"/>
+      <c r="S19" s="185"/>
+      <c r="T19" s="185"/>
+      <c r="U19" s="185"/>
+      <c r="V19" s="185"/>
+      <c r="W19" s="185"/>
+      <c r="X19" s="185"/>
+      <c r="Y19" s="185"/>
+      <c r="Z19" s="185"/>
+      <c r="AA19" s="185"/>
+      <c r="AB19" s="185"/>
+      <c r="AC19" s="185"/>
+      <c r="AD19" s="185"/>
+      <c r="AE19" s="186"/>
+      <c r="AF19" s="181"/>
+      <c r="AG19" s="182"/>
+      <c r="AH19" s="182"/>
+      <c r="AI19" s="183"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="232"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="235"/>
-      <c r="F20" s="236"/>
-      <c r="G20" s="232"/>
-      <c r="H20" s="237"/>
-      <c r="I20" s="233"/>
-      <c r="J20" s="238"/>
-      <c r="K20" s="239"/>
-      <c r="L20" s="239"/>
-      <c r="M20" s="239"/>
-      <c r="N20" s="239"/>
-      <c r="O20" s="239"/>
-      <c r="P20" s="240"/>
-      <c r="Q20" s="241"/>
-      <c r="R20" s="242"/>
-      <c r="S20" s="242"/>
-      <c r="T20" s="242"/>
-      <c r="U20" s="242"/>
-      <c r="V20" s="242"/>
-      <c r="W20" s="242"/>
-      <c r="X20" s="242"/>
-      <c r="Y20" s="242"/>
-      <c r="Z20" s="242"/>
-      <c r="AA20" s="242"/>
-      <c r="AB20" s="242"/>
-      <c r="AC20" s="242"/>
-      <c r="AD20" s="242"/>
-      <c r="AE20" s="243"/>
-      <c r="AF20" s="238"/>
-      <c r="AG20" s="239"/>
-      <c r="AH20" s="239"/>
-      <c r="AI20" s="240"/>
+      <c r="B20" s="175"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="179"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="180"/>
+      <c r="I20" s="176"/>
+      <c r="J20" s="181"/>
+      <c r="K20" s="182"/>
+      <c r="L20" s="182"/>
+      <c r="M20" s="182"/>
+      <c r="N20" s="182"/>
+      <c r="O20" s="182"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="184"/>
+      <c r="R20" s="185"/>
+      <c r="S20" s="185"/>
+      <c r="T20" s="185"/>
+      <c r="U20" s="185"/>
+      <c r="V20" s="185"/>
+      <c r="W20" s="185"/>
+      <c r="X20" s="185"/>
+      <c r="Y20" s="185"/>
+      <c r="Z20" s="185"/>
+      <c r="AA20" s="185"/>
+      <c r="AB20" s="185"/>
+      <c r="AC20" s="185"/>
+      <c r="AD20" s="185"/>
+      <c r="AE20" s="186"/>
+      <c r="AF20" s="181"/>
+      <c r="AG20" s="182"/>
+      <c r="AH20" s="182"/>
+      <c r="AI20" s="183"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="232"/>
-      <c r="C21" s="233"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="235"/>
-      <c r="F21" s="236"/>
-      <c r="G21" s="232"/>
-      <c r="H21" s="237"/>
-      <c r="I21" s="233"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="239"/>
-      <c r="L21" s="239"/>
-      <c r="M21" s="239"/>
-      <c r="N21" s="239"/>
-      <c r="O21" s="239"/>
-      <c r="P21" s="240"/>
-      <c r="Q21" s="241"/>
-      <c r="R21" s="242"/>
-      <c r="S21" s="242"/>
-      <c r="T21" s="242"/>
-      <c r="U21" s="242"/>
-      <c r="V21" s="242"/>
-      <c r="W21" s="242"/>
-      <c r="X21" s="242"/>
-      <c r="Y21" s="242"/>
-      <c r="Z21" s="242"/>
-      <c r="AA21" s="242"/>
-      <c r="AB21" s="242"/>
-      <c r="AC21" s="242"/>
-      <c r="AD21" s="242"/>
-      <c r="AE21" s="243"/>
-      <c r="AF21" s="238"/>
-      <c r="AG21" s="239"/>
-      <c r="AH21" s="239"/>
-      <c r="AI21" s="240"/>
+      <c r="B21" s="175"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="177"/>
+      <c r="E21" s="178"/>
+      <c r="F21" s="179"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="180"/>
+      <c r="I21" s="176"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="182"/>
+      <c r="L21" s="182"/>
+      <c r="M21" s="182"/>
+      <c r="N21" s="182"/>
+      <c r="O21" s="182"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="184"/>
+      <c r="R21" s="185"/>
+      <c r="S21" s="185"/>
+      <c r="T21" s="185"/>
+      <c r="U21" s="185"/>
+      <c r="V21" s="185"/>
+      <c r="W21" s="185"/>
+      <c r="X21" s="185"/>
+      <c r="Y21" s="185"/>
+      <c r="Z21" s="185"/>
+      <c r="AA21" s="185"/>
+      <c r="AB21" s="185"/>
+      <c r="AC21" s="185"/>
+      <c r="AD21" s="185"/>
+      <c r="AE21" s="186"/>
+      <c r="AF21" s="181"/>
+      <c r="AG21" s="182"/>
+      <c r="AH21" s="182"/>
+      <c r="AI21" s="183"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="232"/>
-      <c r="C22" s="233"/>
-      <c r="D22" s="234"/>
-      <c r="E22" s="235"/>
-      <c r="F22" s="236"/>
-      <c r="G22" s="232"/>
-      <c r="H22" s="237"/>
-      <c r="I22" s="233"/>
-      <c r="J22" s="238"/>
-      <c r="K22" s="239"/>
-      <c r="L22" s="239"/>
-      <c r="M22" s="239"/>
-      <c r="N22" s="239"/>
-      <c r="O22" s="239"/>
-      <c r="P22" s="240"/>
-      <c r="Q22" s="241"/>
-      <c r="R22" s="242"/>
-      <c r="S22" s="242"/>
-      <c r="T22" s="242"/>
-      <c r="U22" s="242"/>
-      <c r="V22" s="242"/>
-      <c r="W22" s="242"/>
-      <c r="X22" s="242"/>
-      <c r="Y22" s="242"/>
-      <c r="Z22" s="242"/>
-      <c r="AA22" s="242"/>
-      <c r="AB22" s="242"/>
-      <c r="AC22" s="242"/>
-      <c r="AD22" s="242"/>
-      <c r="AE22" s="243"/>
-      <c r="AF22" s="238"/>
-      <c r="AG22" s="239"/>
-      <c r="AH22" s="239"/>
-      <c r="AI22" s="240"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="178"/>
+      <c r="F22" s="179"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="180"/>
+      <c r="I22" s="176"/>
+      <c r="J22" s="181"/>
+      <c r="K22" s="182"/>
+      <c r="L22" s="182"/>
+      <c r="M22" s="182"/>
+      <c r="N22" s="182"/>
+      <c r="O22" s="182"/>
+      <c r="P22" s="183"/>
+      <c r="Q22" s="184"/>
+      <c r="R22" s="185"/>
+      <c r="S22" s="185"/>
+      <c r="T22" s="185"/>
+      <c r="U22" s="185"/>
+      <c r="V22" s="185"/>
+      <c r="W22" s="185"/>
+      <c r="X22" s="185"/>
+      <c r="Y22" s="185"/>
+      <c r="Z22" s="185"/>
+      <c r="AA22" s="185"/>
+      <c r="AB22" s="185"/>
+      <c r="AC22" s="185"/>
+      <c r="AD22" s="185"/>
+      <c r="AE22" s="186"/>
+      <c r="AF22" s="181"/>
+      <c r="AG22" s="182"/>
+      <c r="AH22" s="182"/>
+      <c r="AI22" s="183"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="232"/>
-      <c r="C23" s="233"/>
-      <c r="D23" s="234"/>
-      <c r="E23" s="235"/>
-      <c r="F23" s="236"/>
-      <c r="G23" s="232"/>
-      <c r="H23" s="237"/>
-      <c r="I23" s="233"/>
-      <c r="J23" s="238"/>
-      <c r="K23" s="239"/>
-      <c r="L23" s="239"/>
-      <c r="M23" s="239"/>
-      <c r="N23" s="239"/>
-      <c r="O23" s="239"/>
-      <c r="P23" s="240"/>
-      <c r="Q23" s="241"/>
-      <c r="R23" s="242"/>
-      <c r="S23" s="242"/>
-      <c r="T23" s="242"/>
-      <c r="U23" s="242"/>
-      <c r="V23" s="242"/>
-      <c r="W23" s="242"/>
-      <c r="X23" s="242"/>
-      <c r="Y23" s="242"/>
-      <c r="Z23" s="242"/>
-      <c r="AA23" s="242"/>
-      <c r="AB23" s="242"/>
-      <c r="AC23" s="242"/>
-      <c r="AD23" s="242"/>
-      <c r="AE23" s="243"/>
-      <c r="AF23" s="238"/>
-      <c r="AG23" s="239"/>
-      <c r="AH23" s="239"/>
-      <c r="AI23" s="240"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="177"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="179"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="180"/>
+      <c r="I23" s="176"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="182"/>
+      <c r="L23" s="182"/>
+      <c r="M23" s="182"/>
+      <c r="N23" s="182"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="184"/>
+      <c r="R23" s="185"/>
+      <c r="S23" s="185"/>
+      <c r="T23" s="185"/>
+      <c r="U23" s="185"/>
+      <c r="V23" s="185"/>
+      <c r="W23" s="185"/>
+      <c r="X23" s="185"/>
+      <c r="Y23" s="185"/>
+      <c r="Z23" s="185"/>
+      <c r="AA23" s="185"/>
+      <c r="AB23" s="185"/>
+      <c r="AC23" s="185"/>
+      <c r="AD23" s="185"/>
+      <c r="AE23" s="186"/>
+      <c r="AF23" s="181"/>
+      <c r="AG23" s="182"/>
+      <c r="AH23" s="182"/>
+      <c r="AI23" s="183"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="232"/>
-      <c r="C24" s="233"/>
-      <c r="D24" s="234"/>
-      <c r="E24" s="235"/>
-      <c r="F24" s="236"/>
-      <c r="G24" s="232"/>
-      <c r="H24" s="237"/>
-      <c r="I24" s="233"/>
-      <c r="J24" s="238"/>
-      <c r="K24" s="239"/>
-      <c r="L24" s="239"/>
-      <c r="M24" s="239"/>
-      <c r="N24" s="239"/>
-      <c r="O24" s="239"/>
-      <c r="P24" s="240"/>
-      <c r="Q24" s="241"/>
-      <c r="R24" s="242"/>
-      <c r="S24" s="242"/>
-      <c r="T24" s="242"/>
-      <c r="U24" s="242"/>
-      <c r="V24" s="242"/>
-      <c r="W24" s="242"/>
-      <c r="X24" s="242"/>
-      <c r="Y24" s="242"/>
-      <c r="Z24" s="242"/>
-      <c r="AA24" s="242"/>
-      <c r="AB24" s="242"/>
-      <c r="AC24" s="242"/>
-      <c r="AD24" s="242"/>
-      <c r="AE24" s="243"/>
-      <c r="AF24" s="238"/>
-      <c r="AG24" s="239"/>
-      <c r="AH24" s="239"/>
-      <c r="AI24" s="240"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="177"/>
+      <c r="E24" s="178"/>
+      <c r="F24" s="179"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="180"/>
+      <c r="I24" s="176"/>
+      <c r="J24" s="181"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="182"/>
+      <c r="N24" s="182"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="183"/>
+      <c r="Q24" s="184"/>
+      <c r="R24" s="185"/>
+      <c r="S24" s="185"/>
+      <c r="T24" s="185"/>
+      <c r="U24" s="185"/>
+      <c r="V24" s="185"/>
+      <c r="W24" s="185"/>
+      <c r="X24" s="185"/>
+      <c r="Y24" s="185"/>
+      <c r="Z24" s="185"/>
+      <c r="AA24" s="185"/>
+      <c r="AB24" s="185"/>
+      <c r="AC24" s="185"/>
+      <c r="AD24" s="185"/>
+      <c r="AE24" s="186"/>
+      <c r="AF24" s="181"/>
+      <c r="AG24" s="182"/>
+      <c r="AH24" s="182"/>
+      <c r="AI24" s="183"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="232"/>
-      <c r="C25" s="233"/>
-      <c r="D25" s="234"/>
-      <c r="E25" s="235"/>
-      <c r="F25" s="236"/>
-      <c r="G25" s="232"/>
-      <c r="H25" s="237"/>
-      <c r="I25" s="233"/>
-      <c r="J25" s="238"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="239"/>
-      <c r="M25" s="239"/>
-      <c r="N25" s="239"/>
-      <c r="O25" s="239"/>
-      <c r="P25" s="240"/>
-      <c r="Q25" s="241"/>
-      <c r="R25" s="242"/>
-      <c r="S25" s="242"/>
-      <c r="T25" s="242"/>
-      <c r="U25" s="242"/>
-      <c r="V25" s="242"/>
-      <c r="W25" s="242"/>
-      <c r="X25" s="242"/>
-      <c r="Y25" s="242"/>
-      <c r="Z25" s="242"/>
-      <c r="AA25" s="242"/>
-      <c r="AB25" s="242"/>
-      <c r="AC25" s="242"/>
-      <c r="AD25" s="242"/>
-      <c r="AE25" s="243"/>
-      <c r="AF25" s="238"/>
-      <c r="AG25" s="239"/>
-      <c r="AH25" s="239"/>
-      <c r="AI25" s="240"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="177"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="179"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="180"/>
+      <c r="I25" s="176"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="182"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="183"/>
+      <c r="Q25" s="184"/>
+      <c r="R25" s="185"/>
+      <c r="S25" s="185"/>
+      <c r="T25" s="185"/>
+      <c r="U25" s="185"/>
+      <c r="V25" s="185"/>
+      <c r="W25" s="185"/>
+      <c r="X25" s="185"/>
+      <c r="Y25" s="185"/>
+      <c r="Z25" s="185"/>
+      <c r="AA25" s="185"/>
+      <c r="AB25" s="185"/>
+      <c r="AC25" s="185"/>
+      <c r="AD25" s="185"/>
+      <c r="AE25" s="186"/>
+      <c r="AF25" s="181"/>
+      <c r="AG25" s="182"/>
+      <c r="AH25" s="182"/>
+      <c r="AI25" s="183"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="232"/>
-      <c r="C26" s="233"/>
-      <c r="D26" s="234"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="236"/>
-      <c r="G26" s="232"/>
-      <c r="H26" s="237"/>
-      <c r="I26" s="233"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
-      <c r="M26" s="239"/>
-      <c r="N26" s="239"/>
-      <c r="O26" s="239"/>
-      <c r="P26" s="240"/>
-      <c r="Q26" s="241"/>
-      <c r="R26" s="242"/>
-      <c r="S26" s="242"/>
-      <c r="T26" s="242"/>
-      <c r="U26" s="242"/>
-      <c r="V26" s="242"/>
-      <c r="W26" s="242"/>
-      <c r="X26" s="242"/>
-      <c r="Y26" s="242"/>
-      <c r="Z26" s="242"/>
-      <c r="AA26" s="242"/>
-      <c r="AB26" s="242"/>
-      <c r="AC26" s="242"/>
-      <c r="AD26" s="242"/>
-      <c r="AE26" s="243"/>
-      <c r="AF26" s="238"/>
-      <c r="AG26" s="239"/>
-      <c r="AH26" s="239"/>
-      <c r="AI26" s="240"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="177"/>
+      <c r="E26" s="178"/>
+      <c r="F26" s="179"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="180"/>
+      <c r="I26" s="176"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="182"/>
+      <c r="N26" s="182"/>
+      <c r="O26" s="182"/>
+      <c r="P26" s="183"/>
+      <c r="Q26" s="184"/>
+      <c r="R26" s="185"/>
+      <c r="S26" s="185"/>
+      <c r="T26" s="185"/>
+      <c r="U26" s="185"/>
+      <c r="V26" s="185"/>
+      <c r="W26" s="185"/>
+      <c r="X26" s="185"/>
+      <c r="Y26" s="185"/>
+      <c r="Z26" s="185"/>
+      <c r="AA26" s="185"/>
+      <c r="AB26" s="185"/>
+      <c r="AC26" s="185"/>
+      <c r="AD26" s="185"/>
+      <c r="AE26" s="186"/>
+      <c r="AF26" s="181"/>
+      <c r="AG26" s="182"/>
+      <c r="AH26" s="182"/>
+      <c r="AI26" s="183"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="232"/>
-      <c r="C27" s="233"/>
-      <c r="D27" s="234"/>
-      <c r="E27" s="235"/>
-      <c r="F27" s="236"/>
-      <c r="G27" s="232"/>
-      <c r="H27" s="237"/>
-      <c r="I27" s="233"/>
-      <c r="J27" s="238"/>
-      <c r="K27" s="239"/>
-      <c r="L27" s="239"/>
-      <c r="M27" s="239"/>
-      <c r="N27" s="239"/>
-      <c r="O27" s="239"/>
-      <c r="P27" s="240"/>
-      <c r="Q27" s="241"/>
-      <c r="R27" s="242"/>
-      <c r="S27" s="242"/>
-      <c r="T27" s="242"/>
-      <c r="U27" s="242"/>
-      <c r="V27" s="242"/>
-      <c r="W27" s="242"/>
-      <c r="X27" s="242"/>
-      <c r="Y27" s="242"/>
-      <c r="Z27" s="242"/>
-      <c r="AA27" s="242"/>
-      <c r="AB27" s="242"/>
-      <c r="AC27" s="242"/>
-      <c r="AD27" s="242"/>
-      <c r="AE27" s="243"/>
-      <c r="AF27" s="238"/>
-      <c r="AG27" s="239"/>
-      <c r="AH27" s="239"/>
-      <c r="AI27" s="240"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="177"/>
+      <c r="E27" s="178"/>
+      <c r="F27" s="179"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="180"/>
+      <c r="I27" s="176"/>
+      <c r="J27" s="181"/>
+      <c r="K27" s="182"/>
+      <c r="L27" s="182"/>
+      <c r="M27" s="182"/>
+      <c r="N27" s="182"/>
+      <c r="O27" s="182"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="184"/>
+      <c r="R27" s="185"/>
+      <c r="S27" s="185"/>
+      <c r="T27" s="185"/>
+      <c r="U27" s="185"/>
+      <c r="V27" s="185"/>
+      <c r="W27" s="185"/>
+      <c r="X27" s="185"/>
+      <c r="Y27" s="185"/>
+      <c r="Z27" s="185"/>
+      <c r="AA27" s="185"/>
+      <c r="AB27" s="185"/>
+      <c r="AC27" s="185"/>
+      <c r="AD27" s="185"/>
+      <c r="AE27" s="186"/>
+      <c r="AF27" s="181"/>
+      <c r="AG27" s="182"/>
+      <c r="AH27" s="182"/>
+      <c r="AI27" s="183"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="232"/>
-      <c r="C28" s="233"/>
-      <c r="D28" s="234"/>
-      <c r="E28" s="235"/>
-      <c r="F28" s="236"/>
-      <c r="G28" s="232"/>
-      <c r="H28" s="237"/>
-      <c r="I28" s="233"/>
-      <c r="J28" s="238"/>
-      <c r="K28" s="239"/>
-      <c r="L28" s="239"/>
-      <c r="M28" s="239"/>
-      <c r="N28" s="239"/>
-      <c r="O28" s="239"/>
-      <c r="P28" s="240"/>
-      <c r="Q28" s="241"/>
-      <c r="R28" s="242"/>
-      <c r="S28" s="242"/>
-      <c r="T28" s="242"/>
-      <c r="U28" s="242"/>
-      <c r="V28" s="242"/>
-      <c r="W28" s="242"/>
-      <c r="X28" s="242"/>
-      <c r="Y28" s="242"/>
-      <c r="Z28" s="242"/>
-      <c r="AA28" s="242"/>
-      <c r="AB28" s="242"/>
-      <c r="AC28" s="242"/>
-      <c r="AD28" s="242"/>
-      <c r="AE28" s="243"/>
-      <c r="AF28" s="238"/>
-      <c r="AG28" s="239"/>
-      <c r="AH28" s="239"/>
-      <c r="AI28" s="240"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="177"/>
+      <c r="E28" s="178"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="180"/>
+      <c r="I28" s="176"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="182"/>
+      <c r="L28" s="182"/>
+      <c r="M28" s="182"/>
+      <c r="N28" s="182"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="183"/>
+      <c r="Q28" s="184"/>
+      <c r="R28" s="185"/>
+      <c r="S28" s="185"/>
+      <c r="T28" s="185"/>
+      <c r="U28" s="185"/>
+      <c r="V28" s="185"/>
+      <c r="W28" s="185"/>
+      <c r="X28" s="185"/>
+      <c r="Y28" s="185"/>
+      <c r="Z28" s="185"/>
+      <c r="AA28" s="185"/>
+      <c r="AB28" s="185"/>
+      <c r="AC28" s="185"/>
+      <c r="AD28" s="185"/>
+      <c r="AE28" s="186"/>
+      <c r="AF28" s="181"/>
+      <c r="AG28" s="182"/>
+      <c r="AH28" s="182"/>
+      <c r="AI28" s="183"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="232"/>
-      <c r="C29" s="233"/>
-      <c r="D29" s="234"/>
-      <c r="E29" s="235"/>
-      <c r="F29" s="236"/>
-      <c r="G29" s="232"/>
-      <c r="H29" s="237"/>
-      <c r="I29" s="233"/>
-      <c r="J29" s="238"/>
-      <c r="K29" s="239"/>
-      <c r="L29" s="239"/>
-      <c r="M29" s="239"/>
-      <c r="N29" s="239"/>
-      <c r="O29" s="239"/>
-      <c r="P29" s="240"/>
-      <c r="Q29" s="241"/>
-      <c r="R29" s="242"/>
-      <c r="S29" s="242"/>
-      <c r="T29" s="242"/>
-      <c r="U29" s="242"/>
-      <c r="V29" s="242"/>
-      <c r="W29" s="242"/>
-      <c r="X29" s="242"/>
-      <c r="Y29" s="242"/>
-      <c r="Z29" s="242"/>
-      <c r="AA29" s="242"/>
-      <c r="AB29" s="242"/>
-      <c r="AC29" s="242"/>
-      <c r="AD29" s="242"/>
-      <c r="AE29" s="243"/>
-      <c r="AF29" s="238"/>
-      <c r="AG29" s="239"/>
-      <c r="AH29" s="239"/>
-      <c r="AI29" s="240"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="176"/>
+      <c r="D29" s="177"/>
+      <c r="E29" s="178"/>
+      <c r="F29" s="179"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="180"/>
+      <c r="I29" s="176"/>
+      <c r="J29" s="181"/>
+      <c r="K29" s="182"/>
+      <c r="L29" s="182"/>
+      <c r="M29" s="182"/>
+      <c r="N29" s="182"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="184"/>
+      <c r="R29" s="185"/>
+      <c r="S29" s="185"/>
+      <c r="T29" s="185"/>
+      <c r="U29" s="185"/>
+      <c r="V29" s="185"/>
+      <c r="W29" s="185"/>
+      <c r="X29" s="185"/>
+      <c r="Y29" s="185"/>
+      <c r="Z29" s="185"/>
+      <c r="AA29" s="185"/>
+      <c r="AB29" s="185"/>
+      <c r="AC29" s="185"/>
+      <c r="AD29" s="185"/>
+      <c r="AE29" s="186"/>
+      <c r="AF29" s="181"/>
+      <c r="AG29" s="182"/>
+      <c r="AH29" s="182"/>
+      <c r="AI29" s="183"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="232"/>
-      <c r="C30" s="233"/>
-      <c r="D30" s="234"/>
-      <c r="E30" s="235"/>
-      <c r="F30" s="236"/>
-      <c r="G30" s="232"/>
-      <c r="H30" s="237"/>
-      <c r="I30" s="233"/>
-      <c r="J30" s="238"/>
-      <c r="K30" s="239"/>
-      <c r="L30" s="239"/>
-      <c r="M30" s="239"/>
-      <c r="N30" s="239"/>
-      <c r="O30" s="239"/>
-      <c r="P30" s="240"/>
-      <c r="Q30" s="241"/>
-      <c r="R30" s="242"/>
-      <c r="S30" s="242"/>
-      <c r="T30" s="242"/>
-      <c r="U30" s="242"/>
-      <c r="V30" s="242"/>
-      <c r="W30" s="242"/>
-      <c r="X30" s="242"/>
-      <c r="Y30" s="242"/>
-      <c r="Z30" s="242"/>
-      <c r="AA30" s="242"/>
-      <c r="AB30" s="242"/>
-      <c r="AC30" s="242"/>
-      <c r="AD30" s="242"/>
-      <c r="AE30" s="243"/>
-      <c r="AF30" s="238"/>
-      <c r="AG30" s="239"/>
-      <c r="AH30" s="239"/>
-      <c r="AI30" s="240"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="178"/>
+      <c r="F30" s="179"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="180"/>
+      <c r="I30" s="176"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="182"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="182"/>
+      <c r="N30" s="182"/>
+      <c r="O30" s="182"/>
+      <c r="P30" s="183"/>
+      <c r="Q30" s="184"/>
+      <c r="R30" s="185"/>
+      <c r="S30" s="185"/>
+      <c r="T30" s="185"/>
+      <c r="U30" s="185"/>
+      <c r="V30" s="185"/>
+      <c r="W30" s="185"/>
+      <c r="X30" s="185"/>
+      <c r="Y30" s="185"/>
+      <c r="Z30" s="185"/>
+      <c r="AA30" s="185"/>
+      <c r="AB30" s="185"/>
+      <c r="AC30" s="185"/>
+      <c r="AD30" s="185"/>
+      <c r="AE30" s="186"/>
+      <c r="AF30" s="181"/>
+      <c r="AG30" s="182"/>
+      <c r="AH30" s="182"/>
+      <c r="AI30" s="183"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="232"/>
-      <c r="C31" s="233"/>
-      <c r="D31" s="234"/>
-      <c r="E31" s="235"/>
-      <c r="F31" s="236"/>
-      <c r="G31" s="232"/>
-      <c r="H31" s="237"/>
-      <c r="I31" s="233"/>
-      <c r="J31" s="238"/>
-      <c r="K31" s="239"/>
-      <c r="L31" s="239"/>
-      <c r="M31" s="239"/>
-      <c r="N31" s="239"/>
-      <c r="O31" s="239"/>
-      <c r="P31" s="240"/>
-      <c r="Q31" s="241"/>
-      <c r="R31" s="242"/>
-      <c r="S31" s="242"/>
-      <c r="T31" s="242"/>
-      <c r="U31" s="242"/>
-      <c r="V31" s="242"/>
-      <c r="W31" s="242"/>
-      <c r="X31" s="242"/>
-      <c r="Y31" s="242"/>
-      <c r="Z31" s="242"/>
-      <c r="AA31" s="242"/>
-      <c r="AB31" s="242"/>
-      <c r="AC31" s="242"/>
-      <c r="AD31" s="242"/>
-      <c r="AE31" s="243"/>
-      <c r="AF31" s="238"/>
-      <c r="AG31" s="239"/>
-      <c r="AH31" s="239"/>
-      <c r="AI31" s="240"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="177"/>
+      <c r="E31" s="178"/>
+      <c r="F31" s="179"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="180"/>
+      <c r="I31" s="176"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="182"/>
+      <c r="L31" s="182"/>
+      <c r="M31" s="182"/>
+      <c r="N31" s="182"/>
+      <c r="O31" s="182"/>
+      <c r="P31" s="183"/>
+      <c r="Q31" s="184"/>
+      <c r="R31" s="185"/>
+      <c r="S31" s="185"/>
+      <c r="T31" s="185"/>
+      <c r="U31" s="185"/>
+      <c r="V31" s="185"/>
+      <c r="W31" s="185"/>
+      <c r="X31" s="185"/>
+      <c r="Y31" s="185"/>
+      <c r="Z31" s="185"/>
+      <c r="AA31" s="185"/>
+      <c r="AB31" s="185"/>
+      <c r="AC31" s="185"/>
+      <c r="AD31" s="185"/>
+      <c r="AE31" s="186"/>
+      <c r="AF31" s="181"/>
+      <c r="AG31" s="182"/>
+      <c r="AH31" s="182"/>
+      <c r="AI31" s="183"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="232"/>
-      <c r="C32" s="233"/>
-      <c r="D32" s="234"/>
-      <c r="E32" s="235"/>
-      <c r="F32" s="236"/>
-      <c r="G32" s="232"/>
-      <c r="H32" s="237"/>
-      <c r="I32" s="233"/>
-      <c r="J32" s="238"/>
-      <c r="K32" s="244"/>
-      <c r="L32" s="239"/>
-      <c r="M32" s="239"/>
-      <c r="N32" s="239"/>
-      <c r="O32" s="239"/>
-      <c r="P32" s="240"/>
-      <c r="Q32" s="241"/>
-      <c r="R32" s="242"/>
-      <c r="S32" s="242"/>
-      <c r="T32" s="242"/>
-      <c r="U32" s="242"/>
-      <c r="V32" s="242"/>
-      <c r="W32" s="242"/>
-      <c r="X32" s="242"/>
-      <c r="Y32" s="242"/>
-      <c r="Z32" s="242"/>
-      <c r="AA32" s="242"/>
-      <c r="AB32" s="242"/>
-      <c r="AC32" s="242"/>
-      <c r="AD32" s="242"/>
-      <c r="AE32" s="243"/>
-      <c r="AF32" s="238"/>
-      <c r="AG32" s="239"/>
-      <c r="AH32" s="239"/>
-      <c r="AI32" s="240"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="176"/>
+      <c r="D32" s="177"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="179"/>
+      <c r="G32" s="175"/>
+      <c r="H32" s="180"/>
+      <c r="I32" s="176"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="187"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="182"/>
+      <c r="N32" s="182"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="183"/>
+      <c r="Q32" s="184"/>
+      <c r="R32" s="185"/>
+      <c r="S32" s="185"/>
+      <c r="T32" s="185"/>
+      <c r="U32" s="185"/>
+      <c r="V32" s="185"/>
+      <c r="W32" s="185"/>
+      <c r="X32" s="185"/>
+      <c r="Y32" s="185"/>
+      <c r="Z32" s="185"/>
+      <c r="AA32" s="185"/>
+      <c r="AB32" s="185"/>
+      <c r="AC32" s="185"/>
+      <c r="AD32" s="185"/>
+      <c r="AE32" s="186"/>
+      <c r="AF32" s="181"/>
+      <c r="AG32" s="182"/>
+      <c r="AH32" s="182"/>
+      <c r="AI32" s="183"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="232"/>
-      <c r="C33" s="233"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="236"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="237"/>
-      <c r="I33" s="233"/>
-      <c r="J33" s="238"/>
-      <c r="K33" s="239"/>
-      <c r="L33" s="239"/>
-      <c r="M33" s="239"/>
-      <c r="N33" s="239"/>
-      <c r="O33" s="239"/>
-      <c r="P33" s="240"/>
-      <c r="Q33" s="241"/>
-      <c r="R33" s="242"/>
-      <c r="S33" s="242"/>
-      <c r="T33" s="242"/>
-      <c r="U33" s="242"/>
-      <c r="V33" s="242"/>
-      <c r="W33" s="242"/>
-      <c r="X33" s="242"/>
-      <c r="Y33" s="242"/>
-      <c r="Z33" s="242"/>
-      <c r="AA33" s="242"/>
-      <c r="AB33" s="242"/>
-      <c r="AC33" s="242"/>
-      <c r="AD33" s="242"/>
-      <c r="AE33" s="243"/>
-      <c r="AF33" s="238"/>
-      <c r="AG33" s="239"/>
-      <c r="AH33" s="239"/>
-      <c r="AI33" s="240"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="178"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="175"/>
+      <c r="H33" s="180"/>
+      <c r="I33" s="176"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="182"/>
+      <c r="L33" s="182"/>
+      <c r="M33" s="182"/>
+      <c r="N33" s="182"/>
+      <c r="O33" s="182"/>
+      <c r="P33" s="183"/>
+      <c r="Q33" s="184"/>
+      <c r="R33" s="185"/>
+      <c r="S33" s="185"/>
+      <c r="T33" s="185"/>
+      <c r="U33" s="185"/>
+      <c r="V33" s="185"/>
+      <c r="W33" s="185"/>
+      <c r="X33" s="185"/>
+      <c r="Y33" s="185"/>
+      <c r="Z33" s="185"/>
+      <c r="AA33" s="185"/>
+      <c r="AB33" s="185"/>
+      <c r="AC33" s="185"/>
+      <c r="AD33" s="185"/>
+      <c r="AE33" s="186"/>
+      <c r="AF33" s="181"/>
+      <c r="AG33" s="182"/>
+      <c r="AH33" s="182"/>
+      <c r="AI33" s="183"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -14452,6 +14269,161 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -15764,16 +15736,16 @@
         <v>178</v>
       </c>
       <c r="I42" s="36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J42" s="145" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K42" s="146" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L42" s="147" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M42" s="147" t="s">
         <v>167</v>
@@ -15809,16 +15781,16 @@
         <v>178</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J43" s="145" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="K43" s="146" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L43" s="147" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M43" s="147" t="s">
         <v>169</v>
@@ -16391,7 +16363,7 @@
         <v>160</v>
       </c>
       <c r="G59" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H59" s="56"/>
       <c r="I59" s="56"/>
@@ -16426,7 +16398,7 @@
         <v>161</v>
       </c>
       <c r="G60" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H60" s="56"/>
       <c r="I60" s="56"/>
@@ -16461,7 +16433,7 @@
         <v>162</v>
       </c>
       <c r="G61" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H61" s="56"/>
       <c r="I61" s="56"/>
@@ -16496,7 +16468,7 @@
         <v>163</v>
       </c>
       <c r="G62" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H62" s="56"/>
       <c r="I62" s="56"/>
@@ -16531,7 +16503,7 @@
         <v>164</v>
       </c>
       <c r="G63" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H63" s="56"/>
       <c r="I63" s="56"/>
@@ -16568,7 +16540,7 @@
         <v>166</v>
       </c>
       <c r="G64" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H64" s="56"/>
       <c r="I64" s="56"/>
@@ -16603,7 +16575,7 @@
         <v>168</v>
       </c>
       <c r="G65" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H65" s="56"/>
       <c r="I65" s="56"/>
@@ -16636,7 +16608,7 @@
       <c r="E66" s="55"/>
       <c r="F66" s="70"/>
       <c r="G66" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H66" s="56"/>
       <c r="I66" s="56"/>
@@ -16671,7 +16643,7 @@
         <v>170</v>
       </c>
       <c r="G67" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H67" s="56"/>
       <c r="I67" s="56"/>
@@ -16706,7 +16678,7 @@
         <v>171</v>
       </c>
       <c r="G68" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H68" s="56"/>
       <c r="I68" s="56"/>
@@ -16741,7 +16713,7 @@
         <v>172</v>
       </c>
       <c r="G69" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H69" s="56"/>
       <c r="I69" s="56"/>
@@ -16776,7 +16748,7 @@
         <v>173</v>
       </c>
       <c r="G70" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H70" s="56"/>
       <c r="I70" s="56"/>
@@ -16811,7 +16783,7 @@
         <v>174</v>
       </c>
       <c r="G71" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H71" s="56"/>
       <c r="I71" s="56"/>
@@ -16846,7 +16818,7 @@
         <v>175</v>
       </c>
       <c r="G72" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H72" s="56"/>
       <c r="I72" s="56"/>
@@ -16883,7 +16855,7 @@
         <v>177</v>
       </c>
       <c r="G73" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H73" s="54"/>
       <c r="I73" s="54"/>
@@ -16920,7 +16892,7 @@
         <v>180</v>
       </c>
       <c r="G74" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H74" s="54"/>
       <c r="I74" s="54"/>
@@ -16955,7 +16927,7 @@
         <v>181</v>
       </c>
       <c r="G75" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H75" s="56"/>
       <c r="I75" s="56"/>
@@ -16990,7 +16962,7 @@
         <v>182</v>
       </c>
       <c r="G76" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H76" s="56"/>
       <c r="I76" s="56"/>
@@ -17025,7 +16997,7 @@
         <v>184</v>
       </c>
       <c r="G77" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H77" s="56"/>
       <c r="I77" s="56"/>
@@ -17060,7 +17032,7 @@
         <v>185</v>
       </c>
       <c r="G78" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H78" s="56"/>
       <c r="I78" s="56"/>
@@ -17107,16 +17079,16 @@
         <v>178</v>
       </c>
       <c r="I79" s="36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J79" s="145" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="K79" s="146" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="L79" s="147" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M79" s="147" t="s">
         <v>167</v>
@@ -17150,16 +17122,16 @@
         <v>178</v>
       </c>
       <c r="I80" s="36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J80" s="37" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="K80" s="37" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L80" s="147" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M80" s="147" t="s">
         <v>34</v>
@@ -17193,16 +17165,16 @@
         <v>178</v>
       </c>
       <c r="I81" s="36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J81" s="37" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="K81" s="37" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L81" s="147" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M81" s="147" t="s">
         <v>38</v>
@@ -17240,16 +17212,16 @@
         <v>178</v>
       </c>
       <c r="I82" s="36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J82" s="145" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="K82" s="146" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="L82" s="147" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M82" s="147" t="s">
         <v>169</v>
@@ -17283,7 +17255,7 @@
         <v>191</v>
       </c>
       <c r="G83" s="56" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H83" s="68"/>
       <c r="I83" s="68"/>
@@ -17324,16 +17296,16 @@
         <v>178</v>
       </c>
       <c r="I84" s="36" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J84" s="145" t="s">
+        <v>546</v>
+      </c>
+      <c r="K84" s="146" t="s">
         <v>547</v>
       </c>
-      <c r="K84" s="146" t="s">
-        <v>548</v>
-      </c>
       <c r="L84" s="147" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="M84" s="147" t="s">
         <v>33</v>
@@ -17402,7 +17374,7 @@
         <v>196</v>
       </c>
       <c r="G86" s="56" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H86" s="68"/>
       <c r="I86" s="68"/>
@@ -17480,7 +17452,7 @@
         <v>200</v>
       </c>
       <c r="G88" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H88" s="56"/>
       <c r="I88" s="56"/>
@@ -17517,7 +17489,7 @@
         <v>201</v>
       </c>
       <c r="G89" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H89" s="56"/>
       <c r="I89" s="56"/>
@@ -17554,7 +17526,7 @@
         <v>203</v>
       </c>
       <c r="G90" s="56" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H90" s="56"/>
       <c r="I90" s="56"/>
@@ -25187,7 +25159,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>21</v>
@@ -25765,8 +25737,8 @@
       <c r="C24" s="114"/>
       <c r="D24" s="117"/>
       <c r="E24" s="115"/>
-      <c r="F24" s="112" t="s">
-        <v>469</v>
+      <c r="F24" s="54" t="s">
+        <v>105</v>
       </c>
       <c r="G24" s="58" t="s">
         <v>467</v>
@@ -26090,7 +26062,7 @@
       <c r="C33" s="114"/>
       <c r="D33" s="116"/>
       <c r="E33" s="116" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F33" s="112" t="s">
         <v>119</v>
@@ -26165,7 +26137,7 @@
         <v>121</v>
       </c>
       <c r="F35" s="112" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G35" s="58" t="s">
         <v>467</v>
@@ -26200,10 +26172,10 @@
         <v>123</v>
       </c>
       <c r="D36" s="118" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E36" s="110" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F36" s="115" t="s">
         <v>125</v>
@@ -26241,7 +26213,7 @@
       <c r="D37" s="116"/>
       <c r="E37" s="111"/>
       <c r="F37" s="112" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G37" s="58" t="s">
         <v>467</v>
@@ -26350,7 +26322,7 @@
         <v>90</v>
       </c>
       <c r="F40" s="112" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G40" s="58" t="s">
         <v>467</v>
@@ -26385,7 +26357,7 @@
       <c r="D41" s="117"/>
       <c r="E41" s="115"/>
       <c r="F41" s="112" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G41" s="58" t="s">
         <v>467</v>
@@ -26960,7 +26932,7 @@
       <c r="C57" s="111"/>
       <c r="D57" s="111"/>
       <c r="E57" s="112" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F57" s="112" t="s">
         <v>156</v>
@@ -27036,10 +27008,10 @@
         <v>159</v>
       </c>
       <c r="E59" s="116" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F59" s="112" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G59" s="58" t="s">
         <v>137</v>
@@ -27074,7 +27046,7 @@
       <c r="D60" s="111"/>
       <c r="E60" s="116"/>
       <c r="F60" s="110" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G60" s="58" t="s">
         <v>137</v>
@@ -27109,7 +27081,7 @@
       <c r="D61" s="111"/>
       <c r="E61" s="116"/>
       <c r="F61" s="112" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G61" s="58" t="s">
         <v>137</v>
@@ -27144,7 +27116,7 @@
       <c r="D62" s="111"/>
       <c r="E62" s="116"/>
       <c r="F62" s="112" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G62" s="58" t="s">
         <v>137</v>
@@ -27972,7 +27944,7 @@
         <v>187</v>
       </c>
       <c r="E85" s="112" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F85" s="112" t="s">
         <v>200</v>
@@ -28046,7 +28018,7 @@
       <c r="C87" s="115"/>
       <c r="D87" s="115"/>
       <c r="E87" s="115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F87" s="112" t="s">
         <v>203</v>
@@ -28087,7 +28059,7 @@
         <v>187</v>
       </c>
       <c r="E88" s="116" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F88" s="110" t="s">
         <v>206</v>
@@ -28268,7 +28240,7 @@
       <c r="C93" s="115"/>
       <c r="D93" s="115"/>
       <c r="E93" s="115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F93" s="112" t="s">
         <v>212</v>
@@ -28663,7 +28635,7 @@
       <c r="C104" s="115"/>
       <c r="D104" s="111"/>
       <c r="E104" s="117" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F104" s="112" t="s">
         <v>227</v>
@@ -28817,7 +28789,7 @@
       </c>
       <c r="B108" s="111"/>
       <c r="C108" s="112" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D108" s="112" t="s">
         <v>90</v>
@@ -28858,7 +28830,7 @@
       </c>
       <c r="B109" s="111"/>
       <c r="C109" s="111" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D109" s="111" t="s">
         <v>90</v>
@@ -28939,16 +28911,16 @@
         <v>240</v>
       </c>
       <c r="D111" s="110" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E111" s="127" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F111" s="112" t="s">
         <v>241</v>
       </c>
       <c r="G111" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H111" s="61"/>
       <c r="I111" s="61"/>
@@ -28976,7 +28948,7 @@
         <v>43-2-1</v>
       </c>
       <c r="B112" s="246" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C112" s="116"/>
       <c r="D112" s="111"/>
@@ -28985,7 +28957,7 @@
         <v>243</v>
       </c>
       <c r="G112" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H112" s="61"/>
       <c r="I112" s="61"/>
@@ -29020,7 +28992,7 @@
         <v>244</v>
       </c>
       <c r="G113" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H113" s="61"/>
       <c r="I113" s="61"/>
@@ -29055,7 +29027,7 @@
         <v>245</v>
       </c>
       <c r="G114" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H114" s="61"/>
       <c r="I114" s="61"/>
@@ -29092,7 +29064,7 @@
         <v>246</v>
       </c>
       <c r="G115" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H115" s="61"/>
       <c r="I115" s="61"/>
@@ -29127,7 +29099,7 @@
         <v>247</v>
       </c>
       <c r="G116" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H116" s="61"/>
       <c r="I116" s="61"/>
@@ -29162,7 +29134,7 @@
         <v>248</v>
       </c>
       <c r="G117" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H117" s="61"/>
       <c r="I117" s="61"/>
@@ -29197,7 +29169,7 @@
         <v>249</v>
       </c>
       <c r="G118" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H118" s="61"/>
       <c r="I118" s="61"/>
@@ -29232,7 +29204,7 @@
         <v>250</v>
       </c>
       <c r="G119" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H119" s="61"/>
       <c r="I119" s="61"/>
@@ -29269,7 +29241,7 @@
         <v>252</v>
       </c>
       <c r="G120" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H120" s="61"/>
       <c r="I120" s="61"/>
@@ -29304,7 +29276,7 @@
         <v>253</v>
       </c>
       <c r="G121" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H121" s="61"/>
       <c r="I121" s="61"/>
@@ -29339,7 +29311,7 @@
         <v>254</v>
       </c>
       <c r="G122" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H122" s="61"/>
       <c r="I122" s="61"/>
@@ -29374,7 +29346,7 @@
         <v>255</v>
       </c>
       <c r="G123" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H123" s="61"/>
       <c r="I123" s="61"/>
@@ -29409,7 +29381,7 @@
         <v>256</v>
       </c>
       <c r="G124" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H124" s="61"/>
       <c r="I124" s="61"/>
@@ -29440,13 +29412,13 @@
       <c r="C125" s="116"/>
       <c r="D125" s="115"/>
       <c r="E125" s="115" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F125" s="112" t="s">
         <v>258</v>
       </c>
       <c r="G125" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H125" s="61"/>
       <c r="I125" s="61"/>
@@ -29476,16 +29448,16 @@
       <c r="B126" s="111"/>
       <c r="C126" s="117"/>
       <c r="D126" s="115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E126" s="115" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F126" s="112" t="s">
         <v>259</v>
       </c>
       <c r="G126" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H126" s="61"/>
       <c r="I126" s="61"/>
@@ -29526,7 +29498,7 @@
         <v>262</v>
       </c>
       <c r="G127" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H127" s="61"/>
       <c r="I127" s="61"/>
@@ -29557,13 +29529,13 @@
       <c r="C128" s="111"/>
       <c r="D128" s="111"/>
       <c r="E128" s="116" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F128" s="112" t="s">
         <v>264</v>
       </c>
       <c r="G128" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H128" s="61"/>
       <c r="I128" s="61"/>
@@ -29598,7 +29570,7 @@
         <v>265</v>
       </c>
       <c r="G129" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H129" s="61"/>
       <c r="I129" s="61"/>
@@ -29633,7 +29605,7 @@
         <v>266</v>
       </c>
       <c r="G130" s="58" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H130" s="61"/>
       <c r="I130" s="61"/>
@@ -29667,10 +29639,10 @@
         <v>240</v>
       </c>
       <c r="D131" s="110" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E131" s="127" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F131" s="112" t="s">
         <v>268</v>
@@ -29885,10 +29857,10 @@
       <c r="B137" s="111"/>
       <c r="C137" s="117"/>
       <c r="D137" s="115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E137" s="115" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F137" s="112" t="s">
         <v>277</v>
@@ -30077,7 +30049,7 @@
       <c r="C142" s="116"/>
       <c r="D142" s="111"/>
       <c r="E142" s="112" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F142" s="112" t="s">
         <v>287</v>
@@ -30114,7 +30086,7 @@
       <c r="C143" s="116"/>
       <c r="D143" s="111"/>
       <c r="E143" s="124" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F143" s="112" t="s">
         <v>289</v>
@@ -30328,7 +30300,7 @@
         <v>295</v>
       </c>
       <c r="E149" s="110" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F149" s="112" t="s">
         <v>296</v>
@@ -30473,7 +30445,7 @@
       <c r="D153" s="111"/>
       <c r="E153" s="124"/>
       <c r="F153" s="112" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G153" s="56" t="s">
         <v>269</v>
@@ -30508,7 +30480,7 @@
       <c r="D154" s="111"/>
       <c r="E154" s="124"/>
       <c r="F154" s="112" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G154" s="56" t="s">
         <v>269</v>
@@ -31506,7 +31478,7 @@
       <c r="B182" s="115"/>
       <c r="C182" s="117"/>
       <c r="D182" s="117" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E182" s="117" t="s">
         <v>90</v>
@@ -31549,7 +31521,7 @@
         <v>240</v>
       </c>
       <c r="D183" s="110" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E183" s="112" t="s">
         <v>337</v>
@@ -31732,10 +31704,10 @@
       <c r="B188" s="111"/>
       <c r="C188" s="115"/>
       <c r="D188" s="115" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E188" s="115" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F188" s="112" t="s">
         <v>345</v>
@@ -31773,7 +31745,7 @@
         <v>346</v>
       </c>
       <c r="D189" s="111" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E189" s="116" t="s">
         <v>348</v>
@@ -32026,7 +31998,7 @@
         <v>356</v>
       </c>
       <c r="F196" s="112" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G196" s="56" t="s">
         <v>339</v>
@@ -32275,7 +32247,7 @@
       <c r="D203" s="111"/>
       <c r="E203" s="116"/>
       <c r="F203" s="112" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G203" s="56" t="s">
         <v>339</v>
@@ -32518,7 +32490,7 @@
       <c r="B210" s="111"/>
       <c r="C210" s="114"/>
       <c r="D210" s="110" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E210" s="118" t="s">
         <v>165</v>
@@ -32769,7 +32741,7 @@
       <c r="D217" s="111"/>
       <c r="E217" s="116"/>
       <c r="F217" s="112" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G217" s="56" t="s">
         <v>339</v>
@@ -32804,7 +32776,7 @@
       <c r="D218" s="111"/>
       <c r="E218" s="116"/>
       <c r="F218" s="112" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G218" s="56" t="s">
         <v>339</v>
@@ -33158,7 +33130,7 @@
         <v>195</v>
       </c>
       <c r="F228" s="112" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="G228" s="56" t="s">
         <v>339</v>
@@ -33232,10 +33204,10 @@
         <v>240</v>
       </c>
       <c r="D230" s="160" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E230" s="112" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F230" s="112" t="s">
         <v>393</v>
@@ -33279,19 +33251,19 @@
       </c>
       <c r="G231" s="147"/>
       <c r="H231" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="I231" s="39" t="s">
         <v>557</v>
       </c>
-      <c r="I231" s="39" t="s">
-        <v>558</v>
-      </c>
       <c r="J231" s="42" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K231" s="42" t="s">
         <v>28</v>
       </c>
       <c r="L231" s="148" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M231" s="148">
         <v>3</v>
@@ -33323,7 +33295,7 @@
         <v>396</v>
       </c>
       <c r="G232" s="58" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H232" s="61"/>
       <c r="I232" s="61"/>
@@ -33606,19 +33578,19 @@
       </c>
       <c r="G240" s="147"/>
       <c r="H240" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="I240" s="39" t="s">
         <v>557</v>
       </c>
-      <c r="I240" s="39" t="s">
-        <v>558</v>
-      </c>
       <c r="J240" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="K240" s="42" t="s">
         <v>565</v>
       </c>
-      <c r="K240" s="42" t="s">
-        <v>566</v>
-      </c>
       <c r="L240" s="87" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M240" s="87">
         <v>1</v>
@@ -33646,23 +33618,23 @@
       <c r="C241" s="163"/>
       <c r="D241" s="163"/>
       <c r="E241" s="163" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F241" s="160" t="s">
         <v>405</v>
       </c>
       <c r="G241" s="170"/>
       <c r="H241" s="38" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I241" s="39" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J241" s="37" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K241" s="40" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="L241" s="148" t="s">
         <v>32</v>
@@ -33696,13 +33668,13 @@
       <c r="F242" s="165"/>
       <c r="G242" s="173"/>
       <c r="H242" s="38" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I242" s="39" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J242" s="37" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="K242" s="40" t="s">
         <v>31</v>
@@ -33747,19 +33719,19 @@
       </c>
       <c r="G243" s="147"/>
       <c r="H243" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="I243" s="39" t="s">
         <v>557</v>
       </c>
-      <c r="I243" s="39" t="s">
-        <v>558</v>
-      </c>
       <c r="J243" s="42" t="s">
+        <v>564</v>
+      </c>
+      <c r="K243" s="42" t="s">
         <v>565</v>
       </c>
-      <c r="K243" s="42" t="s">
-        <v>566</v>
-      </c>
       <c r="L243" s="87" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M243" s="87">
         <v>1</v>
@@ -33790,10 +33762,10 @@
         <v>408</v>
       </c>
       <c r="D244" s="110" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E244" s="118" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F244" s="112" t="s">
         <v>409</v>
@@ -33864,10 +33836,10 @@
       <c r="B246" s="163"/>
       <c r="C246" s="132"/>
       <c r="D246" s="132" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E246" s="116" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F246" s="112" t="s">
         <v>411</v>
@@ -34024,19 +33996,19 @@
       </c>
       <c r="G250" s="147"/>
       <c r="H250" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="I250" s="39" t="s">
         <v>557</v>
-      </c>
-      <c r="I250" s="39" t="s">
-        <v>558</v>
       </c>
       <c r="J250" s="41" t="s">
         <v>29</v>
       </c>
       <c r="K250" s="41" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="L250" s="148" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M250" s="148">
         <v>2</v>
@@ -34103,26 +34075,26 @@
         <v>295</v>
       </c>
       <c r="E252" s="168" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F252" s="161" t="s">
         <v>418</v>
       </c>
       <c r="G252" s="147"/>
       <c r="H252" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="I252" s="39" t="s">
         <v>557</v>
       </c>
-      <c r="I252" s="39" t="s">
-        <v>558</v>
-      </c>
       <c r="J252" s="42" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="K252" s="41" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="L252" s="148" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M252" s="148">
         <v>2</v>
@@ -34227,19 +34199,19 @@
       </c>
       <c r="G255" s="147"/>
       <c r="H255" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="I255" s="39" t="s">
         <v>557</v>
       </c>
-      <c r="I255" s="39" t="s">
-        <v>558</v>
-      </c>
       <c r="J255" s="42" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="K255" s="41" t="s">
         <v>30</v>
       </c>
       <c r="L255" s="148" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M255" s="148">
         <v>4</v>
@@ -34268,7 +34240,7 @@
       <c r="D256" s="164"/>
       <c r="E256" s="164"/>
       <c r="F256" s="112" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="G256" s="58" t="s">
         <v>183</v>
@@ -34589,19 +34561,19 @@
       </c>
       <c r="G265" s="147"/>
       <c r="H265" s="38" t="s">
+        <v>556</v>
+      </c>
+      <c r="I265" s="39" t="s">
         <v>557</v>
       </c>
-      <c r="I265" s="39" t="s">
-        <v>558</v>
-      </c>
       <c r="J265" s="42" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="K265" s="42" t="s">
         <v>28</v>
       </c>
       <c r="L265" s="148" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M265" s="148">
         <v>3</v>
@@ -34816,16 +34788,16 @@
         <v>27</v>
       </c>
       <c r="I271" s="39" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J271" s="42" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K271" s="42" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L271" s="87" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M271" s="87">
         <v>2</v>
@@ -35138,10 +35110,10 @@
         <v>447</v>
       </c>
       <c r="D280" s="110" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E280" s="118" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F280" s="112" t="s">
         <v>448</v>
@@ -35545,7 +35517,7 @@
       <c r="D291" s="116"/>
       <c r="E291" s="116"/>
       <c r="F291" s="112" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="G291" s="56" t="s">
         <v>449</v>
@@ -35580,7 +35552,7 @@
       <c r="D292" s="116"/>
       <c r="E292" s="116"/>
       <c r="F292" s="112" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="G292" s="56" t="s">
         <v>449</v>
@@ -35615,7 +35587,7 @@
       <c r="D293" s="116"/>
       <c r="E293" s="116"/>
       <c r="F293" s="112" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G293" s="56" t="s">
         <v>449</v>
@@ -35650,7 +35622,7 @@
       <c r="D294" s="116"/>
       <c r="E294" s="116"/>
       <c r="F294" s="112" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G294" s="56" t="s">
         <v>449</v>
@@ -35751,19 +35723,19 @@
         <v>101-1-1</v>
       </c>
       <c r="B297" s="126" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C297" s="126" t="s">
         <v>240</v>
       </c>
       <c r="D297" s="110" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E297" s="110" t="s">
+        <v>508</v>
+      </c>
+      <c r="F297" s="110" t="s">
         <v>509</v>
-      </c>
-      <c r="F297" s="110" t="s">
-        <v>510</v>
       </c>
       <c r="G297" s="58" t="s">
         <v>183</v>
@@ -35800,7 +35772,7 @@
         <v>195</v>
       </c>
       <c r="F298" s="112" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G298" s="58" t="s">
         <v>183</v>
@@ -35834,10 +35806,10 @@
       <c r="C299" s="129"/>
       <c r="D299" s="116"/>
       <c r="E299" s="110" t="s">
+        <v>511</v>
+      </c>
+      <c r="F299" s="110" t="s">
         <v>512</v>
-      </c>
-      <c r="F299" s="110" t="s">
-        <v>513</v>
       </c>
       <c r="G299" s="58" t="s">
         <v>183</v>
@@ -35870,29 +35842,29 @@
       <c r="B300" s="129"/>
       <c r="C300" s="129"/>
       <c r="D300" s="126" t="s">
+        <v>513</v>
+      </c>
+      <c r="E300" s="126" t="s">
+        <v>471</v>
+      </c>
+      <c r="F300" s="126" t="s">
         <v>514</v>
-      </c>
-      <c r="E300" s="126" t="s">
-        <v>472</v>
-      </c>
-      <c r="F300" s="126" t="s">
-        <v>515</v>
       </c>
       <c r="G300" s="136"/>
       <c r="H300" s="38" t="s">
         <v>27</v>
       </c>
       <c r="I300" s="39" t="s">
+        <v>558</v>
+      </c>
+      <c r="J300" s="42" t="s">
         <v>559</v>
       </c>
-      <c r="J300" s="42" t="s">
-        <v>560</v>
-      </c>
       <c r="K300" s="42" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="L300" s="87" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M300" s="87">
         <v>1</v>
@@ -35926,16 +35898,16 @@
         <v>27</v>
       </c>
       <c r="I301" s="39" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J301" s="42" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="K301" s="42" t="s">
         <v>28</v>
       </c>
       <c r="L301" s="87" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M301" s="87">
         <v>2</v>
@@ -35964,20 +35936,20 @@
       <c r="D302" s="129"/>
       <c r="E302" s="128"/>
       <c r="F302" s="126" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="G302" s="136"/>
       <c r="H302" s="38" t="s">
         <v>27</v>
       </c>
       <c r="I302" s="39" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J302" s="37" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="K302" s="40" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L302" s="148" t="s">
         <v>32</v>
@@ -36009,7 +35981,7 @@
       <c r="D303" s="128"/>
       <c r="E303" s="128"/>
       <c r="F303" s="112" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="G303" s="58" t="s">
         <v>183</v>
@@ -36044,7 +36016,7 @@
       <c r="D304" s="128"/>
       <c r="E304" s="129"/>
       <c r="F304" s="114" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G304" s="58" t="s">
         <v>183</v>
@@ -36077,26 +36049,26 @@
       <c r="B305" s="129"/>
       <c r="C305" s="129"/>
       <c r="D305" s="126" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E305" s="126" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F305" s="126" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="G305" s="170"/>
       <c r="H305" s="38" t="s">
         <v>27</v>
       </c>
       <c r="I305" s="39" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J305" s="37" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="K305" s="40" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="L305" s="148" t="s">
         <v>32</v>
@@ -36133,13 +36105,13 @@
         <v>27</v>
       </c>
       <c r="I306" s="39" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="J306" s="37" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="K306" s="40" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L306" s="148" t="s">
         <v>32</v>
@@ -36171,7 +36143,7 @@
       <c r="D307" s="128"/>
       <c r="E307" s="129"/>
       <c r="F307" s="112" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="G307" s="58" t="s">
         <v>183</v>
@@ -36206,7 +36178,7 @@
       <c r="D308" s="128"/>
       <c r="E308" s="129"/>
       <c r="F308" s="112" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="G308" s="58" t="s">
         <v>183</v>
@@ -36241,7 +36213,7 @@
       <c r="D309" s="128"/>
       <c r="E309" s="129"/>
       <c r="F309" s="112" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G309" s="58" t="s">
         <v>183</v>
@@ -36276,7 +36248,7 @@
       <c r="D310" s="128"/>
       <c r="E310" s="129"/>
       <c r="F310" s="112" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G310" s="58" t="s">
         <v>183</v>
@@ -36311,7 +36283,7 @@
       <c r="D311" s="128"/>
       <c r="E311" s="129"/>
       <c r="F311" s="112" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G311" s="58" t="s">
         <v>183</v>
@@ -36346,7 +36318,7 @@
       <c r="D312" s="128"/>
       <c r="E312" s="129"/>
       <c r="F312" s="112" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G312" s="58" t="s">
         <v>183</v>
@@ -36381,7 +36353,7 @@
       <c r="D313" s="128"/>
       <c r="E313" s="129"/>
       <c r="F313" s="112" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G313" s="58" t="s">
         <v>183</v>
@@ -36416,10 +36388,10 @@
       <c r="D314" s="128"/>
       <c r="E314" s="128"/>
       <c r="F314" s="112" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G314" s="58" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H314" s="61"/>
       <c r="I314" s="61"/>
@@ -36451,7 +36423,7 @@
       <c r="D315" s="128"/>
       <c r="E315" s="128"/>
       <c r="F315" s="112" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G315" s="58" t="s">
         <v>183</v>
@@ -36486,7 +36458,7 @@
       <c r="D316" s="131"/>
       <c r="E316" s="131"/>
       <c r="F316" s="112" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="G316" s="58" t="s">
         <v>183</v>
@@ -36684,7 +36656,7 @@
         <v>26</v>
       </c>
       <c r="C11" s="138" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D11" s="138" t="s">
         <v>18</v>
@@ -36693,17 +36665,17 @@
         <v>0</v>
       </c>
       <c r="F11" s="138" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G11" s="136"/>
       <c r="H11" s="43" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I11" s="37" t="s">
         <v>35</v>
       </c>
       <c r="J11" s="139" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K11" s="140">
         <v>1</v>
@@ -36744,10 +36716,10 @@
         <v>36</v>
       </c>
       <c r="I12" s="37" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J12" s="139" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K12" s="140">
         <v>1</v>
@@ -36782,10 +36754,10 @@
         <v>37</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J13" s="140" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K13" s="140">
         <v>2</v>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A084154A-592F-41F3-BF33-FCF33A599CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5DC6C3-320C-4EF2-9AA5-454CB8EA0C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8641,108 +8641,6 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8849,6 +8747,108 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13017,57 +13017,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="181" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="216"/>
-      <c r="C1" s="216"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218" t="s">
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="219"/>
-      <c r="M1" s="219"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="224" t="s">
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="186"/>
+      <c r="O1" s="190" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="233" t="s">
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="199" t="s">
         <v>572</v>
       </c>
-      <c r="T1" s="234"/>
-      <c r="U1" s="234"/>
-      <c r="V1" s="234"/>
-      <c r="W1" s="234"/>
-      <c r="X1" s="234"/>
-      <c r="Y1" s="234"/>
-      <c r="Z1" s="235"/>
-      <c r="AA1" s="215" t="s">
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="201"/>
+      <c r="AA1" s="181" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="242" t="str">
+      <c r="AB1" s="183"/>
+      <c r="AC1" s="208" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="243"/>
-      <c r="AE1" s="243"/>
-      <c r="AF1" s="244"/>
-      <c r="AG1" s="209">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="175">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="210"/>
-      <c r="AI1" s="211"/>
+      <c r="AH1" s="176"/>
+      <c r="AI1" s="177"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -13075,53 +13075,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="215" t="s">
+      <c r="A2" s="181" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="216"/>
-      <c r="C2" s="216"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="218" t="s">
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="184" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="219"/>
-      <c r="G2" s="219"/>
-      <c r="H2" s="219"/>
-      <c r="I2" s="219"/>
-      <c r="J2" s="219"/>
-      <c r="K2" s="219"/>
-      <c r="L2" s="219"/>
-      <c r="M2" s="219"/>
-      <c r="N2" s="220"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="228"/>
-      <c r="Q2" s="228"/>
-      <c r="R2" s="229"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="215" t="s">
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="195"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="203"/>
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="203"/>
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="204"/>
+      <c r="AA2" s="181" t="s">
         <v>43</v>
       </c>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="221" t="str">
+      <c r="AB2" s="183"/>
+      <c r="AC2" s="187" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="222"/>
-      <c r="AE2" s="222"/>
-      <c r="AF2" s="223"/>
-      <c r="AG2" s="209">
+      <c r="AD2" s="188"/>
+      <c r="AE2" s="188"/>
+      <c r="AF2" s="189"/>
+      <c r="AG2" s="175">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="210"/>
-      <c r="AI2" s="211"/>
+      <c r="AH2" s="176"/>
+      <c r="AI2" s="177"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -13129,45 +13129,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="215" t="s">
+      <c r="A3" s="181" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="216"/>
-      <c r="C3" s="216"/>
-      <c r="D3" s="217"/>
-      <c r="E3" s="218" t="s">
+      <c r="B3" s="182"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="184" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="219"/>
-      <c r="G3" s="219"/>
-      <c r="H3" s="219"/>
-      <c r="I3" s="219"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="219"/>
-      <c r="L3" s="219"/>
-      <c r="M3" s="219"/>
-      <c r="N3" s="220"/>
-      <c r="O3" s="230"/>
-      <c r="P3" s="231"/>
-      <c r="Q3" s="231"/>
-      <c r="R3" s="232"/>
-      <c r="S3" s="239"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="241"/>
-      <c r="AA3" s="215"/>
-      <c r="AB3" s="217"/>
-      <c r="AC3" s="242"/>
-      <c r="AD3" s="243"/>
-      <c r="AE3" s="243"/>
-      <c r="AF3" s="244"/>
-      <c r="AG3" s="209"/>
-      <c r="AH3" s="210"/>
-      <c r="AI3" s="211"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="186"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="197"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="198"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="206"/>
+      <c r="U3" s="206"/>
+      <c r="V3" s="206"/>
+      <c r="W3" s="206"/>
+      <c r="X3" s="206"/>
+      <c r="Y3" s="206"/>
+      <c r="Z3" s="207"/>
+      <c r="AA3" s="181"/>
+      <c r="AB3" s="183"/>
+      <c r="AC3" s="208"/>
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="175"/>
+      <c r="AH3" s="176"/>
+      <c r="AI3" s="177"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -13204,97 +13204,97 @@
       <c r="A7" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="212" t="s">
+      <c r="B7" s="178" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="213"/>
-      <c r="D7" s="212" t="s">
+      <c r="C7" s="179"/>
+      <c r="D7" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="214"/>
-      <c r="F7" s="213"/>
-      <c r="G7" s="212" t="s">
+      <c r="E7" s="180"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="178" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="214"/>
-      <c r="I7" s="213"/>
-      <c r="J7" s="212" t="s">
+      <c r="H7" s="180"/>
+      <c r="I7" s="179"/>
+      <c r="J7" s="178" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="214"/>
-      <c r="L7" s="214"/>
-      <c r="M7" s="214"/>
-      <c r="N7" s="214"/>
-      <c r="O7" s="214"/>
-      <c r="P7" s="213"/>
-      <c r="Q7" s="212" t="s">
+      <c r="K7" s="180"/>
+      <c r="L7" s="180"/>
+      <c r="M7" s="180"/>
+      <c r="N7" s="180"/>
+      <c r="O7" s="180"/>
+      <c r="P7" s="179"/>
+      <c r="Q7" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="214"/>
-      <c r="S7" s="214"/>
-      <c r="T7" s="214"/>
-      <c r="U7" s="214"/>
-      <c r="V7" s="214"/>
-      <c r="W7" s="214"/>
-      <c r="X7" s="214"/>
-      <c r="Y7" s="214"/>
-      <c r="Z7" s="214"/>
-      <c r="AA7" s="214"/>
-      <c r="AB7" s="214"/>
-      <c r="AC7" s="214"/>
-      <c r="AD7" s="214"/>
-      <c r="AE7" s="213"/>
-      <c r="AF7" s="212" t="s">
+      <c r="R7" s="180"/>
+      <c r="S7" s="180"/>
+      <c r="T7" s="180"/>
+      <c r="U7" s="180"/>
+      <c r="V7" s="180"/>
+      <c r="W7" s="180"/>
+      <c r="X7" s="180"/>
+      <c r="Y7" s="180"/>
+      <c r="Z7" s="180"/>
+      <c r="AA7" s="180"/>
+      <c r="AB7" s="180"/>
+      <c r="AC7" s="180"/>
+      <c r="AD7" s="180"/>
+      <c r="AE7" s="179"/>
+      <c r="AF7" s="178" t="s">
         <v>51</v>
       </c>
-      <c r="AG7" s="214"/>
-      <c r="AH7" s="214"/>
-      <c r="AI7" s="213"/>
+      <c r="AG7" s="180"/>
+      <c r="AH7" s="180"/>
+      <c r="AI7" s="179"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="223" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="201"/>
-      <c r="D8" s="202">
+      <c r="C8" s="224"/>
+      <c r="D8" s="225">
         <v>43336</v>
       </c>
-      <c r="E8" s="203"/>
-      <c r="F8" s="204"/>
-      <c r="G8" s="200" t="s">
+      <c r="E8" s="226"/>
+      <c r="F8" s="227"/>
+      <c r="G8" s="223" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="205"/>
-      <c r="I8" s="201"/>
-      <c r="J8" s="206" t="s">
+      <c r="H8" s="228"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="229" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="207"/>
-      <c r="L8" s="207"/>
-      <c r="M8" s="207"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="207"/>
-      <c r="P8" s="208"/>
-      <c r="Q8" s="206" t="s">
+      <c r="K8" s="230"/>
+      <c r="L8" s="230"/>
+      <c r="M8" s="230"/>
+      <c r="N8" s="230"/>
+      <c r="O8" s="230"/>
+      <c r="P8" s="231"/>
+      <c r="Q8" s="229" t="s">
         <v>60</v>
       </c>
-      <c r="R8" s="207"/>
-      <c r="S8" s="207"/>
-      <c r="T8" s="207"/>
-      <c r="U8" s="207"/>
-      <c r="V8" s="207"/>
-      <c r="W8" s="207"/>
-      <c r="X8" s="207"/>
-      <c r="Y8" s="207"/>
-      <c r="Z8" s="207"/>
-      <c r="AA8" s="207"/>
-      <c r="AB8" s="207"/>
-      <c r="AC8" s="207"/>
-      <c r="AD8" s="207"/>
-      <c r="AE8" s="208"/>
+      <c r="R8" s="230"/>
+      <c r="S8" s="230"/>
+      <c r="T8" s="230"/>
+      <c r="U8" s="230"/>
+      <c r="V8" s="230"/>
+      <c r="W8" s="230"/>
+      <c r="X8" s="230"/>
+      <c r="Y8" s="230"/>
+      <c r="Z8" s="230"/>
+      <c r="AA8" s="230"/>
+      <c r="AB8" s="230"/>
+      <c r="AC8" s="230"/>
+      <c r="AD8" s="230"/>
+      <c r="AE8" s="231"/>
       <c r="AF8" s="25" t="s">
         <v>61</v>
       </c>
@@ -13306,946 +13306,1101 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="188" t="s">
+      <c r="B9" s="211" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="189"/>
-      <c r="D9" s="190">
+      <c r="C9" s="212"/>
+      <c r="D9" s="213">
         <v>44852</v>
       </c>
-      <c r="E9" s="191"/>
-      <c r="F9" s="192"/>
-      <c r="G9" s="190" t="s">
+      <c r="E9" s="214"/>
+      <c r="F9" s="215"/>
+      <c r="G9" s="213" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="193"/>
-      <c r="I9" s="189"/>
-      <c r="J9" s="194" t="s">
+      <c r="H9" s="216"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="217" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="195"/>
-      <c r="L9" s="195"/>
-      <c r="M9" s="195"/>
-      <c r="N9" s="195"/>
-      <c r="O9" s="195"/>
-      <c r="P9" s="196"/>
-      <c r="Q9" s="194" t="s">
+      <c r="K9" s="218"/>
+      <c r="L9" s="218"/>
+      <c r="M9" s="218"/>
+      <c r="N9" s="218"/>
+      <c r="O9" s="218"/>
+      <c r="P9" s="219"/>
+      <c r="Q9" s="217" t="s">
         <v>67</v>
       </c>
-      <c r="R9" s="197"/>
-      <c r="S9" s="197"/>
-      <c r="T9" s="197"/>
-      <c r="U9" s="197"/>
-      <c r="V9" s="197"/>
-      <c r="W9" s="197"/>
-      <c r="X9" s="197"/>
-      <c r="Y9" s="197"/>
-      <c r="Z9" s="197"/>
-      <c r="AA9" s="197"/>
-      <c r="AB9" s="197"/>
-      <c r="AC9" s="197"/>
-      <c r="AD9" s="197"/>
-      <c r="AE9" s="198"/>
-      <c r="AF9" s="199" t="s">
+      <c r="R9" s="220"/>
+      <c r="S9" s="220"/>
+      <c r="T9" s="220"/>
+      <c r="U9" s="220"/>
+      <c r="V9" s="220"/>
+      <c r="W9" s="220"/>
+      <c r="X9" s="220"/>
+      <c r="Y9" s="220"/>
+      <c r="Z9" s="220"/>
+      <c r="AA9" s="220"/>
+      <c r="AB9" s="220"/>
+      <c r="AC9" s="220"/>
+      <c r="AD9" s="220"/>
+      <c r="AE9" s="221"/>
+      <c r="AF9" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="AG9" s="195"/>
-      <c r="AH9" s="195"/>
-      <c r="AI9" s="196"/>
+      <c r="AG9" s="218"/>
+      <c r="AH9" s="218"/>
+      <c r="AI9" s="219"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="175"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="179"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="180"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="181"/>
-      <c r="K10" s="182"/>
-      <c r="L10" s="182"/>
-      <c r="M10" s="182"/>
-      <c r="N10" s="182"/>
-      <c r="O10" s="182"/>
-      <c r="P10" s="183"/>
-      <c r="Q10" s="184"/>
-      <c r="R10" s="185"/>
-      <c r="S10" s="185"/>
-      <c r="T10" s="185"/>
-      <c r="U10" s="185"/>
-      <c r="V10" s="185"/>
-      <c r="W10" s="185"/>
-      <c r="X10" s="185"/>
-      <c r="Y10" s="185"/>
-      <c r="Z10" s="185"/>
-      <c r="AA10" s="185"/>
-      <c r="AB10" s="185"/>
-      <c r="AC10" s="185"/>
-      <c r="AD10" s="185"/>
-      <c r="AE10" s="186"/>
-      <c r="AF10" s="181"/>
-      <c r="AG10" s="182"/>
-      <c r="AH10" s="182"/>
-      <c r="AI10" s="183"/>
+      <c r="B10" s="232"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="232"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
+      <c r="N10" s="239"/>
+      <c r="O10" s="239"/>
+      <c r="P10" s="240"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="242"/>
+      <c r="S10" s="242"/>
+      <c r="T10" s="242"/>
+      <c r="U10" s="242"/>
+      <c r="V10" s="242"/>
+      <c r="W10" s="242"/>
+      <c r="X10" s="242"/>
+      <c r="Y10" s="242"/>
+      <c r="Z10" s="242"/>
+      <c r="AA10" s="242"/>
+      <c r="AB10" s="242"/>
+      <c r="AC10" s="242"/>
+      <c r="AD10" s="242"/>
+      <c r="AE10" s="243"/>
+      <c r="AF10" s="238"/>
+      <c r="AG10" s="239"/>
+      <c r="AH10" s="239"/>
+      <c r="AI10" s="240"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="175"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="177"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="179"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="180"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
-      <c r="L11" s="182"/>
-      <c r="M11" s="182"/>
-      <c r="N11" s="182"/>
-      <c r="O11" s="182"/>
-      <c r="P11" s="183"/>
-      <c r="Q11" s="184"/>
-      <c r="R11" s="185"/>
-      <c r="S11" s="185"/>
-      <c r="T11" s="185"/>
-      <c r="U11" s="185"/>
-      <c r="V11" s="185"/>
-      <c r="W11" s="185"/>
-      <c r="X11" s="185"/>
-      <c r="Y11" s="185"/>
-      <c r="Z11" s="185"/>
-      <c r="AA11" s="185"/>
-      <c r="AB11" s="185"/>
-      <c r="AC11" s="185"/>
-      <c r="AD11" s="185"/>
-      <c r="AE11" s="186"/>
-      <c r="AF11" s="181"/>
-      <c r="AG11" s="182"/>
-      <c r="AH11" s="182"/>
-      <c r="AI11" s="183"/>
+      <c r="B11" s="232"/>
+      <c r="C11" s="233"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="235"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="232"/>
+      <c r="H11" s="237"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="238"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
+      <c r="N11" s="239"/>
+      <c r="O11" s="239"/>
+      <c r="P11" s="240"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="242"/>
+      <c r="S11" s="242"/>
+      <c r="T11" s="242"/>
+      <c r="U11" s="242"/>
+      <c r="V11" s="242"/>
+      <c r="W11" s="242"/>
+      <c r="X11" s="242"/>
+      <c r="Y11" s="242"/>
+      <c r="Z11" s="242"/>
+      <c r="AA11" s="242"/>
+      <c r="AB11" s="242"/>
+      <c r="AC11" s="242"/>
+      <c r="AD11" s="242"/>
+      <c r="AE11" s="243"/>
+      <c r="AF11" s="238"/>
+      <c r="AG11" s="239"/>
+      <c r="AH11" s="239"/>
+      <c r="AI11" s="240"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="175"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="177"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="175"/>
-      <c r="H12" s="180"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="182"/>
-      <c r="L12" s="182"/>
-      <c r="M12" s="182"/>
-      <c r="N12" s="182"/>
-      <c r="O12" s="182"/>
-      <c r="P12" s="183"/>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185"/>
-      <c r="S12" s="185"/>
-      <c r="T12" s="185"/>
-      <c r="U12" s="185"/>
-      <c r="V12" s="185"/>
-      <c r="W12" s="185"/>
-      <c r="X12" s="185"/>
-      <c r="Y12" s="185"/>
-      <c r="Z12" s="185"/>
-      <c r="AA12" s="185"/>
-      <c r="AB12" s="185"/>
-      <c r="AC12" s="185"/>
-      <c r="AD12" s="185"/>
-      <c r="AE12" s="186"/>
-      <c r="AF12" s="181"/>
-      <c r="AG12" s="182"/>
-      <c r="AH12" s="182"/>
-      <c r="AI12" s="183"/>
+      <c r="B12" s="232"/>
+      <c r="C12" s="233"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="232"/>
+      <c r="H12" s="237"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="238"/>
+      <c r="K12" s="239"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="239"/>
+      <c r="N12" s="239"/>
+      <c r="O12" s="239"/>
+      <c r="P12" s="240"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="242"/>
+      <c r="S12" s="242"/>
+      <c r="T12" s="242"/>
+      <c r="U12" s="242"/>
+      <c r="V12" s="242"/>
+      <c r="W12" s="242"/>
+      <c r="X12" s="242"/>
+      <c r="Y12" s="242"/>
+      <c r="Z12" s="242"/>
+      <c r="AA12" s="242"/>
+      <c r="AB12" s="242"/>
+      <c r="AC12" s="242"/>
+      <c r="AD12" s="242"/>
+      <c r="AE12" s="243"/>
+      <c r="AF12" s="238"/>
+      <c r="AG12" s="239"/>
+      <c r="AH12" s="239"/>
+      <c r="AI12" s="240"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="177"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="180"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="182"/>
-      <c r="L13" s="182"/>
-      <c r="M13" s="182"/>
-      <c r="N13" s="182"/>
-      <c r="O13" s="182"/>
-      <c r="P13" s="183"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
-      <c r="S13" s="185"/>
-      <c r="T13" s="185"/>
-      <c r="U13" s="185"/>
-      <c r="V13" s="185"/>
-      <c r="W13" s="185"/>
-      <c r="X13" s="185"/>
-      <c r="Y13" s="185"/>
-      <c r="Z13" s="185"/>
-      <c r="AA13" s="185"/>
-      <c r="AB13" s="185"/>
-      <c r="AC13" s="185"/>
-      <c r="AD13" s="185"/>
-      <c r="AE13" s="186"/>
-      <c r="AF13" s="181"/>
-      <c r="AG13" s="182"/>
-      <c r="AH13" s="182"/>
-      <c r="AI13" s="183"/>
+      <c r="B13" s="232"/>
+      <c r="C13" s="233"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="237"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="238"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
+      <c r="M13" s="239"/>
+      <c r="N13" s="239"/>
+      <c r="O13" s="239"/>
+      <c r="P13" s="240"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="242"/>
+      <c r="S13" s="242"/>
+      <c r="T13" s="242"/>
+      <c r="U13" s="242"/>
+      <c r="V13" s="242"/>
+      <c r="W13" s="242"/>
+      <c r="X13" s="242"/>
+      <c r="Y13" s="242"/>
+      <c r="Z13" s="242"/>
+      <c r="AA13" s="242"/>
+      <c r="AB13" s="242"/>
+      <c r="AC13" s="242"/>
+      <c r="AD13" s="242"/>
+      <c r="AE13" s="243"/>
+      <c r="AF13" s="238"/>
+      <c r="AG13" s="239"/>
+      <c r="AH13" s="239"/>
+      <c r="AI13" s="240"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="175"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="179"/>
-      <c r="G14" s="175"/>
-      <c r="H14" s="180"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="181"/>
-      <c r="K14" s="182"/>
-      <c r="L14" s="182"/>
-      <c r="M14" s="182"/>
-      <c r="N14" s="182"/>
-      <c r="O14" s="182"/>
-      <c r="P14" s="183"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
-      <c r="S14" s="185"/>
-      <c r="T14" s="185"/>
-      <c r="U14" s="185"/>
-      <c r="V14" s="185"/>
-      <c r="W14" s="185"/>
-      <c r="X14" s="185"/>
-      <c r="Y14" s="185"/>
-      <c r="Z14" s="185"/>
-      <c r="AA14" s="185"/>
-      <c r="AB14" s="185"/>
-      <c r="AC14" s="185"/>
-      <c r="AD14" s="185"/>
-      <c r="AE14" s="186"/>
-      <c r="AF14" s="181"/>
-      <c r="AG14" s="182"/>
-      <c r="AH14" s="182"/>
-      <c r="AI14" s="183"/>
+      <c r="B14" s="232"/>
+      <c r="C14" s="233"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="237"/>
+      <c r="I14" s="233"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="239"/>
+      <c r="L14" s="239"/>
+      <c r="M14" s="239"/>
+      <c r="N14" s="239"/>
+      <c r="O14" s="239"/>
+      <c r="P14" s="240"/>
+      <c r="Q14" s="241"/>
+      <c r="R14" s="242"/>
+      <c r="S14" s="242"/>
+      <c r="T14" s="242"/>
+      <c r="U14" s="242"/>
+      <c r="V14" s="242"/>
+      <c r="W14" s="242"/>
+      <c r="X14" s="242"/>
+      <c r="Y14" s="242"/>
+      <c r="Z14" s="242"/>
+      <c r="AA14" s="242"/>
+      <c r="AB14" s="242"/>
+      <c r="AC14" s="242"/>
+      <c r="AD14" s="242"/>
+      <c r="AE14" s="243"/>
+      <c r="AF14" s="238"/>
+      <c r="AG14" s="239"/>
+      <c r="AH14" s="239"/>
+      <c r="AI14" s="240"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="175"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="177"/>
-      <c r="E15" s="178"/>
-      <c r="F15" s="179"/>
-      <c r="G15" s="175"/>
-      <c r="H15" s="180"/>
-      <c r="I15" s="176"/>
-      <c r="J15" s="181"/>
-      <c r="K15" s="182"/>
-      <c r="L15" s="182"/>
-      <c r="M15" s="182"/>
-      <c r="N15" s="182"/>
-      <c r="O15" s="182"/>
-      <c r="P15" s="183"/>
-      <c r="Q15" s="184"/>
-      <c r="R15" s="185"/>
-      <c r="S15" s="185"/>
-      <c r="T15" s="185"/>
-      <c r="U15" s="185"/>
-      <c r="V15" s="185"/>
-      <c r="W15" s="185"/>
-      <c r="X15" s="185"/>
-      <c r="Y15" s="185"/>
-      <c r="Z15" s="185"/>
-      <c r="AA15" s="185"/>
-      <c r="AB15" s="185"/>
-      <c r="AC15" s="185"/>
-      <c r="AD15" s="185"/>
-      <c r="AE15" s="186"/>
-      <c r="AF15" s="181"/>
-      <c r="AG15" s="182"/>
-      <c r="AH15" s="182"/>
-      <c r="AI15" s="183"/>
+      <c r="B15" s="232"/>
+      <c r="C15" s="233"/>
+      <c r="D15" s="234"/>
+      <c r="E15" s="235"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="232"/>
+      <c r="H15" s="237"/>
+      <c r="I15" s="233"/>
+      <c r="J15" s="238"/>
+      <c r="K15" s="239"/>
+      <c r="L15" s="239"/>
+      <c r="M15" s="239"/>
+      <c r="N15" s="239"/>
+      <c r="O15" s="239"/>
+      <c r="P15" s="240"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="242"/>
+      <c r="S15" s="242"/>
+      <c r="T15" s="242"/>
+      <c r="U15" s="242"/>
+      <c r="V15" s="242"/>
+      <c r="W15" s="242"/>
+      <c r="X15" s="242"/>
+      <c r="Y15" s="242"/>
+      <c r="Z15" s="242"/>
+      <c r="AA15" s="242"/>
+      <c r="AB15" s="242"/>
+      <c r="AC15" s="242"/>
+      <c r="AD15" s="242"/>
+      <c r="AE15" s="243"/>
+      <c r="AF15" s="238"/>
+      <c r="AG15" s="239"/>
+      <c r="AH15" s="239"/>
+      <c r="AI15" s="240"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="175"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="177"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="179"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="180"/>
-      <c r="I16" s="176"/>
-      <c r="J16" s="181"/>
-      <c r="K16" s="182"/>
-      <c r="L16" s="182"/>
-      <c r="M16" s="182"/>
-      <c r="N16" s="182"/>
-      <c r="O16" s="182"/>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="184"/>
-      <c r="R16" s="185"/>
-      <c r="S16" s="185"/>
-      <c r="T16" s="185"/>
-      <c r="U16" s="185"/>
-      <c r="V16" s="185"/>
-      <c r="W16" s="185"/>
-      <c r="X16" s="185"/>
-      <c r="Y16" s="185"/>
-      <c r="Z16" s="185"/>
-      <c r="AA16" s="185"/>
-      <c r="AB16" s="185"/>
-      <c r="AC16" s="185"/>
-      <c r="AD16" s="185"/>
-      <c r="AE16" s="186"/>
-      <c r="AF16" s="181"/>
-      <c r="AG16" s="182"/>
-      <c r="AH16" s="182"/>
-      <c r="AI16" s="183"/>
+      <c r="B16" s="232"/>
+      <c r="C16" s="233"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="233"/>
+      <c r="J16" s="238"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="239"/>
+      <c r="M16" s="239"/>
+      <c r="N16" s="239"/>
+      <c r="O16" s="239"/>
+      <c r="P16" s="240"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="242"/>
+      <c r="S16" s="242"/>
+      <c r="T16" s="242"/>
+      <c r="U16" s="242"/>
+      <c r="V16" s="242"/>
+      <c r="W16" s="242"/>
+      <c r="X16" s="242"/>
+      <c r="Y16" s="242"/>
+      <c r="Z16" s="242"/>
+      <c r="AA16" s="242"/>
+      <c r="AB16" s="242"/>
+      <c r="AC16" s="242"/>
+      <c r="AD16" s="242"/>
+      <c r="AE16" s="243"/>
+      <c r="AF16" s="238"/>
+      <c r="AG16" s="239"/>
+      <c r="AH16" s="239"/>
+      <c r="AI16" s="240"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="175"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="175"/>
-      <c r="H17" s="180"/>
-      <c r="I17" s="176"/>
-      <c r="J17" s="181"/>
-      <c r="K17" s="182"/>
-      <c r="L17" s="182"/>
-      <c r="M17" s="182"/>
-      <c r="N17" s="182"/>
-      <c r="O17" s="182"/>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="184"/>
-      <c r="R17" s="185"/>
-      <c r="S17" s="185"/>
-      <c r="T17" s="185"/>
-      <c r="U17" s="185"/>
-      <c r="V17" s="185"/>
-      <c r="W17" s="185"/>
-      <c r="X17" s="185"/>
-      <c r="Y17" s="185"/>
-      <c r="Z17" s="185"/>
-      <c r="AA17" s="185"/>
-      <c r="AB17" s="185"/>
-      <c r="AC17" s="185"/>
-      <c r="AD17" s="185"/>
-      <c r="AE17" s="186"/>
-      <c r="AF17" s="181"/>
-      <c r="AG17" s="182"/>
-      <c r="AH17" s="182"/>
-      <c r="AI17" s="183"/>
+      <c r="B17" s="232"/>
+      <c r="C17" s="233"/>
+      <c r="D17" s="234"/>
+      <c r="E17" s="235"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="232"/>
+      <c r="H17" s="237"/>
+      <c r="I17" s="233"/>
+      <c r="J17" s="238"/>
+      <c r="K17" s="239"/>
+      <c r="L17" s="239"/>
+      <c r="M17" s="239"/>
+      <c r="N17" s="239"/>
+      <c r="O17" s="239"/>
+      <c r="P17" s="240"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="242"/>
+      <c r="S17" s="242"/>
+      <c r="T17" s="242"/>
+      <c r="U17" s="242"/>
+      <c r="V17" s="242"/>
+      <c r="W17" s="242"/>
+      <c r="X17" s="242"/>
+      <c r="Y17" s="242"/>
+      <c r="Z17" s="242"/>
+      <c r="AA17" s="242"/>
+      <c r="AB17" s="242"/>
+      <c r="AC17" s="242"/>
+      <c r="AD17" s="242"/>
+      <c r="AE17" s="243"/>
+      <c r="AF17" s="238"/>
+      <c r="AG17" s="239"/>
+      <c r="AH17" s="239"/>
+      <c r="AI17" s="240"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="175"/>
-      <c r="C18" s="176"/>
-      <c r="D18" s="177"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="179"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="180"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="181"/>
-      <c r="K18" s="182"/>
-      <c r="L18" s="182"/>
-      <c r="M18" s="182"/>
-      <c r="N18" s="182"/>
-      <c r="O18" s="182"/>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="184"/>
-      <c r="R18" s="185"/>
-      <c r="S18" s="185"/>
-      <c r="T18" s="185"/>
-      <c r="U18" s="185"/>
-      <c r="V18" s="185"/>
-      <c r="W18" s="185"/>
-      <c r="X18" s="185"/>
-      <c r="Y18" s="185"/>
-      <c r="Z18" s="185"/>
-      <c r="AA18" s="185"/>
-      <c r="AB18" s="185"/>
-      <c r="AC18" s="185"/>
-      <c r="AD18" s="185"/>
-      <c r="AE18" s="186"/>
-      <c r="AF18" s="181"/>
-      <c r="AG18" s="182"/>
-      <c r="AH18" s="182"/>
-      <c r="AI18" s="183"/>
+      <c r="B18" s="232"/>
+      <c r="C18" s="233"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="237"/>
+      <c r="I18" s="233"/>
+      <c r="J18" s="238"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
+      <c r="M18" s="239"/>
+      <c r="N18" s="239"/>
+      <c r="O18" s="239"/>
+      <c r="P18" s="240"/>
+      <c r="Q18" s="241"/>
+      <c r="R18" s="242"/>
+      <c r="S18" s="242"/>
+      <c r="T18" s="242"/>
+      <c r="U18" s="242"/>
+      <c r="V18" s="242"/>
+      <c r="W18" s="242"/>
+      <c r="X18" s="242"/>
+      <c r="Y18" s="242"/>
+      <c r="Z18" s="242"/>
+      <c r="AA18" s="242"/>
+      <c r="AB18" s="242"/>
+      <c r="AC18" s="242"/>
+      <c r="AD18" s="242"/>
+      <c r="AE18" s="243"/>
+      <c r="AF18" s="238"/>
+      <c r="AG18" s="239"/>
+      <c r="AH18" s="239"/>
+      <c r="AI18" s="240"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="177"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="179"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="180"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="181"/>
-      <c r="K19" s="182"/>
-      <c r="L19" s="182"/>
-      <c r="M19" s="182"/>
-      <c r="N19" s="182"/>
-      <c r="O19" s="182"/>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="184"/>
-      <c r="R19" s="185"/>
-      <c r="S19" s="185"/>
-      <c r="T19" s="185"/>
-      <c r="U19" s="185"/>
-      <c r="V19" s="185"/>
-      <c r="W19" s="185"/>
-      <c r="X19" s="185"/>
-      <c r="Y19" s="185"/>
-      <c r="Z19" s="185"/>
-      <c r="AA19" s="185"/>
-      <c r="AB19" s="185"/>
-      <c r="AC19" s="185"/>
-      <c r="AD19" s="185"/>
-      <c r="AE19" s="186"/>
-      <c r="AF19" s="181"/>
-      <c r="AG19" s="182"/>
-      <c r="AH19" s="182"/>
-      <c r="AI19" s="183"/>
+      <c r="B19" s="232"/>
+      <c r="C19" s="233"/>
+      <c r="D19" s="234"/>
+      <c r="E19" s="235"/>
+      <c r="F19" s="236"/>
+      <c r="G19" s="232"/>
+      <c r="H19" s="237"/>
+      <c r="I19" s="233"/>
+      <c r="J19" s="238"/>
+      <c r="K19" s="239"/>
+      <c r="L19" s="239"/>
+      <c r="M19" s="239"/>
+      <c r="N19" s="239"/>
+      <c r="O19" s="239"/>
+      <c r="P19" s="240"/>
+      <c r="Q19" s="241"/>
+      <c r="R19" s="242"/>
+      <c r="S19" s="242"/>
+      <c r="T19" s="242"/>
+      <c r="U19" s="242"/>
+      <c r="V19" s="242"/>
+      <c r="W19" s="242"/>
+      <c r="X19" s="242"/>
+      <c r="Y19" s="242"/>
+      <c r="Z19" s="242"/>
+      <c r="AA19" s="242"/>
+      <c r="AB19" s="242"/>
+      <c r="AC19" s="242"/>
+      <c r="AD19" s="242"/>
+      <c r="AE19" s="243"/>
+      <c r="AF19" s="238"/>
+      <c r="AG19" s="239"/>
+      <c r="AH19" s="239"/>
+      <c r="AI19" s="240"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="176"/>
-      <c r="D20" s="177"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="180"/>
-      <c r="I20" s="176"/>
-      <c r="J20" s="181"/>
-      <c r="K20" s="182"/>
-      <c r="L20" s="182"/>
-      <c r="M20" s="182"/>
-      <c r="N20" s="182"/>
-      <c r="O20" s="182"/>
-      <c r="P20" s="183"/>
-      <c r="Q20" s="184"/>
-      <c r="R20" s="185"/>
-      <c r="S20" s="185"/>
-      <c r="T20" s="185"/>
-      <c r="U20" s="185"/>
-      <c r="V20" s="185"/>
-      <c r="W20" s="185"/>
-      <c r="X20" s="185"/>
-      <c r="Y20" s="185"/>
-      <c r="Z20" s="185"/>
-      <c r="AA20" s="185"/>
-      <c r="AB20" s="185"/>
-      <c r="AC20" s="185"/>
-      <c r="AD20" s="185"/>
-      <c r="AE20" s="186"/>
-      <c r="AF20" s="181"/>
-      <c r="AG20" s="182"/>
-      <c r="AH20" s="182"/>
-      <c r="AI20" s="183"/>
+      <c r="B20" s="232"/>
+      <c r="C20" s="233"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="235"/>
+      <c r="F20" s="236"/>
+      <c r="G20" s="232"/>
+      <c r="H20" s="237"/>
+      <c r="I20" s="233"/>
+      <c r="J20" s="238"/>
+      <c r="K20" s="239"/>
+      <c r="L20" s="239"/>
+      <c r="M20" s="239"/>
+      <c r="N20" s="239"/>
+      <c r="O20" s="239"/>
+      <c r="P20" s="240"/>
+      <c r="Q20" s="241"/>
+      <c r="R20" s="242"/>
+      <c r="S20" s="242"/>
+      <c r="T20" s="242"/>
+      <c r="U20" s="242"/>
+      <c r="V20" s="242"/>
+      <c r="W20" s="242"/>
+      <c r="X20" s="242"/>
+      <c r="Y20" s="242"/>
+      <c r="Z20" s="242"/>
+      <c r="AA20" s="242"/>
+      <c r="AB20" s="242"/>
+      <c r="AC20" s="242"/>
+      <c r="AD20" s="242"/>
+      <c r="AE20" s="243"/>
+      <c r="AF20" s="238"/>
+      <c r="AG20" s="239"/>
+      <c r="AH20" s="239"/>
+      <c r="AI20" s="240"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="177"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="180"/>
-      <c r="I21" s="176"/>
-      <c r="J21" s="181"/>
-      <c r="K21" s="182"/>
-      <c r="L21" s="182"/>
-      <c r="M21" s="182"/>
-      <c r="N21" s="182"/>
-      <c r="O21" s="182"/>
-      <c r="P21" s="183"/>
-      <c r="Q21" s="184"/>
-      <c r="R21" s="185"/>
-      <c r="S21" s="185"/>
-      <c r="T21" s="185"/>
-      <c r="U21" s="185"/>
-      <c r="V21" s="185"/>
-      <c r="W21" s="185"/>
-      <c r="X21" s="185"/>
-      <c r="Y21" s="185"/>
-      <c r="Z21" s="185"/>
-      <c r="AA21" s="185"/>
-      <c r="AB21" s="185"/>
-      <c r="AC21" s="185"/>
-      <c r="AD21" s="185"/>
-      <c r="AE21" s="186"/>
-      <c r="AF21" s="181"/>
-      <c r="AG21" s="182"/>
-      <c r="AH21" s="182"/>
-      <c r="AI21" s="183"/>
+      <c r="B21" s="232"/>
+      <c r="C21" s="233"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="232"/>
+      <c r="H21" s="237"/>
+      <c r="I21" s="233"/>
+      <c r="J21" s="238"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="239"/>
+      <c r="M21" s="239"/>
+      <c r="N21" s="239"/>
+      <c r="O21" s="239"/>
+      <c r="P21" s="240"/>
+      <c r="Q21" s="241"/>
+      <c r="R21" s="242"/>
+      <c r="S21" s="242"/>
+      <c r="T21" s="242"/>
+      <c r="U21" s="242"/>
+      <c r="V21" s="242"/>
+      <c r="W21" s="242"/>
+      <c r="X21" s="242"/>
+      <c r="Y21" s="242"/>
+      <c r="Z21" s="242"/>
+      <c r="AA21" s="242"/>
+      <c r="AB21" s="242"/>
+      <c r="AC21" s="242"/>
+      <c r="AD21" s="242"/>
+      <c r="AE21" s="243"/>
+      <c r="AF21" s="238"/>
+      <c r="AG21" s="239"/>
+      <c r="AH21" s="239"/>
+      <c r="AI21" s="240"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="175"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="177"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="180"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="181"/>
-      <c r="K22" s="182"/>
-      <c r="L22" s="182"/>
-      <c r="M22" s="182"/>
-      <c r="N22" s="182"/>
-      <c r="O22" s="182"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="184"/>
-      <c r="R22" s="185"/>
-      <c r="S22" s="185"/>
-      <c r="T22" s="185"/>
-      <c r="U22" s="185"/>
-      <c r="V22" s="185"/>
-      <c r="W22" s="185"/>
-      <c r="X22" s="185"/>
-      <c r="Y22" s="185"/>
-      <c r="Z22" s="185"/>
-      <c r="AA22" s="185"/>
-      <c r="AB22" s="185"/>
-      <c r="AC22" s="185"/>
-      <c r="AD22" s="185"/>
-      <c r="AE22" s="186"/>
-      <c r="AF22" s="181"/>
-      <c r="AG22" s="182"/>
-      <c r="AH22" s="182"/>
-      <c r="AI22" s="183"/>
+      <c r="B22" s="232"/>
+      <c r="C22" s="233"/>
+      <c r="D22" s="234"/>
+      <c r="E22" s="235"/>
+      <c r="F22" s="236"/>
+      <c r="G22" s="232"/>
+      <c r="H22" s="237"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="238"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="239"/>
+      <c r="M22" s="239"/>
+      <c r="N22" s="239"/>
+      <c r="O22" s="239"/>
+      <c r="P22" s="240"/>
+      <c r="Q22" s="241"/>
+      <c r="R22" s="242"/>
+      <c r="S22" s="242"/>
+      <c r="T22" s="242"/>
+      <c r="U22" s="242"/>
+      <c r="V22" s="242"/>
+      <c r="W22" s="242"/>
+      <c r="X22" s="242"/>
+      <c r="Y22" s="242"/>
+      <c r="Z22" s="242"/>
+      <c r="AA22" s="242"/>
+      <c r="AB22" s="242"/>
+      <c r="AC22" s="242"/>
+      <c r="AD22" s="242"/>
+      <c r="AE22" s="243"/>
+      <c r="AF22" s="238"/>
+      <c r="AG22" s="239"/>
+      <c r="AH22" s="239"/>
+      <c r="AI22" s="240"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="175"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="177"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="180"/>
-      <c r="I23" s="176"/>
-      <c r="J23" s="181"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="182"/>
-      <c r="M23" s="182"/>
-      <c r="N23" s="182"/>
-      <c r="O23" s="182"/>
-      <c r="P23" s="183"/>
-      <c r="Q23" s="184"/>
-      <c r="R23" s="185"/>
-      <c r="S23" s="185"/>
-      <c r="T23" s="185"/>
-      <c r="U23" s="185"/>
-      <c r="V23" s="185"/>
-      <c r="W23" s="185"/>
-      <c r="X23" s="185"/>
-      <c r="Y23" s="185"/>
-      <c r="Z23" s="185"/>
-      <c r="AA23" s="185"/>
-      <c r="AB23" s="185"/>
-      <c r="AC23" s="185"/>
-      <c r="AD23" s="185"/>
-      <c r="AE23" s="186"/>
-      <c r="AF23" s="181"/>
-      <c r="AG23" s="182"/>
-      <c r="AH23" s="182"/>
-      <c r="AI23" s="183"/>
+      <c r="B23" s="232"/>
+      <c r="C23" s="233"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="235"/>
+      <c r="F23" s="236"/>
+      <c r="G23" s="232"/>
+      <c r="H23" s="237"/>
+      <c r="I23" s="233"/>
+      <c r="J23" s="238"/>
+      <c r="K23" s="239"/>
+      <c r="L23" s="239"/>
+      <c r="M23" s="239"/>
+      <c r="N23" s="239"/>
+      <c r="O23" s="239"/>
+      <c r="P23" s="240"/>
+      <c r="Q23" s="241"/>
+      <c r="R23" s="242"/>
+      <c r="S23" s="242"/>
+      <c r="T23" s="242"/>
+      <c r="U23" s="242"/>
+      <c r="V23" s="242"/>
+      <c r="W23" s="242"/>
+      <c r="X23" s="242"/>
+      <c r="Y23" s="242"/>
+      <c r="Z23" s="242"/>
+      <c r="AA23" s="242"/>
+      <c r="AB23" s="242"/>
+      <c r="AC23" s="242"/>
+      <c r="AD23" s="242"/>
+      <c r="AE23" s="243"/>
+      <c r="AF23" s="238"/>
+      <c r="AG23" s="239"/>
+      <c r="AH23" s="239"/>
+      <c r="AI23" s="240"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="175"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="177"/>
-      <c r="E24" s="178"/>
-      <c r="F24" s="179"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="180"/>
-      <c r="I24" s="176"/>
-      <c r="J24" s="181"/>
-      <c r="K24" s="182"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="182"/>
-      <c r="N24" s="182"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="183"/>
-      <c r="Q24" s="184"/>
-      <c r="R24" s="185"/>
-      <c r="S24" s="185"/>
-      <c r="T24" s="185"/>
-      <c r="U24" s="185"/>
-      <c r="V24" s="185"/>
-      <c r="W24" s="185"/>
-      <c r="X24" s="185"/>
-      <c r="Y24" s="185"/>
-      <c r="Z24" s="185"/>
-      <c r="AA24" s="185"/>
-      <c r="AB24" s="185"/>
-      <c r="AC24" s="185"/>
-      <c r="AD24" s="185"/>
-      <c r="AE24" s="186"/>
-      <c r="AF24" s="181"/>
-      <c r="AG24" s="182"/>
-      <c r="AH24" s="182"/>
-      <c r="AI24" s="183"/>
+      <c r="B24" s="232"/>
+      <c r="C24" s="233"/>
+      <c r="D24" s="234"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="236"/>
+      <c r="G24" s="232"/>
+      <c r="H24" s="237"/>
+      <c r="I24" s="233"/>
+      <c r="J24" s="238"/>
+      <c r="K24" s="239"/>
+      <c r="L24" s="239"/>
+      <c r="M24" s="239"/>
+      <c r="N24" s="239"/>
+      <c r="O24" s="239"/>
+      <c r="P24" s="240"/>
+      <c r="Q24" s="241"/>
+      <c r="R24" s="242"/>
+      <c r="S24" s="242"/>
+      <c r="T24" s="242"/>
+      <c r="U24" s="242"/>
+      <c r="V24" s="242"/>
+      <c r="W24" s="242"/>
+      <c r="X24" s="242"/>
+      <c r="Y24" s="242"/>
+      <c r="Z24" s="242"/>
+      <c r="AA24" s="242"/>
+      <c r="AB24" s="242"/>
+      <c r="AC24" s="242"/>
+      <c r="AD24" s="242"/>
+      <c r="AE24" s="243"/>
+      <c r="AF24" s="238"/>
+      <c r="AG24" s="239"/>
+      <c r="AH24" s="239"/>
+      <c r="AI24" s="240"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="177"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="179"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="180"/>
-      <c r="I25" s="176"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="182"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="182"/>
-      <c r="N25" s="182"/>
-      <c r="O25" s="182"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="184"/>
-      <c r="R25" s="185"/>
-      <c r="S25" s="185"/>
-      <c r="T25" s="185"/>
-      <c r="U25" s="185"/>
-      <c r="V25" s="185"/>
-      <c r="W25" s="185"/>
-      <c r="X25" s="185"/>
-      <c r="Y25" s="185"/>
-      <c r="Z25" s="185"/>
-      <c r="AA25" s="185"/>
-      <c r="AB25" s="185"/>
-      <c r="AC25" s="185"/>
-      <c r="AD25" s="185"/>
-      <c r="AE25" s="186"/>
-      <c r="AF25" s="181"/>
-      <c r="AG25" s="182"/>
-      <c r="AH25" s="182"/>
-      <c r="AI25" s="183"/>
+      <c r="B25" s="232"/>
+      <c r="C25" s="233"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="236"/>
+      <c r="G25" s="232"/>
+      <c r="H25" s="237"/>
+      <c r="I25" s="233"/>
+      <c r="J25" s="238"/>
+      <c r="K25" s="239"/>
+      <c r="L25" s="239"/>
+      <c r="M25" s="239"/>
+      <c r="N25" s="239"/>
+      <c r="O25" s="239"/>
+      <c r="P25" s="240"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="242"/>
+      <c r="S25" s="242"/>
+      <c r="T25" s="242"/>
+      <c r="U25" s="242"/>
+      <c r="V25" s="242"/>
+      <c r="W25" s="242"/>
+      <c r="X25" s="242"/>
+      <c r="Y25" s="242"/>
+      <c r="Z25" s="242"/>
+      <c r="AA25" s="242"/>
+      <c r="AB25" s="242"/>
+      <c r="AC25" s="242"/>
+      <c r="AD25" s="242"/>
+      <c r="AE25" s="243"/>
+      <c r="AF25" s="238"/>
+      <c r="AG25" s="239"/>
+      <c r="AH25" s="239"/>
+      <c r="AI25" s="240"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="175"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="177"/>
-      <c r="E26" s="178"/>
-      <c r="F26" s="179"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="180"/>
-      <c r="I26" s="176"/>
-      <c r="J26" s="181"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="182"/>
-      <c r="M26" s="182"/>
-      <c r="N26" s="182"/>
-      <c r="O26" s="182"/>
-      <c r="P26" s="183"/>
-      <c r="Q26" s="184"/>
-      <c r="R26" s="185"/>
-      <c r="S26" s="185"/>
-      <c r="T26" s="185"/>
-      <c r="U26" s="185"/>
-      <c r="V26" s="185"/>
-      <c r="W26" s="185"/>
-      <c r="X26" s="185"/>
-      <c r="Y26" s="185"/>
-      <c r="Z26" s="185"/>
-      <c r="AA26" s="185"/>
-      <c r="AB26" s="185"/>
-      <c r="AC26" s="185"/>
-      <c r="AD26" s="185"/>
-      <c r="AE26" s="186"/>
-      <c r="AF26" s="181"/>
-      <c r="AG26" s="182"/>
-      <c r="AH26" s="182"/>
-      <c r="AI26" s="183"/>
+      <c r="B26" s="232"/>
+      <c r="C26" s="233"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="236"/>
+      <c r="G26" s="232"/>
+      <c r="H26" s="237"/>
+      <c r="I26" s="233"/>
+      <c r="J26" s="238"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
+      <c r="M26" s="239"/>
+      <c r="N26" s="239"/>
+      <c r="O26" s="239"/>
+      <c r="P26" s="240"/>
+      <c r="Q26" s="241"/>
+      <c r="R26" s="242"/>
+      <c r="S26" s="242"/>
+      <c r="T26" s="242"/>
+      <c r="U26" s="242"/>
+      <c r="V26" s="242"/>
+      <c r="W26" s="242"/>
+      <c r="X26" s="242"/>
+      <c r="Y26" s="242"/>
+      <c r="Z26" s="242"/>
+      <c r="AA26" s="242"/>
+      <c r="AB26" s="242"/>
+      <c r="AC26" s="242"/>
+      <c r="AD26" s="242"/>
+      <c r="AE26" s="243"/>
+      <c r="AF26" s="238"/>
+      <c r="AG26" s="239"/>
+      <c r="AH26" s="239"/>
+      <c r="AI26" s="240"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="175"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="179"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="180"/>
-      <c r="I27" s="176"/>
-      <c r="J27" s="181"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="182"/>
-      <c r="M27" s="182"/>
-      <c r="N27" s="182"/>
-      <c r="O27" s="182"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="184"/>
-      <c r="R27" s="185"/>
-      <c r="S27" s="185"/>
-      <c r="T27" s="185"/>
-      <c r="U27" s="185"/>
-      <c r="V27" s="185"/>
-      <c r="W27" s="185"/>
-      <c r="X27" s="185"/>
-      <c r="Y27" s="185"/>
-      <c r="Z27" s="185"/>
-      <c r="AA27" s="185"/>
-      <c r="AB27" s="185"/>
-      <c r="AC27" s="185"/>
-      <c r="AD27" s="185"/>
-      <c r="AE27" s="186"/>
-      <c r="AF27" s="181"/>
-      <c r="AG27" s="182"/>
-      <c r="AH27" s="182"/>
-      <c r="AI27" s="183"/>
+      <c r="B27" s="232"/>
+      <c r="C27" s="233"/>
+      <c r="D27" s="234"/>
+      <c r="E27" s="235"/>
+      <c r="F27" s="236"/>
+      <c r="G27" s="232"/>
+      <c r="H27" s="237"/>
+      <c r="I27" s="233"/>
+      <c r="J27" s="238"/>
+      <c r="K27" s="239"/>
+      <c r="L27" s="239"/>
+      <c r="M27" s="239"/>
+      <c r="N27" s="239"/>
+      <c r="O27" s="239"/>
+      <c r="P27" s="240"/>
+      <c r="Q27" s="241"/>
+      <c r="R27" s="242"/>
+      <c r="S27" s="242"/>
+      <c r="T27" s="242"/>
+      <c r="U27" s="242"/>
+      <c r="V27" s="242"/>
+      <c r="W27" s="242"/>
+      <c r="X27" s="242"/>
+      <c r="Y27" s="242"/>
+      <c r="Z27" s="242"/>
+      <c r="AA27" s="242"/>
+      <c r="AB27" s="242"/>
+      <c r="AC27" s="242"/>
+      <c r="AD27" s="242"/>
+      <c r="AE27" s="243"/>
+      <c r="AF27" s="238"/>
+      <c r="AG27" s="239"/>
+      <c r="AH27" s="239"/>
+      <c r="AI27" s="240"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="175"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="177"/>
-      <c r="E28" s="178"/>
-      <c r="F28" s="179"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="180"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="181"/>
-      <c r="K28" s="182"/>
-      <c r="L28" s="182"/>
-      <c r="M28" s="182"/>
-      <c r="N28" s="182"/>
-      <c r="O28" s="182"/>
-      <c r="P28" s="183"/>
-      <c r="Q28" s="184"/>
-      <c r="R28" s="185"/>
-      <c r="S28" s="185"/>
-      <c r="T28" s="185"/>
-      <c r="U28" s="185"/>
-      <c r="V28" s="185"/>
-      <c r="W28" s="185"/>
-      <c r="X28" s="185"/>
-      <c r="Y28" s="185"/>
-      <c r="Z28" s="185"/>
-      <c r="AA28" s="185"/>
-      <c r="AB28" s="185"/>
-      <c r="AC28" s="185"/>
-      <c r="AD28" s="185"/>
-      <c r="AE28" s="186"/>
-      <c r="AF28" s="181"/>
-      <c r="AG28" s="182"/>
-      <c r="AH28" s="182"/>
-      <c r="AI28" s="183"/>
+      <c r="B28" s="232"/>
+      <c r="C28" s="233"/>
+      <c r="D28" s="234"/>
+      <c r="E28" s="235"/>
+      <c r="F28" s="236"/>
+      <c r="G28" s="232"/>
+      <c r="H28" s="237"/>
+      <c r="I28" s="233"/>
+      <c r="J28" s="238"/>
+      <c r="K28" s="239"/>
+      <c r="L28" s="239"/>
+      <c r="M28" s="239"/>
+      <c r="N28" s="239"/>
+      <c r="O28" s="239"/>
+      <c r="P28" s="240"/>
+      <c r="Q28" s="241"/>
+      <c r="R28" s="242"/>
+      <c r="S28" s="242"/>
+      <c r="T28" s="242"/>
+      <c r="U28" s="242"/>
+      <c r="V28" s="242"/>
+      <c r="W28" s="242"/>
+      <c r="X28" s="242"/>
+      <c r="Y28" s="242"/>
+      <c r="Z28" s="242"/>
+      <c r="AA28" s="242"/>
+      <c r="AB28" s="242"/>
+      <c r="AC28" s="242"/>
+      <c r="AD28" s="242"/>
+      <c r="AE28" s="243"/>
+      <c r="AF28" s="238"/>
+      <c r="AG28" s="239"/>
+      <c r="AH28" s="239"/>
+      <c r="AI28" s="240"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="175"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="177"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="180"/>
-      <c r="I29" s="176"/>
-      <c r="J29" s="181"/>
-      <c r="K29" s="182"/>
-      <c r="L29" s="182"/>
-      <c r="M29" s="182"/>
-      <c r="N29" s="182"/>
-      <c r="O29" s="182"/>
-      <c r="P29" s="183"/>
-      <c r="Q29" s="184"/>
-      <c r="R29" s="185"/>
-      <c r="S29" s="185"/>
-      <c r="T29" s="185"/>
-      <c r="U29" s="185"/>
-      <c r="V29" s="185"/>
-      <c r="W29" s="185"/>
-      <c r="X29" s="185"/>
-      <c r="Y29" s="185"/>
-      <c r="Z29" s="185"/>
-      <c r="AA29" s="185"/>
-      <c r="AB29" s="185"/>
-      <c r="AC29" s="185"/>
-      <c r="AD29" s="185"/>
-      <c r="AE29" s="186"/>
-      <c r="AF29" s="181"/>
-      <c r="AG29" s="182"/>
-      <c r="AH29" s="182"/>
-      <c r="AI29" s="183"/>
+      <c r="B29" s="232"/>
+      <c r="C29" s="233"/>
+      <c r="D29" s="234"/>
+      <c r="E29" s="235"/>
+      <c r="F29" s="236"/>
+      <c r="G29" s="232"/>
+      <c r="H29" s="237"/>
+      <c r="I29" s="233"/>
+      <c r="J29" s="238"/>
+      <c r="K29" s="239"/>
+      <c r="L29" s="239"/>
+      <c r="M29" s="239"/>
+      <c r="N29" s="239"/>
+      <c r="O29" s="239"/>
+      <c r="P29" s="240"/>
+      <c r="Q29" s="241"/>
+      <c r="R29" s="242"/>
+      <c r="S29" s="242"/>
+      <c r="T29" s="242"/>
+      <c r="U29" s="242"/>
+      <c r="V29" s="242"/>
+      <c r="W29" s="242"/>
+      <c r="X29" s="242"/>
+      <c r="Y29" s="242"/>
+      <c r="Z29" s="242"/>
+      <c r="AA29" s="242"/>
+      <c r="AB29" s="242"/>
+      <c r="AC29" s="242"/>
+      <c r="AD29" s="242"/>
+      <c r="AE29" s="243"/>
+      <c r="AF29" s="238"/>
+      <c r="AG29" s="239"/>
+      <c r="AH29" s="239"/>
+      <c r="AI29" s="240"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="175"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="177"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="180"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="181"/>
-      <c r="K30" s="182"/>
-      <c r="L30" s="182"/>
-      <c r="M30" s="182"/>
-      <c r="N30" s="182"/>
-      <c r="O30" s="182"/>
-      <c r="P30" s="183"/>
-      <c r="Q30" s="184"/>
-      <c r="R30" s="185"/>
-      <c r="S30" s="185"/>
-      <c r="T30" s="185"/>
-      <c r="U30" s="185"/>
-      <c r="V30" s="185"/>
-      <c r="W30" s="185"/>
-      <c r="X30" s="185"/>
-      <c r="Y30" s="185"/>
-      <c r="Z30" s="185"/>
-      <c r="AA30" s="185"/>
-      <c r="AB30" s="185"/>
-      <c r="AC30" s="185"/>
-      <c r="AD30" s="185"/>
-      <c r="AE30" s="186"/>
-      <c r="AF30" s="181"/>
-      <c r="AG30" s="182"/>
-      <c r="AH30" s="182"/>
-      <c r="AI30" s="183"/>
+      <c r="B30" s="232"/>
+      <c r="C30" s="233"/>
+      <c r="D30" s="234"/>
+      <c r="E30" s="235"/>
+      <c r="F30" s="236"/>
+      <c r="G30" s="232"/>
+      <c r="H30" s="237"/>
+      <c r="I30" s="233"/>
+      <c r="J30" s="238"/>
+      <c r="K30" s="239"/>
+      <c r="L30" s="239"/>
+      <c r="M30" s="239"/>
+      <c r="N30" s="239"/>
+      <c r="O30" s="239"/>
+      <c r="P30" s="240"/>
+      <c r="Q30" s="241"/>
+      <c r="R30" s="242"/>
+      <c r="S30" s="242"/>
+      <c r="T30" s="242"/>
+      <c r="U30" s="242"/>
+      <c r="V30" s="242"/>
+      <c r="W30" s="242"/>
+      <c r="X30" s="242"/>
+      <c r="Y30" s="242"/>
+      <c r="Z30" s="242"/>
+      <c r="AA30" s="242"/>
+      <c r="AB30" s="242"/>
+      <c r="AC30" s="242"/>
+      <c r="AD30" s="242"/>
+      <c r="AE30" s="243"/>
+      <c r="AF30" s="238"/>
+      <c r="AG30" s="239"/>
+      <c r="AH30" s="239"/>
+      <c r="AI30" s="240"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="175"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="177"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="180"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="182"/>
-      <c r="L31" s="182"/>
-      <c r="M31" s="182"/>
-      <c r="N31" s="182"/>
-      <c r="O31" s="182"/>
-      <c r="P31" s="183"/>
-      <c r="Q31" s="184"/>
-      <c r="R31" s="185"/>
-      <c r="S31" s="185"/>
-      <c r="T31" s="185"/>
-      <c r="U31" s="185"/>
-      <c r="V31" s="185"/>
-      <c r="W31" s="185"/>
-      <c r="X31" s="185"/>
-      <c r="Y31" s="185"/>
-      <c r="Z31" s="185"/>
-      <c r="AA31" s="185"/>
-      <c r="AB31" s="185"/>
-      <c r="AC31" s="185"/>
-      <c r="AD31" s="185"/>
-      <c r="AE31" s="186"/>
-      <c r="AF31" s="181"/>
-      <c r="AG31" s="182"/>
-      <c r="AH31" s="182"/>
-      <c r="AI31" s="183"/>
+      <c r="B31" s="232"/>
+      <c r="C31" s="233"/>
+      <c r="D31" s="234"/>
+      <c r="E31" s="235"/>
+      <c r="F31" s="236"/>
+      <c r="G31" s="232"/>
+      <c r="H31" s="237"/>
+      <c r="I31" s="233"/>
+      <c r="J31" s="238"/>
+      <c r="K31" s="239"/>
+      <c r="L31" s="239"/>
+      <c r="M31" s="239"/>
+      <c r="N31" s="239"/>
+      <c r="O31" s="239"/>
+      <c r="P31" s="240"/>
+      <c r="Q31" s="241"/>
+      <c r="R31" s="242"/>
+      <c r="S31" s="242"/>
+      <c r="T31" s="242"/>
+      <c r="U31" s="242"/>
+      <c r="V31" s="242"/>
+      <c r="W31" s="242"/>
+      <c r="X31" s="242"/>
+      <c r="Y31" s="242"/>
+      <c r="Z31" s="242"/>
+      <c r="AA31" s="242"/>
+      <c r="AB31" s="242"/>
+      <c r="AC31" s="242"/>
+      <c r="AD31" s="242"/>
+      <c r="AE31" s="243"/>
+      <c r="AF31" s="238"/>
+      <c r="AG31" s="239"/>
+      <c r="AH31" s="239"/>
+      <c r="AI31" s="240"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="175"/>
-      <c r="C32" s="176"/>
-      <c r="D32" s="177"/>
-      <c r="E32" s="178"/>
-      <c r="F32" s="179"/>
-      <c r="G32" s="175"/>
-      <c r="H32" s="180"/>
-      <c r="I32" s="176"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="187"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="182"/>
-      <c r="N32" s="182"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="183"/>
-      <c r="Q32" s="184"/>
-      <c r="R32" s="185"/>
-      <c r="S32" s="185"/>
-      <c r="T32" s="185"/>
-      <c r="U32" s="185"/>
-      <c r="V32" s="185"/>
-      <c r="W32" s="185"/>
-      <c r="X32" s="185"/>
-      <c r="Y32" s="185"/>
-      <c r="Z32" s="185"/>
-      <c r="AA32" s="185"/>
-      <c r="AB32" s="185"/>
-      <c r="AC32" s="185"/>
-      <c r="AD32" s="185"/>
-      <c r="AE32" s="186"/>
-      <c r="AF32" s="181"/>
-      <c r="AG32" s="182"/>
-      <c r="AH32" s="182"/>
-      <c r="AI32" s="183"/>
+      <c r="B32" s="232"/>
+      <c r="C32" s="233"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="235"/>
+      <c r="F32" s="236"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="237"/>
+      <c r="I32" s="233"/>
+      <c r="J32" s="238"/>
+      <c r="K32" s="244"/>
+      <c r="L32" s="239"/>
+      <c r="M32" s="239"/>
+      <c r="N32" s="239"/>
+      <c r="O32" s="239"/>
+      <c r="P32" s="240"/>
+      <c r="Q32" s="241"/>
+      <c r="R32" s="242"/>
+      <c r="S32" s="242"/>
+      <c r="T32" s="242"/>
+      <c r="U32" s="242"/>
+      <c r="V32" s="242"/>
+      <c r="W32" s="242"/>
+      <c r="X32" s="242"/>
+      <c r="Y32" s="242"/>
+      <c r="Z32" s="242"/>
+      <c r="AA32" s="242"/>
+      <c r="AB32" s="242"/>
+      <c r="AC32" s="242"/>
+      <c r="AD32" s="242"/>
+      <c r="AE32" s="243"/>
+      <c r="AF32" s="238"/>
+      <c r="AG32" s="239"/>
+      <c r="AH32" s="239"/>
+      <c r="AI32" s="240"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="175"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="177"/>
-      <c r="E33" s="178"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="180"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="182"/>
-      <c r="L33" s="182"/>
-      <c r="M33" s="182"/>
-      <c r="N33" s="182"/>
-      <c r="O33" s="182"/>
-      <c r="P33" s="183"/>
-      <c r="Q33" s="184"/>
-      <c r="R33" s="185"/>
-      <c r="S33" s="185"/>
-      <c r="T33" s="185"/>
-      <c r="U33" s="185"/>
-      <c r="V33" s="185"/>
-      <c r="W33" s="185"/>
-      <c r="X33" s="185"/>
-      <c r="Y33" s="185"/>
-      <c r="Z33" s="185"/>
-      <c r="AA33" s="185"/>
-      <c r="AB33" s="185"/>
-      <c r="AC33" s="185"/>
-      <c r="AD33" s="185"/>
-      <c r="AE33" s="186"/>
-      <c r="AF33" s="181"/>
-      <c r="AG33" s="182"/>
-      <c r="AH33" s="182"/>
-      <c r="AI33" s="183"/>
+      <c r="B33" s="232"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="236"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="237"/>
+      <c r="I33" s="233"/>
+      <c r="J33" s="238"/>
+      <c r="K33" s="239"/>
+      <c r="L33" s="239"/>
+      <c r="M33" s="239"/>
+      <c r="N33" s="239"/>
+      <c r="O33" s="239"/>
+      <c r="P33" s="240"/>
+      <c r="Q33" s="241"/>
+      <c r="R33" s="242"/>
+      <c r="S33" s="242"/>
+      <c r="T33" s="242"/>
+      <c r="U33" s="242"/>
+      <c r="V33" s="242"/>
+      <c r="W33" s="242"/>
+      <c r="X33" s="242"/>
+      <c r="Y33" s="242"/>
+      <c r="Z33" s="242"/>
+      <c r="AA33" s="242"/>
+      <c r="AB33" s="242"/>
+      <c r="AC33" s="242"/>
+      <c r="AD33" s="242"/>
+      <c r="AE33" s="243"/>
+      <c r="AF33" s="238"/>
+      <c r="AG33" s="239"/>
+      <c r="AH33" s="239"/>
+      <c r="AI33" s="240"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -14269,161 +14424,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -36645,7 +36645,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -36693,7 +36693,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
@@ -36737,7 +36737,7 @@
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C13)&gt;0)*ROW($C$11:C13),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D13),
 _xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
-_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0)),
+_xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H13),
 _xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
 _xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5DC6C3-320C-4EF2-9AA5-454CB8EA0C82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4D6FE0-479E-45F9-A1D8-85955F4B5EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="XxxAction_クラス単体" sheetId="23" r:id="rId3"/>
-    <sheet name="RMxxxxxxxx_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="XxxAction_リクエスト単体" sheetId="24" r:id="rId4"/>
     <sheet name="取引単体" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">RMxxxxxxxx_リクエスト単体!$A$10:$R$316</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">RMxxxxxxxx_リクエスト単体!$A$1:$R$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XxxAction_リクエスト単体!$A$10:$R$316</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$298</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">XxxAction_リクエスト単体!$A$1:$R$316</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">RMxxxxxxxx_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">XxxAction_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="574">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="574">
   <si>
     <t>システム機能設計書</t>
     <rPh sb="4" eb="6">
@@ -7620,10 +7620,7 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>テストターゲット名：RMxxxxxxxx</t>
-    <rPh sb="8" eb="9">
-      <t>メイ</t>
-    </rPh>
+    <t>リクエストID：XXX</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -8641,6 +8638,108 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8747,108 +8846,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13017,57 +13014,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="181" t="s">
+      <c r="A1" s="215" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="184" t="s">
+      <c r="B1" s="216"/>
+      <c r="C1" s="216"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="218" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
-      <c r="H1" s="185"/>
-      <c r="I1" s="185"/>
-      <c r="J1" s="185"/>
-      <c r="K1" s="185"/>
-      <c r="L1" s="185"/>
-      <c r="M1" s="185"/>
-      <c r="N1" s="186"/>
-      <c r="O1" s="190" t="s">
+      <c r="F1" s="219"/>
+      <c r="G1" s="219"/>
+      <c r="H1" s="219"/>
+      <c r="I1" s="219"/>
+      <c r="J1" s="219"/>
+      <c r="K1" s="219"/>
+      <c r="L1" s="219"/>
+      <c r="M1" s="219"/>
+      <c r="N1" s="220"/>
+      <c r="O1" s="224" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="191"/>
-      <c r="Q1" s="191"/>
-      <c r="R1" s="192"/>
-      <c r="S1" s="199" t="s">
+      <c r="P1" s="225"/>
+      <c r="Q1" s="225"/>
+      <c r="R1" s="226"/>
+      <c r="S1" s="233" t="s">
         <v>572</v>
       </c>
-      <c r="T1" s="200"/>
-      <c r="U1" s="200"/>
-      <c r="V1" s="200"/>
-      <c r="W1" s="200"/>
-      <c r="X1" s="200"/>
-      <c r="Y1" s="200"/>
-      <c r="Z1" s="201"/>
-      <c r="AA1" s="181" t="s">
+      <c r="T1" s="234"/>
+      <c r="U1" s="234"/>
+      <c r="V1" s="234"/>
+      <c r="W1" s="234"/>
+      <c r="X1" s="234"/>
+      <c r="Y1" s="234"/>
+      <c r="Z1" s="235"/>
+      <c r="AA1" s="215" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" s="183"/>
-      <c r="AC1" s="208" t="str">
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="242" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="209"/>
-      <c r="AE1" s="209"/>
-      <c r="AF1" s="210"/>
-      <c r="AG1" s="175">
+      <c r="AD1" s="243"/>
+      <c r="AE1" s="243"/>
+      <c r="AF1" s="244"/>
+      <c r="AG1" s="209">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="176"/>
-      <c r="AI1" s="177"/>
+      <c r="AH1" s="210"/>
+      <c r="AI1" s="211"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -13075,53 +13072,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="181" t="s">
+      <c r="A2" s="215" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="182"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="184" t="s">
+      <c r="B2" s="216"/>
+      <c r="C2" s="216"/>
+      <c r="D2" s="217"/>
+      <c r="E2" s="218" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
-      <c r="M2" s="185"/>
-      <c r="N2" s="186"/>
-      <c r="O2" s="193"/>
-      <c r="P2" s="194"/>
-      <c r="Q2" s="194"/>
-      <c r="R2" s="195"/>
-      <c r="S2" s="202"/>
-      <c r="T2" s="203"/>
-      <c r="U2" s="203"/>
-      <c r="V2" s="203"/>
-      <c r="W2" s="203"/>
-      <c r="X2" s="203"/>
-      <c r="Y2" s="203"/>
-      <c r="Z2" s="204"/>
-      <c r="AA2" s="181" t="s">
+      <c r="F2" s="219"/>
+      <c r="G2" s="219"/>
+      <c r="H2" s="219"/>
+      <c r="I2" s="219"/>
+      <c r="J2" s="219"/>
+      <c r="K2" s="219"/>
+      <c r="L2" s="219"/>
+      <c r="M2" s="219"/>
+      <c r="N2" s="220"/>
+      <c r="O2" s="227"/>
+      <c r="P2" s="228"/>
+      <c r="Q2" s="228"/>
+      <c r="R2" s="229"/>
+      <c r="S2" s="236"/>
+      <c r="T2" s="237"/>
+      <c r="U2" s="237"/>
+      <c r="V2" s="237"/>
+      <c r="W2" s="237"/>
+      <c r="X2" s="237"/>
+      <c r="Y2" s="237"/>
+      <c r="Z2" s="238"/>
+      <c r="AA2" s="215" t="s">
         <v>43</v>
       </c>
-      <c r="AB2" s="183"/>
-      <c r="AC2" s="187" t="str">
+      <c r="AB2" s="217"/>
+      <c r="AC2" s="221" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="188"/>
-      <c r="AE2" s="188"/>
-      <c r="AF2" s="189"/>
-      <c r="AG2" s="175">
+      <c r="AD2" s="222"/>
+      <c r="AE2" s="222"/>
+      <c r="AF2" s="223"/>
+      <c r="AG2" s="209">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="176"/>
-      <c r="AI2" s="177"/>
+      <c r="AH2" s="210"/>
+      <c r="AI2" s="211"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -13129,45 +13126,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="181" t="s">
+      <c r="A3" s="215" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="183"/>
-      <c r="E3" s="184" t="s">
+      <c r="B3" s="216"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="217"/>
+      <c r="E3" s="218" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="185"/>
-      <c r="G3" s="185"/>
-      <c r="H3" s="185"/>
-      <c r="I3" s="185"/>
-      <c r="J3" s="185"/>
-      <c r="K3" s="185"/>
-      <c r="L3" s="185"/>
-      <c r="M3" s="185"/>
-      <c r="N3" s="186"/>
-      <c r="O3" s="196"/>
-      <c r="P3" s="197"/>
-      <c r="Q3" s="197"/>
-      <c r="R3" s="198"/>
-      <c r="S3" s="205"/>
-      <c r="T3" s="206"/>
-      <c r="U3" s="206"/>
-      <c r="V3" s="206"/>
-      <c r="W3" s="206"/>
-      <c r="X3" s="206"/>
-      <c r="Y3" s="206"/>
-      <c r="Z3" s="207"/>
-      <c r="AA3" s="181"/>
-      <c r="AB3" s="183"/>
-      <c r="AC3" s="208"/>
-      <c r="AD3" s="209"/>
-      <c r="AE3" s="209"/>
-      <c r="AF3" s="210"/>
-      <c r="AG3" s="175"/>
-      <c r="AH3" s="176"/>
-      <c r="AI3" s="177"/>
+      <c r="F3" s="219"/>
+      <c r="G3" s="219"/>
+      <c r="H3" s="219"/>
+      <c r="I3" s="219"/>
+      <c r="J3" s="219"/>
+      <c r="K3" s="219"/>
+      <c r="L3" s="219"/>
+      <c r="M3" s="219"/>
+      <c r="N3" s="220"/>
+      <c r="O3" s="230"/>
+      <c r="P3" s="231"/>
+      <c r="Q3" s="231"/>
+      <c r="R3" s="232"/>
+      <c r="S3" s="239"/>
+      <c r="T3" s="240"/>
+      <c r="U3" s="240"/>
+      <c r="V3" s="240"/>
+      <c r="W3" s="240"/>
+      <c r="X3" s="240"/>
+      <c r="Y3" s="240"/>
+      <c r="Z3" s="241"/>
+      <c r="AA3" s="215"/>
+      <c r="AB3" s="217"/>
+      <c r="AC3" s="242"/>
+      <c r="AD3" s="243"/>
+      <c r="AE3" s="243"/>
+      <c r="AF3" s="244"/>
+      <c r="AG3" s="209"/>
+      <c r="AH3" s="210"/>
+      <c r="AI3" s="211"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -13204,97 +13201,97 @@
       <c r="A7" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="178" t="s">
+      <c r="B7" s="212" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="179"/>
-      <c r="D7" s="178" t="s">
+      <c r="C7" s="213"/>
+      <c r="D7" s="212" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="180"/>
-      <c r="F7" s="179"/>
-      <c r="G7" s="178" t="s">
+      <c r="E7" s="214"/>
+      <c r="F7" s="213"/>
+      <c r="G7" s="212" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="180"/>
-      <c r="I7" s="179"/>
-      <c r="J7" s="178" t="s">
+      <c r="H7" s="214"/>
+      <c r="I7" s="213"/>
+      <c r="J7" s="212" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="180"/>
-      <c r="L7" s="180"/>
-      <c r="M7" s="180"/>
-      <c r="N7" s="180"/>
-      <c r="O7" s="180"/>
-      <c r="P7" s="179"/>
-      <c r="Q7" s="178" t="s">
+      <c r="K7" s="214"/>
+      <c r="L7" s="214"/>
+      <c r="M7" s="214"/>
+      <c r="N7" s="214"/>
+      <c r="O7" s="214"/>
+      <c r="P7" s="213"/>
+      <c r="Q7" s="212" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="180"/>
-      <c r="S7" s="180"/>
-      <c r="T7" s="180"/>
-      <c r="U7" s="180"/>
-      <c r="V7" s="180"/>
-      <c r="W7" s="180"/>
-      <c r="X7" s="180"/>
-      <c r="Y7" s="180"/>
-      <c r="Z7" s="180"/>
-      <c r="AA7" s="180"/>
-      <c r="AB7" s="180"/>
-      <c r="AC7" s="180"/>
-      <c r="AD7" s="180"/>
-      <c r="AE7" s="179"/>
-      <c r="AF7" s="178" t="s">
+      <c r="R7" s="214"/>
+      <c r="S7" s="214"/>
+      <c r="T7" s="214"/>
+      <c r="U7" s="214"/>
+      <c r="V7" s="214"/>
+      <c r="W7" s="214"/>
+      <c r="X7" s="214"/>
+      <c r="Y7" s="214"/>
+      <c r="Z7" s="214"/>
+      <c r="AA7" s="214"/>
+      <c r="AB7" s="214"/>
+      <c r="AC7" s="214"/>
+      <c r="AD7" s="214"/>
+      <c r="AE7" s="213"/>
+      <c r="AF7" s="212" t="s">
         <v>51</v>
       </c>
-      <c r="AG7" s="180"/>
-      <c r="AH7" s="180"/>
-      <c r="AI7" s="179"/>
+      <c r="AG7" s="214"/>
+      <c r="AH7" s="214"/>
+      <c r="AI7" s="213"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="223" t="s">
+      <c r="B8" s="200" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="224"/>
-      <c r="D8" s="225">
+      <c r="C8" s="201"/>
+      <c r="D8" s="202">
         <v>43336</v>
       </c>
-      <c r="E8" s="226"/>
-      <c r="F8" s="227"/>
-      <c r="G8" s="223" t="s">
+      <c r="E8" s="203"/>
+      <c r="F8" s="204"/>
+      <c r="G8" s="200" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="228"/>
-      <c r="I8" s="224"/>
-      <c r="J8" s="229" t="s">
+      <c r="H8" s="205"/>
+      <c r="I8" s="201"/>
+      <c r="J8" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="230"/>
-      <c r="L8" s="230"/>
-      <c r="M8" s="230"/>
-      <c r="N8" s="230"/>
-      <c r="O8" s="230"/>
-      <c r="P8" s="231"/>
-      <c r="Q8" s="229" t="s">
+      <c r="K8" s="207"/>
+      <c r="L8" s="207"/>
+      <c r="M8" s="207"/>
+      <c r="N8" s="207"/>
+      <c r="O8" s="207"/>
+      <c r="P8" s="208"/>
+      <c r="Q8" s="206" t="s">
         <v>60</v>
       </c>
-      <c r="R8" s="230"/>
-      <c r="S8" s="230"/>
-      <c r="T8" s="230"/>
-      <c r="U8" s="230"/>
-      <c r="V8" s="230"/>
-      <c r="W8" s="230"/>
-      <c r="X8" s="230"/>
-      <c r="Y8" s="230"/>
-      <c r="Z8" s="230"/>
-      <c r="AA8" s="230"/>
-      <c r="AB8" s="230"/>
-      <c r="AC8" s="230"/>
-      <c r="AD8" s="230"/>
-      <c r="AE8" s="231"/>
+      <c r="R8" s="207"/>
+      <c r="S8" s="207"/>
+      <c r="T8" s="207"/>
+      <c r="U8" s="207"/>
+      <c r="V8" s="207"/>
+      <c r="W8" s="207"/>
+      <c r="X8" s="207"/>
+      <c r="Y8" s="207"/>
+      <c r="Z8" s="207"/>
+      <c r="AA8" s="207"/>
+      <c r="AB8" s="207"/>
+      <c r="AC8" s="207"/>
+      <c r="AD8" s="207"/>
+      <c r="AE8" s="208"/>
       <c r="AF8" s="25" t="s">
         <v>61</v>
       </c>
@@ -13306,1101 +13303,946 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="211" t="s">
+      <c r="B9" s="188" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="212"/>
-      <c r="D9" s="213">
+      <c r="C9" s="189"/>
+      <c r="D9" s="190">
         <v>44852</v>
       </c>
-      <c r="E9" s="214"/>
-      <c r="F9" s="215"/>
-      <c r="G9" s="213" t="s">
+      <c r="E9" s="191"/>
+      <c r="F9" s="192"/>
+      <c r="G9" s="190" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="216"/>
-      <c r="I9" s="212"/>
-      <c r="J9" s="217" t="s">
+      <c r="H9" s="193"/>
+      <c r="I9" s="189"/>
+      <c r="J9" s="194" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="218"/>
-      <c r="L9" s="218"/>
-      <c r="M9" s="218"/>
-      <c r="N9" s="218"/>
-      <c r="O9" s="218"/>
-      <c r="P9" s="219"/>
-      <c r="Q9" s="217" t="s">
+      <c r="K9" s="195"/>
+      <c r="L9" s="195"/>
+      <c r="M9" s="195"/>
+      <c r="N9" s="195"/>
+      <c r="O9" s="195"/>
+      <c r="P9" s="196"/>
+      <c r="Q9" s="194" t="s">
         <v>67</v>
       </c>
-      <c r="R9" s="220"/>
-      <c r="S9" s="220"/>
-      <c r="T9" s="220"/>
-      <c r="U9" s="220"/>
-      <c r="V9" s="220"/>
-      <c r="W9" s="220"/>
-      <c r="X9" s="220"/>
-      <c r="Y9" s="220"/>
-      <c r="Z9" s="220"/>
-      <c r="AA9" s="220"/>
-      <c r="AB9" s="220"/>
-      <c r="AC9" s="220"/>
-      <c r="AD9" s="220"/>
-      <c r="AE9" s="221"/>
-      <c r="AF9" s="222" t="s">
+      <c r="R9" s="197"/>
+      <c r="S9" s="197"/>
+      <c r="T9" s="197"/>
+      <c r="U9" s="197"/>
+      <c r="V9" s="197"/>
+      <c r="W9" s="197"/>
+      <c r="X9" s="197"/>
+      <c r="Y9" s="197"/>
+      <c r="Z9" s="197"/>
+      <c r="AA9" s="197"/>
+      <c r="AB9" s="197"/>
+      <c r="AC9" s="197"/>
+      <c r="AD9" s="197"/>
+      <c r="AE9" s="198"/>
+      <c r="AF9" s="199" t="s">
         <v>61</v>
       </c>
-      <c r="AG9" s="218"/>
-      <c r="AH9" s="218"/>
-      <c r="AI9" s="219"/>
+      <c r="AG9" s="195"/>
+      <c r="AH9" s="195"/>
+      <c r="AI9" s="196"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="232"/>
-      <c r="C10" s="233"/>
-      <c r="D10" s="234"/>
-      <c r="E10" s="235"/>
-      <c r="F10" s="236"/>
-      <c r="G10" s="232"/>
-      <c r="H10" s="237"/>
-      <c r="I10" s="233"/>
-      <c r="J10" s="238"/>
-      <c r="K10" s="239"/>
-      <c r="L10" s="239"/>
-      <c r="M10" s="239"/>
-      <c r="N10" s="239"/>
-      <c r="O10" s="239"/>
-      <c r="P10" s="240"/>
-      <c r="Q10" s="241"/>
-      <c r="R10" s="242"/>
-      <c r="S10" s="242"/>
-      <c r="T10" s="242"/>
-      <c r="U10" s="242"/>
-      <c r="V10" s="242"/>
-      <c r="W10" s="242"/>
-      <c r="X10" s="242"/>
-      <c r="Y10" s="242"/>
-      <c r="Z10" s="242"/>
-      <c r="AA10" s="242"/>
-      <c r="AB10" s="242"/>
-      <c r="AC10" s="242"/>
-      <c r="AD10" s="242"/>
-      <c r="AE10" s="243"/>
-      <c r="AF10" s="238"/>
-      <c r="AG10" s="239"/>
-      <c r="AH10" s="239"/>
-      <c r="AI10" s="240"/>
+      <c r="B10" s="175"/>
+      <c r="C10" s="176"/>
+      <c r="D10" s="177"/>
+      <c r="E10" s="178"/>
+      <c r="F10" s="179"/>
+      <c r="G10" s="175"/>
+      <c r="H10" s="180"/>
+      <c r="I10" s="176"/>
+      <c r="J10" s="181"/>
+      <c r="K10" s="182"/>
+      <c r="L10" s="182"/>
+      <c r="M10" s="182"/>
+      <c r="N10" s="182"/>
+      <c r="O10" s="182"/>
+      <c r="P10" s="183"/>
+      <c r="Q10" s="184"/>
+      <c r="R10" s="185"/>
+      <c r="S10" s="185"/>
+      <c r="T10" s="185"/>
+      <c r="U10" s="185"/>
+      <c r="V10" s="185"/>
+      <c r="W10" s="185"/>
+      <c r="X10" s="185"/>
+      <c r="Y10" s="185"/>
+      <c r="Z10" s="185"/>
+      <c r="AA10" s="185"/>
+      <c r="AB10" s="185"/>
+      <c r="AC10" s="185"/>
+      <c r="AD10" s="185"/>
+      <c r="AE10" s="186"/>
+      <c r="AF10" s="181"/>
+      <c r="AG10" s="182"/>
+      <c r="AH10" s="182"/>
+      <c r="AI10" s="183"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="232"/>
-      <c r="C11" s="233"/>
-      <c r="D11" s="234"/>
-      <c r="E11" s="235"/>
-      <c r="F11" s="236"/>
-      <c r="G11" s="232"/>
-      <c r="H11" s="237"/>
-      <c r="I11" s="233"/>
-      <c r="J11" s="238"/>
-      <c r="K11" s="239"/>
-      <c r="L11" s="239"/>
-      <c r="M11" s="239"/>
-      <c r="N11" s="239"/>
-      <c r="O11" s="239"/>
-      <c r="P11" s="240"/>
-      <c r="Q11" s="241"/>
-      <c r="R11" s="242"/>
-      <c r="S11" s="242"/>
-      <c r="T11" s="242"/>
-      <c r="U11" s="242"/>
-      <c r="V11" s="242"/>
-      <c r="W11" s="242"/>
-      <c r="X11" s="242"/>
-      <c r="Y11" s="242"/>
-      <c r="Z11" s="242"/>
-      <c r="AA11" s="242"/>
-      <c r="AB11" s="242"/>
-      <c r="AC11" s="242"/>
-      <c r="AD11" s="242"/>
-      <c r="AE11" s="243"/>
-      <c r="AF11" s="238"/>
-      <c r="AG11" s="239"/>
-      <c r="AH11" s="239"/>
-      <c r="AI11" s="240"/>
+      <c r="B11" s="175"/>
+      <c r="C11" s="176"/>
+      <c r="D11" s="177"/>
+      <c r="E11" s="178"/>
+      <c r="F11" s="179"/>
+      <c r="G11" s="175"/>
+      <c r="H11" s="180"/>
+      <c r="I11" s="176"/>
+      <c r="J11" s="181"/>
+      <c r="K11" s="182"/>
+      <c r="L11" s="182"/>
+      <c r="M11" s="182"/>
+      <c r="N11" s="182"/>
+      <c r="O11" s="182"/>
+      <c r="P11" s="183"/>
+      <c r="Q11" s="184"/>
+      <c r="R11" s="185"/>
+      <c r="S11" s="185"/>
+      <c r="T11" s="185"/>
+      <c r="U11" s="185"/>
+      <c r="V11" s="185"/>
+      <c r="W11" s="185"/>
+      <c r="X11" s="185"/>
+      <c r="Y11" s="185"/>
+      <c r="Z11" s="185"/>
+      <c r="AA11" s="185"/>
+      <c r="AB11" s="185"/>
+      <c r="AC11" s="185"/>
+      <c r="AD11" s="185"/>
+      <c r="AE11" s="186"/>
+      <c r="AF11" s="181"/>
+      <c r="AG11" s="182"/>
+      <c r="AH11" s="182"/>
+      <c r="AI11" s="183"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="232"/>
-      <c r="C12" s="233"/>
-      <c r="D12" s="234"/>
-      <c r="E12" s="235"/>
-      <c r="F12" s="236"/>
-      <c r="G12" s="232"/>
-      <c r="H12" s="237"/>
-      <c r="I12" s="233"/>
-      <c r="J12" s="238"/>
-      <c r="K12" s="239"/>
-      <c r="L12" s="239"/>
-      <c r="M12" s="239"/>
-      <c r="N12" s="239"/>
-      <c r="O12" s="239"/>
-      <c r="P12" s="240"/>
-      <c r="Q12" s="241"/>
-      <c r="R12" s="242"/>
-      <c r="S12" s="242"/>
-      <c r="T12" s="242"/>
-      <c r="U12" s="242"/>
-      <c r="V12" s="242"/>
-      <c r="W12" s="242"/>
-      <c r="X12" s="242"/>
-      <c r="Y12" s="242"/>
-      <c r="Z12" s="242"/>
-      <c r="AA12" s="242"/>
-      <c r="AB12" s="242"/>
-      <c r="AC12" s="242"/>
-      <c r="AD12" s="242"/>
-      <c r="AE12" s="243"/>
-      <c r="AF12" s="238"/>
-      <c r="AG12" s="239"/>
-      <c r="AH12" s="239"/>
-      <c r="AI12" s="240"/>
+      <c r="B12" s="175"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="177"/>
+      <c r="E12" s="178"/>
+      <c r="F12" s="179"/>
+      <c r="G12" s="175"/>
+      <c r="H12" s="180"/>
+      <c r="I12" s="176"/>
+      <c r="J12" s="181"/>
+      <c r="K12" s="182"/>
+      <c r="L12" s="182"/>
+      <c r="M12" s="182"/>
+      <c r="N12" s="182"/>
+      <c r="O12" s="182"/>
+      <c r="P12" s="183"/>
+      <c r="Q12" s="184"/>
+      <c r="R12" s="185"/>
+      <c r="S12" s="185"/>
+      <c r="T12" s="185"/>
+      <c r="U12" s="185"/>
+      <c r="V12" s="185"/>
+      <c r="W12" s="185"/>
+      <c r="X12" s="185"/>
+      <c r="Y12" s="185"/>
+      <c r="Z12" s="185"/>
+      <c r="AA12" s="185"/>
+      <c r="AB12" s="185"/>
+      <c r="AC12" s="185"/>
+      <c r="AD12" s="185"/>
+      <c r="AE12" s="186"/>
+      <c r="AF12" s="181"/>
+      <c r="AG12" s="182"/>
+      <c r="AH12" s="182"/>
+      <c r="AI12" s="183"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="232"/>
-      <c r="C13" s="233"/>
-      <c r="D13" s="234"/>
-      <c r="E13" s="235"/>
-      <c r="F13" s="236"/>
-      <c r="G13" s="232"/>
-      <c r="H13" s="237"/>
-      <c r="I13" s="233"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="239"/>
-      <c r="L13" s="239"/>
-      <c r="M13" s="239"/>
-      <c r="N13" s="239"/>
-      <c r="O13" s="239"/>
-      <c r="P13" s="240"/>
-      <c r="Q13" s="241"/>
-      <c r="R13" s="242"/>
-      <c r="S13" s="242"/>
-      <c r="T13" s="242"/>
-      <c r="U13" s="242"/>
-      <c r="V13" s="242"/>
-      <c r="W13" s="242"/>
-      <c r="X13" s="242"/>
-      <c r="Y13" s="242"/>
-      <c r="Z13" s="242"/>
-      <c r="AA13" s="242"/>
-      <c r="AB13" s="242"/>
-      <c r="AC13" s="242"/>
-      <c r="AD13" s="242"/>
-      <c r="AE13" s="243"/>
-      <c r="AF13" s="238"/>
-      <c r="AG13" s="239"/>
-      <c r="AH13" s="239"/>
-      <c r="AI13" s="240"/>
+      <c r="B13" s="175"/>
+      <c r="C13" s="176"/>
+      <c r="D13" s="177"/>
+      <c r="E13" s="178"/>
+      <c r="F13" s="179"/>
+      <c r="G13" s="175"/>
+      <c r="H13" s="180"/>
+      <c r="I13" s="176"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="182"/>
+      <c r="L13" s="182"/>
+      <c r="M13" s="182"/>
+      <c r="N13" s="182"/>
+      <c r="O13" s="182"/>
+      <c r="P13" s="183"/>
+      <c r="Q13" s="184"/>
+      <c r="R13" s="185"/>
+      <c r="S13" s="185"/>
+      <c r="T13" s="185"/>
+      <c r="U13" s="185"/>
+      <c r="V13" s="185"/>
+      <c r="W13" s="185"/>
+      <c r="X13" s="185"/>
+      <c r="Y13" s="185"/>
+      <c r="Z13" s="185"/>
+      <c r="AA13" s="185"/>
+      <c r="AB13" s="185"/>
+      <c r="AC13" s="185"/>
+      <c r="AD13" s="185"/>
+      <c r="AE13" s="186"/>
+      <c r="AF13" s="181"/>
+      <c r="AG13" s="182"/>
+      <c r="AH13" s="182"/>
+      <c r="AI13" s="183"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="232"/>
-      <c r="C14" s="233"/>
-      <c r="D14" s="234"/>
-      <c r="E14" s="235"/>
-      <c r="F14" s="236"/>
-      <c r="G14" s="232"/>
-      <c r="H14" s="237"/>
-      <c r="I14" s="233"/>
-      <c r="J14" s="238"/>
-      <c r="K14" s="239"/>
-      <c r="L14" s="239"/>
-      <c r="M14" s="239"/>
-      <c r="N14" s="239"/>
-      <c r="O14" s="239"/>
-      <c r="P14" s="240"/>
-      <c r="Q14" s="241"/>
-      <c r="R14" s="242"/>
-      <c r="S14" s="242"/>
-      <c r="T14" s="242"/>
-      <c r="U14" s="242"/>
-      <c r="V14" s="242"/>
-      <c r="W14" s="242"/>
-      <c r="X14" s="242"/>
-      <c r="Y14" s="242"/>
-      <c r="Z14" s="242"/>
-      <c r="AA14" s="242"/>
-      <c r="AB14" s="242"/>
-      <c r="AC14" s="242"/>
-      <c r="AD14" s="242"/>
-      <c r="AE14" s="243"/>
-      <c r="AF14" s="238"/>
-      <c r="AG14" s="239"/>
-      <c r="AH14" s="239"/>
-      <c r="AI14" s="240"/>
+      <c r="B14" s="175"/>
+      <c r="C14" s="176"/>
+      <c r="D14" s="177"/>
+      <c r="E14" s="178"/>
+      <c r="F14" s="179"/>
+      <c r="G14" s="175"/>
+      <c r="H14" s="180"/>
+      <c r="I14" s="176"/>
+      <c r="J14" s="181"/>
+      <c r="K14" s="182"/>
+      <c r="L14" s="182"/>
+      <c r="M14" s="182"/>
+      <c r="N14" s="182"/>
+      <c r="O14" s="182"/>
+      <c r="P14" s="183"/>
+      <c r="Q14" s="184"/>
+      <c r="R14" s="185"/>
+      <c r="S14" s="185"/>
+      <c r="T14" s="185"/>
+      <c r="U14" s="185"/>
+      <c r="V14" s="185"/>
+      <c r="W14" s="185"/>
+      <c r="X14" s="185"/>
+      <c r="Y14" s="185"/>
+      <c r="Z14" s="185"/>
+      <c r="AA14" s="185"/>
+      <c r="AB14" s="185"/>
+      <c r="AC14" s="185"/>
+      <c r="AD14" s="185"/>
+      <c r="AE14" s="186"/>
+      <c r="AF14" s="181"/>
+      <c r="AG14" s="182"/>
+      <c r="AH14" s="182"/>
+      <c r="AI14" s="183"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="232"/>
-      <c r="C15" s="233"/>
-      <c r="D15" s="234"/>
-      <c r="E15" s="235"/>
-      <c r="F15" s="236"/>
-      <c r="G15" s="232"/>
-      <c r="H15" s="237"/>
-      <c r="I15" s="233"/>
-      <c r="J15" s="238"/>
-      <c r="K15" s="239"/>
-      <c r="L15" s="239"/>
-      <c r="M15" s="239"/>
-      <c r="N15" s="239"/>
-      <c r="O15" s="239"/>
-      <c r="P15" s="240"/>
-      <c r="Q15" s="241"/>
-      <c r="R15" s="242"/>
-      <c r="S15" s="242"/>
-      <c r="T15" s="242"/>
-      <c r="U15" s="242"/>
-      <c r="V15" s="242"/>
-      <c r="W15" s="242"/>
-      <c r="X15" s="242"/>
-      <c r="Y15" s="242"/>
-      <c r="Z15" s="242"/>
-      <c r="AA15" s="242"/>
-      <c r="AB15" s="242"/>
-      <c r="AC15" s="242"/>
-      <c r="AD15" s="242"/>
-      <c r="AE15" s="243"/>
-      <c r="AF15" s="238"/>
-      <c r="AG15" s="239"/>
-      <c r="AH15" s="239"/>
-      <c r="AI15" s="240"/>
+      <c r="B15" s="175"/>
+      <c r="C15" s="176"/>
+      <c r="D15" s="177"/>
+      <c r="E15" s="178"/>
+      <c r="F15" s="179"/>
+      <c r="G15" s="175"/>
+      <c r="H15" s="180"/>
+      <c r="I15" s="176"/>
+      <c r="J15" s="181"/>
+      <c r="K15" s="182"/>
+      <c r="L15" s="182"/>
+      <c r="M15" s="182"/>
+      <c r="N15" s="182"/>
+      <c r="O15" s="182"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="184"/>
+      <c r="R15" s="185"/>
+      <c r="S15" s="185"/>
+      <c r="T15" s="185"/>
+      <c r="U15" s="185"/>
+      <c r="V15" s="185"/>
+      <c r="W15" s="185"/>
+      <c r="X15" s="185"/>
+      <c r="Y15" s="185"/>
+      <c r="Z15" s="185"/>
+      <c r="AA15" s="185"/>
+      <c r="AB15" s="185"/>
+      <c r="AC15" s="185"/>
+      <c r="AD15" s="185"/>
+      <c r="AE15" s="186"/>
+      <c r="AF15" s="181"/>
+      <c r="AG15" s="182"/>
+      <c r="AH15" s="182"/>
+      <c r="AI15" s="183"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="232"/>
-      <c r="C16" s="233"/>
-      <c r="D16" s="234"/>
-      <c r="E16" s="235"/>
-      <c r="F16" s="236"/>
-      <c r="G16" s="232"/>
-      <c r="H16" s="237"/>
-      <c r="I16" s="233"/>
-      <c r="J16" s="238"/>
-      <c r="K16" s="239"/>
-      <c r="L16" s="239"/>
-      <c r="M16" s="239"/>
-      <c r="N16" s="239"/>
-      <c r="O16" s="239"/>
-      <c r="P16" s="240"/>
-      <c r="Q16" s="241"/>
-      <c r="R16" s="242"/>
-      <c r="S16" s="242"/>
-      <c r="T16" s="242"/>
-      <c r="U16" s="242"/>
-      <c r="V16" s="242"/>
-      <c r="W16" s="242"/>
-      <c r="X16" s="242"/>
-      <c r="Y16" s="242"/>
-      <c r="Z16" s="242"/>
-      <c r="AA16" s="242"/>
-      <c r="AB16" s="242"/>
-      <c r="AC16" s="242"/>
-      <c r="AD16" s="242"/>
-      <c r="AE16" s="243"/>
-      <c r="AF16" s="238"/>
-      <c r="AG16" s="239"/>
-      <c r="AH16" s="239"/>
-      <c r="AI16" s="240"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="177"/>
+      <c r="E16" s="178"/>
+      <c r="F16" s="179"/>
+      <c r="G16" s="175"/>
+      <c r="H16" s="180"/>
+      <c r="I16" s="176"/>
+      <c r="J16" s="181"/>
+      <c r="K16" s="182"/>
+      <c r="L16" s="182"/>
+      <c r="M16" s="182"/>
+      <c r="N16" s="182"/>
+      <c r="O16" s="182"/>
+      <c r="P16" s="183"/>
+      <c r="Q16" s="184"/>
+      <c r="R16" s="185"/>
+      <c r="S16" s="185"/>
+      <c r="T16" s="185"/>
+      <c r="U16" s="185"/>
+      <c r="V16" s="185"/>
+      <c r="W16" s="185"/>
+      <c r="X16" s="185"/>
+      <c r="Y16" s="185"/>
+      <c r="Z16" s="185"/>
+      <c r="AA16" s="185"/>
+      <c r="AB16" s="185"/>
+      <c r="AC16" s="185"/>
+      <c r="AD16" s="185"/>
+      <c r="AE16" s="186"/>
+      <c r="AF16" s="181"/>
+      <c r="AG16" s="182"/>
+      <c r="AH16" s="182"/>
+      <c r="AI16" s="183"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="232"/>
-      <c r="C17" s="233"/>
-      <c r="D17" s="234"/>
-      <c r="E17" s="235"/>
-      <c r="F17" s="236"/>
-      <c r="G17" s="232"/>
-      <c r="H17" s="237"/>
-      <c r="I17" s="233"/>
-      <c r="J17" s="238"/>
-      <c r="K17" s="239"/>
-      <c r="L17" s="239"/>
-      <c r="M17" s="239"/>
-      <c r="N17" s="239"/>
-      <c r="O17" s="239"/>
-      <c r="P17" s="240"/>
-      <c r="Q17" s="241"/>
-      <c r="R17" s="242"/>
-      <c r="S17" s="242"/>
-      <c r="T17" s="242"/>
-      <c r="U17" s="242"/>
-      <c r="V17" s="242"/>
-      <c r="W17" s="242"/>
-      <c r="X17" s="242"/>
-      <c r="Y17" s="242"/>
-      <c r="Z17" s="242"/>
-      <c r="AA17" s="242"/>
-      <c r="AB17" s="242"/>
-      <c r="AC17" s="242"/>
-      <c r="AD17" s="242"/>
-      <c r="AE17" s="243"/>
-      <c r="AF17" s="238"/>
-      <c r="AG17" s="239"/>
-      <c r="AH17" s="239"/>
-      <c r="AI17" s="240"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="177"/>
+      <c r="E17" s="178"/>
+      <c r="F17" s="179"/>
+      <c r="G17" s="175"/>
+      <c r="H17" s="180"/>
+      <c r="I17" s="176"/>
+      <c r="J17" s="181"/>
+      <c r="K17" s="182"/>
+      <c r="L17" s="182"/>
+      <c r="M17" s="182"/>
+      <c r="N17" s="182"/>
+      <c r="O17" s="182"/>
+      <c r="P17" s="183"/>
+      <c r="Q17" s="184"/>
+      <c r="R17" s="185"/>
+      <c r="S17" s="185"/>
+      <c r="T17" s="185"/>
+      <c r="U17" s="185"/>
+      <c r="V17" s="185"/>
+      <c r="W17" s="185"/>
+      <c r="X17" s="185"/>
+      <c r="Y17" s="185"/>
+      <c r="Z17" s="185"/>
+      <c r="AA17" s="185"/>
+      <c r="AB17" s="185"/>
+      <c r="AC17" s="185"/>
+      <c r="AD17" s="185"/>
+      <c r="AE17" s="186"/>
+      <c r="AF17" s="181"/>
+      <c r="AG17" s="182"/>
+      <c r="AH17" s="182"/>
+      <c r="AI17" s="183"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="232"/>
-      <c r="C18" s="233"/>
-      <c r="D18" s="234"/>
-      <c r="E18" s="235"/>
-      <c r="F18" s="236"/>
-      <c r="G18" s="232"/>
-      <c r="H18" s="237"/>
-      <c r="I18" s="233"/>
-      <c r="J18" s="238"/>
-      <c r="K18" s="239"/>
-      <c r="L18" s="239"/>
-      <c r="M18" s="239"/>
-      <c r="N18" s="239"/>
-      <c r="O18" s="239"/>
-      <c r="P18" s="240"/>
-      <c r="Q18" s="241"/>
-      <c r="R18" s="242"/>
-      <c r="S18" s="242"/>
-      <c r="T18" s="242"/>
-      <c r="U18" s="242"/>
-      <c r="V18" s="242"/>
-      <c r="W18" s="242"/>
-      <c r="X18" s="242"/>
-      <c r="Y18" s="242"/>
-      <c r="Z18" s="242"/>
-      <c r="AA18" s="242"/>
-      <c r="AB18" s="242"/>
-      <c r="AC18" s="242"/>
-      <c r="AD18" s="242"/>
-      <c r="AE18" s="243"/>
-      <c r="AF18" s="238"/>
-      <c r="AG18" s="239"/>
-      <c r="AH18" s="239"/>
-      <c r="AI18" s="240"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="178"/>
+      <c r="F18" s="179"/>
+      <c r="G18" s="175"/>
+      <c r="H18" s="180"/>
+      <c r="I18" s="176"/>
+      <c r="J18" s="181"/>
+      <c r="K18" s="182"/>
+      <c r="L18" s="182"/>
+      <c r="M18" s="182"/>
+      <c r="N18" s="182"/>
+      <c r="O18" s="182"/>
+      <c r="P18" s="183"/>
+      <c r="Q18" s="184"/>
+      <c r="R18" s="185"/>
+      <c r="S18" s="185"/>
+      <c r="T18" s="185"/>
+      <c r="U18" s="185"/>
+      <c r="V18" s="185"/>
+      <c r="W18" s="185"/>
+      <c r="X18" s="185"/>
+      <c r="Y18" s="185"/>
+      <c r="Z18" s="185"/>
+      <c r="AA18" s="185"/>
+      <c r="AB18" s="185"/>
+      <c r="AC18" s="185"/>
+      <c r="AD18" s="185"/>
+      <c r="AE18" s="186"/>
+      <c r="AF18" s="181"/>
+      <c r="AG18" s="182"/>
+      <c r="AH18" s="182"/>
+      <c r="AI18" s="183"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="232"/>
-      <c r="C19" s="233"/>
-      <c r="D19" s="234"/>
-      <c r="E19" s="235"/>
-      <c r="F19" s="236"/>
-      <c r="G19" s="232"/>
-      <c r="H19" s="237"/>
-      <c r="I19" s="233"/>
-      <c r="J19" s="238"/>
-      <c r="K19" s="239"/>
-      <c r="L19" s="239"/>
-      <c r="M19" s="239"/>
-      <c r="N19" s="239"/>
-      <c r="O19" s="239"/>
-      <c r="P19" s="240"/>
-      <c r="Q19" s="241"/>
-      <c r="R19" s="242"/>
-      <c r="S19" s="242"/>
-      <c r="T19" s="242"/>
-      <c r="U19" s="242"/>
-      <c r="V19" s="242"/>
-      <c r="W19" s="242"/>
-      <c r="X19" s="242"/>
-      <c r="Y19" s="242"/>
-      <c r="Z19" s="242"/>
-      <c r="AA19" s="242"/>
-      <c r="AB19" s="242"/>
-      <c r="AC19" s="242"/>
-      <c r="AD19" s="242"/>
-      <c r="AE19" s="243"/>
-      <c r="AF19" s="238"/>
-      <c r="AG19" s="239"/>
-      <c r="AH19" s="239"/>
-      <c r="AI19" s="240"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="176"/>
+      <c r="D19" s="177"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="179"/>
+      <c r="G19" s="175"/>
+      <c r="H19" s="180"/>
+      <c r="I19" s="176"/>
+      <c r="J19" s="181"/>
+      <c r="K19" s="182"/>
+      <c r="L19" s="182"/>
+      <c r="M19" s="182"/>
+      <c r="N19" s="182"/>
+      <c r="O19" s="182"/>
+      <c r="P19" s="183"/>
+      <c r="Q19" s="184"/>
+      <c r="R19" s="185"/>
+      <c r="S19" s="185"/>
+      <c r="T19" s="185"/>
+      <c r="U19" s="185"/>
+      <c r="V19" s="185"/>
+      <c r="W19" s="185"/>
+      <c r="X19" s="185"/>
+      <c r="Y19" s="185"/>
+      <c r="Z19" s="185"/>
+      <c r="AA19" s="185"/>
+      <c r="AB19" s="185"/>
+      <c r="AC19" s="185"/>
+      <c r="AD19" s="185"/>
+      <c r="AE19" s="186"/>
+      <c r="AF19" s="181"/>
+      <c r="AG19" s="182"/>
+      <c r="AH19" s="182"/>
+      <c r="AI19" s="183"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="232"/>
-      <c r="C20" s="233"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="235"/>
-      <c r="F20" s="236"/>
-      <c r="G20" s="232"/>
-      <c r="H20" s="237"/>
-      <c r="I20" s="233"/>
-      <c r="J20" s="238"/>
-      <c r="K20" s="239"/>
-      <c r="L20" s="239"/>
-      <c r="M20" s="239"/>
-      <c r="N20" s="239"/>
-      <c r="O20" s="239"/>
-      <c r="P20" s="240"/>
-      <c r="Q20" s="241"/>
-      <c r="R20" s="242"/>
-      <c r="S20" s="242"/>
-      <c r="T20" s="242"/>
-      <c r="U20" s="242"/>
-      <c r="V20" s="242"/>
-      <c r="W20" s="242"/>
-      <c r="X20" s="242"/>
-      <c r="Y20" s="242"/>
-      <c r="Z20" s="242"/>
-      <c r="AA20" s="242"/>
-      <c r="AB20" s="242"/>
-      <c r="AC20" s="242"/>
-      <c r="AD20" s="242"/>
-      <c r="AE20" s="243"/>
-      <c r="AF20" s="238"/>
-      <c r="AG20" s="239"/>
-      <c r="AH20" s="239"/>
-      <c r="AI20" s="240"/>
+      <c r="B20" s="175"/>
+      <c r="C20" s="176"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="179"/>
+      <c r="G20" s="175"/>
+      <c r="H20" s="180"/>
+      <c r="I20" s="176"/>
+      <c r="J20" s="181"/>
+      <c r="K20" s="182"/>
+      <c r="L20" s="182"/>
+      <c r="M20" s="182"/>
+      <c r="N20" s="182"/>
+      <c r="O20" s="182"/>
+      <c r="P20" s="183"/>
+      <c r="Q20" s="184"/>
+      <c r="R20" s="185"/>
+      <c r="S20" s="185"/>
+      <c r="T20" s="185"/>
+      <c r="U20" s="185"/>
+      <c r="V20" s="185"/>
+      <c r="W20" s="185"/>
+      <c r="X20" s="185"/>
+      <c r="Y20" s="185"/>
+      <c r="Z20" s="185"/>
+      <c r="AA20" s="185"/>
+      <c r="AB20" s="185"/>
+      <c r="AC20" s="185"/>
+      <c r="AD20" s="185"/>
+      <c r="AE20" s="186"/>
+      <c r="AF20" s="181"/>
+      <c r="AG20" s="182"/>
+      <c r="AH20" s="182"/>
+      <c r="AI20" s="183"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="232"/>
-      <c r="C21" s="233"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="235"/>
-      <c r="F21" s="236"/>
-      <c r="G21" s="232"/>
-      <c r="H21" s="237"/>
-      <c r="I21" s="233"/>
-      <c r="J21" s="238"/>
-      <c r="K21" s="239"/>
-      <c r="L21" s="239"/>
-      <c r="M21" s="239"/>
-      <c r="N21" s="239"/>
-      <c r="O21" s="239"/>
-      <c r="P21" s="240"/>
-      <c r="Q21" s="241"/>
-      <c r="R21" s="242"/>
-      <c r="S21" s="242"/>
-      <c r="T21" s="242"/>
-      <c r="U21" s="242"/>
-      <c r="V21" s="242"/>
-      <c r="W21" s="242"/>
-      <c r="X21" s="242"/>
-      <c r="Y21" s="242"/>
-      <c r="Z21" s="242"/>
-      <c r="AA21" s="242"/>
-      <c r="AB21" s="242"/>
-      <c r="AC21" s="242"/>
-      <c r="AD21" s="242"/>
-      <c r="AE21" s="243"/>
-      <c r="AF21" s="238"/>
-      <c r="AG21" s="239"/>
-      <c r="AH21" s="239"/>
-      <c r="AI21" s="240"/>
+      <c r="B21" s="175"/>
+      <c r="C21" s="176"/>
+      <c r="D21" s="177"/>
+      <c r="E21" s="178"/>
+      <c r="F21" s="179"/>
+      <c r="G21" s="175"/>
+      <c r="H21" s="180"/>
+      <c r="I21" s="176"/>
+      <c r="J21" s="181"/>
+      <c r="K21" s="182"/>
+      <c r="L21" s="182"/>
+      <c r="M21" s="182"/>
+      <c r="N21" s="182"/>
+      <c r="O21" s="182"/>
+      <c r="P21" s="183"/>
+      <c r="Q21" s="184"/>
+      <c r="R21" s="185"/>
+      <c r="S21" s="185"/>
+      <c r="T21" s="185"/>
+      <c r="U21" s="185"/>
+      <c r="V21" s="185"/>
+      <c r="W21" s="185"/>
+      <c r="X21" s="185"/>
+      <c r="Y21" s="185"/>
+      <c r="Z21" s="185"/>
+      <c r="AA21" s="185"/>
+      <c r="AB21" s="185"/>
+      <c r="AC21" s="185"/>
+      <c r="AD21" s="185"/>
+      <c r="AE21" s="186"/>
+      <c r="AF21" s="181"/>
+      <c r="AG21" s="182"/>
+      <c r="AH21" s="182"/>
+      <c r="AI21" s="183"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="232"/>
-      <c r="C22" s="233"/>
-      <c r="D22" s="234"/>
-      <c r="E22" s="235"/>
-      <c r="F22" s="236"/>
-      <c r="G22" s="232"/>
-      <c r="H22" s="237"/>
-      <c r="I22" s="233"/>
-      <c r="J22" s="238"/>
-      <c r="K22" s="239"/>
-      <c r="L22" s="239"/>
-      <c r="M22" s="239"/>
-      <c r="N22" s="239"/>
-      <c r="O22" s="239"/>
-      <c r="P22" s="240"/>
-      <c r="Q22" s="241"/>
-      <c r="R22" s="242"/>
-      <c r="S22" s="242"/>
-      <c r="T22" s="242"/>
-      <c r="U22" s="242"/>
-      <c r="V22" s="242"/>
-      <c r="W22" s="242"/>
-      <c r="X22" s="242"/>
-      <c r="Y22" s="242"/>
-      <c r="Z22" s="242"/>
-      <c r="AA22" s="242"/>
-      <c r="AB22" s="242"/>
-      <c r="AC22" s="242"/>
-      <c r="AD22" s="242"/>
-      <c r="AE22" s="243"/>
-      <c r="AF22" s="238"/>
-      <c r="AG22" s="239"/>
-      <c r="AH22" s="239"/>
-      <c r="AI22" s="240"/>
+      <c r="B22" s="175"/>
+      <c r="C22" s="176"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="178"/>
+      <c r="F22" s="179"/>
+      <c r="G22" s="175"/>
+      <c r="H22" s="180"/>
+      <c r="I22" s="176"/>
+      <c r="J22" s="181"/>
+      <c r="K22" s="182"/>
+      <c r="L22" s="182"/>
+      <c r="M22" s="182"/>
+      <c r="N22" s="182"/>
+      <c r="O22" s="182"/>
+      <c r="P22" s="183"/>
+      <c r="Q22" s="184"/>
+      <c r="R22" s="185"/>
+      <c r="S22" s="185"/>
+      <c r="T22" s="185"/>
+      <c r="U22" s="185"/>
+      <c r="V22" s="185"/>
+      <c r="W22" s="185"/>
+      <c r="X22" s="185"/>
+      <c r="Y22" s="185"/>
+      <c r="Z22" s="185"/>
+      <c r="AA22" s="185"/>
+      <c r="AB22" s="185"/>
+      <c r="AC22" s="185"/>
+      <c r="AD22" s="185"/>
+      <c r="AE22" s="186"/>
+      <c r="AF22" s="181"/>
+      <c r="AG22" s="182"/>
+      <c r="AH22" s="182"/>
+      <c r="AI22" s="183"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="232"/>
-      <c r="C23" s="233"/>
-      <c r="D23" s="234"/>
-      <c r="E23" s="235"/>
-      <c r="F23" s="236"/>
-      <c r="G23" s="232"/>
-      <c r="H23" s="237"/>
-      <c r="I23" s="233"/>
-      <c r="J23" s="238"/>
-      <c r="K23" s="239"/>
-      <c r="L23" s="239"/>
-      <c r="M23" s="239"/>
-      <c r="N23" s="239"/>
-      <c r="O23" s="239"/>
-      <c r="P23" s="240"/>
-      <c r="Q23" s="241"/>
-      <c r="R23" s="242"/>
-      <c r="S23" s="242"/>
-      <c r="T23" s="242"/>
-      <c r="U23" s="242"/>
-      <c r="V23" s="242"/>
-      <c r="W23" s="242"/>
-      <c r="X23" s="242"/>
-      <c r="Y23" s="242"/>
-      <c r="Z23" s="242"/>
-      <c r="AA23" s="242"/>
-      <c r="AB23" s="242"/>
-      <c r="AC23" s="242"/>
-      <c r="AD23" s="242"/>
-      <c r="AE23" s="243"/>
-      <c r="AF23" s="238"/>
-      <c r="AG23" s="239"/>
-      <c r="AH23" s="239"/>
-      <c r="AI23" s="240"/>
+      <c r="B23" s="175"/>
+      <c r="C23" s="176"/>
+      <c r="D23" s="177"/>
+      <c r="E23" s="178"/>
+      <c r="F23" s="179"/>
+      <c r="G23" s="175"/>
+      <c r="H23" s="180"/>
+      <c r="I23" s="176"/>
+      <c r="J23" s="181"/>
+      <c r="K23" s="182"/>
+      <c r="L23" s="182"/>
+      <c r="M23" s="182"/>
+      <c r="N23" s="182"/>
+      <c r="O23" s="182"/>
+      <c r="P23" s="183"/>
+      <c r="Q23" s="184"/>
+      <c r="R23" s="185"/>
+      <c r="S23" s="185"/>
+      <c r="T23" s="185"/>
+      <c r="U23" s="185"/>
+      <c r="V23" s="185"/>
+      <c r="W23" s="185"/>
+      <c r="X23" s="185"/>
+      <c r="Y23" s="185"/>
+      <c r="Z23" s="185"/>
+      <c r="AA23" s="185"/>
+      <c r="AB23" s="185"/>
+      <c r="AC23" s="185"/>
+      <c r="AD23" s="185"/>
+      <c r="AE23" s="186"/>
+      <c r="AF23" s="181"/>
+      <c r="AG23" s="182"/>
+      <c r="AH23" s="182"/>
+      <c r="AI23" s="183"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="232"/>
-      <c r="C24" s="233"/>
-      <c r="D24" s="234"/>
-      <c r="E24" s="235"/>
-      <c r="F24" s="236"/>
-      <c r="G24" s="232"/>
-      <c r="H24" s="237"/>
-      <c r="I24" s="233"/>
-      <c r="J24" s="238"/>
-      <c r="K24" s="239"/>
-      <c r="L24" s="239"/>
-      <c r="M24" s="239"/>
-      <c r="N24" s="239"/>
-      <c r="O24" s="239"/>
-      <c r="P24" s="240"/>
-      <c r="Q24" s="241"/>
-      <c r="R24" s="242"/>
-      <c r="S24" s="242"/>
-      <c r="T24" s="242"/>
-      <c r="U24" s="242"/>
-      <c r="V24" s="242"/>
-      <c r="W24" s="242"/>
-      <c r="X24" s="242"/>
-      <c r="Y24" s="242"/>
-      <c r="Z24" s="242"/>
-      <c r="AA24" s="242"/>
-      <c r="AB24" s="242"/>
-      <c r="AC24" s="242"/>
-      <c r="AD24" s="242"/>
-      <c r="AE24" s="243"/>
-      <c r="AF24" s="238"/>
-      <c r="AG24" s="239"/>
-      <c r="AH24" s="239"/>
-      <c r="AI24" s="240"/>
+      <c r="B24" s="175"/>
+      <c r="C24" s="176"/>
+      <c r="D24" s="177"/>
+      <c r="E24" s="178"/>
+      <c r="F24" s="179"/>
+      <c r="G24" s="175"/>
+      <c r="H24" s="180"/>
+      <c r="I24" s="176"/>
+      <c r="J24" s="181"/>
+      <c r="K24" s="182"/>
+      <c r="L24" s="182"/>
+      <c r="M24" s="182"/>
+      <c r="N24" s="182"/>
+      <c r="O24" s="182"/>
+      <c r="P24" s="183"/>
+      <c r="Q24" s="184"/>
+      <c r="R24" s="185"/>
+      <c r="S24" s="185"/>
+      <c r="T24" s="185"/>
+      <c r="U24" s="185"/>
+      <c r="V24" s="185"/>
+      <c r="W24" s="185"/>
+      <c r="X24" s="185"/>
+      <c r="Y24" s="185"/>
+      <c r="Z24" s="185"/>
+      <c r="AA24" s="185"/>
+      <c r="AB24" s="185"/>
+      <c r="AC24" s="185"/>
+      <c r="AD24" s="185"/>
+      <c r="AE24" s="186"/>
+      <c r="AF24" s="181"/>
+      <c r="AG24" s="182"/>
+      <c r="AH24" s="182"/>
+      <c r="AI24" s="183"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="232"/>
-      <c r="C25" s="233"/>
-      <c r="D25" s="234"/>
-      <c r="E25" s="235"/>
-      <c r="F25" s="236"/>
-      <c r="G25" s="232"/>
-      <c r="H25" s="237"/>
-      <c r="I25" s="233"/>
-      <c r="J25" s="238"/>
-      <c r="K25" s="239"/>
-      <c r="L25" s="239"/>
-      <c r="M25" s="239"/>
-      <c r="N25" s="239"/>
-      <c r="O25" s="239"/>
-      <c r="P25" s="240"/>
-      <c r="Q25" s="241"/>
-      <c r="R25" s="242"/>
-      <c r="S25" s="242"/>
-      <c r="T25" s="242"/>
-      <c r="U25" s="242"/>
-      <c r="V25" s="242"/>
-      <c r="W25" s="242"/>
-      <c r="X25" s="242"/>
-      <c r="Y25" s="242"/>
-      <c r="Z25" s="242"/>
-      <c r="AA25" s="242"/>
-      <c r="AB25" s="242"/>
-      <c r="AC25" s="242"/>
-      <c r="AD25" s="242"/>
-      <c r="AE25" s="243"/>
-      <c r="AF25" s="238"/>
-      <c r="AG25" s="239"/>
-      <c r="AH25" s="239"/>
-      <c r="AI25" s="240"/>
+      <c r="B25" s="175"/>
+      <c r="C25" s="176"/>
+      <c r="D25" s="177"/>
+      <c r="E25" s="178"/>
+      <c r="F25" s="179"/>
+      <c r="G25" s="175"/>
+      <c r="H25" s="180"/>
+      <c r="I25" s="176"/>
+      <c r="J25" s="181"/>
+      <c r="K25" s="182"/>
+      <c r="L25" s="182"/>
+      <c r="M25" s="182"/>
+      <c r="N25" s="182"/>
+      <c r="O25" s="182"/>
+      <c r="P25" s="183"/>
+      <c r="Q25" s="184"/>
+      <c r="R25" s="185"/>
+      <c r="S25" s="185"/>
+      <c r="T25" s="185"/>
+      <c r="U25" s="185"/>
+      <c r="V25" s="185"/>
+      <c r="W25" s="185"/>
+      <c r="X25" s="185"/>
+      <c r="Y25" s="185"/>
+      <c r="Z25" s="185"/>
+      <c r="AA25" s="185"/>
+      <c r="AB25" s="185"/>
+      <c r="AC25" s="185"/>
+      <c r="AD25" s="185"/>
+      <c r="AE25" s="186"/>
+      <c r="AF25" s="181"/>
+      <c r="AG25" s="182"/>
+      <c r="AH25" s="182"/>
+      <c r="AI25" s="183"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="232"/>
-      <c r="C26" s="233"/>
-      <c r="D26" s="234"/>
-      <c r="E26" s="235"/>
-      <c r="F26" s="236"/>
-      <c r="G26" s="232"/>
-      <c r="H26" s="237"/>
-      <c r="I26" s="233"/>
-      <c r="J26" s="238"/>
-      <c r="K26" s="239"/>
-      <c r="L26" s="239"/>
-      <c r="M26" s="239"/>
-      <c r="N26" s="239"/>
-      <c r="O26" s="239"/>
-      <c r="P26" s="240"/>
-      <c r="Q26" s="241"/>
-      <c r="R26" s="242"/>
-      <c r="S26" s="242"/>
-      <c r="T26" s="242"/>
-      <c r="U26" s="242"/>
-      <c r="V26" s="242"/>
-      <c r="W26" s="242"/>
-      <c r="X26" s="242"/>
-      <c r="Y26" s="242"/>
-      <c r="Z26" s="242"/>
-      <c r="AA26" s="242"/>
-      <c r="AB26" s="242"/>
-      <c r="AC26" s="242"/>
-      <c r="AD26" s="242"/>
-      <c r="AE26" s="243"/>
-      <c r="AF26" s="238"/>
-      <c r="AG26" s="239"/>
-      <c r="AH26" s="239"/>
-      <c r="AI26" s="240"/>
+      <c r="B26" s="175"/>
+      <c r="C26" s="176"/>
+      <c r="D26" s="177"/>
+      <c r="E26" s="178"/>
+      <c r="F26" s="179"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="180"/>
+      <c r="I26" s="176"/>
+      <c r="J26" s="181"/>
+      <c r="K26" s="182"/>
+      <c r="L26" s="182"/>
+      <c r="M26" s="182"/>
+      <c r="N26" s="182"/>
+      <c r="O26" s="182"/>
+      <c r="P26" s="183"/>
+      <c r="Q26" s="184"/>
+      <c r="R26" s="185"/>
+      <c r="S26" s="185"/>
+      <c r="T26" s="185"/>
+      <c r="U26" s="185"/>
+      <c r="V26" s="185"/>
+      <c r="W26" s="185"/>
+      <c r="X26" s="185"/>
+      <c r="Y26" s="185"/>
+      <c r="Z26" s="185"/>
+      <c r="AA26" s="185"/>
+      <c r="AB26" s="185"/>
+      <c r="AC26" s="185"/>
+      <c r="AD26" s="185"/>
+      <c r="AE26" s="186"/>
+      <c r="AF26" s="181"/>
+      <c r="AG26" s="182"/>
+      <c r="AH26" s="182"/>
+      <c r="AI26" s="183"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="232"/>
-      <c r="C27" s="233"/>
-      <c r="D27" s="234"/>
-      <c r="E27" s="235"/>
-      <c r="F27" s="236"/>
-      <c r="G27" s="232"/>
-      <c r="H27" s="237"/>
-      <c r="I27" s="233"/>
-      <c r="J27" s="238"/>
-      <c r="K27" s="239"/>
-      <c r="L27" s="239"/>
-      <c r="M27" s="239"/>
-      <c r="N27" s="239"/>
-      <c r="O27" s="239"/>
-      <c r="P27" s="240"/>
-      <c r="Q27" s="241"/>
-      <c r="R27" s="242"/>
-      <c r="S27" s="242"/>
-      <c r="T27" s="242"/>
-      <c r="U27" s="242"/>
-      <c r="V27" s="242"/>
-      <c r="W27" s="242"/>
-      <c r="X27" s="242"/>
-      <c r="Y27" s="242"/>
-      <c r="Z27" s="242"/>
-      <c r="AA27" s="242"/>
-      <c r="AB27" s="242"/>
-      <c r="AC27" s="242"/>
-      <c r="AD27" s="242"/>
-      <c r="AE27" s="243"/>
-      <c r="AF27" s="238"/>
-      <c r="AG27" s="239"/>
-      <c r="AH27" s="239"/>
-      <c r="AI27" s="240"/>
+      <c r="B27" s="175"/>
+      <c r="C27" s="176"/>
+      <c r="D27" s="177"/>
+      <c r="E27" s="178"/>
+      <c r="F27" s="179"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="180"/>
+      <c r="I27" s="176"/>
+      <c r="J27" s="181"/>
+      <c r="K27" s="182"/>
+      <c r="L27" s="182"/>
+      <c r="M27" s="182"/>
+      <c r="N27" s="182"/>
+      <c r="O27" s="182"/>
+      <c r="P27" s="183"/>
+      <c r="Q27" s="184"/>
+      <c r="R27" s="185"/>
+      <c r="S27" s="185"/>
+      <c r="T27" s="185"/>
+      <c r="U27" s="185"/>
+      <c r="V27" s="185"/>
+      <c r="W27" s="185"/>
+      <c r="X27" s="185"/>
+      <c r="Y27" s="185"/>
+      <c r="Z27" s="185"/>
+      <c r="AA27" s="185"/>
+      <c r="AB27" s="185"/>
+      <c r="AC27" s="185"/>
+      <c r="AD27" s="185"/>
+      <c r="AE27" s="186"/>
+      <c r="AF27" s="181"/>
+      <c r="AG27" s="182"/>
+      <c r="AH27" s="182"/>
+      <c r="AI27" s="183"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="232"/>
-      <c r="C28" s="233"/>
-      <c r="D28" s="234"/>
-      <c r="E28" s="235"/>
-      <c r="F28" s="236"/>
-      <c r="G28" s="232"/>
-      <c r="H28" s="237"/>
-      <c r="I28" s="233"/>
-      <c r="J28" s="238"/>
-      <c r="K28" s="239"/>
-      <c r="L28" s="239"/>
-      <c r="M28" s="239"/>
-      <c r="N28" s="239"/>
-      <c r="O28" s="239"/>
-      <c r="P28" s="240"/>
-      <c r="Q28" s="241"/>
-      <c r="R28" s="242"/>
-      <c r="S28" s="242"/>
-      <c r="T28" s="242"/>
-      <c r="U28" s="242"/>
-      <c r="V28" s="242"/>
-      <c r="W28" s="242"/>
-      <c r="X28" s="242"/>
-      <c r="Y28" s="242"/>
-      <c r="Z28" s="242"/>
-      <c r="AA28" s="242"/>
-      <c r="AB28" s="242"/>
-      <c r="AC28" s="242"/>
-      <c r="AD28" s="242"/>
-      <c r="AE28" s="243"/>
-      <c r="AF28" s="238"/>
-      <c r="AG28" s="239"/>
-      <c r="AH28" s="239"/>
-      <c r="AI28" s="240"/>
+      <c r="B28" s="175"/>
+      <c r="C28" s="176"/>
+      <c r="D28" s="177"/>
+      <c r="E28" s="178"/>
+      <c r="F28" s="179"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="180"/>
+      <c r="I28" s="176"/>
+      <c r="J28" s="181"/>
+      <c r="K28" s="182"/>
+      <c r="L28" s="182"/>
+      <c r="M28" s="182"/>
+      <c r="N28" s="182"/>
+      <c r="O28" s="182"/>
+      <c r="P28" s="183"/>
+      <c r="Q28" s="184"/>
+      <c r="R28" s="185"/>
+      <c r="S28" s="185"/>
+      <c r="T28" s="185"/>
+      <c r="U28" s="185"/>
+      <c r="V28" s="185"/>
+      <c r="W28" s="185"/>
+      <c r="X28" s="185"/>
+      <c r="Y28" s="185"/>
+      <c r="Z28" s="185"/>
+      <c r="AA28" s="185"/>
+      <c r="AB28" s="185"/>
+      <c r="AC28" s="185"/>
+      <c r="AD28" s="185"/>
+      <c r="AE28" s="186"/>
+      <c r="AF28" s="181"/>
+      <c r="AG28" s="182"/>
+      <c r="AH28" s="182"/>
+      <c r="AI28" s="183"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="232"/>
-      <c r="C29" s="233"/>
-      <c r="D29" s="234"/>
-      <c r="E29" s="235"/>
-      <c r="F29" s="236"/>
-      <c r="G29" s="232"/>
-      <c r="H29" s="237"/>
-      <c r="I29" s="233"/>
-      <c r="J29" s="238"/>
-      <c r="K29" s="239"/>
-      <c r="L29" s="239"/>
-      <c r="M29" s="239"/>
-      <c r="N29" s="239"/>
-      <c r="O29" s="239"/>
-      <c r="P29" s="240"/>
-      <c r="Q29" s="241"/>
-      <c r="R29" s="242"/>
-      <c r="S29" s="242"/>
-      <c r="T29" s="242"/>
-      <c r="U29" s="242"/>
-      <c r="V29" s="242"/>
-      <c r="W29" s="242"/>
-      <c r="X29" s="242"/>
-      <c r="Y29" s="242"/>
-      <c r="Z29" s="242"/>
-      <c r="AA29" s="242"/>
-      <c r="AB29" s="242"/>
-      <c r="AC29" s="242"/>
-      <c r="AD29" s="242"/>
-      <c r="AE29" s="243"/>
-      <c r="AF29" s="238"/>
-      <c r="AG29" s="239"/>
-      <c r="AH29" s="239"/>
-      <c r="AI29" s="240"/>
+      <c r="B29" s="175"/>
+      <c r="C29" s="176"/>
+      <c r="D29" s="177"/>
+      <c r="E29" s="178"/>
+      <c r="F29" s="179"/>
+      <c r="G29" s="175"/>
+      <c r="H29" s="180"/>
+      <c r="I29" s="176"/>
+      <c r="J29" s="181"/>
+      <c r="K29" s="182"/>
+      <c r="L29" s="182"/>
+      <c r="M29" s="182"/>
+      <c r="N29" s="182"/>
+      <c r="O29" s="182"/>
+      <c r="P29" s="183"/>
+      <c r="Q29" s="184"/>
+      <c r="R29" s="185"/>
+      <c r="S29" s="185"/>
+      <c r="T29" s="185"/>
+      <c r="U29" s="185"/>
+      <c r="V29" s="185"/>
+      <c r="W29" s="185"/>
+      <c r="X29" s="185"/>
+      <c r="Y29" s="185"/>
+      <c r="Z29" s="185"/>
+      <c r="AA29" s="185"/>
+      <c r="AB29" s="185"/>
+      <c r="AC29" s="185"/>
+      <c r="AD29" s="185"/>
+      <c r="AE29" s="186"/>
+      <c r="AF29" s="181"/>
+      <c r="AG29" s="182"/>
+      <c r="AH29" s="182"/>
+      <c r="AI29" s="183"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="232"/>
-      <c r="C30" s="233"/>
-      <c r="D30" s="234"/>
-      <c r="E30" s="235"/>
-      <c r="F30" s="236"/>
-      <c r="G30" s="232"/>
-      <c r="H30" s="237"/>
-      <c r="I30" s="233"/>
-      <c r="J30" s="238"/>
-      <c r="K30" s="239"/>
-      <c r="L30" s="239"/>
-      <c r="M30" s="239"/>
-      <c r="N30" s="239"/>
-      <c r="O30" s="239"/>
-      <c r="P30" s="240"/>
-      <c r="Q30" s="241"/>
-      <c r="R30" s="242"/>
-      <c r="S30" s="242"/>
-      <c r="T30" s="242"/>
-      <c r="U30" s="242"/>
-      <c r="V30" s="242"/>
-      <c r="W30" s="242"/>
-      <c r="X30" s="242"/>
-      <c r="Y30" s="242"/>
-      <c r="Z30" s="242"/>
-      <c r="AA30" s="242"/>
-      <c r="AB30" s="242"/>
-      <c r="AC30" s="242"/>
-      <c r="AD30" s="242"/>
-      <c r="AE30" s="243"/>
-      <c r="AF30" s="238"/>
-      <c r="AG30" s="239"/>
-      <c r="AH30" s="239"/>
-      <c r="AI30" s="240"/>
+      <c r="B30" s="175"/>
+      <c r="C30" s="176"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="178"/>
+      <c r="F30" s="179"/>
+      <c r="G30" s="175"/>
+      <c r="H30" s="180"/>
+      <c r="I30" s="176"/>
+      <c r="J30" s="181"/>
+      <c r="K30" s="182"/>
+      <c r="L30" s="182"/>
+      <c r="M30" s="182"/>
+      <c r="N30" s="182"/>
+      <c r="O30" s="182"/>
+      <c r="P30" s="183"/>
+      <c r="Q30" s="184"/>
+      <c r="R30" s="185"/>
+      <c r="S30" s="185"/>
+      <c r="T30" s="185"/>
+      <c r="U30" s="185"/>
+      <c r="V30" s="185"/>
+      <c r="W30" s="185"/>
+      <c r="X30" s="185"/>
+      <c r="Y30" s="185"/>
+      <c r="Z30" s="185"/>
+      <c r="AA30" s="185"/>
+      <c r="AB30" s="185"/>
+      <c r="AC30" s="185"/>
+      <c r="AD30" s="185"/>
+      <c r="AE30" s="186"/>
+      <c r="AF30" s="181"/>
+      <c r="AG30" s="182"/>
+      <c r="AH30" s="182"/>
+      <c r="AI30" s="183"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="232"/>
-      <c r="C31" s="233"/>
-      <c r="D31" s="234"/>
-      <c r="E31" s="235"/>
-      <c r="F31" s="236"/>
-      <c r="G31" s="232"/>
-      <c r="H31" s="237"/>
-      <c r="I31" s="233"/>
-      <c r="J31" s="238"/>
-      <c r="K31" s="239"/>
-      <c r="L31" s="239"/>
-      <c r="M31" s="239"/>
-      <c r="N31" s="239"/>
-      <c r="O31" s="239"/>
-      <c r="P31" s="240"/>
-      <c r="Q31" s="241"/>
-      <c r="R31" s="242"/>
-      <c r="S31" s="242"/>
-      <c r="T31" s="242"/>
-      <c r="U31" s="242"/>
-      <c r="V31" s="242"/>
-      <c r="W31" s="242"/>
-      <c r="X31" s="242"/>
-      <c r="Y31" s="242"/>
-      <c r="Z31" s="242"/>
-      <c r="AA31" s="242"/>
-      <c r="AB31" s="242"/>
-      <c r="AC31" s="242"/>
-      <c r="AD31" s="242"/>
-      <c r="AE31" s="243"/>
-      <c r="AF31" s="238"/>
-      <c r="AG31" s="239"/>
-      <c r="AH31" s="239"/>
-      <c r="AI31" s="240"/>
+      <c r="B31" s="175"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="177"/>
+      <c r="E31" s="178"/>
+      <c r="F31" s="179"/>
+      <c r="G31" s="175"/>
+      <c r="H31" s="180"/>
+      <c r="I31" s="176"/>
+      <c r="J31" s="181"/>
+      <c r="K31" s="182"/>
+      <c r="L31" s="182"/>
+      <c r="M31" s="182"/>
+      <c r="N31" s="182"/>
+      <c r="O31" s="182"/>
+      <c r="P31" s="183"/>
+      <c r="Q31" s="184"/>
+      <c r="R31" s="185"/>
+      <c r="S31" s="185"/>
+      <c r="T31" s="185"/>
+      <c r="U31" s="185"/>
+      <c r="V31" s="185"/>
+      <c r="W31" s="185"/>
+      <c r="X31" s="185"/>
+      <c r="Y31" s="185"/>
+      <c r="Z31" s="185"/>
+      <c r="AA31" s="185"/>
+      <c r="AB31" s="185"/>
+      <c r="AC31" s="185"/>
+      <c r="AD31" s="185"/>
+      <c r="AE31" s="186"/>
+      <c r="AF31" s="181"/>
+      <c r="AG31" s="182"/>
+      <c r="AH31" s="182"/>
+      <c r="AI31" s="183"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="232"/>
-      <c r="C32" s="233"/>
-      <c r="D32" s="234"/>
-      <c r="E32" s="235"/>
-      <c r="F32" s="236"/>
-      <c r="G32" s="232"/>
-      <c r="H32" s="237"/>
-      <c r="I32" s="233"/>
-      <c r="J32" s="238"/>
-      <c r="K32" s="244"/>
-      <c r="L32" s="239"/>
-      <c r="M32" s="239"/>
-      <c r="N32" s="239"/>
-      <c r="O32" s="239"/>
-      <c r="P32" s="240"/>
-      <c r="Q32" s="241"/>
-      <c r="R32" s="242"/>
-      <c r="S32" s="242"/>
-      <c r="T32" s="242"/>
-      <c r="U32" s="242"/>
-      <c r="V32" s="242"/>
-      <c r="W32" s="242"/>
-      <c r="X32" s="242"/>
-      <c r="Y32" s="242"/>
-      <c r="Z32" s="242"/>
-      <c r="AA32" s="242"/>
-      <c r="AB32" s="242"/>
-      <c r="AC32" s="242"/>
-      <c r="AD32" s="242"/>
-      <c r="AE32" s="243"/>
-      <c r="AF32" s="238"/>
-      <c r="AG32" s="239"/>
-      <c r="AH32" s="239"/>
-      <c r="AI32" s="240"/>
+      <c r="B32" s="175"/>
+      <c r="C32" s="176"/>
+      <c r="D32" s="177"/>
+      <c r="E32" s="178"/>
+      <c r="F32" s="179"/>
+      <c r="G32" s="175"/>
+      <c r="H32" s="180"/>
+      <c r="I32" s="176"/>
+      <c r="J32" s="181"/>
+      <c r="K32" s="187"/>
+      <c r="L32" s="182"/>
+      <c r="M32" s="182"/>
+      <c r="N32" s="182"/>
+      <c r="O32" s="182"/>
+      <c r="P32" s="183"/>
+      <c r="Q32" s="184"/>
+      <c r="R32" s="185"/>
+      <c r="S32" s="185"/>
+      <c r="T32" s="185"/>
+      <c r="U32" s="185"/>
+      <c r="V32" s="185"/>
+      <c r="W32" s="185"/>
+      <c r="X32" s="185"/>
+      <c r="Y32" s="185"/>
+      <c r="Z32" s="185"/>
+      <c r="AA32" s="185"/>
+      <c r="AB32" s="185"/>
+      <c r="AC32" s="185"/>
+      <c r="AD32" s="185"/>
+      <c r="AE32" s="186"/>
+      <c r="AF32" s="181"/>
+      <c r="AG32" s="182"/>
+      <c r="AH32" s="182"/>
+      <c r="AI32" s="183"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="232"/>
-      <c r="C33" s="233"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="235"/>
-      <c r="F33" s="236"/>
-      <c r="G33" s="232"/>
-      <c r="H33" s="237"/>
-      <c r="I33" s="233"/>
-      <c r="J33" s="238"/>
-      <c r="K33" s="239"/>
-      <c r="L33" s="239"/>
-      <c r="M33" s="239"/>
-      <c r="N33" s="239"/>
-      <c r="O33" s="239"/>
-      <c r="P33" s="240"/>
-      <c r="Q33" s="241"/>
-      <c r="R33" s="242"/>
-      <c r="S33" s="242"/>
-      <c r="T33" s="242"/>
-      <c r="U33" s="242"/>
-      <c r="V33" s="242"/>
-      <c r="W33" s="242"/>
-      <c r="X33" s="242"/>
-      <c r="Y33" s="242"/>
-      <c r="Z33" s="242"/>
-      <c r="AA33" s="242"/>
-      <c r="AB33" s="242"/>
-      <c r="AC33" s="242"/>
-      <c r="AD33" s="242"/>
-      <c r="AE33" s="243"/>
-      <c r="AF33" s="238"/>
-      <c r="AG33" s="239"/>
-      <c r="AH33" s="239"/>
-      <c r="AI33" s="240"/>
+      <c r="B33" s="175"/>
+      <c r="C33" s="176"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="178"/>
+      <c r="F33" s="179"/>
+      <c r="G33" s="175"/>
+      <c r="H33" s="180"/>
+      <c r="I33" s="176"/>
+      <c r="J33" s="181"/>
+      <c r="K33" s="182"/>
+      <c r="L33" s="182"/>
+      <c r="M33" s="182"/>
+      <c r="N33" s="182"/>
+      <c r="O33" s="182"/>
+      <c r="P33" s="183"/>
+      <c r="Q33" s="184"/>
+      <c r="R33" s="185"/>
+      <c r="S33" s="185"/>
+      <c r="T33" s="185"/>
+      <c r="U33" s="185"/>
+      <c r="V33" s="185"/>
+      <c r="W33" s="185"/>
+      <c r="X33" s="185"/>
+      <c r="Y33" s="185"/>
+      <c r="Z33" s="185"/>
+      <c r="AA33" s="185"/>
+      <c r="AB33" s="185"/>
+      <c r="AC33" s="185"/>
+      <c r="AD33" s="185"/>
+      <c r="AE33" s="186"/>
+      <c r="AF33" s="181"/>
+      <c r="AG33" s="182"/>
+      <c r="AH33" s="182"/>
+      <c r="AI33" s="183"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -14424,6 +14266,161 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>
@@ -25159,7 +25156,7 @@
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="28" t="s">
-        <v>573</v>
+        <v>70</v>
       </c>
       <c r="O7" s="28" t="s">
         <v>21</v>
@@ -25169,7 +25166,9 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="11.5" thickBot="1">
-      <c r="A8" s="30"/>
+      <c r="A8" s="30" t="s">
+        <v>573</v>
+      </c>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
       <c r="D8" s="31"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26731"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC4D6FE0-479E-45F9-A1D8-85955F4B5EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E795A1D3-5AFC-46C1-A288-45A452DD88DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,19 +11,19 @@
     <sheet name="表紙" sheetId="20" r:id="rId1"/>
     <sheet name="変更履歴" sheetId="21" r:id="rId2"/>
     <sheet name="XxxAction_クラス単体" sheetId="23" r:id="rId3"/>
-    <sheet name="XxxAction_リクエスト単体" sheetId="24" r:id="rId4"/>
+    <sheet name="XXX_リクエスト単体" sheetId="24" r:id="rId4"/>
     <sheet name="取引単体" sheetId="25" r:id="rId5"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XXX_リクエスト単体!$A$10:$R$316</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">XxxAction_クラス単体!$A$10:$R$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">XxxAction_リクエスト単体!$A$10:$R$316</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">XXX_リクエスト単体!$A$1:$R$316</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">XxxAction_クラス単体!$A$1:$R$298</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">XxxAction_リクエスト単体!$A$1:$R$316</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">取引単体!$A$1:$P$21</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$S$39</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">変更履歴!$A$1:$AI$34</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">XXX_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">XxxAction_クラス単体!$1:$10</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">XxxAction_リクエスト単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">取引単体!$1:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">変更履歴!$1:$4</definedName>
   </definedNames>
@@ -8638,108 +8638,6 @@
     <xf numFmtId="31" fontId="12" fillId="0" borderId="0" xfId="3" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="178" fontId="6" fillId="0" borderId="7" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -8846,6 +8744,108 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="22" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -13014,57 +13014,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A1" s="215" t="s">
+      <c r="A1" s="181" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="216"/>
-      <c r="C1" s="216"/>
-      <c r="D1" s="217"/>
-      <c r="E1" s="218" t="s">
+      <c r="B1" s="182"/>
+      <c r="C1" s="182"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="184" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="219"/>
-      <c r="G1" s="219"/>
-      <c r="H1" s="219"/>
-      <c r="I1" s="219"/>
-      <c r="J1" s="219"/>
-      <c r="K1" s="219"/>
-      <c r="L1" s="219"/>
-      <c r="M1" s="219"/>
-      <c r="N1" s="220"/>
-      <c r="O1" s="224" t="s">
+      <c r="F1" s="185"/>
+      <c r="G1" s="185"/>
+      <c r="H1" s="185"/>
+      <c r="I1" s="185"/>
+      <c r="J1" s="185"/>
+      <c r="K1" s="185"/>
+      <c r="L1" s="185"/>
+      <c r="M1" s="185"/>
+      <c r="N1" s="186"/>
+      <c r="O1" s="190" t="s">
         <v>40</v>
       </c>
-      <c r="P1" s="225"/>
-      <c r="Q1" s="225"/>
-      <c r="R1" s="226"/>
-      <c r="S1" s="233" t="s">
+      <c r="P1" s="191"/>
+      <c r="Q1" s="191"/>
+      <c r="R1" s="192"/>
+      <c r="S1" s="199" t="s">
         <v>572</v>
       </c>
-      <c r="T1" s="234"/>
-      <c r="U1" s="234"/>
-      <c r="V1" s="234"/>
-      <c r="W1" s="234"/>
-      <c r="X1" s="234"/>
-      <c r="Y1" s="234"/>
-      <c r="Z1" s="235"/>
-      <c r="AA1" s="215" t="s">
+      <c r="T1" s="200"/>
+      <c r="U1" s="200"/>
+      <c r="V1" s="200"/>
+      <c r="W1" s="200"/>
+      <c r="X1" s="200"/>
+      <c r="Y1" s="200"/>
+      <c r="Z1" s="201"/>
+      <c r="AA1" s="181" t="s">
         <v>41</v>
       </c>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="242" t="str">
+      <c r="AB1" s="183"/>
+      <c r="AC1" s="208" t="str">
         <f>IF(AF8="","",AF8)</f>
         <v>TIS</v>
       </c>
-      <c r="AD1" s="243"/>
-      <c r="AE1" s="243"/>
-      <c r="AF1" s="244"/>
-      <c r="AG1" s="209">
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="210"/>
+      <c r="AG1" s="175">
         <f>IF(D8="","",D8)</f>
         <v>43336</v>
       </c>
-      <c r="AH1" s="210"/>
-      <c r="AI1" s="211"/>
+      <c r="AH1" s="176"/>
+      <c r="AI1" s="177"/>
       <c r="AJ1" s="11"/>
       <c r="AK1" s="11"/>
       <c r="AL1" s="11"/>
@@ -13072,53 +13072,53 @@
       <c r="AN1" s="12"/>
     </row>
     <row r="2" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A2" s="215" t="s">
+      <c r="A2" s="181" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="216"/>
-      <c r="C2" s="216"/>
-      <c r="D2" s="217"/>
-      <c r="E2" s="218" t="s">
+      <c r="B2" s="182"/>
+      <c r="C2" s="182"/>
+      <c r="D2" s="183"/>
+      <c r="E2" s="184" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="219"/>
-      <c r="G2" s="219"/>
-      <c r="H2" s="219"/>
-      <c r="I2" s="219"/>
-      <c r="J2" s="219"/>
-      <c r="K2" s="219"/>
-      <c r="L2" s="219"/>
-      <c r="M2" s="219"/>
-      <c r="N2" s="220"/>
-      <c r="O2" s="227"/>
-      <c r="P2" s="228"/>
-      <c r="Q2" s="228"/>
-      <c r="R2" s="229"/>
-      <c r="S2" s="236"/>
-      <c r="T2" s="237"/>
-      <c r="U2" s="237"/>
-      <c r="V2" s="237"/>
-      <c r="W2" s="237"/>
-      <c r="X2" s="237"/>
-      <c r="Y2" s="237"/>
-      <c r="Z2" s="238"/>
-      <c r="AA2" s="215" t="s">
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+      <c r="M2" s="185"/>
+      <c r="N2" s="186"/>
+      <c r="O2" s="193"/>
+      <c r="P2" s="194"/>
+      <c r="Q2" s="194"/>
+      <c r="R2" s="195"/>
+      <c r="S2" s="202"/>
+      <c r="T2" s="203"/>
+      <c r="U2" s="203"/>
+      <c r="V2" s="203"/>
+      <c r="W2" s="203"/>
+      <c r="X2" s="203"/>
+      <c r="Y2" s="203"/>
+      <c r="Z2" s="204"/>
+      <c r="AA2" s="181" t="s">
         <v>43</v>
       </c>
-      <c r="AB2" s="217"/>
-      <c r="AC2" s="221" t="str">
+      <c r="AB2" s="183"/>
+      <c r="AC2" s="187" t="str">
         <f ca="1">IF(COUNTA(AF9:AF33)&lt;&gt;0,INDIRECT("AF"&amp;(COUNTA(AF9:AF33)+8)),"")</f>
         <v>TIS</v>
       </c>
-      <c r="AD2" s="222"/>
-      <c r="AE2" s="222"/>
-      <c r="AF2" s="223"/>
-      <c r="AG2" s="209">
+      <c r="AD2" s="188"/>
+      <c r="AE2" s="188"/>
+      <c r="AF2" s="189"/>
+      <c r="AG2" s="175">
         <f>IF(D9="","",MAX(D9:F33))</f>
         <v>44852</v>
       </c>
-      <c r="AH2" s="210"/>
-      <c r="AI2" s="211"/>
+      <c r="AH2" s="176"/>
+      <c r="AI2" s="177"/>
       <c r="AJ2" s="11"/>
       <c r="AK2" s="11"/>
       <c r="AL2" s="11"/>
@@ -13126,45 +13126,45 @@
       <c r="AN2" s="11"/>
     </row>
     <row r="3" spans="1:40" s="13" customFormat="1" ht="12" customHeight="1">
-      <c r="A3" s="215" t="s">
+      <c r="A3" s="181" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="216"/>
-      <c r="C3" s="216"/>
-      <c r="D3" s="217"/>
-      <c r="E3" s="218" t="s">
+      <c r="B3" s="182"/>
+      <c r="C3" s="182"/>
+      <c r="D3" s="183"/>
+      <c r="E3" s="184" t="s">
         <v>54</v>
       </c>
-      <c r="F3" s="219"/>
-      <c r="G3" s="219"/>
-      <c r="H3" s="219"/>
-      <c r="I3" s="219"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="219"/>
-      <c r="L3" s="219"/>
-      <c r="M3" s="219"/>
-      <c r="N3" s="220"/>
-      <c r="O3" s="230"/>
-      <c r="P3" s="231"/>
-      <c r="Q3" s="231"/>
-      <c r="R3" s="232"/>
-      <c r="S3" s="239"/>
-      <c r="T3" s="240"/>
-      <c r="U3" s="240"/>
-      <c r="V3" s="240"/>
-      <c r="W3" s="240"/>
-      <c r="X3" s="240"/>
-      <c r="Y3" s="240"/>
-      <c r="Z3" s="241"/>
-      <c r="AA3" s="215"/>
-      <c r="AB3" s="217"/>
-      <c r="AC3" s="242"/>
-      <c r="AD3" s="243"/>
-      <c r="AE3" s="243"/>
-      <c r="AF3" s="244"/>
-      <c r="AG3" s="209"/>
-      <c r="AH3" s="210"/>
-      <c r="AI3" s="211"/>
+      <c r="F3" s="185"/>
+      <c r="G3" s="185"/>
+      <c r="H3" s="185"/>
+      <c r="I3" s="185"/>
+      <c r="J3" s="185"/>
+      <c r="K3" s="185"/>
+      <c r="L3" s="185"/>
+      <c r="M3" s="185"/>
+      <c r="N3" s="186"/>
+      <c r="O3" s="196"/>
+      <c r="P3" s="197"/>
+      <c r="Q3" s="197"/>
+      <c r="R3" s="198"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="206"/>
+      <c r="U3" s="206"/>
+      <c r="V3" s="206"/>
+      <c r="W3" s="206"/>
+      <c r="X3" s="206"/>
+      <c r="Y3" s="206"/>
+      <c r="Z3" s="207"/>
+      <c r="AA3" s="181"/>
+      <c r="AB3" s="183"/>
+      <c r="AC3" s="208"/>
+      <c r="AD3" s="209"/>
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="210"/>
+      <c r="AG3" s="175"/>
+      <c r="AH3" s="176"/>
+      <c r="AI3" s="177"/>
       <c r="AJ3" s="11"/>
       <c r="AK3" s="11"/>
       <c r="AL3" s="11"/>
@@ -13201,97 +13201,97 @@
       <c r="A7" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="212" t="s">
+      <c r="B7" s="178" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="213"/>
-      <c r="D7" s="212" t="s">
+      <c r="C7" s="179"/>
+      <c r="D7" s="178" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="214"/>
-      <c r="F7" s="213"/>
-      <c r="G7" s="212" t="s">
+      <c r="E7" s="180"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="178" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="214"/>
-      <c r="I7" s="213"/>
-      <c r="J7" s="212" t="s">
+      <c r="H7" s="180"/>
+      <c r="I7" s="179"/>
+      <c r="J7" s="178" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="214"/>
-      <c r="L7" s="214"/>
-      <c r="M7" s="214"/>
-      <c r="N7" s="214"/>
-      <c r="O7" s="214"/>
-      <c r="P7" s="213"/>
-      <c r="Q7" s="212" t="s">
+      <c r="K7" s="180"/>
+      <c r="L7" s="180"/>
+      <c r="M7" s="180"/>
+      <c r="N7" s="180"/>
+      <c r="O7" s="180"/>
+      <c r="P7" s="179"/>
+      <c r="Q7" s="178" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="214"/>
-      <c r="S7" s="214"/>
-      <c r="T7" s="214"/>
-      <c r="U7" s="214"/>
-      <c r="V7" s="214"/>
-      <c r="W7" s="214"/>
-      <c r="X7" s="214"/>
-      <c r="Y7" s="214"/>
-      <c r="Z7" s="214"/>
-      <c r="AA7" s="214"/>
-      <c r="AB7" s="214"/>
-      <c r="AC7" s="214"/>
-      <c r="AD7" s="214"/>
-      <c r="AE7" s="213"/>
-      <c r="AF7" s="212" t="s">
+      <c r="R7" s="180"/>
+      <c r="S7" s="180"/>
+      <c r="T7" s="180"/>
+      <c r="U7" s="180"/>
+      <c r="V7" s="180"/>
+      <c r="W7" s="180"/>
+      <c r="X7" s="180"/>
+      <c r="Y7" s="180"/>
+      <c r="Z7" s="180"/>
+      <c r="AA7" s="180"/>
+      <c r="AB7" s="180"/>
+      <c r="AC7" s="180"/>
+      <c r="AD7" s="180"/>
+      <c r="AE7" s="179"/>
+      <c r="AF7" s="178" t="s">
         <v>51</v>
       </c>
-      <c r="AG7" s="214"/>
-      <c r="AH7" s="214"/>
-      <c r="AI7" s="213"/>
+      <c r="AG7" s="180"/>
+      <c r="AH7" s="180"/>
+      <c r="AI7" s="179"/>
     </row>
     <row r="8" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1" thickTop="1">
       <c r="A8" s="24">
         <v>1</v>
       </c>
-      <c r="B8" s="200" t="s">
+      <c r="B8" s="223" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="201"/>
-      <c r="D8" s="202">
+      <c r="C8" s="224"/>
+      <c r="D8" s="225">
         <v>43336</v>
       </c>
-      <c r="E8" s="203"/>
-      <c r="F8" s="204"/>
-      <c r="G8" s="200" t="s">
+      <c r="E8" s="226"/>
+      <c r="F8" s="227"/>
+      <c r="G8" s="223" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="205"/>
-      <c r="I8" s="201"/>
-      <c r="J8" s="206" t="s">
+      <c r="H8" s="228"/>
+      <c r="I8" s="224"/>
+      <c r="J8" s="229" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="207"/>
-      <c r="L8" s="207"/>
-      <c r="M8" s="207"/>
-      <c r="N8" s="207"/>
-      <c r="O8" s="207"/>
-      <c r="P8" s="208"/>
-      <c r="Q8" s="206" t="s">
+      <c r="K8" s="230"/>
+      <c r="L8" s="230"/>
+      <c r="M8" s="230"/>
+      <c r="N8" s="230"/>
+      <c r="O8" s="230"/>
+      <c r="P8" s="231"/>
+      <c r="Q8" s="229" t="s">
         <v>60</v>
       </c>
-      <c r="R8" s="207"/>
-      <c r="S8" s="207"/>
-      <c r="T8" s="207"/>
-      <c r="U8" s="207"/>
-      <c r="V8" s="207"/>
-      <c r="W8" s="207"/>
-      <c r="X8" s="207"/>
-      <c r="Y8" s="207"/>
-      <c r="Z8" s="207"/>
-      <c r="AA8" s="207"/>
-      <c r="AB8" s="207"/>
-      <c r="AC8" s="207"/>
-      <c r="AD8" s="207"/>
-      <c r="AE8" s="208"/>
+      <c r="R8" s="230"/>
+      <c r="S8" s="230"/>
+      <c r="T8" s="230"/>
+      <c r="U8" s="230"/>
+      <c r="V8" s="230"/>
+      <c r="W8" s="230"/>
+      <c r="X8" s="230"/>
+      <c r="Y8" s="230"/>
+      <c r="Z8" s="230"/>
+      <c r="AA8" s="230"/>
+      <c r="AB8" s="230"/>
+      <c r="AC8" s="230"/>
+      <c r="AD8" s="230"/>
+      <c r="AE8" s="231"/>
       <c r="AF8" s="25" t="s">
         <v>61</v>
       </c>
@@ -13303,946 +13303,1101 @@
       <c r="A9" s="24">
         <v>2</v>
       </c>
-      <c r="B9" s="188" t="s">
+      <c r="B9" s="211" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="189"/>
-      <c r="D9" s="190">
+      <c r="C9" s="212"/>
+      <c r="D9" s="213">
         <v>44852</v>
       </c>
-      <c r="E9" s="191"/>
-      <c r="F9" s="192"/>
-      <c r="G9" s="190" t="s">
+      <c r="E9" s="214"/>
+      <c r="F9" s="215"/>
+      <c r="G9" s="213" t="s">
         <v>65</v>
       </c>
-      <c r="H9" s="193"/>
-      <c r="I9" s="189"/>
-      <c r="J9" s="194" t="s">
+      <c r="H9" s="216"/>
+      <c r="I9" s="212"/>
+      <c r="J9" s="217" t="s">
         <v>66</v>
       </c>
-      <c r="K9" s="195"/>
-      <c r="L9" s="195"/>
-      <c r="M9" s="195"/>
-      <c r="N9" s="195"/>
-      <c r="O9" s="195"/>
-      <c r="P9" s="196"/>
-      <c r="Q9" s="194" t="s">
+      <c r="K9" s="218"/>
+      <c r="L9" s="218"/>
+      <c r="M9" s="218"/>
+      <c r="N9" s="218"/>
+      <c r="O9" s="218"/>
+      <c r="P9" s="219"/>
+      <c r="Q9" s="217" t="s">
         <v>67</v>
       </c>
-      <c r="R9" s="197"/>
-      <c r="S9" s="197"/>
-      <c r="T9" s="197"/>
-      <c r="U9" s="197"/>
-      <c r="V9" s="197"/>
-      <c r="W9" s="197"/>
-      <c r="X9" s="197"/>
-      <c r="Y9" s="197"/>
-      <c r="Z9" s="197"/>
-      <c r="AA9" s="197"/>
-      <c r="AB9" s="197"/>
-      <c r="AC9" s="197"/>
-      <c r="AD9" s="197"/>
-      <c r="AE9" s="198"/>
-      <c r="AF9" s="199" t="s">
+      <c r="R9" s="220"/>
+      <c r="S9" s="220"/>
+      <c r="T9" s="220"/>
+      <c r="U9" s="220"/>
+      <c r="V9" s="220"/>
+      <c r="W9" s="220"/>
+      <c r="X9" s="220"/>
+      <c r="Y9" s="220"/>
+      <c r="Z9" s="220"/>
+      <c r="AA9" s="220"/>
+      <c r="AB9" s="220"/>
+      <c r="AC9" s="220"/>
+      <c r="AD9" s="220"/>
+      <c r="AE9" s="221"/>
+      <c r="AF9" s="222" t="s">
         <v>61</v>
       </c>
-      <c r="AG9" s="195"/>
-      <c r="AH9" s="195"/>
-      <c r="AI9" s="196"/>
+      <c r="AG9" s="218"/>
+      <c r="AH9" s="218"/>
+      <c r="AI9" s="219"/>
     </row>
     <row r="10" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="21"/>
-      <c r="B10" s="175"/>
-      <c r="C10" s="176"/>
-      <c r="D10" s="177"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="179"/>
-      <c r="G10" s="175"/>
-      <c r="H10" s="180"/>
-      <c r="I10" s="176"/>
-      <c r="J10" s="181"/>
-      <c r="K10" s="182"/>
-      <c r="L10" s="182"/>
-      <c r="M10" s="182"/>
-      <c r="N10" s="182"/>
-      <c r="O10" s="182"/>
-      <c r="P10" s="183"/>
-      <c r="Q10" s="184"/>
-      <c r="R10" s="185"/>
-      <c r="S10" s="185"/>
-      <c r="T10" s="185"/>
-      <c r="U10" s="185"/>
-      <c r="V10" s="185"/>
-      <c r="W10" s="185"/>
-      <c r="X10" s="185"/>
-      <c r="Y10" s="185"/>
-      <c r="Z10" s="185"/>
-      <c r="AA10" s="185"/>
-      <c r="AB10" s="185"/>
-      <c r="AC10" s="185"/>
-      <c r="AD10" s="185"/>
-      <c r="AE10" s="186"/>
-      <c r="AF10" s="181"/>
-      <c r="AG10" s="182"/>
-      <c r="AH10" s="182"/>
-      <c r="AI10" s="183"/>
+      <c r="B10" s="232"/>
+      <c r="C10" s="233"/>
+      <c r="D10" s="234"/>
+      <c r="E10" s="235"/>
+      <c r="F10" s="236"/>
+      <c r="G10" s="232"/>
+      <c r="H10" s="237"/>
+      <c r="I10" s="233"/>
+      <c r="J10" s="238"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
+      <c r="N10" s="239"/>
+      <c r="O10" s="239"/>
+      <c r="P10" s="240"/>
+      <c r="Q10" s="241"/>
+      <c r="R10" s="242"/>
+      <c r="S10" s="242"/>
+      <c r="T10" s="242"/>
+      <c r="U10" s="242"/>
+      <c r="V10" s="242"/>
+      <c r="W10" s="242"/>
+      <c r="X10" s="242"/>
+      <c r="Y10" s="242"/>
+      <c r="Z10" s="242"/>
+      <c r="AA10" s="242"/>
+      <c r="AB10" s="242"/>
+      <c r="AC10" s="242"/>
+      <c r="AD10" s="242"/>
+      <c r="AE10" s="243"/>
+      <c r="AF10" s="238"/>
+      <c r="AG10" s="239"/>
+      <c r="AH10" s="239"/>
+      <c r="AI10" s="240"/>
     </row>
     <row r="11" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="21"/>
-      <c r="B11" s="175"/>
-      <c r="C11" s="176"/>
-      <c r="D11" s="177"/>
-      <c r="E11" s="178"/>
-      <c r="F11" s="179"/>
-      <c r="G11" s="175"/>
-      <c r="H11" s="180"/>
-      <c r="I11" s="176"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
-      <c r="L11" s="182"/>
-      <c r="M11" s="182"/>
-      <c r="N11" s="182"/>
-      <c r="O11" s="182"/>
-      <c r="P11" s="183"/>
-      <c r="Q11" s="184"/>
-      <c r="R11" s="185"/>
-      <c r="S11" s="185"/>
-      <c r="T11" s="185"/>
-      <c r="U11" s="185"/>
-      <c r="V11" s="185"/>
-      <c r="W11" s="185"/>
-      <c r="X11" s="185"/>
-      <c r="Y11" s="185"/>
-      <c r="Z11" s="185"/>
-      <c r="AA11" s="185"/>
-      <c r="AB11" s="185"/>
-      <c r="AC11" s="185"/>
-      <c r="AD11" s="185"/>
-      <c r="AE11" s="186"/>
-      <c r="AF11" s="181"/>
-      <c r="AG11" s="182"/>
-      <c r="AH11" s="182"/>
-      <c r="AI11" s="183"/>
+      <c r="B11" s="232"/>
+      <c r="C11" s="233"/>
+      <c r="D11" s="234"/>
+      <c r="E11" s="235"/>
+      <c r="F11" s="236"/>
+      <c r="G11" s="232"/>
+      <c r="H11" s="237"/>
+      <c r="I11" s="233"/>
+      <c r="J11" s="238"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
+      <c r="N11" s="239"/>
+      <c r="O11" s="239"/>
+      <c r="P11" s="240"/>
+      <c r="Q11" s="241"/>
+      <c r="R11" s="242"/>
+      <c r="S11" s="242"/>
+      <c r="T11" s="242"/>
+      <c r="U11" s="242"/>
+      <c r="V11" s="242"/>
+      <c r="W11" s="242"/>
+      <c r="X11" s="242"/>
+      <c r="Y11" s="242"/>
+      <c r="Z11" s="242"/>
+      <c r="AA11" s="242"/>
+      <c r="AB11" s="242"/>
+      <c r="AC11" s="242"/>
+      <c r="AD11" s="242"/>
+      <c r="AE11" s="243"/>
+      <c r="AF11" s="238"/>
+      <c r="AG11" s="239"/>
+      <c r="AH11" s="239"/>
+      <c r="AI11" s="240"/>
     </row>
     <row r="12" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="21"/>
-      <c r="B12" s="175"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="177"/>
-      <c r="E12" s="178"/>
-      <c r="F12" s="179"/>
-      <c r="G12" s="175"/>
-      <c r="H12" s="180"/>
-      <c r="I12" s="176"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="182"/>
-      <c r="L12" s="182"/>
-      <c r="M12" s="182"/>
-      <c r="N12" s="182"/>
-      <c r="O12" s="182"/>
-      <c r="P12" s="183"/>
-      <c r="Q12" s="184"/>
-      <c r="R12" s="185"/>
-      <c r="S12" s="185"/>
-      <c r="T12" s="185"/>
-      <c r="U12" s="185"/>
-      <c r="V12" s="185"/>
-      <c r="W12" s="185"/>
-      <c r="X12" s="185"/>
-      <c r="Y12" s="185"/>
-      <c r="Z12" s="185"/>
-      <c r="AA12" s="185"/>
-      <c r="AB12" s="185"/>
-      <c r="AC12" s="185"/>
-      <c r="AD12" s="185"/>
-      <c r="AE12" s="186"/>
-      <c r="AF12" s="181"/>
-      <c r="AG12" s="182"/>
-      <c r="AH12" s="182"/>
-      <c r="AI12" s="183"/>
+      <c r="B12" s="232"/>
+      <c r="C12" s="233"/>
+      <c r="D12" s="234"/>
+      <c r="E12" s="235"/>
+      <c r="F12" s="236"/>
+      <c r="G12" s="232"/>
+      <c r="H12" s="237"/>
+      <c r="I12" s="233"/>
+      <c r="J12" s="238"/>
+      <c r="K12" s="239"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="239"/>
+      <c r="N12" s="239"/>
+      <c r="O12" s="239"/>
+      <c r="P12" s="240"/>
+      <c r="Q12" s="241"/>
+      <c r="R12" s="242"/>
+      <c r="S12" s="242"/>
+      <c r="T12" s="242"/>
+      <c r="U12" s="242"/>
+      <c r="V12" s="242"/>
+      <c r="W12" s="242"/>
+      <c r="X12" s="242"/>
+      <c r="Y12" s="242"/>
+      <c r="Z12" s="242"/>
+      <c r="AA12" s="242"/>
+      <c r="AB12" s="242"/>
+      <c r="AC12" s="242"/>
+      <c r="AD12" s="242"/>
+      <c r="AE12" s="243"/>
+      <c r="AF12" s="238"/>
+      <c r="AG12" s="239"/>
+      <c r="AH12" s="239"/>
+      <c r="AI12" s="240"/>
     </row>
     <row r="13" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="21"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="176"/>
-      <c r="D13" s="177"/>
-      <c r="E13" s="178"/>
-      <c r="F13" s="179"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="180"/>
-      <c r="I13" s="176"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="182"/>
-      <c r="L13" s="182"/>
-      <c r="M13" s="182"/>
-      <c r="N13" s="182"/>
-      <c r="O13" s="182"/>
-      <c r="P13" s="183"/>
-      <c r="Q13" s="184"/>
-      <c r="R13" s="185"/>
-      <c r="S13" s="185"/>
-      <c r="T13" s="185"/>
-      <c r="U13" s="185"/>
-      <c r="V13" s="185"/>
-      <c r="W13" s="185"/>
-      <c r="X13" s="185"/>
-      <c r="Y13" s="185"/>
-      <c r="Z13" s="185"/>
-      <c r="AA13" s="185"/>
-      <c r="AB13" s="185"/>
-      <c r="AC13" s="185"/>
-      <c r="AD13" s="185"/>
-      <c r="AE13" s="186"/>
-      <c r="AF13" s="181"/>
-      <c r="AG13" s="182"/>
-      <c r="AH13" s="182"/>
-      <c r="AI13" s="183"/>
+      <c r="B13" s="232"/>
+      <c r="C13" s="233"/>
+      <c r="D13" s="234"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="236"/>
+      <c r="G13" s="232"/>
+      <c r="H13" s="237"/>
+      <c r="I13" s="233"/>
+      <c r="J13" s="238"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
+      <c r="M13" s="239"/>
+      <c r="N13" s="239"/>
+      <c r="O13" s="239"/>
+      <c r="P13" s="240"/>
+      <c r="Q13" s="241"/>
+      <c r="R13" s="242"/>
+      <c r="S13" s="242"/>
+      <c r="T13" s="242"/>
+      <c r="U13" s="242"/>
+      <c r="V13" s="242"/>
+      <c r="W13" s="242"/>
+      <c r="X13" s="242"/>
+      <c r="Y13" s="242"/>
+      <c r="Z13" s="242"/>
+      <c r="AA13" s="242"/>
+      <c r="AB13" s="242"/>
+      <c r="AC13" s="242"/>
+      <c r="AD13" s="242"/>
+      <c r="AE13" s="243"/>
+      <c r="AF13" s="238"/>
+      <c r="AG13" s="239"/>
+      <c r="AH13" s="239"/>
+      <c r="AI13" s="240"/>
     </row>
     <row r="14" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="21"/>
-      <c r="B14" s="175"/>
-      <c r="C14" s="176"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="178"/>
-      <c r="F14" s="179"/>
-      <c r="G14" s="175"/>
-      <c r="H14" s="180"/>
-      <c r="I14" s="176"/>
-      <c r="J14" s="181"/>
-      <c r="K14" s="182"/>
-      <c r="L14" s="182"/>
-      <c r="M14" s="182"/>
-      <c r="N14" s="182"/>
-      <c r="O14" s="182"/>
-      <c r="P14" s="183"/>
-      <c r="Q14" s="184"/>
-      <c r="R14" s="185"/>
-      <c r="S14" s="185"/>
-      <c r="T14" s="185"/>
-      <c r="U14" s="185"/>
-      <c r="V14" s="185"/>
-      <c r="W14" s="185"/>
-      <c r="X14" s="185"/>
-      <c r="Y14" s="185"/>
-      <c r="Z14" s="185"/>
-      <c r="AA14" s="185"/>
-      <c r="AB14" s="185"/>
-      <c r="AC14" s="185"/>
-      <c r="AD14" s="185"/>
-      <c r="AE14" s="186"/>
-      <c r="AF14" s="181"/>
-      <c r="AG14" s="182"/>
-      <c r="AH14" s="182"/>
-      <c r="AI14" s="183"/>
+      <c r="B14" s="232"/>
+      <c r="C14" s="233"/>
+      <c r="D14" s="234"/>
+      <c r="E14" s="235"/>
+      <c r="F14" s="236"/>
+      <c r="G14" s="232"/>
+      <c r="H14" s="237"/>
+      <c r="I14" s="233"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="239"/>
+      <c r="L14" s="239"/>
+      <c r="M14" s="239"/>
+      <c r="N14" s="239"/>
+      <c r="O14" s="239"/>
+      <c r="P14" s="240"/>
+      <c r="Q14" s="241"/>
+      <c r="R14" s="242"/>
+      <c r="S14" s="242"/>
+      <c r="T14" s="242"/>
+      <c r="U14" s="242"/>
+      <c r="V14" s="242"/>
+      <c r="W14" s="242"/>
+      <c r="X14" s="242"/>
+      <c r="Y14" s="242"/>
+      <c r="Z14" s="242"/>
+      <c r="AA14" s="242"/>
+      <c r="AB14" s="242"/>
+      <c r="AC14" s="242"/>
+      <c r="AD14" s="242"/>
+      <c r="AE14" s="243"/>
+      <c r="AF14" s="238"/>
+      <c r="AG14" s="239"/>
+      <c r="AH14" s="239"/>
+      <c r="AI14" s="240"/>
     </row>
     <row r="15" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="21"/>
-      <c r="B15" s="175"/>
-      <c r="C15" s="176"/>
-      <c r="D15" s="177"/>
-      <c r="E15" s="178"/>
-      <c r="F15" s="179"/>
-      <c r="G15" s="175"/>
-      <c r="H15" s="180"/>
-      <c r="I15" s="176"/>
-      <c r="J15" s="181"/>
-      <c r="K15" s="182"/>
-      <c r="L15" s="182"/>
-      <c r="M15" s="182"/>
-      <c r="N15" s="182"/>
-      <c r="O15" s="182"/>
-      <c r="P15" s="183"/>
-      <c r="Q15" s="184"/>
-      <c r="R15" s="185"/>
-      <c r="S15" s="185"/>
-      <c r="T15" s="185"/>
-      <c r="U15" s="185"/>
-      <c r="V15" s="185"/>
-      <c r="W15" s="185"/>
-      <c r="X15" s="185"/>
-      <c r="Y15" s="185"/>
-      <c r="Z15" s="185"/>
-      <c r="AA15" s="185"/>
-      <c r="AB15" s="185"/>
-      <c r="AC15" s="185"/>
-      <c r="AD15" s="185"/>
-      <c r="AE15" s="186"/>
-      <c r="AF15" s="181"/>
-      <c r="AG15" s="182"/>
-      <c r="AH15" s="182"/>
-      <c r="AI15" s="183"/>
+      <c r="B15" s="232"/>
+      <c r="C15" s="233"/>
+      <c r="D15" s="234"/>
+      <c r="E15" s="235"/>
+      <c r="F15" s="236"/>
+      <c r="G15" s="232"/>
+      <c r="H15" s="237"/>
+      <c r="I15" s="233"/>
+      <c r="J15" s="238"/>
+      <c r="K15" s="239"/>
+      <c r="L15" s="239"/>
+      <c r="M15" s="239"/>
+      <c r="N15" s="239"/>
+      <c r="O15" s="239"/>
+      <c r="P15" s="240"/>
+      <c r="Q15" s="241"/>
+      <c r="R15" s="242"/>
+      <c r="S15" s="242"/>
+      <c r="T15" s="242"/>
+      <c r="U15" s="242"/>
+      <c r="V15" s="242"/>
+      <c r="W15" s="242"/>
+      <c r="X15" s="242"/>
+      <c r="Y15" s="242"/>
+      <c r="Z15" s="242"/>
+      <c r="AA15" s="242"/>
+      <c r="AB15" s="242"/>
+      <c r="AC15" s="242"/>
+      <c r="AD15" s="242"/>
+      <c r="AE15" s="243"/>
+      <c r="AF15" s="238"/>
+      <c r="AG15" s="239"/>
+      <c r="AH15" s="239"/>
+      <c r="AI15" s="240"/>
     </row>
     <row r="16" spans="1:40" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="21"/>
-      <c r="B16" s="175"/>
-      <c r="C16" s="176"/>
-      <c r="D16" s="177"/>
-      <c r="E16" s="178"/>
-      <c r="F16" s="179"/>
-      <c r="G16" s="175"/>
-      <c r="H16" s="180"/>
-      <c r="I16" s="176"/>
-      <c r="J16" s="181"/>
-      <c r="K16" s="182"/>
-      <c r="L16" s="182"/>
-      <c r="M16" s="182"/>
-      <c r="N16" s="182"/>
-      <c r="O16" s="182"/>
-      <c r="P16" s="183"/>
-      <c r="Q16" s="184"/>
-      <c r="R16" s="185"/>
-      <c r="S16" s="185"/>
-      <c r="T16" s="185"/>
-      <c r="U16" s="185"/>
-      <c r="V16" s="185"/>
-      <c r="W16" s="185"/>
-      <c r="X16" s="185"/>
-      <c r="Y16" s="185"/>
-      <c r="Z16" s="185"/>
-      <c r="AA16" s="185"/>
-      <c r="AB16" s="185"/>
-      <c r="AC16" s="185"/>
-      <c r="AD16" s="185"/>
-      <c r="AE16" s="186"/>
-      <c r="AF16" s="181"/>
-      <c r="AG16" s="182"/>
-      <c r="AH16" s="182"/>
-      <c r="AI16" s="183"/>
+      <c r="B16" s="232"/>
+      <c r="C16" s="233"/>
+      <c r="D16" s="234"/>
+      <c r="E16" s="235"/>
+      <c r="F16" s="236"/>
+      <c r="G16" s="232"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="233"/>
+      <c r="J16" s="238"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="239"/>
+      <c r="M16" s="239"/>
+      <c r="N16" s="239"/>
+      <c r="O16" s="239"/>
+      <c r="P16" s="240"/>
+      <c r="Q16" s="241"/>
+      <c r="R16" s="242"/>
+      <c r="S16" s="242"/>
+      <c r="T16" s="242"/>
+      <c r="U16" s="242"/>
+      <c r="V16" s="242"/>
+      <c r="W16" s="242"/>
+      <c r="X16" s="242"/>
+      <c r="Y16" s="242"/>
+      <c r="Z16" s="242"/>
+      <c r="AA16" s="242"/>
+      <c r="AB16" s="242"/>
+      <c r="AC16" s="242"/>
+      <c r="AD16" s="242"/>
+      <c r="AE16" s="243"/>
+      <c r="AF16" s="238"/>
+      <c r="AG16" s="239"/>
+      <c r="AH16" s="239"/>
+      <c r="AI16" s="240"/>
     </row>
     <row r="17" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="21"/>
-      <c r="B17" s="175"/>
-      <c r="C17" s="176"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="178"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="175"/>
-      <c r="H17" s="180"/>
-      <c r="I17" s="176"/>
-      <c r="J17" s="181"/>
-      <c r="K17" s="182"/>
-      <c r="L17" s="182"/>
-      <c r="M17" s="182"/>
-      <c r="N17" s="182"/>
-      <c r="O17" s="182"/>
-      <c r="P17" s="183"/>
-      <c r="Q17" s="184"/>
-      <c r="R17" s="185"/>
-      <c r="S17" s="185"/>
-      <c r="T17" s="185"/>
-      <c r="U17" s="185"/>
-      <c r="V17" s="185"/>
-      <c r="W17" s="185"/>
-      <c r="X17" s="185"/>
-      <c r="Y17" s="185"/>
-      <c r="Z17" s="185"/>
-      <c r="AA17" s="185"/>
-      <c r="AB17" s="185"/>
-      <c r="AC17" s="185"/>
-      <c r="AD17" s="185"/>
-      <c r="AE17" s="186"/>
-      <c r="AF17" s="181"/>
-      <c r="AG17" s="182"/>
-      <c r="AH17" s="182"/>
-      <c r="AI17" s="183"/>
+      <c r="B17" s="232"/>
+      <c r="C17" s="233"/>
+      <c r="D17" s="234"/>
+      <c r="E17" s="235"/>
+      <c r="F17" s="236"/>
+      <c r="G17" s="232"/>
+      <c r="H17" s="237"/>
+      <c r="I17" s="233"/>
+      <c r="J17" s="238"/>
+      <c r="K17" s="239"/>
+      <c r="L17" s="239"/>
+      <c r="M17" s="239"/>
+      <c r="N17" s="239"/>
+      <c r="O17" s="239"/>
+      <c r="P17" s="240"/>
+      <c r="Q17" s="241"/>
+      <c r="R17" s="242"/>
+      <c r="S17" s="242"/>
+      <c r="T17" s="242"/>
+      <c r="U17" s="242"/>
+      <c r="V17" s="242"/>
+      <c r="W17" s="242"/>
+      <c r="X17" s="242"/>
+      <c r="Y17" s="242"/>
+      <c r="Z17" s="242"/>
+      <c r="AA17" s="242"/>
+      <c r="AB17" s="242"/>
+      <c r="AC17" s="242"/>
+      <c r="AD17" s="242"/>
+      <c r="AE17" s="243"/>
+      <c r="AF17" s="238"/>
+      <c r="AG17" s="239"/>
+      <c r="AH17" s="239"/>
+      <c r="AI17" s="240"/>
     </row>
     <row r="18" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="21"/>
-      <c r="B18" s="175"/>
-      <c r="C18" s="176"/>
-      <c r="D18" s="177"/>
-      <c r="E18" s="178"/>
-      <c r="F18" s="179"/>
-      <c r="G18" s="175"/>
-      <c r="H18" s="180"/>
-      <c r="I18" s="176"/>
-      <c r="J18" s="181"/>
-      <c r="K18" s="182"/>
-      <c r="L18" s="182"/>
-      <c r="M18" s="182"/>
-      <c r="N18" s="182"/>
-      <c r="O18" s="182"/>
-      <c r="P18" s="183"/>
-      <c r="Q18" s="184"/>
-      <c r="R18" s="185"/>
-      <c r="S18" s="185"/>
-      <c r="T18" s="185"/>
-      <c r="U18" s="185"/>
-      <c r="V18" s="185"/>
-      <c r="W18" s="185"/>
-      <c r="X18" s="185"/>
-      <c r="Y18" s="185"/>
-      <c r="Z18" s="185"/>
-      <c r="AA18" s="185"/>
-      <c r="AB18" s="185"/>
-      <c r="AC18" s="185"/>
-      <c r="AD18" s="185"/>
-      <c r="AE18" s="186"/>
-      <c r="AF18" s="181"/>
-      <c r="AG18" s="182"/>
-      <c r="AH18" s="182"/>
-      <c r="AI18" s="183"/>
+      <c r="B18" s="232"/>
+      <c r="C18" s="233"/>
+      <c r="D18" s="234"/>
+      <c r="E18" s="235"/>
+      <c r="F18" s="236"/>
+      <c r="G18" s="232"/>
+      <c r="H18" s="237"/>
+      <c r="I18" s="233"/>
+      <c r="J18" s="238"/>
+      <c r="K18" s="239"/>
+      <c r="L18" s="239"/>
+      <c r="M18" s="239"/>
+      <c r="N18" s="239"/>
+      <c r="O18" s="239"/>
+      <c r="P18" s="240"/>
+      <c r="Q18" s="241"/>
+      <c r="R18" s="242"/>
+      <c r="S18" s="242"/>
+      <c r="T18" s="242"/>
+      <c r="U18" s="242"/>
+      <c r="V18" s="242"/>
+      <c r="W18" s="242"/>
+      <c r="X18" s="242"/>
+      <c r="Y18" s="242"/>
+      <c r="Z18" s="242"/>
+      <c r="AA18" s="242"/>
+      <c r="AB18" s="242"/>
+      <c r="AC18" s="242"/>
+      <c r="AD18" s="242"/>
+      <c r="AE18" s="243"/>
+      <c r="AF18" s="238"/>
+      <c r="AG18" s="239"/>
+      <c r="AH18" s="239"/>
+      <c r="AI18" s="240"/>
     </row>
     <row r="19" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="21"/>
-      <c r="B19" s="175"/>
-      <c r="C19" s="176"/>
-      <c r="D19" s="177"/>
-      <c r="E19" s="178"/>
-      <c r="F19" s="179"/>
-      <c r="G19" s="175"/>
-      <c r="H19" s="180"/>
-      <c r="I19" s="176"/>
-      <c r="J19" s="181"/>
-      <c r="K19" s="182"/>
-      <c r="L19" s="182"/>
-      <c r="M19" s="182"/>
-      <c r="N19" s="182"/>
-      <c r="O19" s="182"/>
-      <c r="P19" s="183"/>
-      <c r="Q19" s="184"/>
-      <c r="R19" s="185"/>
-      <c r="S19" s="185"/>
-      <c r="T19" s="185"/>
-      <c r="U19" s="185"/>
-      <c r="V19" s="185"/>
-      <c r="W19" s="185"/>
-      <c r="X19" s="185"/>
-      <c r="Y19" s="185"/>
-      <c r="Z19" s="185"/>
-      <c r="AA19" s="185"/>
-      <c r="AB19" s="185"/>
-      <c r="AC19" s="185"/>
-      <c r="AD19" s="185"/>
-      <c r="AE19" s="186"/>
-      <c r="AF19" s="181"/>
-      <c r="AG19" s="182"/>
-      <c r="AH19" s="182"/>
-      <c r="AI19" s="183"/>
+      <c r="B19" s="232"/>
+      <c r="C19" s="233"/>
+      <c r="D19" s="234"/>
+      <c r="E19" s="235"/>
+      <c r="F19" s="236"/>
+      <c r="G19" s="232"/>
+      <c r="H19" s="237"/>
+      <c r="I19" s="233"/>
+      <c r="J19" s="238"/>
+      <c r="K19" s="239"/>
+      <c r="L19" s="239"/>
+      <c r="M19" s="239"/>
+      <c r="N19" s="239"/>
+      <c r="O19" s="239"/>
+      <c r="P19" s="240"/>
+      <c r="Q19" s="241"/>
+      <c r="R19" s="242"/>
+      <c r="S19" s="242"/>
+      <c r="T19" s="242"/>
+      <c r="U19" s="242"/>
+      <c r="V19" s="242"/>
+      <c r="W19" s="242"/>
+      <c r="X19" s="242"/>
+      <c r="Y19" s="242"/>
+      <c r="Z19" s="242"/>
+      <c r="AA19" s="242"/>
+      <c r="AB19" s="242"/>
+      <c r="AC19" s="242"/>
+      <c r="AD19" s="242"/>
+      <c r="AE19" s="243"/>
+      <c r="AF19" s="238"/>
+      <c r="AG19" s="239"/>
+      <c r="AH19" s="239"/>
+      <c r="AI19" s="240"/>
     </row>
     <row r="20" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="21"/>
-      <c r="B20" s="175"/>
-      <c r="C20" s="176"/>
-      <c r="D20" s="177"/>
-      <c r="E20" s="178"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="175"/>
-      <c r="H20" s="180"/>
-      <c r="I20" s="176"/>
-      <c r="J20" s="181"/>
-      <c r="K20" s="182"/>
-      <c r="L20" s="182"/>
-      <c r="M20" s="182"/>
-      <c r="N20" s="182"/>
-      <c r="O20" s="182"/>
-      <c r="P20" s="183"/>
-      <c r="Q20" s="184"/>
-      <c r="R20" s="185"/>
-      <c r="S20" s="185"/>
-      <c r="T20" s="185"/>
-      <c r="U20" s="185"/>
-      <c r="V20" s="185"/>
-      <c r="W20" s="185"/>
-      <c r="X20" s="185"/>
-      <c r="Y20" s="185"/>
-      <c r="Z20" s="185"/>
-      <c r="AA20" s="185"/>
-      <c r="AB20" s="185"/>
-      <c r="AC20" s="185"/>
-      <c r="AD20" s="185"/>
-      <c r="AE20" s="186"/>
-      <c r="AF20" s="181"/>
-      <c r="AG20" s="182"/>
-      <c r="AH20" s="182"/>
-      <c r="AI20" s="183"/>
+      <c r="B20" s="232"/>
+      <c r="C20" s="233"/>
+      <c r="D20" s="234"/>
+      <c r="E20" s="235"/>
+      <c r="F20" s="236"/>
+      <c r="G20" s="232"/>
+      <c r="H20" s="237"/>
+      <c r="I20" s="233"/>
+      <c r="J20" s="238"/>
+      <c r="K20" s="239"/>
+      <c r="L20" s="239"/>
+      <c r="M20" s="239"/>
+      <c r="N20" s="239"/>
+      <c r="O20" s="239"/>
+      <c r="P20" s="240"/>
+      <c r="Q20" s="241"/>
+      <c r="R20" s="242"/>
+      <c r="S20" s="242"/>
+      <c r="T20" s="242"/>
+      <c r="U20" s="242"/>
+      <c r="V20" s="242"/>
+      <c r="W20" s="242"/>
+      <c r="X20" s="242"/>
+      <c r="Y20" s="242"/>
+      <c r="Z20" s="242"/>
+      <c r="AA20" s="242"/>
+      <c r="AB20" s="242"/>
+      <c r="AC20" s="242"/>
+      <c r="AD20" s="242"/>
+      <c r="AE20" s="243"/>
+      <c r="AF20" s="238"/>
+      <c r="AG20" s="239"/>
+      <c r="AH20" s="239"/>
+      <c r="AI20" s="240"/>
     </row>
     <row r="21" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="21"/>
-      <c r="B21" s="175"/>
-      <c r="C21" s="176"/>
-      <c r="D21" s="177"/>
-      <c r="E21" s="178"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="175"/>
-      <c r="H21" s="180"/>
-      <c r="I21" s="176"/>
-      <c r="J21" s="181"/>
-      <c r="K21" s="182"/>
-      <c r="L21" s="182"/>
-      <c r="M21" s="182"/>
-      <c r="N21" s="182"/>
-      <c r="O21" s="182"/>
-      <c r="P21" s="183"/>
-      <c r="Q21" s="184"/>
-      <c r="R21" s="185"/>
-      <c r="S21" s="185"/>
-      <c r="T21" s="185"/>
-      <c r="U21" s="185"/>
-      <c r="V21" s="185"/>
-      <c r="W21" s="185"/>
-      <c r="X21" s="185"/>
-      <c r="Y21" s="185"/>
-      <c r="Z21" s="185"/>
-      <c r="AA21" s="185"/>
-      <c r="AB21" s="185"/>
-      <c r="AC21" s="185"/>
-      <c r="AD21" s="185"/>
-      <c r="AE21" s="186"/>
-      <c r="AF21" s="181"/>
-      <c r="AG21" s="182"/>
-      <c r="AH21" s="182"/>
-      <c r="AI21" s="183"/>
+      <c r="B21" s="232"/>
+      <c r="C21" s="233"/>
+      <c r="D21" s="234"/>
+      <c r="E21" s="235"/>
+      <c r="F21" s="236"/>
+      <c r="G21" s="232"/>
+      <c r="H21" s="237"/>
+      <c r="I21" s="233"/>
+      <c r="J21" s="238"/>
+      <c r="K21" s="239"/>
+      <c r="L21" s="239"/>
+      <c r="M21" s="239"/>
+      <c r="N21" s="239"/>
+      <c r="O21" s="239"/>
+      <c r="P21" s="240"/>
+      <c r="Q21" s="241"/>
+      <c r="R21" s="242"/>
+      <c r="S21" s="242"/>
+      <c r="T21" s="242"/>
+      <c r="U21" s="242"/>
+      <c r="V21" s="242"/>
+      <c r="W21" s="242"/>
+      <c r="X21" s="242"/>
+      <c r="Y21" s="242"/>
+      <c r="Z21" s="242"/>
+      <c r="AA21" s="242"/>
+      <c r="AB21" s="242"/>
+      <c r="AC21" s="242"/>
+      <c r="AD21" s="242"/>
+      <c r="AE21" s="243"/>
+      <c r="AF21" s="238"/>
+      <c r="AG21" s="239"/>
+      <c r="AH21" s="239"/>
+      <c r="AI21" s="240"/>
     </row>
     <row r="22" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="21"/>
-      <c r="B22" s="175"/>
-      <c r="C22" s="176"/>
-      <c r="D22" s="177"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="175"/>
-      <c r="H22" s="180"/>
-      <c r="I22" s="176"/>
-      <c r="J22" s="181"/>
-      <c r="K22" s="182"/>
-      <c r="L22" s="182"/>
-      <c r="M22" s="182"/>
-      <c r="N22" s="182"/>
-      <c r="O22" s="182"/>
-      <c r="P22" s="183"/>
-      <c r="Q22" s="184"/>
-      <c r="R22" s="185"/>
-      <c r="S22" s="185"/>
-      <c r="T22" s="185"/>
-      <c r="U22" s="185"/>
-      <c r="V22" s="185"/>
-      <c r="W22" s="185"/>
-      <c r="X22" s="185"/>
-      <c r="Y22" s="185"/>
-      <c r="Z22" s="185"/>
-      <c r="AA22" s="185"/>
-      <c r="AB22" s="185"/>
-      <c r="AC22" s="185"/>
-      <c r="AD22" s="185"/>
-      <c r="AE22" s="186"/>
-      <c r="AF22" s="181"/>
-      <c r="AG22" s="182"/>
-      <c r="AH22" s="182"/>
-      <c r="AI22" s="183"/>
+      <c r="B22" s="232"/>
+      <c r="C22" s="233"/>
+      <c r="D22" s="234"/>
+      <c r="E22" s="235"/>
+      <c r="F22" s="236"/>
+      <c r="G22" s="232"/>
+      <c r="H22" s="237"/>
+      <c r="I22" s="233"/>
+      <c r="J22" s="238"/>
+      <c r="K22" s="239"/>
+      <c r="L22" s="239"/>
+      <c r="M22" s="239"/>
+      <c r="N22" s="239"/>
+      <c r="O22" s="239"/>
+      <c r="P22" s="240"/>
+      <c r="Q22" s="241"/>
+      <c r="R22" s="242"/>
+      <c r="S22" s="242"/>
+      <c r="T22" s="242"/>
+      <c r="U22" s="242"/>
+      <c r="V22" s="242"/>
+      <c r="W22" s="242"/>
+      <c r="X22" s="242"/>
+      <c r="Y22" s="242"/>
+      <c r="Z22" s="242"/>
+      <c r="AA22" s="242"/>
+      <c r="AB22" s="242"/>
+      <c r="AC22" s="242"/>
+      <c r="AD22" s="242"/>
+      <c r="AE22" s="243"/>
+      <c r="AF22" s="238"/>
+      <c r="AG22" s="239"/>
+      <c r="AH22" s="239"/>
+      <c r="AI22" s="240"/>
     </row>
     <row r="23" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="21"/>
-      <c r="B23" s="175"/>
-      <c r="C23" s="176"/>
-      <c r="D23" s="177"/>
-      <c r="E23" s="178"/>
-      <c r="F23" s="179"/>
-      <c r="G23" s="175"/>
-      <c r="H23" s="180"/>
-      <c r="I23" s="176"/>
-      <c r="J23" s="181"/>
-      <c r="K23" s="182"/>
-      <c r="L23" s="182"/>
-      <c r="M23" s="182"/>
-      <c r="N23" s="182"/>
-      <c r="O23" s="182"/>
-      <c r="P23" s="183"/>
-      <c r="Q23" s="184"/>
-      <c r="R23" s="185"/>
-      <c r="S23" s="185"/>
-      <c r="T23" s="185"/>
-      <c r="U23" s="185"/>
-      <c r="V23" s="185"/>
-      <c r="W23" s="185"/>
-      <c r="X23" s="185"/>
-      <c r="Y23" s="185"/>
-      <c r="Z23" s="185"/>
-      <c r="AA23" s="185"/>
-      <c r="AB23" s="185"/>
-      <c r="AC23" s="185"/>
-      <c r="AD23" s="185"/>
-      <c r="AE23" s="186"/>
-      <c r="AF23" s="181"/>
-      <c r="AG23" s="182"/>
-      <c r="AH23" s="182"/>
-      <c r="AI23" s="183"/>
+      <c r="B23" s="232"/>
+      <c r="C23" s="233"/>
+      <c r="D23" s="234"/>
+      <c r="E23" s="235"/>
+      <c r="F23" s="236"/>
+      <c r="G23" s="232"/>
+      <c r="H23" s="237"/>
+      <c r="I23" s="233"/>
+      <c r="J23" s="238"/>
+      <c r="K23" s="239"/>
+      <c r="L23" s="239"/>
+      <c r="M23" s="239"/>
+      <c r="N23" s="239"/>
+      <c r="O23" s="239"/>
+      <c r="P23" s="240"/>
+      <c r="Q23" s="241"/>
+      <c r="R23" s="242"/>
+      <c r="S23" s="242"/>
+      <c r="T23" s="242"/>
+      <c r="U23" s="242"/>
+      <c r="V23" s="242"/>
+      <c r="W23" s="242"/>
+      <c r="X23" s="242"/>
+      <c r="Y23" s="242"/>
+      <c r="Z23" s="242"/>
+      <c r="AA23" s="242"/>
+      <c r="AB23" s="242"/>
+      <c r="AC23" s="242"/>
+      <c r="AD23" s="242"/>
+      <c r="AE23" s="243"/>
+      <c r="AF23" s="238"/>
+      <c r="AG23" s="239"/>
+      <c r="AH23" s="239"/>
+      <c r="AI23" s="240"/>
     </row>
     <row r="24" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="21"/>
-      <c r="B24" s="175"/>
-      <c r="C24" s="176"/>
-      <c r="D24" s="177"/>
-      <c r="E24" s="178"/>
-      <c r="F24" s="179"/>
-      <c r="G24" s="175"/>
-      <c r="H24" s="180"/>
-      <c r="I24" s="176"/>
-      <c r="J24" s="181"/>
-      <c r="K24" s="182"/>
-      <c r="L24" s="182"/>
-      <c r="M24" s="182"/>
-      <c r="N24" s="182"/>
-      <c r="O24" s="182"/>
-      <c r="P24" s="183"/>
-      <c r="Q24" s="184"/>
-      <c r="R24" s="185"/>
-      <c r="S24" s="185"/>
-      <c r="T24" s="185"/>
-      <c r="U24" s="185"/>
-      <c r="V24" s="185"/>
-      <c r="W24" s="185"/>
-      <c r="X24" s="185"/>
-      <c r="Y24" s="185"/>
-      <c r="Z24" s="185"/>
-      <c r="AA24" s="185"/>
-      <c r="AB24" s="185"/>
-      <c r="AC24" s="185"/>
-      <c r="AD24" s="185"/>
-      <c r="AE24" s="186"/>
-      <c r="AF24" s="181"/>
-      <c r="AG24" s="182"/>
-      <c r="AH24" s="182"/>
-      <c r="AI24" s="183"/>
+      <c r="B24" s="232"/>
+      <c r="C24" s="233"/>
+      <c r="D24" s="234"/>
+      <c r="E24" s="235"/>
+      <c r="F24" s="236"/>
+      <c r="G24" s="232"/>
+      <c r="H24" s="237"/>
+      <c r="I24" s="233"/>
+      <c r="J24" s="238"/>
+      <c r="K24" s="239"/>
+      <c r="L24" s="239"/>
+      <c r="M24" s="239"/>
+      <c r="N24" s="239"/>
+      <c r="O24" s="239"/>
+      <c r="P24" s="240"/>
+      <c r="Q24" s="241"/>
+      <c r="R24" s="242"/>
+      <c r="S24" s="242"/>
+      <c r="T24" s="242"/>
+      <c r="U24" s="242"/>
+      <c r="V24" s="242"/>
+      <c r="W24" s="242"/>
+      <c r="X24" s="242"/>
+      <c r="Y24" s="242"/>
+      <c r="Z24" s="242"/>
+      <c r="AA24" s="242"/>
+      <c r="AB24" s="242"/>
+      <c r="AC24" s="242"/>
+      <c r="AD24" s="242"/>
+      <c r="AE24" s="243"/>
+      <c r="AF24" s="238"/>
+      <c r="AG24" s="239"/>
+      <c r="AH24" s="239"/>
+      <c r="AI24" s="240"/>
     </row>
     <row r="25" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="21"/>
-      <c r="B25" s="175"/>
-      <c r="C25" s="176"/>
-      <c r="D25" s="177"/>
-      <c r="E25" s="178"/>
-      <c r="F25" s="179"/>
-      <c r="G25" s="175"/>
-      <c r="H25" s="180"/>
-      <c r="I25" s="176"/>
-      <c r="J25" s="181"/>
-      <c r="K25" s="182"/>
-      <c r="L25" s="182"/>
-      <c r="M25" s="182"/>
-      <c r="N25" s="182"/>
-      <c r="O25" s="182"/>
-      <c r="P25" s="183"/>
-      <c r="Q25" s="184"/>
-      <c r="R25" s="185"/>
-      <c r="S25" s="185"/>
-      <c r="T25" s="185"/>
-      <c r="U25" s="185"/>
-      <c r="V25" s="185"/>
-      <c r="W25" s="185"/>
-      <c r="X25" s="185"/>
-      <c r="Y25" s="185"/>
-      <c r="Z25" s="185"/>
-      <c r="AA25" s="185"/>
-      <c r="AB25" s="185"/>
-      <c r="AC25" s="185"/>
-      <c r="AD25" s="185"/>
-      <c r="AE25" s="186"/>
-      <c r="AF25" s="181"/>
-      <c r="AG25" s="182"/>
-      <c r="AH25" s="182"/>
-      <c r="AI25" s="183"/>
+      <c r="B25" s="232"/>
+      <c r="C25" s="233"/>
+      <c r="D25" s="234"/>
+      <c r="E25" s="235"/>
+      <c r="F25" s="236"/>
+      <c r="G25" s="232"/>
+      <c r="H25" s="237"/>
+      <c r="I25" s="233"/>
+      <c r="J25" s="238"/>
+      <c r="K25" s="239"/>
+      <c r="L25" s="239"/>
+      <c r="M25" s="239"/>
+      <c r="N25" s="239"/>
+      <c r="O25" s="239"/>
+      <c r="P25" s="240"/>
+      <c r="Q25" s="241"/>
+      <c r="R25" s="242"/>
+      <c r="S25" s="242"/>
+      <c r="T25" s="242"/>
+      <c r="U25" s="242"/>
+      <c r="V25" s="242"/>
+      <c r="W25" s="242"/>
+      <c r="X25" s="242"/>
+      <c r="Y25" s="242"/>
+      <c r="Z25" s="242"/>
+      <c r="AA25" s="242"/>
+      <c r="AB25" s="242"/>
+      <c r="AC25" s="242"/>
+      <c r="AD25" s="242"/>
+      <c r="AE25" s="243"/>
+      <c r="AF25" s="238"/>
+      <c r="AG25" s="239"/>
+      <c r="AH25" s="239"/>
+      <c r="AI25" s="240"/>
     </row>
     <row r="26" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="21"/>
-      <c r="B26" s="175"/>
-      <c r="C26" s="176"/>
-      <c r="D26" s="177"/>
-      <c r="E26" s="178"/>
-      <c r="F26" s="179"/>
-      <c r="G26" s="175"/>
-      <c r="H26" s="180"/>
-      <c r="I26" s="176"/>
-      <c r="J26" s="181"/>
-      <c r="K26" s="182"/>
-      <c r="L26" s="182"/>
-      <c r="M26" s="182"/>
-      <c r="N26" s="182"/>
-      <c r="O26" s="182"/>
-      <c r="P26" s="183"/>
-      <c r="Q26" s="184"/>
-      <c r="R26" s="185"/>
-      <c r="S26" s="185"/>
-      <c r="T26" s="185"/>
-      <c r="U26" s="185"/>
-      <c r="V26" s="185"/>
-      <c r="W26" s="185"/>
-      <c r="X26" s="185"/>
-      <c r="Y26" s="185"/>
-      <c r="Z26" s="185"/>
-      <c r="AA26" s="185"/>
-      <c r="AB26" s="185"/>
-      <c r="AC26" s="185"/>
-      <c r="AD26" s="185"/>
-      <c r="AE26" s="186"/>
-      <c r="AF26" s="181"/>
-      <c r="AG26" s="182"/>
-      <c r="AH26" s="182"/>
-      <c r="AI26" s="183"/>
+      <c r="B26" s="232"/>
+      <c r="C26" s="233"/>
+      <c r="D26" s="234"/>
+      <c r="E26" s="235"/>
+      <c r="F26" s="236"/>
+      <c r="G26" s="232"/>
+      <c r="H26" s="237"/>
+      <c r="I26" s="233"/>
+      <c r="J26" s="238"/>
+      <c r="K26" s="239"/>
+      <c r="L26" s="239"/>
+      <c r="M26" s="239"/>
+      <c r="N26" s="239"/>
+      <c r="O26" s="239"/>
+      <c r="P26" s="240"/>
+      <c r="Q26" s="241"/>
+      <c r="R26" s="242"/>
+      <c r="S26" s="242"/>
+      <c r="T26" s="242"/>
+      <c r="U26" s="242"/>
+      <c r="V26" s="242"/>
+      <c r="W26" s="242"/>
+      <c r="X26" s="242"/>
+      <c r="Y26" s="242"/>
+      <c r="Z26" s="242"/>
+      <c r="AA26" s="242"/>
+      <c r="AB26" s="242"/>
+      <c r="AC26" s="242"/>
+      <c r="AD26" s="242"/>
+      <c r="AE26" s="243"/>
+      <c r="AF26" s="238"/>
+      <c r="AG26" s="239"/>
+      <c r="AH26" s="239"/>
+      <c r="AI26" s="240"/>
     </row>
     <row r="27" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="21"/>
-      <c r="B27" s="175"/>
-      <c r="C27" s="176"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="178"/>
-      <c r="F27" s="179"/>
-      <c r="G27" s="175"/>
-      <c r="H27" s="180"/>
-      <c r="I27" s="176"/>
-      <c r="J27" s="181"/>
-      <c r="K27" s="182"/>
-      <c r="L27" s="182"/>
-      <c r="M27" s="182"/>
-      <c r="N27" s="182"/>
-      <c r="O27" s="182"/>
-      <c r="P27" s="183"/>
-      <c r="Q27" s="184"/>
-      <c r="R27" s="185"/>
-      <c r="S27" s="185"/>
-      <c r="T27" s="185"/>
-      <c r="U27" s="185"/>
-      <c r="V27" s="185"/>
-      <c r="W27" s="185"/>
-      <c r="X27" s="185"/>
-      <c r="Y27" s="185"/>
-      <c r="Z27" s="185"/>
-      <c r="AA27" s="185"/>
-      <c r="AB27" s="185"/>
-      <c r="AC27" s="185"/>
-      <c r="AD27" s="185"/>
-      <c r="AE27" s="186"/>
-      <c r="AF27" s="181"/>
-      <c r="AG27" s="182"/>
-      <c r="AH27" s="182"/>
-      <c r="AI27" s="183"/>
+      <c r="B27" s="232"/>
+      <c r="C27" s="233"/>
+      <c r="D27" s="234"/>
+      <c r="E27" s="235"/>
+      <c r="F27" s="236"/>
+      <c r="G27" s="232"/>
+      <c r="H27" s="237"/>
+      <c r="I27" s="233"/>
+      <c r="J27" s="238"/>
+      <c r="K27" s="239"/>
+      <c r="L27" s="239"/>
+      <c r="M27" s="239"/>
+      <c r="N27" s="239"/>
+      <c r="O27" s="239"/>
+      <c r="P27" s="240"/>
+      <c r="Q27" s="241"/>
+      <c r="R27" s="242"/>
+      <c r="S27" s="242"/>
+      <c r="T27" s="242"/>
+      <c r="U27" s="242"/>
+      <c r="V27" s="242"/>
+      <c r="W27" s="242"/>
+      <c r="X27" s="242"/>
+      <c r="Y27" s="242"/>
+      <c r="Z27" s="242"/>
+      <c r="AA27" s="242"/>
+      <c r="AB27" s="242"/>
+      <c r="AC27" s="242"/>
+      <c r="AD27" s="242"/>
+      <c r="AE27" s="243"/>
+      <c r="AF27" s="238"/>
+      <c r="AG27" s="239"/>
+      <c r="AH27" s="239"/>
+      <c r="AI27" s="240"/>
     </row>
     <row r="28" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="21"/>
-      <c r="B28" s="175"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="177"/>
-      <c r="E28" s="178"/>
-      <c r="F28" s="179"/>
-      <c r="G28" s="175"/>
-      <c r="H28" s="180"/>
-      <c r="I28" s="176"/>
-      <c r="J28" s="181"/>
-      <c r="K28" s="182"/>
-      <c r="L28" s="182"/>
-      <c r="M28" s="182"/>
-      <c r="N28" s="182"/>
-      <c r="O28" s="182"/>
-      <c r="P28" s="183"/>
-      <c r="Q28" s="184"/>
-      <c r="R28" s="185"/>
-      <c r="S28" s="185"/>
-      <c r="T28" s="185"/>
-      <c r="U28" s="185"/>
-      <c r="V28" s="185"/>
-      <c r="W28" s="185"/>
-      <c r="X28" s="185"/>
-      <c r="Y28" s="185"/>
-      <c r="Z28" s="185"/>
-      <c r="AA28" s="185"/>
-      <c r="AB28" s="185"/>
-      <c r="AC28" s="185"/>
-      <c r="AD28" s="185"/>
-      <c r="AE28" s="186"/>
-      <c r="AF28" s="181"/>
-      <c r="AG28" s="182"/>
-      <c r="AH28" s="182"/>
-      <c r="AI28" s="183"/>
+      <c r="B28" s="232"/>
+      <c r="C28" s="233"/>
+      <c r="D28" s="234"/>
+      <c r="E28" s="235"/>
+      <c r="F28" s="236"/>
+      <c r="G28" s="232"/>
+      <c r="H28" s="237"/>
+      <c r="I28" s="233"/>
+      <c r="J28" s="238"/>
+      <c r="K28" s="239"/>
+      <c r="L28" s="239"/>
+      <c r="M28" s="239"/>
+      <c r="N28" s="239"/>
+      <c r="O28" s="239"/>
+      <c r="P28" s="240"/>
+      <c r="Q28" s="241"/>
+      <c r="R28" s="242"/>
+      <c r="S28" s="242"/>
+      <c r="T28" s="242"/>
+      <c r="U28" s="242"/>
+      <c r="V28" s="242"/>
+      <c r="W28" s="242"/>
+      <c r="X28" s="242"/>
+      <c r="Y28" s="242"/>
+      <c r="Z28" s="242"/>
+      <c r="AA28" s="242"/>
+      <c r="AB28" s="242"/>
+      <c r="AC28" s="242"/>
+      <c r="AD28" s="242"/>
+      <c r="AE28" s="243"/>
+      <c r="AF28" s="238"/>
+      <c r="AG28" s="239"/>
+      <c r="AH28" s="239"/>
+      <c r="AI28" s="240"/>
     </row>
     <row r="29" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="21"/>
-      <c r="B29" s="175"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="177"/>
-      <c r="E29" s="178"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="175"/>
-      <c r="H29" s="180"/>
-      <c r="I29" s="176"/>
-      <c r="J29" s="181"/>
-      <c r="K29" s="182"/>
-      <c r="L29" s="182"/>
-      <c r="M29" s="182"/>
-      <c r="N29" s="182"/>
-      <c r="O29" s="182"/>
-      <c r="P29" s="183"/>
-      <c r="Q29" s="184"/>
-      <c r="R29" s="185"/>
-      <c r="S29" s="185"/>
-      <c r="T29" s="185"/>
-      <c r="U29" s="185"/>
-      <c r="V29" s="185"/>
-      <c r="W29" s="185"/>
-      <c r="X29" s="185"/>
-      <c r="Y29" s="185"/>
-      <c r="Z29" s="185"/>
-      <c r="AA29" s="185"/>
-      <c r="AB29" s="185"/>
-      <c r="AC29" s="185"/>
-      <c r="AD29" s="185"/>
-      <c r="AE29" s="186"/>
-      <c r="AF29" s="181"/>
-      <c r="AG29" s="182"/>
-      <c r="AH29" s="182"/>
-      <c r="AI29" s="183"/>
+      <c r="B29" s="232"/>
+      <c r="C29" s="233"/>
+      <c r="D29" s="234"/>
+      <c r="E29" s="235"/>
+      <c r="F29" s="236"/>
+      <c r="G29" s="232"/>
+      <c r="H29" s="237"/>
+      <c r="I29" s="233"/>
+      <c r="J29" s="238"/>
+      <c r="K29" s="239"/>
+      <c r="L29" s="239"/>
+      <c r="M29" s="239"/>
+      <c r="N29" s="239"/>
+      <c r="O29" s="239"/>
+      <c r="P29" s="240"/>
+      <c r="Q29" s="241"/>
+      <c r="R29" s="242"/>
+      <c r="S29" s="242"/>
+      <c r="T29" s="242"/>
+      <c r="U29" s="242"/>
+      <c r="V29" s="242"/>
+      <c r="W29" s="242"/>
+      <c r="X29" s="242"/>
+      <c r="Y29" s="242"/>
+      <c r="Z29" s="242"/>
+      <c r="AA29" s="242"/>
+      <c r="AB29" s="242"/>
+      <c r="AC29" s="242"/>
+      <c r="AD29" s="242"/>
+      <c r="AE29" s="243"/>
+      <c r="AF29" s="238"/>
+      <c r="AG29" s="239"/>
+      <c r="AH29" s="239"/>
+      <c r="AI29" s="240"/>
     </row>
     <row r="30" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="21"/>
-      <c r="B30" s="175"/>
-      <c r="C30" s="176"/>
-      <c r="D30" s="177"/>
-      <c r="E30" s="178"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="175"/>
-      <c r="H30" s="180"/>
-      <c r="I30" s="176"/>
-      <c r="J30" s="181"/>
-      <c r="K30" s="182"/>
-      <c r="L30" s="182"/>
-      <c r="M30" s="182"/>
-      <c r="N30" s="182"/>
-      <c r="O30" s="182"/>
-      <c r="P30" s="183"/>
-      <c r="Q30" s="184"/>
-      <c r="R30" s="185"/>
-      <c r="S30" s="185"/>
-      <c r="T30" s="185"/>
-      <c r="U30" s="185"/>
-      <c r="V30" s="185"/>
-      <c r="W30" s="185"/>
-      <c r="X30" s="185"/>
-      <c r="Y30" s="185"/>
-      <c r="Z30" s="185"/>
-      <c r="AA30" s="185"/>
-      <c r="AB30" s="185"/>
-      <c r="AC30" s="185"/>
-      <c r="AD30" s="185"/>
-      <c r="AE30" s="186"/>
-      <c r="AF30" s="181"/>
-      <c r="AG30" s="182"/>
-      <c r="AH30" s="182"/>
-      <c r="AI30" s="183"/>
+      <c r="B30" s="232"/>
+      <c r="C30" s="233"/>
+      <c r="D30" s="234"/>
+      <c r="E30" s="235"/>
+      <c r="F30" s="236"/>
+      <c r="G30" s="232"/>
+      <c r="H30" s="237"/>
+      <c r="I30" s="233"/>
+      <c r="J30" s="238"/>
+      <c r="K30" s="239"/>
+      <c r="L30" s="239"/>
+      <c r="M30" s="239"/>
+      <c r="N30" s="239"/>
+      <c r="O30" s="239"/>
+      <c r="P30" s="240"/>
+      <c r="Q30" s="241"/>
+      <c r="R30" s="242"/>
+      <c r="S30" s="242"/>
+      <c r="T30" s="242"/>
+      <c r="U30" s="242"/>
+      <c r="V30" s="242"/>
+      <c r="W30" s="242"/>
+      <c r="X30" s="242"/>
+      <c r="Y30" s="242"/>
+      <c r="Z30" s="242"/>
+      <c r="AA30" s="242"/>
+      <c r="AB30" s="242"/>
+      <c r="AC30" s="242"/>
+      <c r="AD30" s="242"/>
+      <c r="AE30" s="243"/>
+      <c r="AF30" s="238"/>
+      <c r="AG30" s="239"/>
+      <c r="AH30" s="239"/>
+      <c r="AI30" s="240"/>
     </row>
     <row r="31" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="21"/>
-      <c r="B31" s="175"/>
-      <c r="C31" s="176"/>
-      <c r="D31" s="177"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="175"/>
-      <c r="H31" s="180"/>
-      <c r="I31" s="176"/>
-      <c r="J31" s="181"/>
-      <c r="K31" s="182"/>
-      <c r="L31" s="182"/>
-      <c r="M31" s="182"/>
-      <c r="N31" s="182"/>
-      <c r="O31" s="182"/>
-      <c r="P31" s="183"/>
-      <c r="Q31" s="184"/>
-      <c r="R31" s="185"/>
-      <c r="S31" s="185"/>
-      <c r="T31" s="185"/>
-      <c r="U31" s="185"/>
-      <c r="V31" s="185"/>
-      <c r="W31" s="185"/>
-      <c r="X31" s="185"/>
-      <c r="Y31" s="185"/>
-      <c r="Z31" s="185"/>
-      <c r="AA31" s="185"/>
-      <c r="AB31" s="185"/>
-      <c r="AC31" s="185"/>
-      <c r="AD31" s="185"/>
-      <c r="AE31" s="186"/>
-      <c r="AF31" s="181"/>
-      <c r="AG31" s="182"/>
-      <c r="AH31" s="182"/>
-      <c r="AI31" s="183"/>
+      <c r="B31" s="232"/>
+      <c r="C31" s="233"/>
+      <c r="D31" s="234"/>
+      <c r="E31" s="235"/>
+      <c r="F31" s="236"/>
+      <c r="G31" s="232"/>
+      <c r="H31" s="237"/>
+      <c r="I31" s="233"/>
+      <c r="J31" s="238"/>
+      <c r="K31" s="239"/>
+      <c r="L31" s="239"/>
+      <c r="M31" s="239"/>
+      <c r="N31" s="239"/>
+      <c r="O31" s="239"/>
+      <c r="P31" s="240"/>
+      <c r="Q31" s="241"/>
+      <c r="R31" s="242"/>
+      <c r="S31" s="242"/>
+      <c r="T31" s="242"/>
+      <c r="U31" s="242"/>
+      <c r="V31" s="242"/>
+      <c r="W31" s="242"/>
+      <c r="X31" s="242"/>
+      <c r="Y31" s="242"/>
+      <c r="Z31" s="242"/>
+      <c r="AA31" s="242"/>
+      <c r="AB31" s="242"/>
+      <c r="AC31" s="242"/>
+      <c r="AD31" s="242"/>
+      <c r="AE31" s="243"/>
+      <c r="AF31" s="238"/>
+      <c r="AG31" s="239"/>
+      <c r="AH31" s="239"/>
+      <c r="AI31" s="240"/>
     </row>
     <row r="32" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="21"/>
-      <c r="B32" s="175"/>
-      <c r="C32" s="176"/>
-      <c r="D32" s="177"/>
-      <c r="E32" s="178"/>
-      <c r="F32" s="179"/>
-      <c r="G32" s="175"/>
-      <c r="H32" s="180"/>
-      <c r="I32" s="176"/>
-      <c r="J32" s="181"/>
-      <c r="K32" s="187"/>
-      <c r="L32" s="182"/>
-      <c r="M32" s="182"/>
-      <c r="N32" s="182"/>
-      <c r="O32" s="182"/>
-      <c r="P32" s="183"/>
-      <c r="Q32" s="184"/>
-      <c r="R32" s="185"/>
-      <c r="S32" s="185"/>
-      <c r="T32" s="185"/>
-      <c r="U32" s="185"/>
-      <c r="V32" s="185"/>
-      <c r="W32" s="185"/>
-      <c r="X32" s="185"/>
-      <c r="Y32" s="185"/>
-      <c r="Z32" s="185"/>
-      <c r="AA32" s="185"/>
-      <c r="AB32" s="185"/>
-      <c r="AC32" s="185"/>
-      <c r="AD32" s="185"/>
-      <c r="AE32" s="186"/>
-      <c r="AF32" s="181"/>
-      <c r="AG32" s="182"/>
-      <c r="AH32" s="182"/>
-      <c r="AI32" s="183"/>
+      <c r="B32" s="232"/>
+      <c r="C32" s="233"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="235"/>
+      <c r="F32" s="236"/>
+      <c r="G32" s="232"/>
+      <c r="H32" s="237"/>
+      <c r="I32" s="233"/>
+      <c r="J32" s="238"/>
+      <c r="K32" s="244"/>
+      <c r="L32" s="239"/>
+      <c r="M32" s="239"/>
+      <c r="N32" s="239"/>
+      <c r="O32" s="239"/>
+      <c r="P32" s="240"/>
+      <c r="Q32" s="241"/>
+      <c r="R32" s="242"/>
+      <c r="S32" s="242"/>
+      <c r="T32" s="242"/>
+      <c r="U32" s="242"/>
+      <c r="V32" s="242"/>
+      <c r="W32" s="242"/>
+      <c r="X32" s="242"/>
+      <c r="Y32" s="242"/>
+      <c r="Z32" s="242"/>
+      <c r="AA32" s="242"/>
+      <c r="AB32" s="242"/>
+      <c r="AC32" s="242"/>
+      <c r="AD32" s="242"/>
+      <c r="AE32" s="243"/>
+      <c r="AF32" s="238"/>
+      <c r="AG32" s="239"/>
+      <c r="AH32" s="239"/>
+      <c r="AI32" s="240"/>
     </row>
     <row r="33" spans="1:35" s="20" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="21"/>
-      <c r="B33" s="175"/>
-      <c r="C33" s="176"/>
-      <c r="D33" s="177"/>
-      <c r="E33" s="178"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="175"/>
-      <c r="H33" s="180"/>
-      <c r="I33" s="176"/>
-      <c r="J33" s="181"/>
-      <c r="K33" s="182"/>
-      <c r="L33" s="182"/>
-      <c r="M33" s="182"/>
-      <c r="N33" s="182"/>
-      <c r="O33" s="182"/>
-      <c r="P33" s="183"/>
-      <c r="Q33" s="184"/>
-      <c r="R33" s="185"/>
-      <c r="S33" s="185"/>
-      <c r="T33" s="185"/>
-      <c r="U33" s="185"/>
-      <c r="V33" s="185"/>
-      <c r="W33" s="185"/>
-      <c r="X33" s="185"/>
-      <c r="Y33" s="185"/>
-      <c r="Z33" s="185"/>
-      <c r="AA33" s="185"/>
-      <c r="AB33" s="185"/>
-      <c r="AC33" s="185"/>
-      <c r="AD33" s="185"/>
-      <c r="AE33" s="186"/>
-      <c r="AF33" s="181"/>
-      <c r="AG33" s="182"/>
-      <c r="AH33" s="182"/>
-      <c r="AI33" s="183"/>
+      <c r="B33" s="232"/>
+      <c r="C33" s="233"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="235"/>
+      <c r="F33" s="236"/>
+      <c r="G33" s="232"/>
+      <c r="H33" s="237"/>
+      <c r="I33" s="233"/>
+      <c r="J33" s="238"/>
+      <c r="K33" s="239"/>
+      <c r="L33" s="239"/>
+      <c r="M33" s="239"/>
+      <c r="N33" s="239"/>
+      <c r="O33" s="239"/>
+      <c r="P33" s="240"/>
+      <c r="Q33" s="241"/>
+      <c r="R33" s="242"/>
+      <c r="S33" s="242"/>
+      <c r="T33" s="242"/>
+      <c r="U33" s="242"/>
+      <c r="V33" s="242"/>
+      <c r="W33" s="242"/>
+      <c r="X33" s="242"/>
+      <c r="Y33" s="242"/>
+      <c r="Z33" s="242"/>
+      <c r="AA33" s="242"/>
+      <c r="AB33" s="242"/>
+      <c r="AC33" s="242"/>
+      <c r="AD33" s="242"/>
+      <c r="AE33" s="243"/>
+      <c r="AF33" s="238"/>
+      <c r="AG33" s="239"/>
+      <c r="AH33" s="239"/>
+      <c r="AI33" s="240"/>
     </row>
     <row r="34" spans="1:35" ht="14">
       <c r="K34" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="178">
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="J33:P33"/>
+    <mergeCell ref="Q33:AE33"/>
+    <mergeCell ref="AF33:AI33"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:AE32"/>
+    <mergeCell ref="AF32:AI32"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:P31"/>
+    <mergeCell ref="Q31:AE31"/>
+    <mergeCell ref="AF31:AI31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:P30"/>
+    <mergeCell ref="Q30:AE30"/>
+    <mergeCell ref="AF30:AI30"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:P29"/>
+    <mergeCell ref="Q29:AE29"/>
+    <mergeCell ref="AF29:AI29"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="Q28:AE28"/>
+    <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:P27"/>
+    <mergeCell ref="Q27:AE27"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="J26:P26"/>
+    <mergeCell ref="Q26:AE26"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:AE25"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:P24"/>
+    <mergeCell ref="Q24:AE24"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:P23"/>
+    <mergeCell ref="Q23:AE23"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="Q22:AE22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:P21"/>
+    <mergeCell ref="Q21:AE21"/>
+    <mergeCell ref="AF21:AI21"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="Q20:AE20"/>
+    <mergeCell ref="AF20:AI20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:P19"/>
+    <mergeCell ref="Q19:AE19"/>
+    <mergeCell ref="AF19:AI19"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="J18:P18"/>
+    <mergeCell ref="Q18:AE18"/>
+    <mergeCell ref="AF18:AI18"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:AE17"/>
+    <mergeCell ref="AF17:AI17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:P16"/>
+    <mergeCell ref="Q16:AE16"/>
+    <mergeCell ref="AF16:AI16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q15:AE15"/>
+    <mergeCell ref="AF15:AI15"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="Q14:AE14"/>
+    <mergeCell ref="AF14:AI14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AE13"/>
+    <mergeCell ref="AF13:AI13"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="Q12:AE12"/>
+    <mergeCell ref="AF12:AI12"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="Q11:AE11"/>
+    <mergeCell ref="AF11:AI11"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="Q10:AE10"/>
+    <mergeCell ref="AF10:AI10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AE9"/>
+    <mergeCell ref="AF9:AI9"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:P8"/>
+    <mergeCell ref="Q8:AE8"/>
     <mergeCell ref="AG3:AI3"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="D7:F7"/>
@@ -14266,161 +14421,6 @@
     <mergeCell ref="E3:N3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AF3"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="Q9:AE9"/>
-    <mergeCell ref="AF9:AI9"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="Q8:AE8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="Q11:AE11"/>
-    <mergeCell ref="AF11:AI11"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="Q10:AE10"/>
-    <mergeCell ref="AF10:AI10"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AE13"/>
-    <mergeCell ref="AF13:AI13"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="Q12:AE12"/>
-    <mergeCell ref="AF12:AI12"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q15:AE15"/>
-    <mergeCell ref="AF15:AI15"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="Q14:AE14"/>
-    <mergeCell ref="AF14:AI14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:AE17"/>
-    <mergeCell ref="AF17:AI17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:P16"/>
-    <mergeCell ref="Q16:AE16"/>
-    <mergeCell ref="AF16:AI16"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:P19"/>
-    <mergeCell ref="Q19:AE19"/>
-    <mergeCell ref="AF19:AI19"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="J18:P18"/>
-    <mergeCell ref="Q18:AE18"/>
-    <mergeCell ref="AF18:AI18"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:P21"/>
-    <mergeCell ref="Q21:AE21"/>
-    <mergeCell ref="AF21:AI21"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="Q20:AE20"/>
-    <mergeCell ref="AF20:AI20"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:P23"/>
-    <mergeCell ref="Q23:AE23"/>
-    <mergeCell ref="AF23:AI23"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:P22"/>
-    <mergeCell ref="Q22:AE22"/>
-    <mergeCell ref="AF22:AI22"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:AE25"/>
-    <mergeCell ref="AF25:AI25"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:P24"/>
-    <mergeCell ref="Q24:AE24"/>
-    <mergeCell ref="AF24:AI24"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:P27"/>
-    <mergeCell ref="Q27:AE27"/>
-    <mergeCell ref="AF27:AI27"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="J26:P26"/>
-    <mergeCell ref="Q26:AE26"/>
-    <mergeCell ref="AF26:AI26"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:P29"/>
-    <mergeCell ref="Q29:AE29"/>
-    <mergeCell ref="AF29:AI29"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="Q28:AE28"/>
-    <mergeCell ref="AF28:AI28"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:P31"/>
-    <mergeCell ref="Q31:AE31"/>
-    <mergeCell ref="AF31:AI31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:P30"/>
-    <mergeCell ref="Q30:AE30"/>
-    <mergeCell ref="AF30:AI30"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="J33:P33"/>
-    <mergeCell ref="Q33:AE33"/>
-    <mergeCell ref="AF33:AI33"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:AE32"/>
-    <mergeCell ref="AF32:AI32"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1"/>

--- a/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
+++ b/030_設計ドキュメント/020_サンプル/110_テスト仕様書/単体テスト仕様書(メッセージ)_サンプル.xlsx
@@ -14579,8 +14579,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -14622,8 +14622,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -14659,8 +14659,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -14698,8 +14698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -14733,8 +14733,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -14768,8 +14768,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -14803,8 +14803,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -14838,8 +14838,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -14877,8 +14877,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -14912,8 +14912,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -14947,8 +14947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -14984,8 +14984,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -15019,8 +15019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -15054,8 +15054,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -15089,8 +15089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -15128,8 +15128,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -15163,8 +15163,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -15202,8 +15202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -15237,8 +15237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -15274,8 +15274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -15309,8 +15309,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -15344,8 +15344,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -15379,8 +15379,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -15416,8 +15416,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -15451,8 +15451,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -15488,8 +15488,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -15529,8 +15529,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -15564,8 +15564,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -15599,8 +15599,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -15634,8 +15634,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -15673,8 +15673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -15708,8 +15708,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -15761,8 +15761,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -15806,8 +15806,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -15841,8 +15841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -15878,8 +15878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -15913,8 +15913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -15948,8 +15948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -15985,8 +15985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -16020,8 +16020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -16057,8 +16057,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -16092,8 +16092,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -16127,8 +16127,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -16162,8 +16162,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -16197,8 +16197,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -16232,8 +16232,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -16269,8 +16269,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -16306,8 +16306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -16343,8 +16343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -16382,8 +16382,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -16417,8 +16417,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -16452,8 +16452,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -16487,8 +16487,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -16522,8 +16522,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -16559,8 +16559,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -16594,8 +16594,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -16627,8 +16627,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -16662,8 +16662,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -16697,8 +16697,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -16732,8 +16732,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -16767,8 +16767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -16802,8 +16802,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -16837,8 +16837,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -16874,8 +16874,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -16911,8 +16911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -16946,8 +16946,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -16981,8 +16981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -17016,8 +17016,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -17051,8 +17051,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -17104,8 +17104,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-2</v>
       </c>
@@ -17147,8 +17147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-3</v>
       </c>
@@ -17190,8 +17190,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -17237,8 +17237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -17274,8 +17274,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -17321,8 +17321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -17356,8 +17356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -17393,8 +17393,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -17430,8 +17430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -17471,8 +17471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -17508,8 +17508,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -17545,8 +17545,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -17586,8 +17586,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -17621,8 +17621,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -17658,8 +17658,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -17695,8 +17695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -17730,8 +17730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -17767,8 +17767,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -17808,8 +17808,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -17843,8 +17843,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -17878,8 +17878,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -17913,8 +17913,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -17948,8 +17948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -17985,8 +17985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -18020,8 +18020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -18055,8 +18055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -18090,8 +18090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -18125,8 +18125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -18162,8 +18162,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -18205,8 +18205,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -18246,8 +18246,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -18281,8 +18281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -18322,8 +18322,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -18363,8 +18363,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -18398,8 +18398,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -18441,8 +18441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -18478,8 +18478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -18513,8 +18513,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -18548,8 +18548,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -18585,8 +18585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -18620,8 +18620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -18655,8 +18655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -18690,8 +18690,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -18725,8 +18725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -18762,8 +18762,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -18797,8 +18797,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -18832,8 +18832,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -18867,8 +18867,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -18902,8 +18902,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -18939,8 +18939,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -18978,8 +18978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -19019,8 +19019,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -19056,8 +19056,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -19091,8 +19091,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -19126,8 +19126,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -19169,8 +19169,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -19206,8 +19206,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -19241,8 +19241,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -19276,8 +19276,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -19313,8 +19313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -19348,8 +19348,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -19387,8 +19387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -19428,8 +19428,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -19465,8 +19465,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -19502,8 +19502,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -19539,8 +19539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -19576,8 +19576,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -19613,8 +19613,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -19648,8 +19648,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -19683,8 +19683,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -19718,8 +19718,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -19753,8 +19753,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -19788,8 +19788,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -19827,8 +19827,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -19862,8 +19862,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -19899,8 +19899,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -19934,8 +19934,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -19969,8 +19969,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -20004,8 +20004,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -20039,8 +20039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -20074,8 +20074,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -20109,8 +20109,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -20144,8 +20144,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -20179,8 +20179,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -20214,8 +20214,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -20249,8 +20249,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -20286,8 +20286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -20321,8 +20321,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -20356,8 +20356,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -20391,8 +20391,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -20426,8 +20426,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -20461,8 +20461,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -20496,8 +20496,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -20533,8 +20533,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -20568,8 +20568,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -20603,8 +20603,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -20638,8 +20638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -20673,8 +20673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -20708,8 +20708,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -20743,8 +20743,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -20778,8 +20778,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -20813,8 +20813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -20850,8 +20850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -20887,8 +20887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -20930,8 +20930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -20969,8 +20969,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -21008,8 +21008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -21051,8 +21051,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -21088,8 +21088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -21123,8 +21123,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -21160,8 +21160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -21195,8 +21195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -21234,8 +21234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -21275,8 +21275,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -21310,8 +21310,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -21345,8 +21345,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -21380,8 +21380,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -21415,8 +21415,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -21450,8 +21450,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -21485,8 +21485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -21522,8 +21522,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -21561,8 +21561,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -21596,8 +21596,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -21631,8 +21631,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -21666,8 +21666,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -21701,8 +21701,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -21736,8 +21736,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -21771,8 +21771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -21806,8 +21806,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -21841,8 +21841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -21876,8 +21876,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -21911,8 +21911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -21946,8 +21946,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -21981,8 +21981,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -22020,8 +22020,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -22055,8 +22055,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -22090,8 +22090,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -22125,8 +22125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -22160,8 +22160,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -22195,8 +22195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -22230,8 +22230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -22265,8 +22265,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -22300,8 +22300,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -22335,8 +22335,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -22370,8 +22370,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -22405,8 +22405,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -22440,8 +22440,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -22475,8 +22475,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -22510,8 +22510,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -22547,8 +22547,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -22582,8 +22582,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -22617,8 +22617,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -22654,8 +22654,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -22691,8 +22691,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -22734,8 +22734,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -22771,8 +22771,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -22806,8 +22806,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -22841,8 +22841,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -22876,8 +22876,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -22911,8 +22911,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -22948,8 +22948,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -22983,8 +22983,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -23018,8 +23018,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -23053,8 +23053,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -23088,8 +23088,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -23125,8 +23125,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -23166,8 +23166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -23209,8 +23209,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -23244,8 +23244,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -23283,8 +23283,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -23318,8 +23318,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -23359,8 +23359,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -23396,8 +23396,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -23433,8 +23433,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -23470,8 +23470,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -23509,8 +23509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -23544,8 +23544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -23581,8 +23581,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -23616,8 +23616,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -23651,8 +23651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -23686,8 +23686,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -23721,8 +23721,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -23756,8 +23756,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -23791,8 +23791,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -23826,8 +23826,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -23861,8 +23861,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -23896,8 +23896,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -23931,8 +23931,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -23968,8 +23968,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -24003,8 +24003,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -24038,8 +24038,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -24073,8 +24073,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -24108,8 +24108,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -24143,8 +24143,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -24180,8 +24180,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -24215,8 +24215,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -24250,8 +24250,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -24285,8 +24285,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -24320,8 +24320,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -24355,8 +24355,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -24390,8 +24390,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -24425,8 +24425,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -24462,8 +24462,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -24505,8 +24505,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -24540,8 +24540,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -24575,8 +24575,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -24610,8 +24610,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -24651,8 +24651,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -24688,8 +24688,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -24725,8 +24725,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -24762,8 +24762,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -24801,8 +24801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -24836,8 +24836,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -24871,8 +24871,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -24906,8 +24906,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -24941,8 +24941,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -24976,8 +24976,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -25011,8 +25011,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -25046,8 +25046,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -25252,8 +25252,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F11),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F11)&gt;0)*ROW($F$11:F11),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -25295,8 +25295,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F12),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F12)&gt;0)*ROW($F$11:F12),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>2-1-1</v>
       </c>
@@ -25332,8 +25332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F13),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F13)&gt;0)*ROW($F$11:F13),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-1-1</v>
       </c>
@@ -25371,8 +25371,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F14),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F14)&gt;0)*ROW($F$11:F14),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J14),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-2-1</v>
       </c>
@@ -25406,8 +25406,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F15),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F15)&gt;0)*ROW($F$11:F15),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J15),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-3-1</v>
       </c>
@@ -25441,8 +25441,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F16),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F16)&gt;0)*ROW($F$11:F16),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J16),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-4-1</v>
       </c>
@@ -25476,8 +25476,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F17),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F17)&gt;0)*ROW($F$11:F17),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J17),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>3-5-1</v>
       </c>
@@ -25511,8 +25511,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F18),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F18)&gt;0)*ROW($F$11:F18),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J18),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-1-1</v>
       </c>
@@ -25550,8 +25550,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F19),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F19)&gt;0)*ROW($F$11:F19),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J19),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-2-1</v>
       </c>
@@ -25585,8 +25585,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F20),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F20)&gt;0)*ROW($F$11:F20),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J20),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>4-3-1</v>
       </c>
@@ -25620,8 +25620,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F21),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F21)&gt;0)*ROW($F$11:F21),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J21),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-1-1</v>
       </c>
@@ -25657,8 +25657,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F22),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F22)&gt;0)*ROW($F$11:F22),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J22),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-2-1</v>
       </c>
@@ -25692,8 +25692,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F23),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F23)&gt;0)*ROW($F$11:F23),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J23),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-3-1</v>
       </c>
@@ -25727,8 +25727,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F24),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F24)&gt;0)*ROW($F$11:F24),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J24),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>5-4-1</v>
       </c>
@@ -25762,8 +25762,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F25),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F25)&gt;0)*ROW($F$11:F25),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J25),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-1-1</v>
       </c>
@@ -25801,8 +25801,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F26),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F26)&gt;0)*ROW($F$11:F26),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J26),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>6-2-1</v>
       </c>
@@ -25836,8 +25836,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F27),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F27)&gt;0)*ROW($F$11:F27),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J27),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-1-1</v>
       </c>
@@ -25875,8 +25875,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F28),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F28)&gt;0)*ROW($F$11:F28),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J28),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>7-2-1</v>
       </c>
@@ -25910,8 +25910,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F29),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F29)&gt;0)*ROW($F$11:F29),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J29),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-1-1</v>
       </c>
@@ -25947,8 +25947,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F30),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F30)&gt;0)*ROW($F$11:F30),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J30),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-2-1</v>
       </c>
@@ -25982,8 +25982,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F31),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F31)&gt;0)*ROW($F$11:F31),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J31),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-3-1</v>
       </c>
@@ -26017,8 +26017,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F32),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F32)&gt;0)*ROW($F$11:F32),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J32),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>8-4-1</v>
       </c>
@@ -26052,8 +26052,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F33),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F33)&gt;0)*ROW($F$11:F33),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J33),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-1-1</v>
       </c>
@@ -26089,8 +26089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F34),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F34)&gt;0)*ROW($F$11:F34),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J34),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>9-2-1</v>
       </c>
@@ -26124,8 +26124,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F35),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F35)&gt;0)*ROW($F$11:F35),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J35),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>10-1-1</v>
       </c>
@@ -26161,8 +26161,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F36),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F36)&gt;0)*ROW($F$11:F36),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J36),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-1-1</v>
       </c>
@@ -26202,8 +26202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F37),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F37)&gt;0)*ROW($F$11:F37),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J37),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-2-1</v>
       </c>
@@ -26237,8 +26237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F38),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F38)&gt;0)*ROW($F$11:F38),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J38),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-3-1</v>
       </c>
@@ -26272,8 +26272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F39),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F39)&gt;0)*ROW($F$11:F39),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J39),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>11-4-1</v>
       </c>
@@ -26307,8 +26307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F40),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F40)&gt;0)*ROW($F$11:F40),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J40),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-1-1</v>
       </c>
@@ -26346,8 +26346,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F41),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F41)&gt;0)*ROW($F$11:F41),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J41),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>12-2-1</v>
       </c>
@@ -26381,8 +26381,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F42),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F42)&gt;0)*ROW($F$11:F42),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J42),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-1-1</v>
       </c>
@@ -26424,8 +26424,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F43),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F43)&gt;0)*ROW($F$11:F43),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J43),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-2-1</v>
       </c>
@@ -26459,8 +26459,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F44),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F44)&gt;0)*ROW($F$11:F44),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J44),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>13-3-1</v>
       </c>
@@ -26494,8 +26494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F45),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F45)&gt;0)*ROW($F$11:F45),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J45),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-1-1</v>
       </c>
@@ -26531,8 +26531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F46),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F46)&gt;0)*ROW($F$11:F46),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J46),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-2-1</v>
       </c>
@@ -26566,8 +26566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F47),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F47)&gt;0)*ROW($F$11:F47),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J47),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>14-3-1</v>
       </c>
@@ -26601,8 +26601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F48),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F48)&gt;0)*ROW($F$11:F48),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J48),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-1-1</v>
       </c>
@@ -26638,8 +26638,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F49),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F49)&gt;0)*ROW($F$11:F49),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J49),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>15-2-1</v>
       </c>
@@ -26673,8 +26673,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F50),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F50)&gt;0)*ROW($F$11:F50),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J50),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-1-1</v>
       </c>
@@ -26710,8 +26710,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F51),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F51)&gt;0)*ROW($F$11:F51),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J51),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-2-1</v>
       </c>
@@ -26745,8 +26745,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F52),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F52)&gt;0)*ROW($F$11:F52),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J52),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-3-1</v>
       </c>
@@ -26780,8 +26780,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F53),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F53)&gt;0)*ROW($F$11:F53),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J53),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-4-1</v>
       </c>
@@ -26815,8 +26815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F54),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F54)&gt;0)*ROW($F$11:F54),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J54),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-5-1</v>
       </c>
@@ -26850,8 +26850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F55),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F55)&gt;0)*ROW($F$11:F55),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J55),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>16-6-1</v>
       </c>
@@ -26885,8 +26885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F56),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F56)&gt;0)*ROW($F$11:F56),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J56),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>17-1-1</v>
       </c>
@@ -26922,8 +26922,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F57),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F57)&gt;0)*ROW($F$11:F57),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J57),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>18-1-1</v>
       </c>
@@ -26959,8 +26959,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F58),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F58)&gt;0)*ROW($F$11:F58),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J58),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>19-1-1</v>
       </c>
@@ -26996,8 +26996,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F59),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F59)&gt;0)*ROW($F$11:F59),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J59),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-1-1</v>
       </c>
@@ -27035,8 +27035,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F60),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F60)&gt;0)*ROW($F$11:F60),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J60),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-2-1</v>
       </c>
@@ -27070,8 +27070,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F61),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F61)&gt;0)*ROW($F$11:F61),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J61),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-3-1</v>
       </c>
@@ -27105,8 +27105,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F62),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F62)&gt;0)*ROW($F$11:F62),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J62),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-4-1</v>
       </c>
@@ -27140,8 +27140,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F63),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F63)&gt;0)*ROW($F$11:F63),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J63),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>20-5-1</v>
       </c>
@@ -27175,8 +27175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F64),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F64)&gt;0)*ROW($F$11:F64),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J64),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-1-1</v>
       </c>
@@ -27212,8 +27212,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F65),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F65)&gt;0)*ROW($F$11:F65),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J65),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-2-1</v>
       </c>
@@ -27247,8 +27247,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F66),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F66)&gt;0)*ROW($F$11:F66),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J66),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-3-1</v>
       </c>
@@ -27282,8 +27282,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F67),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F67)&gt;0)*ROW($F$11:F67),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J67),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-4-1</v>
       </c>
@@ -27317,8 +27317,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F68),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F68)&gt;0)*ROW($F$11:F68),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J68),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-5-1</v>
       </c>
@@ -27352,8 +27352,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F69),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F69)&gt;0)*ROW($F$11:F69),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J69),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-6-1</v>
       </c>
@@ -27387,8 +27387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F70),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F70)&gt;0)*ROW($F$11:F70),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J70),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-7-1</v>
       </c>
@@ -27422,8 +27422,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F71),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F71)&gt;0)*ROW($F$11:F71),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J71),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>21-8-1</v>
       </c>
@@ -27457,8 +27457,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F72),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F72)&gt;0)*ROW($F$11:F72),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J72),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>22-1-1</v>
       </c>
@@ -27494,8 +27494,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F73),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F73)&gt;0)*ROW($F$11:F73),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J73),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-1-1</v>
       </c>
@@ -27531,8 +27531,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F74),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F74)&gt;0)*ROW($F$11:F74),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J74),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-2-1</v>
       </c>
@@ -27566,8 +27566,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F75),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F75)&gt;0)*ROW($F$11:F75),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J75),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-3-1</v>
       </c>
@@ -27601,8 +27601,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F76),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F76)&gt;0)*ROW($F$11:F76),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J76),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-4-1</v>
       </c>
@@ -27636,8 +27636,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F77),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F77)&gt;0)*ROW($F$11:F77),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J77),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>23-5-1</v>
       </c>
@@ -27671,8 +27671,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F78),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F78)&gt;0)*ROW($F$11:F78),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J78),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-1-1</v>
       </c>
@@ -27712,8 +27712,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F79),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F79)&gt;0)*ROW($F$11:F79),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J79),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>24-2-1</v>
       </c>
@@ -27747,8 +27747,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F80),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F80)&gt;0)*ROW($F$11:F80),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J80),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>25-1-1</v>
       </c>
@@ -27784,8 +27784,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F81),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F81)&gt;0)*ROW($F$11:F81),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J81),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-1-1</v>
       </c>
@@ -27821,8 +27821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F82),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F82)&gt;0)*ROW($F$11:F82),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J82),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>26-2-1</v>
       </c>
@@ -27856,8 +27856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F83),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F83)&gt;0)*ROW($F$11:F83),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J83),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>27-1-1</v>
       </c>
@@ -27893,8 +27893,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F84),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F84)&gt;0)*ROW($F$11:F84),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J84),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>28-1-1</v>
       </c>
@@ -27930,8 +27930,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F85),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F85)&gt;0)*ROW($F$11:F85),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J85),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>29-1-1</v>
       </c>
@@ -27971,8 +27971,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F86),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F86)&gt;0)*ROW($F$11:F86),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J86),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>30-1-1</v>
       </c>
@@ -28008,8 +28008,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F87),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F87)&gt;0)*ROW($F$11:F87),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J87),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>31-1-1</v>
       </c>
@@ -28045,8 +28045,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F88),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F88)&gt;0)*ROW($F$11:F88),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J88),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-1-1</v>
       </c>
@@ -28086,8 +28086,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F89),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F89)&gt;0)*ROW($F$11:F89),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J89),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>32-2-1</v>
       </c>
@@ -28121,8 +28121,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F90),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F90)&gt;0)*ROW($F$11:F90),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J90),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>33-1-1</v>
       </c>
@@ -28158,8 +28158,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F91),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F91)&gt;0)*ROW($F$11:F91),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J91),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-1-1</v>
       </c>
@@ -28195,8 +28195,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F92),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F92)&gt;0)*ROW($F$11:F92),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J92),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>34-2-1</v>
       </c>
@@ -28230,8 +28230,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F93),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F93)&gt;0)*ROW($F$11:F93),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J93),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>35-1-1</v>
       </c>
@@ -28267,8 +28267,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F94),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F94)&gt;0)*ROW($F$11:F94),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J94),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-1-1</v>
       </c>
@@ -28308,8 +28308,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F95),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F95)&gt;0)*ROW($F$11:F95),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J95),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-2-1</v>
       </c>
@@ -28343,8 +28343,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F96),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F96)&gt;0)*ROW($F$11:F96),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J96),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-3-1</v>
       </c>
@@ -28378,8 +28378,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F97),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F97)&gt;0)*ROW($F$11:F97),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J97),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-4-1</v>
       </c>
@@ -28413,8 +28413,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F98),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F98)&gt;0)*ROW($F$11:F98),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J98),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>36-5-1</v>
       </c>
@@ -28448,8 +28448,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F99),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F99)&gt;0)*ROW($F$11:F99),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J99),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-1-1</v>
       </c>
@@ -28485,8 +28485,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F100),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F100)&gt;0)*ROW($F$11:F100),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J100),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-2-1</v>
       </c>
@@ -28520,8 +28520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F101),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F101)&gt;0)*ROW($F$11:F101),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J101),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-3-1</v>
       </c>
@@ -28555,8 +28555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F102),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F102)&gt;0)*ROW($F$11:F102),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J102),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-4-1</v>
       </c>
@@ -28590,8 +28590,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F103),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F103)&gt;0)*ROW($F$11:F103),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J103),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>37-5-1</v>
       </c>
@@ -28625,8 +28625,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F104),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F104)&gt;0)*ROW($F$11:F104),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J104),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>38-1-1</v>
       </c>
@@ -28662,8 +28662,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F105),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F105)&gt;0)*ROW($F$11:F105),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J105),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>39-1-1</v>
       </c>
@@ -28705,8 +28705,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F106),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F106)&gt;0)*ROW($F$11:F106),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J106),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-1-1</v>
       </c>
@@ -28746,8 +28746,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F107),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F107)&gt;0)*ROW($F$11:F107),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J107),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>40-2-1</v>
       </c>
@@ -28781,8 +28781,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F108),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F108)&gt;0)*ROW($F$11:F108),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J108),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>41-1-1</v>
       </c>
@@ -28822,8 +28822,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F109),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F109)&gt;0)*ROW($F$11:F109),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J109),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-1-1</v>
       </c>
@@ -28863,8 +28863,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F110),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F110)&gt;0)*ROW($F$11:F110),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J110),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>42-2-1</v>
       </c>
@@ -28898,8 +28898,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F111),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F111)&gt;0)*ROW($F$11:F111),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J111),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-1-1</v>
       </c>
@@ -28941,8 +28941,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F112),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F112)&gt;0)*ROW($F$11:F112),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J112),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-2-1</v>
       </c>
@@ -28978,8 +28978,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F113),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F113)&gt;0)*ROW($F$11:F113),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J113),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-3-1</v>
       </c>
@@ -29013,8 +29013,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F114),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F114)&gt;0)*ROW($F$11:F114),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J114),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>43-4-1</v>
       </c>
@@ -29048,8 +29048,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F115),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F115)&gt;0)*ROW($F$11:F115),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J115),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-1-1</v>
       </c>
@@ -29085,8 +29085,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F116),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F116)&gt;0)*ROW($F$11:F116),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J116),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-2-1</v>
       </c>
@@ -29120,8 +29120,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F117),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F117)&gt;0)*ROW($F$11:F117),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J117),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-3-1</v>
       </c>
@@ -29155,8 +29155,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F118),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F118)&gt;0)*ROW($F$11:F118),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J118),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-4-1</v>
       </c>
@@ -29190,8 +29190,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F119),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F119)&gt;0)*ROW($F$11:F119),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J119),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>44-5-1</v>
       </c>
@@ -29225,8 +29225,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F120),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F120)&gt;0)*ROW($F$11:F120),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J120),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-1-1</v>
       </c>
@@ -29262,8 +29262,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F121),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F121)&gt;0)*ROW($F$11:F121),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J121),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-2-1</v>
       </c>
@@ -29297,8 +29297,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F122),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F122)&gt;0)*ROW($F$11:F122),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J122),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-3-1</v>
       </c>
@@ -29332,8 +29332,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F123),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F123)&gt;0)*ROW($F$11:F123),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J123),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-4-1</v>
       </c>
@@ -29367,8 +29367,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F124),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F124)&gt;0)*ROW($F$11:F124),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J124),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>45-5-1</v>
       </c>
@@ -29402,8 +29402,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F125),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F125)&gt;0)*ROW($F$11:F125),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J125),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>46-1-1</v>
       </c>
@@ -29439,8 +29439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F126),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F126)&gt;0)*ROW($F$11:F126),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J126),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>47-1-1</v>
       </c>
@@ -29478,8 +29478,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F127),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F127)&gt;0)*ROW($F$11:F127),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J127),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>48-1-1</v>
       </c>
@@ -29519,8 +29519,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F128),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F128)&gt;0)*ROW($F$11:F128),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J128),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-1-1</v>
       </c>
@@ -29556,8 +29556,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F129),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F129)&gt;0)*ROW($F$11:F129),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J129),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-2-1</v>
       </c>
@@ -29591,8 +29591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F130),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F130)&gt;0)*ROW($F$11:F130),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J130),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>49-3-1</v>
       </c>
@@ -29626,8 +29626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F131),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F131)&gt;0)*ROW($F$11:F131),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J131),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-1-1</v>
       </c>
@@ -29669,8 +29669,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F132),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F132)&gt;0)*ROW($F$11:F132),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J132),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-2-1</v>
       </c>
@@ -29706,8 +29706,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F133),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F133)&gt;0)*ROW($F$11:F133),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J133),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-3-1</v>
       </c>
@@ -29741,8 +29741,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F134),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F134)&gt;0)*ROW($F$11:F134),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J134),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>50-4-1</v>
       </c>
@@ -29776,8 +29776,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F135),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F135)&gt;0)*ROW($F$11:F135),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J135),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-1-1</v>
       </c>
@@ -29813,8 +29813,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F136),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F136)&gt;0)*ROW($F$11:F136),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J136),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>51-2-1</v>
       </c>
@@ -29848,8 +29848,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F137),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F137)&gt;0)*ROW($F$11:F137),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J137),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>52-1-1</v>
       </c>
@@ -29887,8 +29887,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F138),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F138)&gt;0)*ROW($F$11:F138),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J138),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>53-1-1</v>
       </c>
@@ -29928,8 +29928,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F139),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F139)&gt;0)*ROW($F$11:F139),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J139),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>54-1-1</v>
       </c>
@@ -29965,8 +29965,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F140),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F140)&gt;0)*ROW($F$11:F140),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J140),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>55-1-1</v>
       </c>
@@ -30002,8 +30002,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F141),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F141)&gt;0)*ROW($F$11:F141),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J141),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>56-1-1</v>
       </c>
@@ -30039,8 +30039,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F142),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F142)&gt;0)*ROW($F$11:F142),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J142),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>57-1-1</v>
       </c>
@@ -30076,8 +30076,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F143),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F143)&gt;0)*ROW($F$11:F143),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J143),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-1-1</v>
       </c>
@@ -30113,8 +30113,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F144),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F144)&gt;0)*ROW($F$11:F144),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J144),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-2-1</v>
       </c>
@@ -30148,8 +30148,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F145),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F145)&gt;0)*ROW($F$11:F145),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J145),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-3-1</v>
       </c>
@@ -30183,8 +30183,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F146),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F146)&gt;0)*ROW($F$11:F146),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J146),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-4-1</v>
       </c>
@@ -30218,8 +30218,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F147),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F147)&gt;0)*ROW($F$11:F147),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J147),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-5-1</v>
       </c>
@@ -30253,8 +30253,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F148),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F148)&gt;0)*ROW($F$11:F148),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J148),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>58-6-1</v>
       </c>
@@ -30288,8 +30288,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F149),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F149)&gt;0)*ROW($F$11:F149),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J149),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-1-1</v>
       </c>
@@ -30327,8 +30327,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F150),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F150)&gt;0)*ROW($F$11:F150),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J150),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>59-2-1</v>
       </c>
@@ -30362,8 +30362,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F151),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F151)&gt;0)*ROW($F$11:F151),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J151),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-1-1</v>
       </c>
@@ -30399,8 +30399,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F152),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F152)&gt;0)*ROW($F$11:F152),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J152),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-2-1</v>
       </c>
@@ -30434,8 +30434,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F153),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F153)&gt;0)*ROW($F$11:F153),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J153),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-3-1</v>
       </c>
@@ -30469,8 +30469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F154),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F154)&gt;0)*ROW($F$11:F154),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J154),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-4-1</v>
       </c>
@@ -30504,8 +30504,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F155),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F155)&gt;0)*ROW($F$11:F155),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J155),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-5-1</v>
       </c>
@@ -30539,8 +30539,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F156),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F156)&gt;0)*ROW($F$11:F156),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J156),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-6-1</v>
       </c>
@@ -30574,8 +30574,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F157),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F157)&gt;0)*ROW($F$11:F157),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J157),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-7-1</v>
       </c>
@@ -30609,8 +30609,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F158),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F158)&gt;0)*ROW($F$11:F158),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J158),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-8-1</v>
       </c>
@@ -30644,8 +30644,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F159),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F159)&gt;0)*ROW($F$11:F159),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J159),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-9-1</v>
       </c>
@@ -30679,8 +30679,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F160),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F160)&gt;0)*ROW($F$11:F160),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J160),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-10-1</v>
       </c>
@@ -30714,8 +30714,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F161),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F161)&gt;0)*ROW($F$11:F161),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J161),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>60-11-1</v>
       </c>
@@ -30749,8 +30749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F162),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F162)&gt;0)*ROW($F$11:F162),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J162),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-1-1</v>
       </c>
@@ -30786,8 +30786,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F163),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F163)&gt;0)*ROW($F$11:F163),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J163),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-2-1</v>
       </c>
@@ -30821,8 +30821,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F164),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F164)&gt;0)*ROW($F$11:F164),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J164),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-3-1</v>
       </c>
@@ -30856,8 +30856,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F165),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F165)&gt;0)*ROW($F$11:F165),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J165),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-4-1</v>
       </c>
@@ -30891,8 +30891,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F166),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F166)&gt;0)*ROW($F$11:F166),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J166),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-5-1</v>
       </c>
@@ -30926,8 +30926,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F167),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F167)&gt;0)*ROW($F$11:F167),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J167),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-6-1</v>
       </c>
@@ -30961,8 +30961,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F168),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F168)&gt;0)*ROW($F$11:F168),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J168),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>61-7-1</v>
       </c>
@@ -30996,8 +30996,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F169),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F169)&gt;0)*ROW($F$11:F169),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J169),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-1-1</v>
       </c>
@@ -31033,8 +31033,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F170),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F170)&gt;0)*ROW($F$11:F170),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J170),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-2-1</v>
       </c>
@@ -31068,8 +31068,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F171),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F171)&gt;0)*ROW($F$11:F171),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J171),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-3-1</v>
       </c>
@@ -31103,8 +31103,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F172),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F172)&gt;0)*ROW($F$11:F172),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J172),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-4-1</v>
       </c>
@@ -31138,8 +31138,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F173),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F173)&gt;0)*ROW($F$11:F173),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J173),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-5-1</v>
       </c>
@@ -31173,8 +31173,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F174),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F174)&gt;0)*ROW($F$11:F174),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J174),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-6-1</v>
       </c>
@@ -31208,8 +31208,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F175),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F175)&gt;0)*ROW($F$11:F175),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J175),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-7-1</v>
       </c>
@@ -31243,8 +31243,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F176),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F176)&gt;0)*ROW($F$11:F176),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J176),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-8-1</v>
       </c>
@@ -31278,8 +31278,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F177),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F177)&gt;0)*ROW($F$11:F177),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J177),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>62-9-1</v>
       </c>
@@ -31313,8 +31313,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F178),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F178)&gt;0)*ROW($F$11:F178),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J178),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>63-1-1</v>
       </c>
@@ -31350,8 +31350,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F179),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F179)&gt;0)*ROW($F$11:F179),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J179),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>64-1-1</v>
       </c>
@@ -31387,8 +31387,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F180),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F180)&gt;0)*ROW($F$11:F180),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J180),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>65-1-1</v>
       </c>
@@ -31430,8 +31430,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F181),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F181)&gt;0)*ROW($F$11:F181),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J181),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>66-1-1</v>
       </c>
@@ -31469,8 +31469,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F182),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F182)&gt;0)*ROW($F$11:F182),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J182),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>67-1-1</v>
       </c>
@@ -31508,8 +31508,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F183),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F183)&gt;0)*ROW($F$11:F183),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J183),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>68-1-1</v>
       </c>
@@ -31551,8 +31551,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F184),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F184)&gt;0)*ROW($F$11:F184),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J184),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-1-1</v>
       </c>
@@ -31588,8 +31588,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F185),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F185)&gt;0)*ROW($F$11:F185),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J185),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>69-2-1</v>
       </c>
@@ -31623,8 +31623,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F186),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F186)&gt;0)*ROW($F$11:F186),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J186),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-1-1</v>
       </c>
@@ -31660,8 +31660,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F187),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F187)&gt;0)*ROW($F$11:F187),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J187),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>70-2-1</v>
       </c>
@@ -31695,8 +31695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F188),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F188)&gt;0)*ROW($F$11:F188),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J188),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>71-1-1</v>
       </c>
@@ -31734,8 +31734,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F189),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F189)&gt;0)*ROW($F$11:F189),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J189),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-1-1</v>
       </c>
@@ -31775,8 +31775,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F190),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F190)&gt;0)*ROW($F$11:F190),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J190),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-2-1</v>
       </c>
@@ -31810,8 +31810,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F191),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F191)&gt;0)*ROW($F$11:F191),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J191),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-3-1</v>
       </c>
@@ -31845,8 +31845,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F192),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F192)&gt;0)*ROW($F$11:F192),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J192),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-4-1</v>
       </c>
@@ -31880,8 +31880,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F193),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F193)&gt;0)*ROW($F$11:F193),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J193),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-5-1</v>
       </c>
@@ -31915,8 +31915,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F194),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F194)&gt;0)*ROW($F$11:F194),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J194),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-6-1</v>
       </c>
@@ -31950,8 +31950,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F195),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F195)&gt;0)*ROW($F$11:F195),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J195),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>72-7-1</v>
       </c>
@@ -31985,8 +31985,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F196),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F196)&gt;0)*ROW($F$11:F196),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J196),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>73-1-1</v>
       </c>
@@ -32022,8 +32022,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F197),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F197)&gt;0)*ROW($F$11:F197),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J197),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-1-1</v>
       </c>
@@ -32061,8 +32061,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F198),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F198)&gt;0)*ROW($F$11:F198),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J198),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-2-1</v>
       </c>
@@ -32096,8 +32096,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F199),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F199)&gt;0)*ROW($F$11:F199),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J199),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-3-1</v>
       </c>
@@ -32131,8 +32131,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F200),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F200)&gt;0)*ROW($F$11:F200),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J200),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-4-1</v>
       </c>
@@ -32166,8 +32166,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F201),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F201)&gt;0)*ROW($F$11:F201),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J201),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-5-1</v>
       </c>
@@ -32201,8 +32201,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F202),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F202)&gt;0)*ROW($F$11:F202),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J202),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-6-1</v>
       </c>
@@ -32236,8 +32236,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F203),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F203)&gt;0)*ROW($F$11:F203),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J203),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-7-1</v>
       </c>
@@ -32271,8 +32271,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F204),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F204)&gt;0)*ROW($F$11:F204),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J204),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-8-1</v>
       </c>
@@ -32306,8 +32306,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F205),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F205)&gt;0)*ROW($F$11:F205),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J205),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-9-1</v>
       </c>
@@ -32341,8 +32341,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F206),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F206)&gt;0)*ROW($F$11:F206),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J206),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-10-1</v>
       </c>
@@ -32376,8 +32376,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F207),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F207)&gt;0)*ROW($F$11:F207),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J207),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-11-1</v>
       </c>
@@ -32411,8 +32411,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F208),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F208)&gt;0)*ROW($F$11:F208),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J208),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-12-1</v>
       </c>
@@ -32446,8 +32446,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F209),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F209)&gt;0)*ROW($F$11:F209),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J209),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>74-13-1</v>
       </c>
@@ -32481,8 +32481,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F210),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F210)&gt;0)*ROW($F$11:F210),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J210),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-1-1</v>
       </c>
@@ -32520,8 +32520,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F211),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F211)&gt;0)*ROW($F$11:F211),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J211),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-2-1</v>
       </c>
@@ -32555,8 +32555,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F212),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F212)&gt;0)*ROW($F$11:F212),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J212),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-3-1</v>
       </c>
@@ -32590,8 +32590,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F213),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F213)&gt;0)*ROW($F$11:F213),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J213),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-4-1</v>
       </c>
@@ -32625,8 +32625,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F214),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F214)&gt;0)*ROW($F$11:F214),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J214),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-5-1</v>
       </c>
@@ -32660,8 +32660,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F215),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F215)&gt;0)*ROW($F$11:F215),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J215),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-6-1</v>
       </c>
@@ -32695,8 +32695,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F216),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F216)&gt;0)*ROW($F$11:F216),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J216),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-7-1</v>
       </c>
@@ -32730,8 +32730,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F217),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F217)&gt;0)*ROW($F$11:F217),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J217),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-8-1</v>
       </c>
@@ -32765,8 +32765,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F218),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F218)&gt;0)*ROW($F$11:F218),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J218),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-9-1</v>
       </c>
@@ -32800,8 +32800,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F219),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F219)&gt;0)*ROW($F$11:F219),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J219),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-10-1</v>
       </c>
@@ -32835,8 +32835,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F220),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F220)&gt;0)*ROW($F$11:F220),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J220),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-11-1</v>
       </c>
@@ -32870,8 +32870,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F221),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F221)&gt;0)*ROW($F$11:F221),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J221),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-12-1</v>
       </c>
@@ -32905,8 +32905,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F222),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F222)&gt;0)*ROW($F$11:F222),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J222),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-13-1</v>
       </c>
@@ -32940,8 +32940,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F223),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F223)&gt;0)*ROW($F$11:F223),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J223),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-14-1</v>
       </c>
@@ -32975,8 +32975,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F224),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F224)&gt;0)*ROW($F$11:F224),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J224),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>75-15-1</v>
       </c>
@@ -33010,8 +33010,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F225),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F225)&gt;0)*ROW($F$11:F225),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J225),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-1-1</v>
       </c>
@@ -33047,8 +33047,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F226),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F226)&gt;0)*ROW($F$11:F226),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J226),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-2-1</v>
       </c>
@@ -33082,8 +33082,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F227),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F227)&gt;0)*ROW($F$11:F227),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J227),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>76-3-1</v>
       </c>
@@ -33117,8 +33117,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F228),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F228)&gt;0)*ROW($F$11:F228),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J228),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>77-1-1</v>
       </c>
@@ -33154,8 +33154,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F229),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F229)&gt;0)*ROW($F$11:F229),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J229),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>78-1-1</v>
       </c>
@@ -33191,8 +33191,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F230),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F230)&gt;0)*ROW($F$11:F230),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J230),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>79-1-1</v>
       </c>
@@ -33234,8 +33234,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F231),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F231)&gt;0)*ROW($F$11:F231),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J231),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-1-1</v>
       </c>
@@ -33281,8 +33281,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F232),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F232)&gt;0)*ROW($F$11:F232),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J232),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-2-1</v>
       </c>
@@ -33316,8 +33316,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F233),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F233)&gt;0)*ROW($F$11:F233),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J233),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-3-1</v>
       </c>
@@ -33351,8 +33351,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F234),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F234)&gt;0)*ROW($F$11:F234),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J234),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-4-1</v>
       </c>
@@ -33386,8 +33386,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F235),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F235)&gt;0)*ROW($F$11:F235),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J235),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>80-5-1</v>
       </c>
@@ -33421,8 +33421,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F236),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F236)&gt;0)*ROW($F$11:F236),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J236),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-1-1</v>
       </c>
@@ -33458,8 +33458,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F237),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F237)&gt;0)*ROW($F$11:F237),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J237),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-2-1</v>
       </c>
@@ -33493,8 +33493,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F238),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F238)&gt;0)*ROW($F$11:F238),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J238),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-3-1</v>
       </c>
@@ -33528,8 +33528,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F239),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F239)&gt;0)*ROW($F$11:F239),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J239),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-4-1</v>
       </c>
@@ -33563,8 +33563,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F240),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F240)&gt;0)*ROW($F$11:F240),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J240),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>81-5-1</v>
       </c>
@@ -33608,8 +33608,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F241),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F241)&gt;0)*ROW($F$11:F241),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J241),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-1</v>
       </c>
@@ -33655,8 +33655,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F242),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F242)&gt;0)*ROW($F$11:F242),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J242),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>82-1-2</v>
       </c>
@@ -33698,8 +33698,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F243),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F243)&gt;0)*ROW($F$11:F243),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J243),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>83-1-1</v>
       </c>
@@ -33749,8 +33749,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F244),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F244)&gt;0)*ROW($F$11:F244),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J244),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-1-1</v>
       </c>
@@ -33792,8 +33792,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F245),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F245)&gt;0)*ROW($F$11:F245),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J245),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>84-2-1</v>
       </c>
@@ -33827,8 +33827,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F246),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F246)&gt;0)*ROW($F$11:F246),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J246),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-1-1</v>
       </c>
@@ -33866,8 +33866,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F247),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F247)&gt;0)*ROW($F$11:F247),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J247),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>85-2-1</v>
       </c>
@@ -33901,8 +33901,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F248),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F248)&gt;0)*ROW($F$11:F248),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J248),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>86-1-1</v>
       </c>
@@ -33942,8 +33942,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F249),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F249)&gt;0)*ROW($F$11:F249),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J249),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>87-1-1</v>
       </c>
@@ -33979,8 +33979,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F250),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F250)&gt;0)*ROW($F$11:F250),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J250),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>88-1-1</v>
       </c>
@@ -34026,8 +34026,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F251),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F251)&gt;0)*ROW($F$11:F251),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J251),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>89-1-1</v>
       </c>
@@ -34063,8 +34063,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F252),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F252)&gt;0)*ROW($F$11:F252),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J252),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-1-1</v>
       </c>
@@ -34112,8 +34112,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F253),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F253)&gt;0)*ROW($F$11:F253),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J253),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>90-2-1</v>
       </c>
@@ -34147,8 +34147,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F254),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F254)&gt;0)*ROW($F$11:F254),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J254),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-1-1</v>
       </c>
@@ -34184,8 +34184,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F255),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F255)&gt;0)*ROW($F$11:F255),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J255),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-2-1</v>
       </c>
@@ -34229,8 +34229,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F256),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F256)&gt;0)*ROW($F$11:F256),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J256),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-3-1</v>
       </c>
@@ -34264,8 +34264,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F257),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F257)&gt;0)*ROW($F$11:F257),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J257),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-4-1</v>
       </c>
@@ -34299,8 +34299,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F258),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F258)&gt;0)*ROW($F$11:F258),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J258),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-5-1</v>
       </c>
@@ -34334,8 +34334,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F259),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F259)&gt;0)*ROW($F$11:F259),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J259),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-6-1</v>
       </c>
@@ -34369,8 +34369,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F260),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F260)&gt;0)*ROW($F$11:F260),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J260),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-7-1</v>
       </c>
@@ -34404,8 +34404,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F261),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F261)&gt;0)*ROW($F$11:F261),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J261),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-8-1</v>
       </c>
@@ -34439,8 +34439,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F262),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F262)&gt;0)*ROW($F$11:F262),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J262),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-9-1</v>
       </c>
@@ -34474,8 +34474,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F263),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F263)&gt;0)*ROW($F$11:F263),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J263),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-10-1</v>
       </c>
@@ -34509,8 +34509,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F264),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F264)&gt;0)*ROW($F$11:F264),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J264),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>91-11-1</v>
       </c>
@@ -34544,8 +34544,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F265),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F265)&gt;0)*ROW($F$11:F265),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J265),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-1-1</v>
       </c>
@@ -34591,8 +34591,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F266),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F266)&gt;0)*ROW($F$11:F266),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J266),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-2-1</v>
       </c>
@@ -34626,8 +34626,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F267),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F267)&gt;0)*ROW($F$11:F267),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J267),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-3-1</v>
       </c>
@@ -34661,8 +34661,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F268),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F268)&gt;0)*ROW($F$11:F268),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J268),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-4-1</v>
       </c>
@@ -34696,8 +34696,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F269),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F269)&gt;0)*ROW($F$11:F269),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J269),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-5-1</v>
       </c>
@@ -34731,8 +34731,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F270),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F270)&gt;0)*ROW($F$11:F270),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J270),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>92-6-1</v>
       </c>
@@ -34766,8 +34766,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F271),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F271)&gt;0)*ROW($F$11:F271),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J271),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-1-1</v>
       </c>
@@ -34815,8 +34815,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F272),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F272)&gt;0)*ROW($F$11:F272),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J272),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-2-1</v>
       </c>
@@ -34850,8 +34850,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F273),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F273)&gt;0)*ROW($F$11:F273),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J273),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-3-1</v>
       </c>
@@ -34885,8 +34885,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F274),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F274)&gt;0)*ROW($F$11:F274),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J274),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-4-1</v>
       </c>
@@ -34920,8 +34920,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F275),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F275)&gt;0)*ROW($F$11:F275),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J275),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-5-1</v>
       </c>
@@ -34955,8 +34955,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F276),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F276)&gt;0)*ROW($F$11:F276),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J276),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-6-1</v>
       </c>
@@ -34990,8 +34990,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F277),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F277)&gt;0)*ROW($F$11:F277),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J277),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-7-1</v>
       </c>
@@ -35025,8 +35025,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F278),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F278)&gt;0)*ROW($F$11:F278),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J278),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>93-8-1</v>
       </c>
@@ -35060,8 +35060,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F279),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F279)&gt;0)*ROW($F$11:F279),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J279),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>94-1-1</v>
       </c>
@@ -35097,8 +35097,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F280),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F280)&gt;0)*ROW($F$11:F280),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J280),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-1-1</v>
       </c>
@@ -35140,8 +35140,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F281),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F281)&gt;0)*ROW($F$11:F281),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J281),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-2-1</v>
       </c>
@@ -35175,8 +35175,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F282),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F282)&gt;0)*ROW($F$11:F282),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J282),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-3-1</v>
       </c>
@@ -35210,8 +35210,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F283),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F283)&gt;0)*ROW($F$11:F283),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J283),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>95-4-1</v>
       </c>
@@ -35245,8 +35245,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F284),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F284)&gt;0)*ROW($F$11:F284),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J284),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>96-1-1</v>
       </c>
@@ -35286,8 +35286,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F285),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F285)&gt;0)*ROW($F$11:F285),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J285),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>97-1-1</v>
       </c>
@@ -35323,8 +35323,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F286),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F286)&gt;0)*ROW($F$11:F286),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J286),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>98-1-1</v>
       </c>
@@ -35360,8 +35360,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F287),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F287)&gt;0)*ROW($F$11:F287),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J287),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>99-1-1</v>
       </c>
@@ -35397,8 +35397,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F288),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F288)&gt;0)*ROW($F$11:F288),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J288),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-1-1</v>
       </c>
@@ -35436,8 +35436,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F289),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F289)&gt;0)*ROW($F$11:F289),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J289),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-2-1</v>
       </c>
@@ -35471,8 +35471,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F290),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F290)&gt;0)*ROW($F$11:F290),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J290),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-3-1</v>
       </c>
@@ -35506,8 +35506,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F291),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F291)&gt;0)*ROW($F$11:F291),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J291),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-4-1</v>
       </c>
@@ -35541,8 +35541,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F292),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F292)&gt;0)*ROW($F$11:F292),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J292),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-5-1</v>
       </c>
@@ -35576,8 +35576,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F293),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F293)&gt;0)*ROW($F$11:F293),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J293),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-6-1</v>
       </c>
@@ -35611,8 +35611,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F294),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F294)&gt;0)*ROW($F$11:F294),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J294),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-7-1</v>
       </c>
@@ -35646,8 +35646,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F295),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F295)&gt;0)*ROW($F$11:F295),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J295),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-8-1</v>
       </c>
@@ -35681,8 +35681,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F296),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F296)&gt;0)*ROW($F$11:F296),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J296),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>100-9-1</v>
       </c>
@@ -35716,8 +35716,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F297),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F297)&gt;0)*ROW($F$11:F297),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J297),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>101-1-1</v>
       </c>
@@ -35759,8 +35759,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F298),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F298)&gt;0)*ROW($F$11:F298),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J298),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>102-1-1</v>
       </c>
@@ -35796,8 +35796,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F299),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F299)&gt;0)*ROW($F$11:F299),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J299),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>103-1-1</v>
       </c>
@@ -35833,8 +35833,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F300),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F300)&gt;0)*ROW($F$11:F300),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J300),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-1</v>
       </c>
@@ -35882,8 +35882,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F301),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F301)&gt;0)*ROW($F$11:F301),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J301),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-1-2</v>
       </c>
@@ -35925,8 +35925,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F302),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F302)&gt;0)*ROW($F$11:F302),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J302),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-2-1</v>
       </c>
@@ -35970,8 +35970,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F303),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F303)&gt;0)*ROW($F$11:F303),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J303),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-3-1</v>
       </c>
@@ -36005,8 +36005,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F304),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F304)&gt;0)*ROW($F$11:F304),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J304),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>104-4-1</v>
       </c>
@@ -36040,8 +36040,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F305),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F305)&gt;0)*ROW($F$11:F305),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J305),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-1</v>
       </c>
@@ -36089,8 +36089,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F306),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F306)&gt;0)*ROW($F$11:F306),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J306),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-1-2</v>
       </c>
@@ -36132,8 +36132,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F307),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F307)&gt;0)*ROW($F$11:F307),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J307),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-2-1</v>
       </c>
@@ -36167,8 +36167,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F308),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F308)&gt;0)*ROW($F$11:F308),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J308),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-3-1</v>
       </c>
@@ -36202,8 +36202,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F309),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F309)&gt;0)*ROW($F$11:F309),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J309),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-4-1</v>
       </c>
@@ -36237,8 +36237,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F310),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F310)&gt;0)*ROW($F$11:F310),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J310),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-5-1</v>
       </c>
@@ -36272,8 +36272,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F311),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F311)&gt;0)*ROW($F$11:F311),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J311),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-6-1</v>
       </c>
@@ -36307,8 +36307,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F312),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F312)&gt;0)*ROW($F$11:F312),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J312),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-7-1</v>
       </c>
@@ -36342,8 +36342,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F313),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F313)&gt;0)*ROW($F$11:F313),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J313),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-8-1</v>
       </c>
@@ -36377,8 +36377,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F314),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F314)&gt;0)*ROW($F$11:F314),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J314),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-9-1</v>
       </c>
@@ -36412,8 +36412,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F315),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F315)&gt;0)*ROW($F$11:F315),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J315),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-10-1</v>
       </c>
@@ -36447,8 +36447,8 @@
 _xlpm.観点数, COUNTA(INDIRECT("F"&amp;_xlpm.直近で詳細項目が空でないセルの行番号):F316),
 _xlpm.直近で観点が空でないセルの行番号, MAX(INDEX((LEN($F$11:F316)&gt;0)*ROW($F$11:F316),0)),
 _xlpm.テスト内容数, COUNTA(INDIRECT("J"&amp;_xlpm.直近で観点が空でないセルの行番号):J316),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
-_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(_xlpm.テスト内容数=0,1,_xlpm.テスト内容数),
+_xlpm.詳細項目数&amp;"-"&amp;_xlpm.観点数&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>105-11-1</v>
       </c>
@@ -36643,11 +36643,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C11),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C11)&gt;0)*ROW($C$11:C11),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D11),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D11)&gt;0)*ROW($D$11:D11),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H11),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-1-1</v>
       </c>
@@ -36691,11 +36691,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C12),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C12)&gt;0)*ROW($C$11:C12),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D12),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D12)&gt;0)*ROW($D$11:D12),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H12),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-2-1</v>
       </c>
@@ -36735,11 +36735,11 @@
 _xlpm.確認観点1数, COUNTA($C$11:C13),
 _xlpm.直近で確認観点1が空でないセルの行番号, MAX(INDEX((LEN($C$11:C13)&gt;0)*ROW($C$11:C13),0)),
 _xlpm.確認観点2数, COUNTA(INDIRECT("D"&amp;_xlpm.直近で確認観点1が空でないセルの行番号):D13),
-_xlpm.確認観点2数（確認観点2が空の場合は1）,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
+_xlpm.確認観点2数_空なら1,IF(_xlpm.確認観点2数=0,1,_xlpm.確認観点2数),
 _xlpm.直近で確認観点2が空でないセルの行番号, MAX(INDEX((LEN($D$11:D13)&gt;0)*ROW($D$11:D13),0),_xlpm.直近で確認観点1が空でないセルの行番号),
 _xlpm.テスト内容数, COUNTA(INDIRECT("H"&amp;_xlpm.直近で確認観点2が空でないセルの行番号):H13),
-_xlpm.テスト内容数（テスト内容が空の場合は1）, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
-_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数（確認観点2が空の場合は1）&amp;"-"&amp;_xlpm.テスト内容数（テスト内容が空の場合は1）
+_xlpm.テスト内容数_空なら1, IF(OR(_xlpm.テスト内容数=0,_xlpm.直近で確認観点1が空でないセルの行番号&gt;_xlpm.直近で確認観点2が空でないセルの行番号),1,_xlpm.テスト内容数),
+_xlpm.確認観点1数&amp;"-"&amp;_xlpm.確認観点2数_空なら1&amp;"-"&amp;_xlpm.テスト内容数_空なら1
 )</f>
         <v>1-2-2</v>
       </c>
